--- a/Results/Ammonia/ammonia water use results.xlsx
+++ b/Results/Ammonia/ammonia water use results.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.491225505566489</v>
+        <v>6.491225505566486</v>
       </c>
       <c r="C2" t="n">
         <v>6.639490404758444</v>
@@ -524,22 +524,22 @@
         <v>6.537427915876171</v>
       </c>
       <c r="E2" t="n">
-        <v>6.644441448965915</v>
+        <v>6.644441448965914</v>
       </c>
       <c r="F2" t="n">
-        <v>6.628721421725531</v>
+        <v>6.62872142172553</v>
       </c>
       <c r="G2" t="n">
-        <v>6.618843619443799</v>
+        <v>6.618843619443798</v>
       </c>
       <c r="H2" t="n">
         <v>6.634493297760852</v>
       </c>
       <c r="I2" t="n">
-        <v>6.618228299817511</v>
+        <v>6.61822829981751</v>
       </c>
       <c r="J2" t="n">
-        <v>6.62794247485332</v>
+        <v>6.627942474853321</v>
       </c>
       <c r="K2" t="n">
         <v>6.54694377780394</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.681732470129889</v>
+        <v>6.681732470129892</v>
       </c>
       <c r="C3" t="n">
         <v>6.84901918413682</v>
@@ -570,7 +570,7 @@
         <v>6.838303643893549</v>
       </c>
       <c r="G3" t="n">
-        <v>6.828519737101447</v>
+        <v>6.828519737101446</v>
       </c>
       <c r="H3" t="n">
         <v>6.846667210889946</v>
@@ -579,10 +579,10 @@
         <v>6.827799348139285</v>
       </c>
       <c r="J3" t="n">
-        <v>6.832504879351636</v>
+        <v>6.832504879351635</v>
       </c>
       <c r="K3" t="n">
-        <v>6.742363990838284</v>
+        <v>6.742363990838283</v>
       </c>
       <c r="L3" t="n">
         <v>6.69908316303466</v>
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.228934709179642</v>
+        <v>2.119593681223303</v>
       </c>
       <c r="C4" t="n">
-        <v>2.306030682845309</v>
+        <v>2.195367948191963</v>
       </c>
       <c r="D4" t="n">
-        <v>2.256400084346552</v>
+        <v>2.147059056390215</v>
       </c>
       <c r="E4" t="n">
-        <v>2.306752041155186</v>
+        <v>2.195494908039985</v>
       </c>
       <c r="F4" t="n">
-        <v>2.306752041155186</v>
+        <v>2.195494908039985</v>
       </c>
       <c r="G4" t="n">
-        <v>2.304945444550289</v>
+        <v>2.19548314496337</v>
       </c>
       <c r="H4" t="n">
-        <v>2.314102216906725</v>
+        <v>2.204761188950388</v>
       </c>
       <c r="I4" t="n">
-        <v>2.304943392364047</v>
+        <v>2.195176338039683</v>
       </c>
       <c r="J4" t="n">
-        <v>2.284560313530083</v>
+        <v>2.175219285573747</v>
       </c>
       <c r="K4" t="n">
-        <v>2.248379309760301</v>
+        <v>2.139038281803965</v>
       </c>
       <c r="L4" t="n">
-        <v>2.237956675557847</v>
+        <v>2.128615647601511</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.535863518317684</v>
+        <v>2.701613148477835</v>
       </c>
       <c r="C5" t="n">
-        <v>13.29332951376418</v>
+        <v>4.129132531955372</v>
       </c>
       <c r="D5" t="n">
-        <v>8.472804113648023</v>
+        <v>3.241146159618843</v>
       </c>
       <c r="E5" t="n">
-        <v>13.29332951471826</v>
+        <v>4.129132532909463</v>
       </c>
       <c r="F5" t="n">
-        <v>13.29332951471826</v>
+        <v>4.129132532909463</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7958080113694</v>
+        <v>4.217874945765017</v>
       </c>
       <c r="H5" t="n">
-        <v>16.06740955701555</v>
+        <v>4.625343267693369</v>
       </c>
       <c r="I5" t="n">
-        <v>13.29332921397217</v>
+        <v>4.129132232163367</v>
       </c>
       <c r="J5" t="n">
-        <v>11.9207576867261</v>
+        <v>3.871190014066447</v>
       </c>
       <c r="K5" t="n">
-        <v>7.635348969569489</v>
+        <v>3.087144936792961</v>
       </c>
       <c r="L5" t="n">
-        <v>7.271457647984964</v>
+        <v>12.81239218836569</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90.11001954091897</v>
+        <v>3.373741105498577</v>
       </c>
       <c r="C6" t="n">
-        <v>9.522334360072604</v>
+        <v>3.465437388501965</v>
       </c>
       <c r="D6" t="n">
-        <v>9.359357964061532</v>
+        <v>3.397179806152655</v>
       </c>
       <c r="E6" t="n">
-        <v>9.498053568693688</v>
+        <v>3.461163970028605</v>
       </c>
       <c r="F6" t="n">
-        <v>9.522540837163278</v>
+        <v>3.465473729255891</v>
       </c>
       <c r="G6" t="n">
-        <v>90.18603027628959</v>
+        <v>17.66255399153954</v>
       </c>
       <c r="H6" t="n">
-        <v>90.18409660025428</v>
+        <v>17.66988011662018</v>
       </c>
       <c r="I6" t="n">
-        <v>90.18602822410335</v>
+        <v>3.449323762314956</v>
       </c>
       <c r="J6" t="n">
-        <v>9.412693014652179</v>
+        <v>3.429770634173319</v>
       </c>
       <c r="K6" t="n">
-        <v>9.25712815193166</v>
+        <v>3.372578071342062</v>
       </c>
       <c r="L6" t="n">
-        <v>9.348216277967023</v>
+        <v>3.380021330844657</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.629606287186042</v>
+        <v>2.190111878570321</v>
       </c>
       <c r="C7" t="n">
-        <v>2.705615270162456</v>
+        <v>2.265694835178707</v>
       </c>
       <c r="D7" t="n">
-        <v>2.657043048593488</v>
+        <v>2.217572217715593</v>
       </c>
       <c r="E7" t="n">
-        <v>2.705560222911669</v>
+        <v>2.265685147648794</v>
       </c>
       <c r="F7" t="n">
-        <v>2.705560222911669</v>
+        <v>2.265685147648794</v>
       </c>
       <c r="G7" t="n">
-        <v>2.705617022556691</v>
+        <v>2.266001342310386</v>
       </c>
       <c r="H7" t="n">
-        <v>2.714773794913126</v>
+        <v>2.275279386297405</v>
       </c>
       <c r="I7" t="n">
-        <v>2.705614970370448</v>
+        <v>2.2656945353867</v>
       </c>
       <c r="J7" t="n">
-        <v>2.685231891536486</v>
+        <v>2.245737482920763</v>
       </c>
       <c r="K7" t="n">
-        <v>2.649050887766704</v>
+        <v>2.209556479150981</v>
       </c>
       <c r="L7" t="n">
-        <v>2.638628253564251</v>
+        <v>2.199133844948528</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.691081423121038</v>
+        <v>2.200931502436253</v>
       </c>
       <c r="C8" t="n">
-        <v>3.092142647345322</v>
+        <v>2.333723653194269</v>
       </c>
       <c r="D8" t="n">
-        <v>3.11094378209954</v>
+        <v>2.297458746379784</v>
       </c>
       <c r="E8" t="n">
-        <v>3.003244092600117</v>
+        <v>2.318077508430067</v>
       </c>
       <c r="F8" t="n">
-        <v>2.777376796400534</v>
+        <v>2.278324864514345</v>
       </c>
       <c r="G8" t="n">
-        <v>3.092097224631135</v>
+        <v>2.334021857506912</v>
       </c>
       <c r="H8" t="n">
-        <v>3.101253996987548</v>
+        <v>2.343299901493928</v>
       </c>
       <c r="I8" t="n">
-        <v>3.092095172444899</v>
+        <v>2.333715050583226</v>
       </c>
       <c r="J8" t="n">
-        <v>3.071775966381197</v>
+        <v>2.313769239724795</v>
       </c>
       <c r="K8" t="n">
-        <v>2.704488887744498</v>
+        <v>2.219313567094203</v>
       </c>
       <c r="L8" t="n">
-        <v>3.364603423666128</v>
+        <v>2.326905474194115</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.706101314468272</v>
+        <v>2.731575000438018</v>
       </c>
       <c r="C9" t="n">
-        <v>6.757389043716207</v>
+        <v>2.978807015460094</v>
       </c>
       <c r="D9" t="n">
-        <v>6.708845358167731</v>
+        <v>2.930689420336561</v>
       </c>
       <c r="E9" t="n">
-        <v>7.882839217939893</v>
+        <v>3.176886245836324</v>
       </c>
       <c r="F9" t="n">
-        <v>6.757388444346879</v>
+        <v>2.978806910757267</v>
       </c>
       <c r="G9" t="n">
-        <v>6.757390796110446</v>
+        <v>2.979113522591775</v>
       </c>
       <c r="H9" t="n">
-        <v>6.766547568466886</v>
+        <v>2.988391566578795</v>
       </c>
       <c r="I9" t="n">
-        <v>6.757388743924198</v>
+        <v>2.978806715668087</v>
       </c>
       <c r="J9" t="n">
-        <v>6.737005665090238</v>
+        <v>2.958849663202151</v>
       </c>
       <c r="K9" t="n">
-        <v>5.472774653272621</v>
+        <v>2.823214515115028</v>
       </c>
       <c r="L9" t="n">
-        <v>6.690402027118016</v>
+        <v>2.912246025229919</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +926,7 @@
         <v>6.572306463094841</v>
       </c>
       <c r="G2" t="n">
-        <v>6.570910040197682</v>
+        <v>6.570910040197683</v>
       </c>
       <c r="H2" t="n">
         <v>6.657478327167045</v>
@@ -935,7 +935,7 @@
         <v>6.562577341608246</v>
       </c>
       <c r="J2" t="n">
-        <v>6.563894173329429</v>
+        <v>6.563894173329428</v>
       </c>
       <c r="K2" t="n">
         <v>6.487771275066654</v>
@@ -966,22 +966,22 @@
         <v>6.77359466371667</v>
       </c>
       <c r="G3" t="n">
-        <v>6.773451617069462</v>
+        <v>6.773451617069461</v>
       </c>
       <c r="H3" t="n">
         <v>6.873150977748995</v>
       </c>
       <c r="I3" t="n">
-        <v>6.763848342993219</v>
+        <v>6.763848342993218</v>
       </c>
       <c r="J3" t="n">
-        <v>6.758936741484164</v>
+        <v>6.758936741484163</v>
       </c>
       <c r="K3" t="n">
         <v>6.67459558874666</v>
       </c>
       <c r="L3" t="n">
-        <v>6.709614331693824</v>
+        <v>6.709614331693823</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.182749268662651</v>
+        <v>2.08834256003733</v>
       </c>
       <c r="C4" t="n">
-        <v>2.254536985529063</v>
+        <v>2.15913919869676</v>
       </c>
       <c r="D4" t="n">
-        <v>2.20780418592029</v>
+        <v>2.113397477294969</v>
       </c>
       <c r="E4" t="n">
-        <v>2.255104909313884</v>
+        <v>2.159239153876659</v>
       </c>
       <c r="F4" t="n">
-        <v>2.255104909313884</v>
+        <v>2.15923915387666</v>
       </c>
       <c r="G4" t="n">
-        <v>2.25843087064383</v>
+        <v>2.16391184619022</v>
       </c>
       <c r="H4" t="n">
-        <v>2.30974004239125</v>
+        <v>2.21533333376593</v>
       </c>
       <c r="I4" t="n">
-        <v>2.253778837573551</v>
+        <v>2.159004680263322</v>
       </c>
       <c r="J4" t="n">
-        <v>2.228616597361477</v>
+        <v>2.134209888736156</v>
       </c>
       <c r="K4" t="n">
-        <v>2.196092153161978</v>
+        <v>2.101685444536658</v>
       </c>
       <c r="L4" t="n">
-        <v>2.225343257046154</v>
+        <v>2.130936548420834</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.780031549294179</v>
+        <v>2.193464240858866</v>
       </c>
       <c r="C5" t="n">
-        <v>8.794455623021955</v>
+        <v>3.310164872658557</v>
       </c>
       <c r="D5" t="n">
-        <v>4.913867581048263</v>
+        <v>2.589664632256791</v>
       </c>
       <c r="E5" t="n">
-        <v>8.794455623743202</v>
+        <v>3.310164873379809</v>
       </c>
       <c r="F5" t="n">
-        <v>8.794455623743206</v>
+        <v>3.310164873379809</v>
       </c>
       <c r="G5" t="n">
-        <v>9.432509917283346</v>
+        <v>3.426549751557051</v>
       </c>
       <c r="H5" t="n">
-        <v>15.10729613021571</v>
+        <v>4.467703193018334</v>
       </c>
       <c r="I5" t="n">
-        <v>8.794454307009831</v>
+        <v>3.31016355664643</v>
       </c>
       <c r="J5" t="n">
-        <v>7.180035929678058</v>
+        <v>3.005659686501829</v>
       </c>
       <c r="K5" t="n">
-        <v>3.880746433826883</v>
+        <v>2.39818459632707</v>
       </c>
       <c r="L5" t="n">
-        <v>11.27070771229215</v>
+        <v>3.019720681250444</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78.78084682140822</v>
+        <v>15.5696076562709</v>
       </c>
       <c r="C6" t="n">
-        <v>8.532394787133953</v>
+        <v>3.26404216579219</v>
       </c>
       <c r="D6" t="n">
-        <v>8.387115328421958</v>
+        <v>15.59313059909953</v>
       </c>
       <c r="E6" t="n">
-        <v>8.511783611626681</v>
+        <v>3.260414599516879</v>
       </c>
       <c r="F6" t="n">
-        <v>8.533120175973046</v>
+        <v>3.264169834821485</v>
       </c>
       <c r="G6" t="n">
-        <v>78.85652842338934</v>
+        <v>3.254223898668407</v>
       </c>
       <c r="H6" t="n">
-        <v>78.89867145605642</v>
+        <v>15.6949851895301</v>
       </c>
       <c r="I6" t="n">
-        <v>8.448733714767647</v>
+        <v>3.249316732741507</v>
       </c>
       <c r="J6" t="n">
-        <v>78.81892196059034</v>
+        <v>15.61410355962223</v>
       </c>
       <c r="K6" t="n">
-        <v>8.292497218164485</v>
+        <v>3.174652730163112</v>
       </c>
       <c r="L6" t="n">
-        <v>8.412295929666262</v>
+        <v>3.219840212901636</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.524650933835844</v>
+        <v>2.148517252781749</v>
       </c>
       <c r="C7" t="n">
-        <v>2.595681818758866</v>
+        <v>2.219180689019864</v>
       </c>
       <c r="D7" t="n">
-        <v>2.549680864164829</v>
+        <v>2.173567772339968</v>
       </c>
       <c r="E7" t="n">
-        <v>2.595669958816174</v>
+        <v>2.219178602264274</v>
       </c>
       <c r="F7" t="n">
-        <v>2.595669958816174</v>
+        <v>2.219178602264274</v>
       </c>
       <c r="G7" t="n">
-        <v>2.600332535817024</v>
+        <v>2.224086538934639</v>
       </c>
       <c r="H7" t="n">
-        <v>2.651641707564442</v>
+        <v>2.275508026510348</v>
       </c>
       <c r="I7" t="n">
-        <v>2.595680502746744</v>
+        <v>2.219179373007741</v>
       </c>
       <c r="J7" t="n">
-        <v>2.570518262534669</v>
+        <v>2.194384581480575</v>
       </c>
       <c r="K7" t="n">
-        <v>2.537993818335173</v>
+        <v>2.161860137281077</v>
       </c>
       <c r="L7" t="n">
-        <v>2.567244922219346</v>
+        <v>2.191111241165252</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.573136045129646</v>
+        <v>2.157050632323218</v>
       </c>
       <c r="C8" t="n">
-        <v>2.919502030840338</v>
+        <v>2.276173046037384</v>
       </c>
       <c r="D8" t="n">
-        <v>2.930528977167481</v>
+        <v>2.24059703986523</v>
       </c>
       <c r="E8" t="n">
-        <v>2.844206080711332</v>
+        <v>2.262920959480799</v>
       </c>
       <c r="F8" t="n">
-        <v>2.652900106069757</v>
+        <v>2.229251108126326</v>
       </c>
       <c r="G8" t="n">
-        <v>2.924078525584807</v>
+        <v>2.28106583282502</v>
       </c>
       <c r="H8" t="n">
-        <v>2.975387697332241</v>
+        <v>2.332487320400732</v>
       </c>
       <c r="I8" t="n">
-        <v>2.919426492514527</v>
+        <v>2.276158666898123</v>
       </c>
       <c r="J8" t="n">
-        <v>2.894318348911165</v>
+        <v>2.251373396374037</v>
       </c>
       <c r="K8" t="n">
-        <v>2.581365817496552</v>
+        <v>2.169493609092117</v>
       </c>
       <c r="L8" t="n">
-        <v>3.178523916453668</v>
+        <v>2.298696343567531</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.30031823460112</v>
+        <v>2.461034696023029</v>
       </c>
       <c r="C9" t="n">
-        <v>4.968818540303594</v>
+        <v>2.636852749748535</v>
       </c>
       <c r="D9" t="n">
-        <v>4.92284243130918</v>
+        <v>2.59124420589415</v>
       </c>
       <c r="E9" t="n">
-        <v>5.658284767125826</v>
+        <v>2.758198805606034</v>
       </c>
       <c r="F9" t="n">
-        <v>4.968817989566712</v>
+        <v>2.636852653413156</v>
       </c>
       <c r="G9" t="n">
-        <v>4.97346925736175</v>
+        <v>2.641758599663307</v>
       </c>
       <c r="H9" t="n">
-        <v>5.024778429109159</v>
+        <v>2.69318008723902</v>
       </c>
       <c r="I9" t="n">
-        <v>4.968817224291477</v>
+        <v>2.636851433736412</v>
       </c>
       <c r="J9" t="n">
-        <v>4.94365498407939</v>
+        <v>2.612056642209247</v>
       </c>
       <c r="K9" t="n">
-        <v>4.564954351594591</v>
+        <v>2.518605189201674</v>
       </c>
       <c r="L9" t="n">
-        <v>4.940381643764069</v>
+        <v>2.608783301893923</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +1310,7 @@
         <v>6.980716642081835</v>
       </c>
       <c r="C2" t="n">
-        <v>6.98136930216386</v>
+        <v>6.981369302163861</v>
       </c>
       <c r="D2" t="n">
         <v>6.518116251304467</v>
@@ -1331,7 +1331,7 @@
         <v>6.5386704479566</v>
       </c>
       <c r="J2" t="n">
-        <v>6.575843290069747</v>
+        <v>6.575843290069748</v>
       </c>
       <c r="K2" t="n">
         <v>6.513837796658112</v>
@@ -1350,7 +1350,7 @@
         <v>7.243706136023093</v>
       </c>
       <c r="C3" t="n">
-        <v>7.243637643452908</v>
+        <v>7.243637643452911</v>
       </c>
       <c r="D3" t="n">
         <v>6.711619859246863</v>
@@ -1362,7 +1362,7 @@
         <v>6.735121287376209</v>
       </c>
       <c r="G3" t="n">
-        <v>6.814276622926516</v>
+        <v>6.814276622926515</v>
       </c>
       <c r="H3" t="n">
         <v>6.837745095875483</v>
@@ -1371,13 +1371,13 @@
         <v>6.73522708206266</v>
       </c>
       <c r="J3" t="n">
-        <v>6.776585576060242</v>
+        <v>6.776585576060243</v>
       </c>
       <c r="K3" t="n">
         <v>6.705764262533624</v>
       </c>
       <c r="L3" t="n">
-        <v>7.026899333062343</v>
+        <v>7.026899333062342</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.517310354244358</v>
+        <v>2.403204130209005</v>
       </c>
       <c r="C4" t="n">
-        <v>2.530468312365806</v>
+        <v>2.403271500690576</v>
       </c>
       <c r="D4" t="n">
-        <v>2.242314023968567</v>
+        <v>2.128207799933211</v>
       </c>
       <c r="E4" t="n">
-        <v>2.255993496126192</v>
+        <v>2.14067291206103</v>
       </c>
       <c r="F4" t="n">
-        <v>2.255993496126192</v>
+        <v>2.14067291206103</v>
       </c>
       <c r="G4" t="n">
-        <v>2.295375894305855</v>
+        <v>2.181264622173742</v>
       </c>
       <c r="H4" t="n">
-        <v>2.307422542623252</v>
+        <v>2.193316318587897</v>
       </c>
       <c r="I4" t="n">
-        <v>2.254119582916961</v>
+        <v>2.140335275259472</v>
       </c>
       <c r="J4" t="n">
-        <v>2.270961710770856</v>
+        <v>2.156855486735501</v>
       </c>
       <c r="K4" t="n">
-        <v>2.236072349497813</v>
+        <v>2.12196612546246</v>
       </c>
       <c r="L4" t="n">
-        <v>2.405251993673225</v>
+        <v>2.291145769637868</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.89141805787007</v>
+        <v>7.925047056126449</v>
       </c>
       <c r="C5" t="n">
-        <v>33.52310629893772</v>
+        <v>7.857975756770358</v>
       </c>
       <c r="D5" t="n">
-        <v>6.265182020994375</v>
+        <v>2.836232563573246</v>
       </c>
       <c r="E5" t="n">
-        <v>7.501864391506988</v>
+        <v>3.063946184645203</v>
       </c>
       <c r="F5" t="n">
-        <v>7.501864391506988</v>
+        <v>3.063946184645203</v>
       </c>
       <c r="G5" t="n">
-        <v>11.68563492028243</v>
+        <v>3.833950201790383</v>
       </c>
       <c r="H5" t="n">
-        <v>13.95508005514042</v>
+        <v>4.243304029682843</v>
       </c>
       <c r="I5" t="n">
-        <v>7.501854891411686</v>
+        <v>3.063936684549922</v>
       </c>
       <c r="J5" t="n">
-        <v>9.404681125231088</v>
+        <v>3.41239009687726</v>
       </c>
       <c r="K5" t="n">
-        <v>5.67444949387843</v>
+        <v>2.727120499594363</v>
       </c>
       <c r="L5" t="n">
-        <v>25.14896595283707</v>
+        <v>6.294039404760627</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.44256539952114</v>
+        <v>3.560456110088748</v>
       </c>
       <c r="C6" t="n">
-        <v>9.222914732769278</v>
+        <v>3.581142064299175</v>
       </c>
       <c r="D6" t="n">
-        <v>8.801631269302273</v>
+        <v>3.282647760819785</v>
       </c>
       <c r="E6" t="n">
-        <v>8.887311265023694</v>
+        <v>3.307784833062871</v>
       </c>
       <c r="F6" t="n">
-        <v>8.917086872726669</v>
+        <v>3.313025339990205</v>
       </c>
       <c r="G6" t="n">
-        <v>83.22063093958276</v>
+        <v>16.42410943296614</v>
       </c>
       <c r="H6" t="n">
-        <v>83.22908490686279</v>
+        <v>16.43552881752117</v>
       </c>
       <c r="I6" t="n">
-        <v>83.1793746281939</v>
+        <v>16.38318008605186</v>
       </c>
       <c r="J6" t="n">
-        <v>83.19170943193396</v>
+        <v>16.39890700848815</v>
       </c>
       <c r="K6" t="n">
-        <v>8.70940649543788</v>
+        <v>3.261272928974456</v>
       </c>
       <c r="L6" t="n">
-        <v>8.976934928816597</v>
+        <v>3.44776195995586</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.879869543794105</v>
+        <v>2.467014547223996</v>
       </c>
       <c r="C7" t="n">
-        <v>2.878423664734982</v>
+        <v>2.464511642375715</v>
       </c>
       <c r="D7" t="n">
-        <v>2.604846982818063</v>
+        <v>2.192013600344985</v>
       </c>
       <c r="E7" t="n">
-        <v>2.61752092445149</v>
+        <v>2.204301739101503</v>
       </c>
       <c r="F7" t="n">
-        <v>2.61752092445149</v>
+        <v>2.204301739101503</v>
       </c>
       <c r="G7" t="n">
-        <v>2.657935083855601</v>
+        <v>2.245075039188734</v>
       </c>
       <c r="H7" t="n">
-        <v>2.669981732172998</v>
+        <v>2.25712673560289</v>
       </c>
       <c r="I7" t="n">
-        <v>2.616678772466706</v>
+        <v>2.204145692274465</v>
       </c>
       <c r="J7" t="n">
-        <v>2.633520900320601</v>
+        <v>2.220665903750493</v>
       </c>
       <c r="K7" t="n">
-        <v>2.598631539047559</v>
+        <v>2.185776542477451</v>
       </c>
       <c r="L7" t="n">
-        <v>2.767811183222968</v>
+        <v>2.354956186652861</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.937033209965694</v>
+        <v>2.477075352415679</v>
       </c>
       <c r="C8" t="n">
-        <v>3.232801715215602</v>
+        <v>2.526882178922585</v>
       </c>
       <c r="D8" t="n">
-        <v>3.019809038914476</v>
+        <v>2.265046921822214</v>
       </c>
       <c r="E8" t="n">
-        <v>2.889922348010749</v>
+        <v>2.252244389388151</v>
       </c>
       <c r="F8" t="n">
-        <v>2.683757407674229</v>
+        <v>2.215959360085537</v>
       </c>
       <c r="G8" t="n">
-        <v>3.011425605402752</v>
+        <v>2.307289370643916</v>
       </c>
       <c r="H8" t="n">
-        <v>3.023472253720294</v>
+        <v>2.3193410670581</v>
       </c>
       <c r="I8" t="n">
-        <v>2.970169294013851</v>
+        <v>2.266360023729647</v>
       </c>
       <c r="J8" t="n">
-        <v>2.987069658533581</v>
+        <v>2.282890484858807</v>
       </c>
       <c r="K8" t="n">
-        <v>2.650290781750658</v>
+        <v>2.19486856914393</v>
       </c>
       <c r="L8" t="n">
-        <v>3.430839883611111</v>
+        <v>2.471649237288859</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.291148361931499</v>
+        <v>2.891399616916602</v>
       </c>
       <c r="C9" t="n">
-        <v>6.069722503812438</v>
+        <v>3.026180235009889</v>
       </c>
       <c r="D9" t="n">
-        <v>5.796171846031244</v>
+        <v>2.753686773227019</v>
       </c>
       <c r="E9" t="n">
-        <v>6.708112600274322</v>
+        <v>2.924245870145234</v>
       </c>
       <c r="F9" t="n">
-        <v>5.807986399875741</v>
+        <v>2.765823659733508</v>
       </c>
       <c r="G9" t="n">
-        <v>5.849233922933066</v>
+        <v>2.80674363182291</v>
       </c>
       <c r="H9" t="n">
-        <v>5.861280571250453</v>
+        <v>2.818795328237065</v>
       </c>
       <c r="I9" t="n">
-        <v>5.807977611544176</v>
+        <v>2.765814284908639</v>
       </c>
       <c r="J9" t="n">
-        <v>5.824819739398074</v>
+        <v>2.782334496384669</v>
       </c>
       <c r="K9" t="n">
-        <v>4.807745992217474</v>
+        <v>2.667902507474399</v>
       </c>
       <c r="L9" t="n">
-        <v>5.959110022300437</v>
+        <v>2.916624779287036</v>
       </c>
     </row>
   </sheetData>
@@ -1743,16 +1743,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.18092189794068</v>
+        <v>7.180921897940681</v>
       </c>
       <c r="C3" t="n">
-        <v>7.163728521693672</v>
+        <v>7.16372852169367</v>
       </c>
       <c r="D3" t="n">
-        <v>6.699295271751199</v>
+        <v>6.6992952717512</v>
       </c>
       <c r="E3" t="n">
-        <v>6.708542321671891</v>
+        <v>6.708542321671892</v>
       </c>
       <c r="F3" t="n">
         <v>6.708542321671891</v>
@@ -1761,7 +1761,7 @@
         <v>6.777003230613362</v>
       </c>
       <c r="H3" t="n">
-        <v>6.791104034157028</v>
+        <v>6.791104034157029</v>
       </c>
       <c r="I3" t="n">
         <v>6.707666107174751</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.479177599330605</v>
+        <v>2.369779116287195</v>
       </c>
       <c r="C4" t="n">
-        <v>2.480018921531985</v>
+        <v>2.360805144725701</v>
       </c>
       <c r="D4" t="n">
-        <v>2.230260157656163</v>
+        <v>2.120861674612752</v>
       </c>
       <c r="E4" t="n">
-        <v>2.250998951461708</v>
+        <v>2.12803723717138</v>
       </c>
       <c r="F4" t="n">
-        <v>2.250998951461708</v>
+        <v>2.12803723717138</v>
       </c>
       <c r="G4" t="n">
-        <v>2.270464291869864</v>
+        <v>2.161030710005164</v>
       </c>
       <c r="H4" t="n">
-        <v>2.277637913648421</v>
+        <v>2.168239430605013</v>
       </c>
       <c r="I4" t="n">
-        <v>2.234365194979168</v>
+        <v>2.125102865836663</v>
       </c>
       <c r="J4" t="n">
-        <v>2.24515529082094</v>
+        <v>2.135756807777532</v>
       </c>
       <c r="K4" t="n">
-        <v>2.219444955880322</v>
+        <v>2.11004647283691</v>
       </c>
       <c r="L4" t="n">
-        <v>2.339844331203661</v>
+        <v>2.230445848160253</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.22266082215754</v>
+        <v>7.076632138000154</v>
       </c>
       <c r="C5" t="n">
-        <v>28.0974399374335</v>
+        <v>6.869471219093692</v>
       </c>
       <c r="D5" t="n">
-        <v>5.530589731707349</v>
+        <v>2.701719676498321</v>
       </c>
       <c r="E5" t="n">
-        <v>5.961700043423722</v>
+        <v>2.781120625817891</v>
       </c>
       <c r="F5" t="n">
-        <v>5.961700043423722</v>
+        <v>2.781120625817891</v>
       </c>
       <c r="G5" t="n">
-        <v>9.431833739902064</v>
+        <v>3.42143172602921</v>
       </c>
       <c r="H5" t="n">
-        <v>10.90475618486039</v>
+        <v>3.68661223811086</v>
       </c>
       <c r="I5" t="n">
-        <v>5.961691754334345</v>
+        <v>2.781112336728515</v>
       </c>
       <c r="J5" t="n">
-        <v>7.14829743608843</v>
+        <v>2.998709820668611</v>
       </c>
       <c r="K5" t="n">
-        <v>4.546553154321876</v>
+        <v>2.519617513543321</v>
       </c>
       <c r="L5" t="n">
-        <v>17.68265896197308</v>
+        <v>4.930781208543627</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.11219434789744</v>
+        <v>15.85718999095203</v>
       </c>
       <c r="C6" t="n">
-        <v>8.808540930461225</v>
+        <v>3.474625012261898</v>
       </c>
       <c r="D6" t="n">
-        <v>8.435641203544771</v>
+        <v>15.60786731378191</v>
       </c>
       <c r="E6" t="n">
-        <v>8.511103299256439</v>
+        <v>3.229815596413161</v>
       </c>
       <c r="F6" t="n">
-        <v>8.537348677753503</v>
+        <v>3.234434783003602</v>
       </c>
       <c r="G6" t="n">
-        <v>8.48886563940359</v>
+        <v>3.255469341240774</v>
       </c>
       <c r="H6" t="n">
-        <v>78.91205370657602</v>
+        <v>15.65589653707601</v>
       </c>
       <c r="I6" t="n">
-        <v>8.45276654251291</v>
+        <v>3.219541497072275</v>
       </c>
       <c r="J6" t="n">
-        <v>8.471126474625223</v>
+        <v>3.231527730189529</v>
       </c>
       <c r="K6" t="n">
-        <v>8.342617160740268</v>
+        <v>3.187724775052752</v>
       </c>
       <c r="L6" t="n">
-        <v>8.553834186667533</v>
+        <v>3.324108056795769</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.824660898885979</v>
+        <v>2.430584176679461</v>
       </c>
       <c r="C7" t="n">
-        <v>2.814850536676536</v>
+        <v>2.419735508671822</v>
       </c>
       <c r="D7" t="n">
-        <v>2.57571873718064</v>
+        <v>2.181662384279606</v>
       </c>
       <c r="E7" t="n">
-        <v>2.584859362291851</v>
+        <v>2.186796669159091</v>
       </c>
       <c r="F7" t="n">
-        <v>2.584859362291851</v>
+        <v>2.186796669159091</v>
       </c>
       <c r="G7" t="n">
-        <v>2.615947591425238</v>
+        <v>2.221835770397431</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6231212132038</v>
+        <v>2.229044490997281</v>
       </c>
       <c r="I7" t="n">
-        <v>2.579848494534546</v>
+        <v>2.185907926228931</v>
       </c>
       <c r="J7" t="n">
-        <v>2.590638590376318</v>
+        <v>2.196561868169799</v>
       </c>
       <c r="K7" t="n">
-        <v>2.564928255435696</v>
+        <v>2.170851533229178</v>
       </c>
       <c r="L7" t="n">
-        <v>2.68532763075904</v>
+        <v>2.291250908552521</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.87662293616826</v>
+        <v>2.43972949519159</v>
       </c>
       <c r="C8" t="n">
-        <v>3.154313543636722</v>
+        <v>2.479480997573444</v>
       </c>
       <c r="D8" t="n">
-        <v>2.968943605819096</v>
+        <v>2.250869960784965</v>
       </c>
       <c r="E8" t="n">
-        <v>2.841500760104256</v>
+        <v>2.231965554929321</v>
       </c>
       <c r="F8" t="n">
-        <v>2.643776860423503</v>
+        <v>2.197166148774074</v>
       </c>
       <c r="G8" t="n">
-        <v>2.950542063505081</v>
+        <v>2.28072439716439</v>
       </c>
       <c r="H8" t="n">
-        <v>2.957715685284365</v>
+        <v>2.287933117764364</v>
       </c>
       <c r="I8" t="n">
-        <v>2.91444296661439</v>
+        <v>2.24479655299589</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92528860773472</v>
+        <v>2.255460270905731</v>
       </c>
       <c r="K8" t="n">
-        <v>2.611640250144939</v>
+        <v>2.179072844253456</v>
       </c>
       <c r="L8" t="n">
-        <v>3.315155314241193</v>
+        <v>2.402100580244728</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.80012739604957</v>
+        <v>2.778266278296306</v>
       </c>
       <c r="C9" t="n">
-        <v>5.445288886882415</v>
+        <v>2.882692655799473</v>
       </c>
       <c r="D9" t="n">
-        <v>5.206181650489422</v>
+        <v>2.644623854513348</v>
       </c>
       <c r="E9" t="n">
-        <v>5.966117876365538</v>
+        <v>2.781898164411441</v>
       </c>
       <c r="F9" t="n">
-        <v>5.210294536734147</v>
+        <v>2.648873257357124</v>
       </c>
       <c r="G9" t="n">
-        <v>5.246385941631108</v>
+        <v>2.684792917525085</v>
       </c>
       <c r="H9" t="n">
-        <v>5.253559563409672</v>
+        <v>2.692001638124934</v>
       </c>
       <c r="I9" t="n">
-        <v>5.210286844740412</v>
+        <v>2.648865073356585</v>
       </c>
       <c r="J9" t="n">
-        <v>5.221076940582191</v>
+        <v>2.659519015297453</v>
       </c>
       <c r="K9" t="n">
-        <v>4.815873275712834</v>
+        <v>2.567017854651286</v>
       </c>
       <c r="L9" t="n">
-        <v>5.315765980964913</v>
+        <v>2.754208055680172</v>
       </c>
     </row>
   </sheetData>
@@ -2099,34 +2099,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.885334228729079</v>
+        <v>6.885334228729078</v>
       </c>
       <c r="C2" t="n">
         <v>6.860590935556651</v>
       </c>
       <c r="D2" t="n">
-        <v>6.496883386591978</v>
+        <v>6.496883386591977</v>
       </c>
       <c r="E2" t="n">
-        <v>6.495622747006123</v>
+        <v>6.495622747006122</v>
       </c>
       <c r="F2" t="n">
-        <v>6.495622747006123</v>
+        <v>6.495622747006122</v>
       </c>
       <c r="G2" t="n">
-        <v>6.552514848352313</v>
+        <v>6.552514848352312</v>
       </c>
       <c r="H2" t="n">
         <v>6.555195072201269</v>
       </c>
       <c r="I2" t="n">
-        <v>6.493905822819515</v>
+        <v>6.493905822819513</v>
       </c>
       <c r="J2" t="n">
-        <v>6.520160597343118</v>
+        <v>6.520160597343116</v>
       </c>
       <c r="K2" t="n">
-        <v>6.4860570199753</v>
+        <v>6.486057019975298</v>
       </c>
       <c r="L2" t="n">
         <v>6.623725646160929</v>
@@ -2139,34 +2139,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.134528486871744</v>
+        <v>7.134528486871743</v>
       </c>
       <c r="C3" t="n">
         <v>7.10541626288827</v>
       </c>
       <c r="D3" t="n">
-        <v>6.687729551064548</v>
+        <v>6.687729551064547</v>
       </c>
       <c r="E3" t="n">
-        <v>6.686019107316028</v>
+        <v>6.686019107316027</v>
       </c>
       <c r="F3" t="n">
-        <v>6.686019107316028</v>
+        <v>6.686019107316027</v>
       </c>
       <c r="G3" t="n">
-        <v>6.751717256111519</v>
+        <v>6.751717256111517</v>
       </c>
       <c r="H3" t="n">
-        <v>6.75493783461951</v>
+        <v>6.754937834619509</v>
       </c>
       <c r="I3" t="n">
-        <v>6.684397947321233</v>
+        <v>6.684397947321231</v>
       </c>
       <c r="J3" t="n">
         <v>6.712564535578373</v>
       </c>
       <c r="K3" t="n">
-        <v>6.6738524068144</v>
+        <v>6.673852406814401</v>
       </c>
       <c r="L3" t="n">
         <v>6.833627875836017</v>
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.452613010874728</v>
+        <v>2.345732687346413</v>
       </c>
       <c r="C4" t="n">
-        <v>2.445749405051673</v>
+        <v>2.33042694024444</v>
       </c>
       <c r="D4" t="n">
-        <v>2.221695445282671</v>
+        <v>2.114815121754356</v>
       </c>
       <c r="E4" t="n">
-        <v>2.23877037203826</v>
+        <v>2.116353474801968</v>
       </c>
       <c r="F4" t="n">
-        <v>2.23877037203826</v>
+        <v>2.116353474801968</v>
       </c>
       <c r="G4" t="n">
-        <v>2.254812085522869</v>
+        <v>2.147893780926878</v>
       </c>
       <c r="H4" t="n">
-        <v>2.256363080587207</v>
+        <v>2.149482757058889</v>
       </c>
       <c r="I4" t="n">
-        <v>2.219768305756891</v>
+        <v>2.113002480405915</v>
       </c>
       <c r="J4" t="n">
-        <v>2.227860468034853</v>
+        <v>2.120980144506539</v>
       </c>
       <c r="K4" t="n">
-        <v>2.209621732159045</v>
+        <v>2.10274140863073</v>
       </c>
       <c r="L4" t="n">
-        <v>2.297114326594031</v>
+        <v>2.190234003065711</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.05799137042547</v>
+        <v>6.67627925516182</v>
       </c>
       <c r="C5" t="n">
-        <v>25.37086158220241</v>
+        <v>6.365246661559886</v>
       </c>
       <c r="D5" t="n">
-        <v>5.086862356974248</v>
+        <v>2.619084495479634</v>
       </c>
       <c r="E5" t="n">
-        <v>4.951098460999497</v>
+        <v>2.593723215872467</v>
       </c>
       <c r="F5" t="n">
-        <v>4.951098460999497</v>
+        <v>2.593723215872467</v>
       </c>
       <c r="G5" t="n">
-        <v>8.303833131469235</v>
+        <v>3.212521479244641</v>
       </c>
       <c r="H5" t="n">
-        <v>9.080224304074985</v>
+        <v>3.350482325884998</v>
       </c>
       <c r="I5" t="n">
-        <v>4.951090413974476</v>
+        <v>2.59371516884741</v>
       </c>
       <c r="J5" t="n">
-        <v>5.836848107274667</v>
+        <v>2.756161965570945</v>
       </c>
       <c r="K5" t="n">
-        <v>3.984859993227292</v>
+        <v>2.415183340885743</v>
       </c>
       <c r="L5" t="n">
-        <v>13.54428755592056</v>
+        <v>4.169736480701032</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.07293513022283</v>
+        <v>3.438905451893313</v>
       </c>
       <c r="C6" t="n">
-        <v>8.765753794846368</v>
+        <v>3.442747706821078</v>
       </c>
       <c r="D6" t="n">
-        <v>8.42129424254199</v>
+        <v>3.205944504159584</v>
       </c>
       <c r="E6" t="n">
-        <v>8.490480105440261</v>
+        <v>3.216654381918636</v>
       </c>
       <c r="F6" t="n">
-        <v>8.516135503255331</v>
+        <v>3.221169731909608</v>
       </c>
       <c r="G6" t="n">
-        <v>8.466021008649991</v>
+        <v>15.63307040086132</v>
       </c>
       <c r="H6" t="n">
-        <v>78.8805822676277</v>
+        <v>15.63534526090347</v>
       </c>
       <c r="I6" t="n">
-        <v>8.430977228884013</v>
+        <v>15.59817910034035</v>
       </c>
       <c r="J6" t="n">
-        <v>8.446597792606719</v>
+        <v>15.60601907808969</v>
       </c>
       <c r="K6" t="n">
-        <v>8.326651490372795</v>
+        <v>3.179338640242691</v>
       </c>
       <c r="L6" t="n">
-        <v>8.503345326004927</v>
+        <v>3.282530653043302</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.796188745517282</v>
+        <v>2.406202016315842</v>
       </c>
       <c r="C7" t="n">
-        <v>2.780294305223553</v>
+        <v>2.389306842355644</v>
       </c>
       <c r="D7" t="n">
-        <v>2.565245836324507</v>
+        <v>2.175279990250084</v>
       </c>
       <c r="E7" t="n">
-        <v>2.569256406263582</v>
+        <v>2.174519016510449</v>
       </c>
       <c r="F7" t="n">
-        <v>2.569256406263582</v>
+        <v>2.174519016510449</v>
       </c>
       <c r="G7" t="n">
-        <v>2.598387820165419</v>
+        <v>2.208363109896308</v>
       </c>
       <c r="H7" t="n">
-        <v>2.599938815229758</v>
+        <v>2.209952086028319</v>
       </c>
       <c r="I7" t="n">
-        <v>2.563344040399445</v>
+        <v>2.173471809375345</v>
       </c>
       <c r="J7" t="n">
-        <v>2.571436202677405</v>
+        <v>2.181449473475968</v>
       </c>
       <c r="K7" t="n">
-        <v>2.553197466801598</v>
+        <v>2.163210737600159</v>
       </c>
       <c r="L7" t="n">
-        <v>2.640690061236582</v>
+        <v>2.250703332035141</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.846118677542525</v>
+        <v>2.414989684304668</v>
       </c>
       <c r="C8" t="n">
-        <v>3.116553874957366</v>
+        <v>2.448488526307543</v>
       </c>
       <c r="D8" t="n">
-        <v>2.95398173980969</v>
+        <v>2.243697508892748</v>
       </c>
       <c r="E8" t="n">
-        <v>2.822256164265206</v>
+        <v>2.219046973677456</v>
       </c>
       <c r="F8" t="n">
-        <v>2.625713842922823</v>
+        <v>2.184455525308632</v>
       </c>
       <c r="G8" t="n">
-        <v>2.928914762128142</v>
+        <v>2.266535851366532</v>
       </c>
       <c r="H8" t="n">
-        <v>2.930465757193827</v>
+        <v>2.26812482749878</v>
       </c>
       <c r="I8" t="n">
-        <v>2.893870982362166</v>
+        <v>2.23164455084557</v>
       </c>
       <c r="J8" t="n">
-        <v>2.902018289879431</v>
+        <v>2.239631920508257</v>
       </c>
       <c r="K8" t="n">
-        <v>2.597915165315686</v>
+        <v>2.171081052495992</v>
       </c>
       <c r="L8" t="n">
-        <v>3.264324043120499</v>
+        <v>2.360462912251967</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.536919151546881</v>
+        <v>2.712570566116963</v>
       </c>
       <c r="C9" t="n">
-        <v>5.110755145249053</v>
+        <v>2.799467947977632</v>
       </c>
       <c r="D9" t="n">
-        <v>4.895731887489709</v>
+        <v>2.585445533032632</v>
       </c>
       <c r="E9" t="n">
-        <v>5.574348536424838</v>
+        <v>2.703415228552952</v>
       </c>
       <c r="F9" t="n">
-        <v>4.893812377201901</v>
+        <v>2.583640865178724</v>
       </c>
       <c r="G9" t="n">
-        <v>4.928848660190923</v>
+        <v>2.618524215518295</v>
       </c>
       <c r="H9" t="n">
-        <v>4.93039965525526</v>
+        <v>2.620113191650306</v>
       </c>
       <c r="I9" t="n">
-        <v>4.893804880424945</v>
+        <v>2.583632914997331</v>
       </c>
       <c r="J9" t="n">
-        <v>4.90189704270291</v>
+        <v>2.591610579097955</v>
       </c>
       <c r="K9" t="n">
-        <v>4.528103243405289</v>
+        <v>2.442678494580285</v>
       </c>
       <c r="L9" t="n">
-        <v>4.971150901262081</v>
+        <v>2.660864437657128</v>
       </c>
     </row>
   </sheetData>
@@ -2498,7 +2498,7 @@
         <v>6.970095143568499</v>
       </c>
       <c r="C2" t="n">
-        <v>7.051477830862398</v>
+        <v>7.051477830862397</v>
       </c>
       <c r="D2" t="n">
         <v>6.504161237759538</v>
@@ -2513,7 +2513,7 @@
         <v>6.595051609198262</v>
       </c>
       <c r="H2" t="n">
-        <v>6.681341837976552</v>
+        <v>6.681341837976551</v>
       </c>
       <c r="I2" t="n">
         <v>6.52982481266763</v>
@@ -2544,13 +2544,13 @@
         <v>6.69577200211426</v>
       </c>
       <c r="E3" t="n">
-        <v>6.726082035653668</v>
+        <v>6.726082035653669</v>
       </c>
       <c r="F3" t="n">
         <v>6.726082035653669</v>
       </c>
       <c r="G3" t="n">
-        <v>6.800314757152514</v>
+        <v>6.800314757152513</v>
       </c>
       <c r="H3" t="n">
         <v>6.899712018863305</v>
@@ -2559,7 +2559,7 @@
         <v>6.725415594706487</v>
       </c>
       <c r="J3" t="n">
-        <v>6.785305704872569</v>
+        <v>6.78530570487257</v>
       </c>
       <c r="K3" t="n">
         <v>6.70088108631735</v>
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.517941653057976</v>
+        <v>2.397462718636511</v>
       </c>
       <c r="C4" t="n">
-        <v>2.579805600387587</v>
+        <v>2.44478445094221</v>
       </c>
       <c r="D4" t="n">
-        <v>2.240963689348916</v>
+        <v>2.120484754927451</v>
       </c>
       <c r="E4" t="n">
-        <v>2.281897969487462</v>
+        <v>2.140251726238716</v>
       </c>
       <c r="F4" t="n">
-        <v>2.281897969487461</v>
+        <v>2.140251726238716</v>
       </c>
       <c r="G4" t="n">
-        <v>2.295040046614828</v>
+        <v>2.17452330476832</v>
       </c>
       <c r="H4" t="n">
-        <v>2.34627466702342</v>
+        <v>2.225795732601954</v>
       </c>
       <c r="I4" t="n">
-        <v>2.256047682481781</v>
+        <v>2.135694730874941</v>
       </c>
       <c r="J4" t="n">
-        <v>2.28144109092857</v>
+        <v>2.160962156507105</v>
       </c>
       <c r="K4" t="n">
-        <v>2.23915487150646</v>
+        <v>2.118675937084995</v>
       </c>
       <c r="L4" t="n">
-        <v>2.418474668559907</v>
+        <v>2.297995734138444</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33.18643400326025</v>
+        <v>7.795117343024327</v>
       </c>
       <c r="C5" t="n">
-        <v>37.49982659246004</v>
+        <v>8.590708112244627</v>
       </c>
       <c r="D5" t="n">
-        <v>5.389797509932498</v>
+        <v>2.6746795043472</v>
       </c>
       <c r="E5" t="n">
-        <v>6.915544706411816</v>
+        <v>2.955773547518416</v>
       </c>
       <c r="F5" t="n">
-        <v>6.915544706411816</v>
+        <v>2.955773547518416</v>
       </c>
       <c r="G5" t="n">
-        <v>10.88131126550419</v>
+        <v>3.685707031104339</v>
       </c>
       <c r="H5" t="n">
-        <v>17.37805371877812</v>
+        <v>4.871388831375361</v>
       </c>
       <c r="I5" t="n">
-        <v>6.915535792728061</v>
+        <v>2.955764633834655</v>
       </c>
       <c r="J5" t="n">
-        <v>9.690503019310375</v>
+        <v>3.464957048836464</v>
       </c>
       <c r="K5" t="n">
-        <v>5.227019311402302</v>
+        <v>2.644540075657209</v>
       </c>
       <c r="L5" t="n">
-        <v>25.76949773892426</v>
+        <v>6.407775772253297</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.4499646083781</v>
+        <v>3.555666440751517</v>
       </c>
       <c r="C6" t="n">
-        <v>9.284708542566278</v>
+        <v>3.624847362371365</v>
       </c>
       <c r="D6" t="n">
-        <v>8.804777923928054</v>
+        <v>3.275716053953643</v>
       </c>
       <c r="E6" t="n">
-        <v>8.897495874902138</v>
+        <v>3.304596951282578</v>
       </c>
       <c r="F6" t="n">
-        <v>8.925929389157627</v>
+        <v>3.30960124976442</v>
       </c>
       <c r="G6" t="n">
-        <v>8.875743048835568</v>
+        <v>3.332727026883318</v>
       </c>
       <c r="H6" t="n">
-        <v>83.2770337147897</v>
+        <v>16.46960924782719</v>
       </c>
       <c r="I6" t="n">
-        <v>83.18807063780196</v>
+        <v>3.293898452989944</v>
       </c>
       <c r="J6" t="n">
-        <v>83.21173559491328</v>
+        <v>16.40469391202726</v>
       </c>
       <c r="K6" t="n">
-        <v>8.718235366234671</v>
+        <v>3.258994097978229</v>
       </c>
       <c r="L6" t="n">
-        <v>8.995848861815571</v>
+        <v>3.455613585878766</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.886424822087416</v>
+        <v>2.462315756034279</v>
       </c>
       <c r="C7" t="n">
-        <v>2.932102479102942</v>
+        <v>2.506788701260134</v>
       </c>
       <c r="D7" t="n">
-        <v>2.609420934544128</v>
+        <v>2.18533322973042</v>
       </c>
       <c r="E7" t="n">
-        <v>2.632042629447027</v>
+        <v>2.201877186057675</v>
       </c>
       <c r="F7" t="n">
-        <v>2.632042629447027</v>
+        <v>2.201877186057675</v>
       </c>
       <c r="G7" t="n">
-        <v>2.663523215644266</v>
+        <v>2.239376342166087</v>
       </c>
       <c r="H7" t="n">
-        <v>2.714757836052859</v>
+        <v>2.290648769999723</v>
       </c>
       <c r="I7" t="n">
-        <v>2.624530851511219</v>
+        <v>2.200547768272709</v>
       </c>
       <c r="J7" t="n">
-        <v>2.649924259958008</v>
+        <v>2.225815193904872</v>
       </c>
       <c r="K7" t="n">
-        <v>2.607638040535899</v>
+        <v>2.183528974482763</v>
       </c>
       <c r="L7" t="n">
-        <v>2.786957837589348</v>
+        <v>2.362848771536211</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.943605156617294</v>
+        <v>2.472379494857007</v>
       </c>
       <c r="C8" t="n">
-        <v>3.298959311098435</v>
+        <v>2.571355503341479</v>
       </c>
       <c r="D8" t="n">
-        <v>3.031748881306621</v>
+        <v>2.259662947957855</v>
       </c>
       <c r="E8" t="n">
-        <v>2.907915320891363</v>
+        <v>2.250430779488785</v>
       </c>
       <c r="F8" t="n">
-        <v>2.695797448764929</v>
+        <v>2.213098034196824</v>
       </c>
       <c r="G8" t="n">
-        <v>3.023117695501055</v>
+        <v>2.302664970277946</v>
       </c>
       <c r="H8" t="n">
-        <v>3.074352315909211</v>
+        <v>2.353937398111505</v>
       </c>
       <c r="I8" t="n">
-        <v>2.984125331368005</v>
+        <v>2.263836396384568</v>
       </c>
       <c r="J8" t="n">
-        <v>3.009578172763351</v>
+        <v>2.289114282215621</v>
       </c>
       <c r="K8" t="n">
-        <v>2.659200877066251</v>
+        <v>2.192604033662931</v>
       </c>
       <c r="L8" t="n">
-        <v>3.462449179608913</v>
+        <v>2.481735247087457</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.284016507665624</v>
+        <v>2.884291890409524</v>
       </c>
       <c r="C9" t="n">
-        <v>6.10857392193774</v>
+        <v>3.06584767216974</v>
       </c>
       <c r="D9" t="n">
-        <v>5.785918017218334</v>
+        <v>2.744396713251733</v>
       </c>
       <c r="E9" t="n">
-        <v>6.699820711227935</v>
+        <v>2.917806124571782</v>
       </c>
       <c r="F9" t="n">
-        <v>5.801010436003574</v>
+        <v>2.759615516989465</v>
       </c>
       <c r="G9" t="n">
-        <v>5.83999465847906</v>
+        <v>2.798435313075692</v>
       </c>
       <c r="H9" t="n">
-        <v>5.891229278887653</v>
+        <v>2.849707740909329</v>
       </c>
       <c r="I9" t="n">
-        <v>5.801002294346014</v>
+        <v>2.759606739182315</v>
       </c>
       <c r="J9" t="n">
-        <v>5.826395702792805</v>
+        <v>2.784874164814477</v>
       </c>
       <c r="K9" t="n">
-        <v>4.803360913045264</v>
+        <v>2.569976197950409</v>
       </c>
       <c r="L9" t="n">
-        <v>5.963429280424148</v>
+        <v>2.921907742445817</v>
       </c>
     </row>
   </sheetData>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.859616661830868</v>
+        <v>6.859616661830869</v>
       </c>
       <c r="C2" t="n">
         <v>6.914738976881194</v>
       </c>
       <c r="D2" t="n">
-        <v>6.480451604497502</v>
+        <v>6.480451604497501</v>
       </c>
       <c r="E2" t="n">
         <v>6.505222679226359</v>
@@ -2909,13 +2909,13 @@
         <v>6.548717649896679</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7193444019632</v>
+        <v>6.719344401963199</v>
       </c>
       <c r="I2" t="n">
         <v>6.502816792281746</v>
       </c>
       <c r="J2" t="n">
-        <v>6.535368872036807</v>
+        <v>6.535368872036806</v>
       </c>
       <c r="K2" t="n">
         <v>6.487379477657186</v>
@@ -2937,7 +2937,7 @@
         <v>7.167519326877866</v>
       </c>
       <c r="D3" t="n">
-        <v>6.668838907816116</v>
+        <v>6.668838907816115</v>
       </c>
       <c r="E3" t="n">
         <v>6.696967468059001</v>
@@ -2946,22 +2946,22 @@
         <v>6.696967468059001</v>
       </c>
       <c r="G3" t="n">
-        <v>6.747359001293872</v>
+        <v>6.747359001293871</v>
       </c>
       <c r="H3" t="n">
-        <v>6.94375331261921</v>
+        <v>6.943753312619209</v>
       </c>
       <c r="I3" t="n">
         <v>6.694746311023635</v>
       </c>
       <c r="J3" t="n">
-        <v>6.729995289357078</v>
+        <v>6.729995289357077</v>
       </c>
       <c r="K3" t="n">
-        <v>6.675198090938998</v>
+        <v>6.675198090938997</v>
       </c>
       <c r="L3" t="n">
-        <v>6.855366781315193</v>
+        <v>6.855366781315192</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.443025562577845</v>
+        <v>2.331080669649154</v>
       </c>
       <c r="C4" t="n">
-        <v>2.487314090540623</v>
+        <v>2.36325761892032</v>
       </c>
       <c r="D4" t="n">
-        <v>2.217628002579528</v>
+        <v>2.105683109650837</v>
       </c>
       <c r="E4" t="n">
-        <v>2.262671476976411</v>
+        <v>2.124559690584047</v>
       </c>
       <c r="F4" t="n">
-        <v>2.262671476976411</v>
+        <v>2.124559690584047</v>
       </c>
       <c r="G4" t="n">
-        <v>2.258297532488525</v>
+        <v>2.146279914475898</v>
       </c>
       <c r="H4" t="n">
-        <v>2.359604683895579</v>
+        <v>2.247659790966888</v>
       </c>
       <c r="I4" t="n">
-        <v>2.231026491006144</v>
+        <v>2.118985038231564</v>
       </c>
       <c r="J4" t="n">
-        <v>2.242319829271589</v>
+        <v>2.130374936342899</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2153773631736</v>
+        <v>2.103432470244909</v>
       </c>
       <c r="L4" t="n">
-        <v>2.314040663246545</v>
+        <v>2.202095770317853</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.5500103263921</v>
+        <v>6.397909966043914</v>
       </c>
       <c r="C5" t="n">
-        <v>28.28084686167425</v>
+        <v>6.902919362041216</v>
       </c>
       <c r="D5" t="n">
-        <v>4.133762108480517</v>
+        <v>2.442922710462044</v>
       </c>
       <c r="E5" t="n">
-        <v>5.387249455450035</v>
+        <v>2.674485411815575</v>
       </c>
       <c r="F5" t="n">
-        <v>5.387249455450035</v>
+        <v>2.674485411815575</v>
       </c>
       <c r="G5" t="n">
-        <v>8.032955249779532</v>
+        <v>3.162619667211971</v>
       </c>
       <c r="H5" t="n">
-        <v>19.16764407180425</v>
+        <v>5.205874707209419</v>
       </c>
       <c r="I5" t="n">
-        <v>5.387243223833673</v>
+        <v>2.674479180199197</v>
       </c>
       <c r="J5" t="n">
-        <v>6.625539131478349</v>
+        <v>2.901821529351125</v>
       </c>
       <c r="K5" t="n">
-        <v>3.934226226534014</v>
+        <v>2.405949868557119</v>
       </c>
       <c r="L5" t="n">
-        <v>14.67099494316948</v>
+        <v>4.376919711799776</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.659380760932484</v>
+        <v>3.425159178631191</v>
       </c>
       <c r="C6" t="n">
-        <v>8.814745895091557</v>
+        <v>3.47688561048698</v>
       </c>
       <c r="D6" t="n">
-        <v>78.84296792037435</v>
+        <v>3.197437333859377</v>
       </c>
       <c r="E6" t="n">
-        <v>8.509564854071717</v>
+        <v>3.224012918995321</v>
       </c>
       <c r="F6" t="n">
-        <v>8.533992120700498</v>
+        <v>3.228312117898687</v>
       </c>
       <c r="G6" t="n">
-        <v>8.474652730843177</v>
+        <v>15.63243256427428</v>
       </c>
       <c r="H6" t="n">
-        <v>78.99608730088325</v>
+        <v>15.73568065847047</v>
       </c>
       <c r="I6" t="n">
-        <v>8.447381689360776</v>
+        <v>15.60513768802992</v>
       </c>
       <c r="J6" t="n">
-        <v>8.467186388252074</v>
+        <v>3.22595144478697</v>
       </c>
       <c r="K6" t="n">
-        <v>8.338411350260024</v>
+        <v>3.181086446132742</v>
       </c>
       <c r="L6" t="n">
-        <v>8.52621534324048</v>
+        <v>3.2954385080724</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.789752451533746</v>
+        <v>2.392104601774727</v>
       </c>
       <c r="C7" t="n">
-        <v>2.820688998727958</v>
+        <v>2.421931602443359</v>
       </c>
       <c r="D7" t="n">
-        <v>2.56432946969266</v>
+        <v>2.166702567532107</v>
       </c>
       <c r="E7" t="n">
-        <v>2.586941242241759</v>
+        <v>2.1816311689615</v>
       </c>
       <c r="F7" t="n">
-        <v>2.586941242241759</v>
+        <v>2.1816311689615</v>
       </c>
       <c r="G7" t="n">
-        <v>2.605024421444425</v>
+        <v>2.20730384660147</v>
       </c>
       <c r="H7" t="n">
-        <v>2.706331572851481</v>
+        <v>2.308683723092461</v>
       </c>
       <c r="I7" t="n">
-        <v>2.577753379962044</v>
+        <v>2.180008970357137</v>
       </c>
       <c r="J7" t="n">
-        <v>2.589046718227491</v>
+        <v>2.191398868468471</v>
       </c>
       <c r="K7" t="n">
-        <v>2.562104252129501</v>
+        <v>2.164456402370481</v>
       </c>
       <c r="L7" t="n">
-        <v>2.660767552202445</v>
+        <v>2.263119702443426</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.838768371554585</v>
+        <v>2.40073140365165</v>
       </c>
       <c r="C8" t="n">
-        <v>3.161105013291591</v>
+        <v>2.481844820681911</v>
       </c>
       <c r="D8" t="n">
-        <v>2.954492410427618</v>
+        <v>2.235371244729372</v>
       </c>
       <c r="E8" t="n">
-        <v>2.839960094230497</v>
+        <v>2.22616248667022</v>
       </c>
       <c r="F8" t="n">
-        <v>2.641223938192891</v>
+        <v>2.191184923397132</v>
       </c>
       <c r="G8" t="n">
-        <v>2.936576274152836</v>
+        <v>2.265656972361958</v>
       </c>
       <c r="H8" t="n">
-        <v>3.037883425562189</v>
+        <v>2.367036848853354</v>
       </c>
       <c r="I8" t="n">
-        <v>2.909305232670456</v>
+        <v>2.238362096117626</v>
       </c>
       <c r="J8" t="n">
-        <v>2.920654097223006</v>
+        <v>2.249761766855437</v>
       </c>
       <c r="K8" t="n">
-        <v>2.60587192215746</v>
+        <v>2.172159512253663</v>
       </c>
       <c r="L8" t="n">
-        <v>3.287451811764912</v>
+        <v>2.373416131528768</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.739846217917135</v>
+        <v>2.735321102798451</v>
       </c>
       <c r="C9" t="n">
-        <v>5.41951054844318</v>
+        <v>2.879324192714809</v>
       </c>
       <c r="D9" t="n">
-        <v>5.16317615732051</v>
+        <v>2.624099582076156</v>
       </c>
       <c r="E9" t="n">
-        <v>5.925198151666661</v>
+        <v>2.769164381836672</v>
       </c>
       <c r="F9" t="n">
-        <v>5.176580473553789</v>
+        <v>2.637407671202744</v>
       </c>
       <c r="G9" t="n">
-        <v>5.203845971159647</v>
+        <v>2.66469643687292</v>
       </c>
       <c r="H9" t="n">
-        <v>5.305153122566701</v>
+        <v>2.76607631336391</v>
       </c>
       <c r="I9" t="n">
-        <v>5.176574929677264</v>
+        <v>2.637401560628587</v>
       </c>
       <c r="J9" t="n">
-        <v>5.187868267942708</v>
+        <v>2.648791458739922</v>
       </c>
       <c r="K9" t="n">
-        <v>4.785050257011962</v>
+        <v>2.478080928870821</v>
       </c>
       <c r="L9" t="n">
-        <v>5.259589101917669</v>
+        <v>2.720512292714876</v>
       </c>
     </row>
   </sheetData>
@@ -3296,10 +3296,10 @@
         <v>6.474994184473312</v>
       </c>
       <c r="E2" t="n">
-        <v>6.483416504105328</v>
+        <v>6.483416504105327</v>
       </c>
       <c r="F2" t="n">
-        <v>6.483416504105328</v>
+        <v>6.483416504105327</v>
       </c>
       <c r="G2" t="n">
         <v>6.515837814519633</v>
@@ -3314,7 +3314,7 @@
         <v>6.513289203952197</v>
       </c>
       <c r="K2" t="n">
-        <v>6.475532300340209</v>
+        <v>6.47553230034021</v>
       </c>
       <c r="L2" t="n">
         <v>6.54216865662598</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.998083493368709</v>
+        <v>6.99808349336871</v>
       </c>
       <c r="C3" t="n">
         <v>7.007435851644481</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.392051764586097</v>
+        <v>2.277405737707265</v>
       </c>
       <c r="C4" t="n">
-        <v>2.415445622794644</v>
+        <v>2.28391385628848</v>
       </c>
       <c r="D4" t="n">
-        <v>2.218985053724525</v>
+        <v>2.104339026845691</v>
       </c>
       <c r="E4" t="n">
-        <v>2.243734626002878</v>
+        <v>2.110973597773795</v>
       </c>
       <c r="F4" t="n">
-        <v>2.243734626002878</v>
+        <v>2.110973597773795</v>
       </c>
       <c r="G4" t="n">
-        <v>2.243354994455558</v>
+        <v>2.128634697688072</v>
       </c>
       <c r="H4" t="n">
-        <v>2.315993293605422</v>
+        <v>2.201347266726589</v>
       </c>
       <c r="I4" t="n">
-        <v>2.221889048517698</v>
+        <v>2.107124697855573</v>
       </c>
       <c r="J4" t="n">
-        <v>2.232184014670899</v>
+        <v>2.117537987792066</v>
       </c>
       <c r="K4" t="n">
-        <v>2.212073316747486</v>
+        <v>2.097427289868652</v>
       </c>
       <c r="L4" t="n">
-        <v>2.258943003081266</v>
+        <v>2.144296976202433</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.48529349276886</v>
+        <v>5.461816264612366</v>
       </c>
       <c r="C5" t="n">
-        <v>20.7161196543948</v>
+        <v>5.504832468397226</v>
       </c>
       <c r="D5" t="n">
-        <v>4.03561366158605</v>
+        <v>2.424065660096847</v>
       </c>
       <c r="E5" t="n">
-        <v>4.311369875449851</v>
+        <v>2.474877399704606</v>
       </c>
       <c r="F5" t="n">
-        <v>4.311369875449851</v>
+        <v>2.474877399704606</v>
       </c>
       <c r="G5" t="n">
-        <v>6.389059423728218</v>
+        <v>2.8582786732864</v>
       </c>
       <c r="H5" t="n">
-        <v>14.3770849261864</v>
+        <v>4.324099382558485</v>
       </c>
       <c r="I5" t="n">
-        <v>4.311364926054622</v>
+        <v>2.474872450309386</v>
       </c>
       <c r="J5" t="n">
-        <v>5.410497666811663</v>
+        <v>2.676921187537767</v>
       </c>
       <c r="K5" t="n">
-        <v>3.405556129757031</v>
+        <v>2.307480263820139</v>
       </c>
       <c r="L5" t="n">
-        <v>8.565431508926471</v>
+        <v>3.254238947216853</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.00045553025106</v>
+        <v>15.76048472740482</v>
       </c>
       <c r="C6" t="n">
-        <v>8.714768264439019</v>
+        <v>3.392594635210383</v>
       </c>
       <c r="D6" t="n">
-        <v>8.411978467287259</v>
+        <v>3.194305861726631</v>
       </c>
       <c r="E6" t="n">
-        <v>8.487808748085392</v>
+        <v>3.2099306373055</v>
       </c>
       <c r="F6" t="n">
-        <v>8.512116119026143</v>
+        <v>3.214208734567899</v>
       </c>
       <c r="G6" t="n">
-        <v>78.85175876012056</v>
+        <v>15.61171368738564</v>
       </c>
       <c r="H6" t="n">
-        <v>78.93897870246482</v>
+        <v>15.68699262561247</v>
       </c>
       <c r="I6" t="n">
-        <v>8.424688727894887</v>
+        <v>3.198817435510513</v>
       </c>
       <c r="J6" t="n">
-        <v>78.83977723077092</v>
+        <v>15.600474320767</v>
       </c>
       <c r="K6" t="n">
-        <v>8.324014849369249</v>
+        <v>3.173128993781289</v>
       </c>
       <c r="L6" t="n">
-        <v>8.457435797847957</v>
+        <v>3.235231702170027</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.734568674924887</v>
+        <v>2.337688713600242</v>
       </c>
       <c r="C7" t="n">
-        <v>2.738630798092156</v>
+        <v>2.340794446832629</v>
       </c>
       <c r="D7" t="n">
-        <v>2.56147386392038</v>
+        <v>2.164617057113539</v>
       </c>
       <c r="E7" t="n">
-        <v>2.571023669569336</v>
+        <v>2.168576469129365</v>
       </c>
       <c r="F7" t="n">
-        <v>2.571023669569336</v>
+        <v>2.168576469129365</v>
       </c>
       <c r="G7" t="n">
-        <v>2.585871904794347</v>
+        <v>2.188917673581049</v>
       </c>
       <c r="H7" t="n">
-        <v>2.658510203944211</v>
+        <v>2.261630242619566</v>
       </c>
       <c r="I7" t="n">
-        <v>2.564405958856486</v>
+        <v>2.16740767374855</v>
       </c>
       <c r="J7" t="n">
-        <v>2.574700925009688</v>
+        <v>2.177820963685044</v>
       </c>
       <c r="K7" t="n">
-        <v>2.554590227086275</v>
+        <v>2.15771026576163</v>
       </c>
       <c r="L7" t="n">
-        <v>2.601459913420056</v>
+        <v>2.20457995209541</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.783613979251386</v>
+        <v>2.346320687114932</v>
       </c>
       <c r="C8" t="n">
-        <v>3.076791069901105</v>
+        <v>2.400310654348508</v>
       </c>
       <c r="D8" t="n">
-        <v>2.95186578239218</v>
+        <v>2.233326034392269</v>
       </c>
       <c r="E8" t="n">
-        <v>2.82456577805747</v>
+        <v>2.213199879981479</v>
       </c>
       <c r="F8" t="n">
-        <v>2.626378931593947</v>
+        <v>2.178318995192905</v>
       </c>
       <c r="G8" t="n">
-        <v>2.917616237907423</v>
+        <v>2.247304675892573</v>
       </c>
       <c r="H8" t="n">
-        <v>2.990254537060774</v>
+        <v>2.320017244931705</v>
       </c>
       <c r="I8" t="n">
-        <v>2.896150291969563</v>
+        <v>2.225794676060076</v>
       </c>
       <c r="J8" t="n">
-        <v>2.906500816376357</v>
+        <v>2.236217744249147</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5983842518297</v>
+        <v>2.165418014074707</v>
       </c>
       <c r="L8" t="n">
-        <v>3.228507020824286</v>
+        <v>2.314940242400555</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.441727952110485</v>
+        <v>2.638148744756832</v>
       </c>
       <c r="C9" t="n">
-        <v>5.027395873911437</v>
+        <v>2.743617097994087</v>
       </c>
       <c r="D9" t="n">
-        <v>4.85026683612456</v>
+        <v>2.567444618038711</v>
       </c>
       <c r="E9" t="n">
-        <v>5.52433584260706</v>
+        <v>2.688359408767508</v>
       </c>
       <c r="F9" t="n">
-        <v>4.853175410582989</v>
+        <v>2.570235173371338</v>
       </c>
       <c r="G9" t="n">
-        <v>4.874636980613631</v>
+        <v>2.591740324742504</v>
       </c>
       <c r="H9" t="n">
-        <v>4.947275279763485</v>
+        <v>2.664452893781023</v>
       </c>
       <c r="I9" t="n">
-        <v>4.853171034675766</v>
+        <v>2.570230324910005</v>
       </c>
       <c r="J9" t="n">
-        <v>4.86346600082897</v>
+        <v>2.580643614846497</v>
       </c>
       <c r="K9" t="n">
-        <v>4.506370533335359</v>
+        <v>2.498817345259346</v>
       </c>
       <c r="L9" t="n">
-        <v>4.890224989239335</v>
+        <v>2.607402603256869</v>
       </c>
     </row>
   </sheetData>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.960973509632158</v>
+        <v>6.960973509632156</v>
       </c>
       <c r="C2" t="n">
         <v>7.041156551097612</v>
@@ -3692,25 +3692,25 @@
         <v>6.490193119586618</v>
       </c>
       <c r="E2" t="n">
-        <v>6.529432273248585</v>
+        <v>6.529432273248582</v>
       </c>
       <c r="F2" t="n">
-        <v>6.529432273248585</v>
+        <v>6.529432273248582</v>
       </c>
       <c r="G2" t="n">
-        <v>6.592564185747463</v>
+        <v>6.592564185747462</v>
       </c>
       <c r="H2" t="n">
         <v>6.677738238429038</v>
       </c>
       <c r="I2" t="n">
-        <v>6.52809299102699</v>
+        <v>6.528092991026989</v>
       </c>
       <c r="J2" t="n">
-        <v>6.564310945516739</v>
+        <v>6.564310945516738</v>
       </c>
       <c r="K2" t="n">
-        <v>6.504323449675638</v>
+        <v>6.504323449675639</v>
       </c>
       <c r="L2" t="n">
         <v>6.818094847103302</v>
@@ -3723,31 +3723,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.221334791311018</v>
+        <v>7.221334791311013</v>
       </c>
       <c r="C3" t="n">
-        <v>7.312376163046433</v>
+        <v>7.312376163046432</v>
       </c>
       <c r="D3" t="n">
-        <v>6.679839820894645</v>
+        <v>6.679839820894643</v>
       </c>
       <c r="E3" t="n">
-        <v>6.724769379933312</v>
+        <v>6.724769379933313</v>
       </c>
       <c r="F3" t="n">
-        <v>6.724769379933312</v>
+        <v>6.72476937993331</v>
       </c>
       <c r="G3" t="n">
-        <v>6.797587753082087</v>
+        <v>6.797587753082084</v>
       </c>
       <c r="H3" t="n">
         <v>6.895700596519558</v>
       </c>
       <c r="I3" t="n">
-        <v>6.723586569593988</v>
+        <v>6.723586569593985</v>
       </c>
       <c r="J3" t="n">
-        <v>6.763316677783259</v>
+        <v>6.763316677783257</v>
       </c>
       <c r="K3" t="n">
         <v>6.694691612229247</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.513099032186886</v>
+        <v>2.392250140087168</v>
       </c>
       <c r="C4" t="n">
-        <v>2.572795227173801</v>
+        <v>2.438266382212747</v>
       </c>
       <c r="D4" t="n">
-        <v>2.233240038962137</v>
+        <v>2.112391146862418</v>
       </c>
       <c r="E4" t="n">
-        <v>2.285799217651013</v>
+        <v>2.140198260997822</v>
       </c>
       <c r="F4" t="n">
-        <v>2.285799217651013</v>
+        <v>2.140198260997822</v>
       </c>
       <c r="G4" t="n">
-        <v>2.294147219091046</v>
+        <v>2.173255545631184</v>
       </c>
       <c r="H4" t="n">
-        <v>2.344712564915579</v>
+        <v>2.223863672815862</v>
       </c>
       <c r="I4" t="n">
-        <v>2.255634254295482</v>
+        <v>2.134881976233304</v>
       </c>
       <c r="J4" t="n">
-        <v>2.270279203556876</v>
+        <v>2.149430311457157</v>
       </c>
       <c r="K4" t="n">
-        <v>2.236095283478613</v>
+        <v>2.115246391378895</v>
       </c>
       <c r="L4" t="n">
-        <v>2.428146176396315</v>
+        <v>2.307297284296598</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.65217787926502</v>
+        <v>7.696727988430064</v>
       </c>
       <c r="C5" t="n">
-        <v>36.85618200109844</v>
+        <v>8.4721424217283</v>
       </c>
       <c r="D5" t="n">
-        <v>4.592902606415908</v>
+        <v>2.527691756483934</v>
       </c>
       <c r="E5" t="n">
-        <v>6.82313052370089</v>
+        <v>2.938768566535492</v>
       </c>
       <c r="F5" t="n">
-        <v>6.82313052370089</v>
+        <v>2.938768566535492</v>
       </c>
       <c r="G5" t="n">
-        <v>10.74216708785877</v>
+        <v>3.660107034477641</v>
       </c>
       <c r="H5" t="n">
-        <v>17.1522904437483</v>
+        <v>4.829997365368806</v>
       </c>
       <c r="I5" t="n">
-        <v>6.823121723649067</v>
+        <v>2.93875976648366</v>
       </c>
       <c r="J5" t="n">
-        <v>8.500595540193089</v>
+        <v>3.245965980763438</v>
       </c>
       <c r="K5" t="n">
-        <v>4.880938845856856</v>
+        <v>2.580738855835147</v>
       </c>
       <c r="L5" t="n">
-        <v>26.7975503223911</v>
+        <v>6.596312390751208</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>83.44463648258342</v>
+        <v>3.550159637346336</v>
       </c>
       <c r="C6" t="n">
-        <v>9.27609093685512</v>
+        <v>3.618046420723904</v>
       </c>
       <c r="D6" t="n">
-        <v>8.794135715308196</v>
+        <v>3.267108779642359</v>
       </c>
       <c r="E6" t="n">
-        <v>8.89626760581155</v>
+        <v>3.303640691009842</v>
       </c>
       <c r="F6" t="n">
-        <v>8.924253534577273</v>
+        <v>3.308566214445919</v>
       </c>
       <c r="G6" t="n">
-        <v>83.22568466948769</v>
+        <v>16.41720605971867</v>
       </c>
       <c r="H6" t="n">
-        <v>83.27501732015826</v>
+        <v>16.46759723255743</v>
       </c>
       <c r="I6" t="n">
-        <v>8.834665524371763</v>
+        <v>16.37883249032079</v>
       </c>
       <c r="J6" t="n">
-        <v>83.20042207500461</v>
+        <v>16.39313537965096</v>
       </c>
       <c r="K6" t="n">
-        <v>8.713135013659242</v>
+        <v>3.255205377713696</v>
       </c>
       <c r="L6" t="n">
-        <v>9.004296299441066</v>
+        <v>3.464699699680962</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.883349955573953</v>
+        <v>2.457414302250193</v>
       </c>
       <c r="C7" t="n">
-        <v>2.927900094706323</v>
+        <v>2.500764838559817</v>
       </c>
       <c r="D7" t="n">
-        <v>2.603465213284452</v>
+        <v>2.177550777190073</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6345965415756</v>
+        <v>2.20158658967591</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6345965415756</v>
+        <v>2.20158658967591</v>
       </c>
       <c r="G7" t="n">
-        <v>2.66439814247811</v>
+        <v>2.238419707794209</v>
       </c>
       <c r="H7" t="n">
-        <v>2.714963488302647</v>
+        <v>2.289027834978886</v>
       </c>
       <c r="I7" t="n">
-        <v>2.625885177682547</v>
+        <v>2.200046138396328</v>
       </c>
       <c r="J7" t="n">
-        <v>2.640530126943942</v>
+        <v>2.214594473620183</v>
       </c>
       <c r="K7" t="n">
-        <v>2.60634620686568</v>
+        <v>2.18041055354192</v>
       </c>
       <c r="L7" t="n">
-        <v>2.798397099783382</v>
+        <v>2.372461446459624</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.940969665291034</v>
+        <v>2.46755537110545</v>
       </c>
       <c r="C8" t="n">
-        <v>3.298554786226448</v>
+        <v>2.566000063913874</v>
       </c>
       <c r="D8" t="n">
-        <v>3.028902936772254</v>
+        <v>2.252427816118196</v>
       </c>
       <c r="E8" t="n">
-        <v>2.912341601815323</v>
+        <v>2.250469720013223</v>
       </c>
       <c r="F8" t="n">
-        <v>2.698376725733998</v>
+        <v>2.212811902026963</v>
       </c>
       <c r="G8" t="n">
-        <v>3.026643917760001</v>
+        <v>2.302174963898359</v>
       </c>
       <c r="H8" t="n">
-        <v>3.077209263583979</v>
+        <v>2.352783091082938</v>
       </c>
       <c r="I8" t="n">
-        <v>2.988130952964441</v>
+        <v>2.263801394500477</v>
       </c>
       <c r="J8" t="n">
-        <v>3.002835769867716</v>
+        <v>2.278360266429243</v>
       </c>
       <c r="K8" t="n">
-        <v>2.658307331030466</v>
+        <v>2.189555711345369</v>
       </c>
       <c r="L8" t="n">
-        <v>3.478850272862339</v>
+        <v>2.49222120427259</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.277349735244202</v>
+        <v>2.87875826118906</v>
       </c>
       <c r="C9" t="n">
-        <v>6.100627503180793</v>
+        <v>3.059164859425573</v>
       </c>
       <c r="D9" t="n">
-        <v>5.776218090179251</v>
+        <v>2.735955280497782</v>
       </c>
       <c r="E9" t="n">
-        <v>6.697255347241734</v>
+        <v>2.916614535598695</v>
       </c>
       <c r="F9" t="n">
-        <v>5.798620620434163</v>
+        <v>2.758454824537568</v>
       </c>
       <c r="G9" t="n">
-        <v>5.83712555095257</v>
+        <v>2.796819728659967</v>
       </c>
       <c r="H9" t="n">
-        <v>5.88769089677711</v>
+        <v>2.847427855844643</v>
       </c>
       <c r="I9" t="n">
-        <v>5.798612586157013</v>
+        <v>2.758446159262083</v>
       </c>
       <c r="J9" t="n">
-        <v>5.813257535418402</v>
+        <v>2.772994494485939</v>
       </c>
       <c r="K9" t="n">
-        <v>5.30956999089324</v>
+        <v>2.659399733091905</v>
       </c>
       <c r="L9" t="n">
-        <v>5.971124508257842</v>
+        <v>2.930861467325378</v>
       </c>
     </row>
   </sheetData>
@@ -4082,7 +4082,7 @@
         <v>6.831843648859834</v>
       </c>
       <c r="C2" t="n">
-        <v>6.889428674804728</v>
+        <v>6.889428674804726</v>
       </c>
       <c r="D2" t="n">
         <v>6.482133424369983</v>
@@ -4097,7 +4097,7 @@
         <v>6.546314061514162</v>
       </c>
       <c r="H2" t="n">
-        <v>6.692411405916044</v>
+        <v>6.692411405916043</v>
       </c>
       <c r="I2" t="n">
         <v>6.497606397626091</v>
@@ -4119,19 +4119,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.07358581621303</v>
+        <v>7.073585816213031</v>
       </c>
       <c r="C3" t="n">
-        <v>7.138608096926844</v>
+        <v>7.138608096926845</v>
       </c>
       <c r="D3" t="n">
         <v>6.67134661579494</v>
       </c>
       <c r="E3" t="n">
-        <v>6.694196957390959</v>
+        <v>6.694196957390958</v>
       </c>
       <c r="F3" t="n">
-        <v>6.694196957390959</v>
+        <v>6.694196957390958</v>
       </c>
       <c r="G3" t="n">
         <v>6.74516764348968</v>
@@ -4140,10 +4140,10 @@
         <v>6.913348334037714</v>
       </c>
       <c r="I3" t="n">
-        <v>6.689376110614901</v>
+        <v>6.6893761106149</v>
       </c>
       <c r="J3" t="n">
-        <v>6.729436433311217</v>
+        <v>6.729436433311216</v>
       </c>
       <c r="K3" t="n">
         <v>6.677341506185445</v>
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.425250451824631</v>
+        <v>2.315372602683306</v>
       </c>
       <c r="C4" t="n">
-        <v>2.465405766009322</v>
+        <v>2.346827117198273</v>
       </c>
       <c r="D4" t="n">
-        <v>2.217362541844643</v>
+        <v>2.107484692703318</v>
       </c>
       <c r="E4" t="n">
-        <v>2.265220143747138</v>
+        <v>2.12348091826648</v>
       </c>
       <c r="F4" t="n">
-        <v>2.265220143747138</v>
+        <v>2.12348091826648</v>
       </c>
       <c r="G4" t="n">
-        <v>2.255601069723897</v>
+        <v>2.145652473045555</v>
       </c>
       <c r="H4" t="n">
-        <v>2.342334646435984</v>
+        <v>2.23245679729466</v>
       </c>
       <c r="I4" t="n">
-        <v>2.226643925279646</v>
+        <v>2.116686031898254</v>
       </c>
       <c r="J4" t="n">
-        <v>2.239013001588074</v>
+        <v>2.129135152446748</v>
       </c>
       <c r="K4" t="n">
-        <v>2.213135821944023</v>
+        <v>2.1032579728027</v>
       </c>
       <c r="L4" t="n">
-        <v>2.319400074059999</v>
+        <v>2.209522224918674</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.08864912658946</v>
+        <v>6.1281307487821</v>
       </c>
       <c r="C5" t="n">
-        <v>26.82676643024217</v>
+        <v>6.634426570870446</v>
       </c>
       <c r="D5" t="n">
-        <v>4.327382999557688</v>
+        <v>2.478848291248541</v>
       </c>
       <c r="E5" t="n">
-        <v>5.202563504440982</v>
+        <v>2.640453346947315</v>
       </c>
       <c r="F5" t="n">
-        <v>5.202563504440982</v>
+        <v>2.640453346947315</v>
       </c>
       <c r="G5" t="n">
-        <v>8.002633967911297</v>
+        <v>3.157130257645744</v>
       </c>
       <c r="H5" t="n">
-        <v>17.61779100561866</v>
+        <v>4.920937101942997</v>
       </c>
       <c r="I5" t="n">
-        <v>5.202556863719198</v>
+        <v>2.640446706225557</v>
       </c>
       <c r="J5" t="n">
-        <v>6.535347191760954</v>
+        <v>2.885289965819871</v>
       </c>
       <c r="K5" t="n">
-        <v>3.946320131361007</v>
+        <v>2.408298409607194</v>
       </c>
       <c r="L5" t="n">
-        <v>15.49233179123194</v>
+        <v>4.527958194578241</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.05048249100734</v>
+        <v>3.409226500413517</v>
       </c>
       <c r="C6" t="n">
-        <v>8.792806898670454</v>
+        <v>3.46044971051235</v>
       </c>
       <c r="D6" t="n">
-        <v>8.420025092220882</v>
+        <v>3.199153385899486</v>
       </c>
       <c r="E6" t="n">
-        <v>8.505022478105957</v>
+        <v>3.221686123162881</v>
       </c>
       <c r="F6" t="n">
-        <v>8.529158232368367</v>
+        <v>3.225934015890054</v>
       </c>
       <c r="G6" t="n">
-        <v>8.470680067777137</v>
+        <v>3.239506370775768</v>
       </c>
       <c r="H6" t="n">
-        <v>78.97754755727647</v>
+        <v>15.72025419651757</v>
       </c>
       <c r="I6" t="n">
-        <v>8.441722923332916</v>
+        <v>15.60272679771888</v>
       </c>
       <c r="J6" t="n">
-        <v>8.463047839630978</v>
+        <v>15.61537826299657</v>
       </c>
       <c r="K6" t="n">
-        <v>8.33564503837759</v>
+        <v>3.180819589056127</v>
       </c>
       <c r="L6" t="n">
-        <v>8.530981462982478</v>
+        <v>3.302760543445206</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.774263051550933</v>
+        <v>2.376798819902291</v>
       </c>
       <c r="C7" t="n">
-        <v>2.805170089582711</v>
+        <v>2.406625637823165</v>
       </c>
       <c r="D7" t="n">
-        <v>2.566350709739669</v>
+        <v>2.168906609920021</v>
       </c>
       <c r="E7" t="n">
-        <v>2.586844563645927</v>
+        <v>2.180086815861943</v>
       </c>
       <c r="F7" t="n">
-        <v>2.586844563645927</v>
+        <v>2.180086815861943</v>
       </c>
       <c r="G7" t="n">
-        <v>2.604613669450198</v>
+        <v>2.207078690264541</v>
       </c>
       <c r="H7" t="n">
-        <v>2.69134724616229</v>
+        <v>2.293883014513645</v>
       </c>
       <c r="I7" t="n">
-        <v>2.57565652500595</v>
+        <v>2.178112249117239</v>
       </c>
       <c r="J7" t="n">
-        <v>2.588025601314379</v>
+        <v>2.190561369665734</v>
       </c>
       <c r="K7" t="n">
-        <v>2.562148421670332</v>
+        <v>2.164684190021685</v>
       </c>
       <c r="L7" t="n">
-        <v>2.668412673786303</v>
+        <v>2.27094844213766</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.823383272871991</v>
+        <v>2.385443978807953</v>
       </c>
       <c r="C8" t="n">
-        <v>3.150081747850427</v>
+        <v>2.467330089349349</v>
       </c>
       <c r="D8" t="n">
-        <v>2.959612969418774</v>
+        <v>2.238120767248499</v>
       </c>
       <c r="E8" t="n">
-        <v>2.84147969499777</v>
+        <v>2.224902598737027</v>
       </c>
       <c r="F8" t="n">
-        <v>2.640502819767641</v>
+        <v>2.189530668888192</v>
       </c>
       <c r="G8" t="n">
-        <v>2.938751284088701</v>
+        <v>2.265886910122259</v>
       </c>
       <c r="H8" t="n">
-        <v>3.025484860802763</v>
+        <v>2.352691234371708</v>
       </c>
       <c r="I8" t="n">
-        <v>2.90979413964445</v>
+        <v>2.236920468974956</v>
       </c>
       <c r="J8" t="n">
-        <v>2.922219229901015</v>
+        <v>2.249379447978269</v>
       </c>
       <c r="K8" t="n">
-        <v>2.605974298595201</v>
+        <v>2.172397544318667</v>
       </c>
       <c r="L8" t="n">
-        <v>3.300274788387055</v>
+        <v>2.382156173704802</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.722879138325333</v>
+        <v>2.719755249316241</v>
       </c>
       <c r="C9" t="n">
-        <v>5.403156489369171</v>
+        <v>2.86387124170795</v>
       </c>
       <c r="D9" t="n">
-        <v>5.164361287459836</v>
+        <v>2.626156469121113</v>
       </c>
       <c r="E9" t="n">
-        <v>5.923008084376058</v>
+        <v>2.76725159232883</v>
       </c>
       <c r="F9" t="n">
-        <v>5.17364890634462</v>
+        <v>2.635364377709943</v>
       </c>
       <c r="G9" t="n">
-        <v>5.202600069236671</v>
+        <v>2.664324294149326</v>
       </c>
       <c r="H9" t="n">
-        <v>5.289333645948758</v>
+        <v>2.751128618398429</v>
       </c>
       <c r="I9" t="n">
-        <v>5.173642924792413</v>
+        <v>2.635357853002023</v>
       </c>
       <c r="J9" t="n">
-        <v>5.186012001100847</v>
+        <v>2.64780697355052</v>
       </c>
       <c r="K9" t="n">
-        <v>4.34246175098869</v>
+        <v>2.555710178575134</v>
       </c>
       <c r="L9" t="n">
-        <v>5.266399073572772</v>
+        <v>2.728194046022444</v>
       </c>
     </row>
   </sheetData>
@@ -4478,7 +4478,7 @@
         <v>6.77287225692178</v>
       </c>
       <c r="C2" t="n">
-        <v>6.795101842256028</v>
+        <v>6.795101842256027</v>
       </c>
       <c r="D2" t="n">
         <v>6.481266650802941</v>
@@ -4505,7 +4505,7 @@
         <v>6.479451620098476</v>
       </c>
       <c r="L2" t="n">
-        <v>6.560362691012198</v>
+        <v>6.560362691012197</v>
       </c>
     </row>
     <row r="3">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.00610391156033</v>
+        <v>7.006103911560329</v>
       </c>
       <c r="C3" t="n">
         <v>7.030918392043924</v>
@@ -4530,7 +4530,7 @@
         <v>6.672801977771634</v>
       </c>
       <c r="G3" t="n">
-        <v>6.716495605931854</v>
+        <v>6.716495605931855</v>
       </c>
       <c r="H3" t="n">
         <v>6.844073844365798</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.391105693255533</v>
+        <v>2.280229464279694</v>
       </c>
       <c r="C4" t="n">
-        <v>2.417160967670721</v>
+        <v>2.29337965784965</v>
       </c>
       <c r="D4" t="n">
-        <v>2.217758516795574</v>
+        <v>2.106882287819736</v>
       </c>
       <c r="E4" t="n">
-        <v>2.245172029076407</v>
+        <v>2.111203984474094</v>
       </c>
       <c r="F4" t="n">
-        <v>2.245172029076407</v>
+        <v>2.111203984474094</v>
       </c>
       <c r="G4" t="n">
-        <v>2.241501299464671</v>
+        <v>2.130565020565388</v>
       </c>
       <c r="H4" t="n">
-        <v>2.307273265752332</v>
+        <v>2.196397036776495</v>
       </c>
       <c r="I4" t="n">
-        <v>2.21716853220368</v>
+        <v>2.106270751067509</v>
       </c>
       <c r="J4" t="n">
-        <v>2.228303184818839</v>
+        <v>2.117426955843001</v>
       </c>
       <c r="K4" t="n">
-        <v>2.209428433871364</v>
+        <v>2.098552204895525</v>
       </c>
       <c r="L4" t="n">
-        <v>2.26480042152626</v>
+        <v>2.153924192550421</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.81978289702948</v>
+        <v>5.52367663456896</v>
       </c>
       <c r="C5" t="n">
-        <v>21.75739313698695</v>
+        <v>5.697260501205013</v>
       </c>
       <c r="D5" t="n">
-        <v>4.334173634074571</v>
+        <v>2.479371346442471</v>
       </c>
       <c r="E5" t="n">
-        <v>4.299491152990809</v>
+        <v>2.472764148323872</v>
       </c>
       <c r="F5" t="n">
-        <v>4.299491152990809</v>
+        <v>2.472764148323872</v>
       </c>
       <c r="G5" t="n">
-        <v>6.638899997524251</v>
+        <v>2.904507187230187</v>
       </c>
       <c r="H5" t="n">
-        <v>13.93571130053252</v>
+        <v>4.243002119808069</v>
       </c>
       <c r="I5" t="n">
-        <v>4.299485548641653</v>
+        <v>2.47275854397474</v>
       </c>
       <c r="J5" t="n">
-        <v>5.468163341928305</v>
+        <v>2.687642340404494</v>
       </c>
       <c r="K5" t="n">
-        <v>3.574489623662872</v>
+        <v>2.338802972997007</v>
       </c>
       <c r="L5" t="n">
-        <v>9.662673376313597</v>
+        <v>3.455949825537832</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79.0000830299377</v>
+        <v>3.372211225835743</v>
       </c>
       <c r="C6" t="n">
-        <v>8.723510635588891</v>
+        <v>3.403297193389036</v>
       </c>
       <c r="D6" t="n">
-        <v>8.412807567615207</v>
+        <v>3.197210914855931</v>
       </c>
       <c r="E6" t="n">
-        <v>8.485242735593943</v>
+        <v>3.209456422870184</v>
       </c>
       <c r="F6" t="n">
-        <v>8.509280305442289</v>
+        <v>3.213687035140568</v>
       </c>
       <c r="G6" t="n">
-        <v>78.85047863614699</v>
+        <v>15.61374495876146</v>
       </c>
       <c r="H6" t="n">
-        <v>78.92785284186087</v>
+        <v>15.68161896910052</v>
       </c>
       <c r="I6" t="n">
-        <v>8.421610392846098</v>
+        <v>15.58945068926357</v>
       </c>
       <c r="J6" t="n">
-        <v>78.83711838532516</v>
+        <v>3.21102851475545</v>
       </c>
       <c r="K6" t="n">
-        <v>8.323416900034887</v>
+        <v>3.174614169109554</v>
       </c>
       <c r="L6" t="n">
-        <v>8.465367549339007</v>
+        <v>3.245224001132138</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.734806960487346</v>
+        <v>2.340720886984714</v>
       </c>
       <c r="C7" t="n">
-        <v>2.74638614916835</v>
+        <v>2.35132328947926</v>
       </c>
       <c r="D7" t="n">
-        <v>2.561432565850787</v>
+        <v>2.167368920125701</v>
       </c>
       <c r="E7" t="n">
-        <v>2.56931623592407</v>
+        <v>2.168253364570154</v>
       </c>
       <c r="F7" t="n">
-        <v>2.56931623592407</v>
+        <v>2.168253364570154</v>
       </c>
       <c r="G7" t="n">
-        <v>2.585202566696484</v>
+        <v>2.191056443270408</v>
       </c>
       <c r="H7" t="n">
-        <v>2.650974532984144</v>
+        <v>2.256888459481514</v>
       </c>
       <c r="I7" t="n">
-        <v>2.560869799435493</v>
+        <v>2.166762173772529</v>
       </c>
       <c r="J7" t="n">
-        <v>2.572004452050651</v>
+        <v>2.177918378548021</v>
       </c>
       <c r="K7" t="n">
-        <v>2.553129701103176</v>
+        <v>2.159043627600545</v>
       </c>
       <c r="L7" t="n">
-        <v>2.608501688758071</v>
+        <v>2.214415615255441</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.781920550609356</v>
+        <v>2.349012878801257</v>
       </c>
       <c r="C8" t="n">
-        <v>3.082742085375389</v>
+        <v>2.410521933930923</v>
       </c>
       <c r="D8" t="n">
-        <v>2.947938280317686</v>
+        <v>2.235393925503275</v>
       </c>
       <c r="E8" t="n">
-        <v>2.819484555805865</v>
+        <v>2.212282988630772</v>
       </c>
       <c r="F8" t="n">
-        <v>2.621950428887469</v>
+        <v>2.177516982481517</v>
       </c>
       <c r="G8" t="n">
-        <v>2.913397098641128</v>
+        <v>2.248818680579674</v>
       </c>
       <c r="H8" t="n">
-        <v>2.979169064931727</v>
+        <v>2.314650696791298</v>
       </c>
       <c r="I8" t="n">
-        <v>2.889064331380137</v>
+        <v>2.224524411081796</v>
       </c>
       <c r="J8" t="n">
-        <v>2.900254224283531</v>
+        <v>2.235690338147964</v>
       </c>
       <c r="K8" t="n">
-        <v>2.595022068437265</v>
+        <v>2.166416684211393</v>
       </c>
       <c r="L8" t="n">
-        <v>3.230308767889544</v>
+        <v>2.323853660589579</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.446382051610237</v>
+        <v>2.641958101390056</v>
       </c>
       <c r="C9" t="n">
-        <v>5.040618202300891</v>
+        <v>2.755108128642637</v>
       </c>
       <c r="D9" t="n">
-        <v>4.855691633053263</v>
+        <v>2.571158513765361</v>
       </c>
       <c r="E9" t="n">
-        <v>5.527480328017739</v>
+        <v>2.688890241957515</v>
       </c>
       <c r="F9" t="n">
-        <v>4.855106877534816</v>
+        <v>2.570552515313747</v>
       </c>
       <c r="G9" t="n">
-        <v>4.879434619829017</v>
+        <v>2.594841282433785</v>
       </c>
       <c r="H9" t="n">
-        <v>4.945206586116681</v>
+        <v>2.660673298644889</v>
       </c>
       <c r="I9" t="n">
-        <v>4.855101852568032</v>
+        <v>2.570547012935906</v>
       </c>
       <c r="J9" t="n">
-        <v>4.866236505183184</v>
+        <v>2.581703217711399</v>
       </c>
       <c r="K9" t="n">
-        <v>4.496071336974249</v>
+        <v>2.501001353660921</v>
       </c>
       <c r="L9" t="n">
-        <v>4.902733741890613</v>
+        <v>2.618200454418817</v>
       </c>
     </row>
   </sheetData>
@@ -4929,19 +4929,19 @@
         <v>6.832464945424198</v>
       </c>
       <c r="H3" t="n">
-        <v>6.847091673517506</v>
+        <v>6.847091673517507</v>
       </c>
       <c r="I3" t="n">
-        <v>6.846728484943629</v>
+        <v>6.84672848494363</v>
       </c>
       <c r="J3" t="n">
-        <v>6.807158358390694</v>
+        <v>6.807158358390695</v>
       </c>
       <c r="K3" t="n">
-        <v>6.73987907172849</v>
+        <v>6.739879071728489</v>
       </c>
       <c r="L3" t="n">
-        <v>6.698042496989069</v>
+        <v>6.69804249698907</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.225115553458736</v>
+        <v>2.114762697201099</v>
       </c>
       <c r="C4" t="n">
-        <v>2.317558425400377</v>
+        <v>2.20544867570852</v>
       </c>
       <c r="D4" t="n">
-        <v>2.255025541529452</v>
+        <v>2.144672685271816</v>
       </c>
       <c r="E4" t="n">
-        <v>2.318248154702267</v>
+        <v>2.20557006913461</v>
       </c>
       <c r="F4" t="n">
-        <v>2.318248154702267</v>
+        <v>2.20557006913461</v>
       </c>
       <c r="G4" t="n">
-        <v>2.30822698836997</v>
+        <v>2.197732270339194</v>
       </c>
       <c r="H4" t="n">
-        <v>2.315542829770118</v>
+        <v>2.205189973512482</v>
       </c>
       <c r="I4" t="n">
-        <v>2.316104491175996</v>
+        <v>2.205193992137677</v>
       </c>
       <c r="J4" t="n">
-        <v>2.272519604006943</v>
+        <v>2.162166747749306</v>
       </c>
       <c r="K4" t="n">
-        <v>2.248231309151957</v>
+        <v>2.137878452894321</v>
       </c>
       <c r="L4" t="n">
-        <v>2.238637450648523</v>
+        <v>2.128284594390887</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.796518928215725</v>
+        <v>2.567329688706049</v>
       </c>
       <c r="C5" t="n">
-        <v>13.08634878794749</v>
+        <v>4.100755769246889</v>
       </c>
       <c r="D5" t="n">
-        <v>7.739614215700176</v>
+        <v>3.109960286695349</v>
       </c>
       <c r="E5" t="n">
-        <v>13.08634878924549</v>
+        <v>4.100755770544967</v>
       </c>
       <c r="F5" t="n">
-        <v>13.08634878924549</v>
+        <v>4.100755770544967</v>
       </c>
       <c r="G5" t="n">
-        <v>13.12885129012828</v>
+        <v>4.1021621371293</v>
       </c>
       <c r="H5" t="n">
-        <v>15.09813316064477</v>
+        <v>4.454925859555992</v>
       </c>
       <c r="I5" t="n">
-        <v>13.08635025499997</v>
+        <v>4.10075723629939</v>
       </c>
       <c r="J5" t="n">
-        <v>9.89180023566955</v>
+        <v>3.503160131655608</v>
       </c>
       <c r="K5" t="n">
-        <v>7.085123302925871</v>
+        <v>2.989171439185711</v>
       </c>
       <c r="L5" t="n">
-        <v>37.44826103556259</v>
+        <v>8.325178311757268</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84.46166699962055</v>
+        <v>16.58839567329868</v>
       </c>
       <c r="C6" t="n">
-        <v>9.072031597659455</v>
+        <v>3.394235947584551</v>
       </c>
       <c r="D6" t="n">
-        <v>8.901436305628943</v>
+        <v>3.314440973414808</v>
       </c>
       <c r="E6" t="n">
-        <v>9.04922631609586</v>
+        <v>3.390222219120718</v>
       </c>
       <c r="F6" t="n">
-        <v>9.071180267597624</v>
+        <v>3.394086114564105</v>
       </c>
       <c r="G6" t="n">
-        <v>8.976415950167665</v>
+        <v>16.67136524643676</v>
       </c>
       <c r="H6" t="n">
-        <v>8.972309202546921</v>
+        <v>16.67692163721</v>
       </c>
       <c r="I6" t="n">
-        <v>84.55265593733768</v>
+        <v>16.67882696823526</v>
       </c>
       <c r="J6" t="n">
-        <v>84.5012870485839</v>
+        <v>16.63442973957541</v>
       </c>
       <c r="K6" t="n">
-        <v>8.806613810533264</v>
+        <v>3.292153766882871</v>
       </c>
       <c r="L6" t="n">
-        <v>8.892809677188366</v>
+        <v>3.299418899915987</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.602704264035163</v>
+        <v>2.181218309902455</v>
       </c>
       <c r="C7" t="n">
-        <v>2.693691734699922</v>
+        <v>2.271648137786531</v>
       </c>
       <c r="D7" t="n">
-        <v>2.632587193593429</v>
+        <v>2.211123535675005</v>
       </c>
       <c r="E7" t="n">
-        <v>2.693615826206611</v>
+        <v>2.271634778961397</v>
       </c>
       <c r="F7" t="n">
-        <v>2.693615826206611</v>
+        <v>2.271634778961397</v>
       </c>
       <c r="G7" t="n">
-        <v>2.685815698946398</v>
+        <v>2.264187883040547</v>
       </c>
       <c r="H7" t="n">
-        <v>2.693131540346547</v>
+        <v>2.271645586213837</v>
       </c>
       <c r="I7" t="n">
-        <v>2.693693201752424</v>
+        <v>2.271649604839032</v>
       </c>
       <c r="J7" t="n">
-        <v>2.650108314583373</v>
+        <v>2.228622360450661</v>
       </c>
       <c r="K7" t="n">
-        <v>2.625820019728387</v>
+        <v>2.204334065595676</v>
       </c>
       <c r="L7" t="n">
-        <v>2.61622616122495</v>
+        <v>2.194740207092241</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.662844059648631</v>
+        <v>2.191802913873071</v>
       </c>
       <c r="C8" t="n">
-        <v>3.062172839794096</v>
+        <v>2.336500811931695</v>
       </c>
       <c r="D8" t="n">
-        <v>3.065005377040326</v>
+        <v>2.287229135549273</v>
       </c>
       <c r="E8" t="n">
-        <v>2.97784076954103</v>
+        <v>2.321658368717197</v>
       </c>
       <c r="F8" t="n">
-        <v>2.763575635577209</v>
+        <v>2.283947705343903</v>
       </c>
       <c r="G8" t="n">
-        <v>3.054274806118654</v>
+        <v>2.329036685551475</v>
       </c>
       <c r="H8" t="n">
-        <v>3.061590647518708</v>
+        <v>2.336494388724748</v>
       </c>
       <c r="I8" t="n">
-        <v>3.062152308924681</v>
+        <v>2.33649840734996</v>
       </c>
       <c r="J8" t="n">
-        <v>3.018628015294018</v>
+        <v>2.293481827424288</v>
       </c>
       <c r="K8" t="n">
-        <v>2.680232625842656</v>
+        <v>2.213910684219896</v>
       </c>
       <c r="L8" t="n">
-        <v>3.306750570522292</v>
+        <v>2.316272502470039</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.102656653476894</v>
+        <v>2.621209928060057</v>
       </c>
       <c r="C9" t="n">
-        <v>6.002583831495556</v>
+        <v>2.854013143666957</v>
       </c>
       <c r="D9" t="n">
-        <v>5.941506277746891</v>
+        <v>2.793493291330382</v>
       </c>
       <c r="E9" t="n">
-        <v>6.936082345824096</v>
+        <v>3.018308882368146</v>
       </c>
       <c r="F9" t="n">
-        <v>6.002583278680095</v>
+        <v>2.854013047441051</v>
       </c>
       <c r="G9" t="n">
-        <v>5.994707795742049</v>
+        <v>2.846552888920975</v>
       </c>
       <c r="H9" t="n">
-        <v>6.002023637142192</v>
+        <v>2.854010592094265</v>
       </c>
       <c r="I9" t="n">
-        <v>6.002585298548064</v>
+        <v>2.854014610719458</v>
       </c>
       <c r="J9" t="n">
-        <v>5.959000411379004</v>
+        <v>2.810987366331088</v>
       </c>
       <c r="K9" t="n">
-        <v>5.466009243204644</v>
+        <v>2.704207366218886</v>
       </c>
       <c r="L9" t="n">
-        <v>5.925118258020588</v>
+        <v>2.777105212972668</v>
       </c>
     </row>
   </sheetData>
@@ -5273,10 +5273,10 @@
         <v>6.639803167246678</v>
       </c>
       <c r="D2" t="n">
-        <v>6.524879013269049</v>
+        <v>6.524879013269048</v>
       </c>
       <c r="E2" t="n">
-        <v>6.644774248001858</v>
+        <v>6.644774248001859</v>
       </c>
       <c r="F2" t="n">
         <v>6.628947741739689</v>
@@ -5310,7 +5310,7 @@
         <v>6.663641901193023</v>
       </c>
       <c r="C3" t="n">
-        <v>6.849308359341036</v>
+        <v>6.849308359341035</v>
       </c>
       <c r="D3" t="n">
         <v>6.720471719265166</v>
@@ -5331,7 +5331,7 @@
         <v>6.827485083865504</v>
       </c>
       <c r="J3" t="n">
-        <v>6.791145526364306</v>
+        <v>6.791145526364305</v>
       </c>
       <c r="K3" t="n">
         <v>6.727071929551938</v>
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.213941122677338</v>
+        <v>2.10931096694163</v>
       </c>
       <c r="C4" t="n">
-        <v>2.301566368289053</v>
+        <v>2.19450497734559</v>
       </c>
       <c r="D4" t="n">
-        <v>2.243312283149219</v>
+        <v>2.138682127413511</v>
       </c>
       <c r="E4" t="n">
-        <v>2.30214632467041</v>
+        <v>2.194607048544149</v>
       </c>
       <c r="F4" t="n">
-        <v>2.30214632467041</v>
+        <v>2.194607048544149</v>
       </c>
       <c r="G4" t="n">
-        <v>2.285847135759938</v>
+        <v>2.181057065093114</v>
       </c>
       <c r="H4" t="n">
-        <v>2.282309320822531</v>
+        <v>2.177679165086824</v>
       </c>
       <c r="I4" t="n">
-        <v>2.299433613714233</v>
+        <v>2.194131889256622</v>
       </c>
       <c r="J4" t="n">
-        <v>2.257217335153266</v>
+        <v>2.152587179417556</v>
       </c>
       <c r="K4" t="n">
-        <v>2.234702030011973</v>
+        <v>2.130071874276264</v>
       </c>
       <c r="L4" t="n">
-        <v>2.238466055939221</v>
+        <v>2.133835900203513</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.334093230816273</v>
+        <v>2.482457735952149</v>
       </c>
       <c r="C5" t="n">
-        <v>11.44202570618571</v>
+        <v>3.803225812098383</v>
       </c>
       <c r="D5" t="n">
-        <v>6.943299638288296</v>
+        <v>2.965879897435718</v>
       </c>
       <c r="E5" t="n">
-        <v>11.44202570482162</v>
+        <v>3.803225810734296</v>
       </c>
       <c r="F5" t="n">
-        <v>11.44202570482162</v>
+        <v>3.803225810734296</v>
       </c>
       <c r="G5" t="n">
-        <v>10.92645621008131</v>
+        <v>3.701804253933356</v>
       </c>
       <c r="H5" t="n">
-        <v>11.63545180135926</v>
+        <v>3.823832232741435</v>
       </c>
       <c r="I5" t="n">
-        <v>11.44202846918832</v>
+        <v>3.803228575101004</v>
       </c>
       <c r="J5" t="n">
-        <v>8.64561635432478</v>
+        <v>3.276945400699288</v>
       </c>
       <c r="K5" t="n">
-        <v>6.028348437294016</v>
+        <v>2.797753638339997</v>
       </c>
       <c r="L5" t="n">
-        <v>7.349507022497163</v>
+        <v>5.708623184360368</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.4185558630345</v>
+        <v>15.59324260596944</v>
       </c>
       <c r="C6" t="n">
-        <v>8.590194343556213</v>
+        <v>3.301303494995302</v>
       </c>
       <c r="D6" t="n">
-        <v>8.432739999408305</v>
+        <v>3.228021399572415</v>
       </c>
       <c r="E6" t="n">
-        <v>8.569098784716452</v>
+        <v>3.297590675535617</v>
       </c>
       <c r="F6" t="n">
-        <v>8.588710703899514</v>
+        <v>3.301042373293136</v>
       </c>
       <c r="G6" t="n">
-        <v>8.490461876117127</v>
+        <v>15.66498870412094</v>
       </c>
       <c r="H6" t="n">
-        <v>78.88557140935124</v>
+        <v>15.65985321961333</v>
       </c>
       <c r="I6" t="n">
-        <v>8.504048354071417</v>
+        <v>15.67806352828443</v>
       </c>
       <c r="J6" t="n">
-        <v>8.467417406991325</v>
+        <v>15.63531749906761</v>
       </c>
       <c r="K6" t="n">
-        <v>8.34176113857075</v>
+        <v>3.204914271558462</v>
       </c>
       <c r="L6" t="n">
-        <v>8.43411406186455</v>
+        <v>3.224269943337743</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.561938287102576</v>
+        <v>2.170558467548596</v>
       </c>
       <c r="C7" t="n">
-        <v>2.647428015136847</v>
+        <v>2.255376626860963</v>
       </c>
       <c r="D7" t="n">
-        <v>2.591284116039515</v>
+        <v>2.199925169670351</v>
       </c>
       <c r="E7" t="n">
-        <v>2.647485459229449</v>
+        <v>2.2553867358972</v>
       </c>
       <c r="F7" t="n">
-        <v>2.647485459229449</v>
+        <v>2.2553867358972</v>
       </c>
       <c r="G7" t="n">
-        <v>2.63384430018518</v>
+        <v>2.242304565700081</v>
       </c>
       <c r="H7" t="n">
-        <v>2.630306485247771</v>
+        <v>2.23892666569379</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64743077813947</v>
+        <v>2.255379389863588</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6052144995785</v>
+        <v>2.213834680024521</v>
       </c>
       <c r="K7" t="n">
-        <v>2.582699194437211</v>
+        <v>2.191319374883229</v>
       </c>
       <c r="L7" t="n">
-        <v>2.586463220364458</v>
+        <v>2.195083400810478</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.614193043290699</v>
+        <v>2.179755304587871</v>
       </c>
       <c r="C8" t="n">
-        <v>2.982077147844122</v>
+        <v>2.314274873898493</v>
       </c>
       <c r="D8" t="n">
-        <v>2.984343130007305</v>
+        <v>2.269103555753832</v>
       </c>
       <c r="E8" t="n">
-        <v>2.904861879677672</v>
+        <v>2.300684985650633</v>
       </c>
       <c r="F8" t="n">
-        <v>2.708679106606994</v>
+        <v>2.266156817777288</v>
       </c>
       <c r="G8" t="n">
-        <v>2.968351168475282</v>
+        <v>2.301177774200129</v>
       </c>
       <c r="H8" t="n">
-        <v>2.964813353537774</v>
+        <v>2.29779987419382</v>
       </c>
       <c r="I8" t="n">
-        <v>2.981937646429575</v>
+        <v>2.314252598363636</v>
       </c>
       <c r="J8" t="n">
-        <v>2.939776838454919</v>
+        <v>2.272717651347706</v>
       </c>
       <c r="K8" t="n">
-        <v>2.629710972738929</v>
+        <v>2.199593447819499</v>
       </c>
       <c r="L8" t="n">
-        <v>3.215806021242934</v>
+        <v>2.305847733164902</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.586527405547692</v>
+        <v>2.526886150464137</v>
       </c>
       <c r="C9" t="n">
-        <v>5.340327500299351</v>
+        <v>2.729326933681416</v>
       </c>
       <c r="D9" t="n">
-        <v>5.284208882729417</v>
+        <v>2.673879926039599</v>
       </c>
       <c r="E9" t="n">
-        <v>6.111542863873022</v>
+        <v>2.865060835810888</v>
       </c>
       <c r="F9" t="n">
-        <v>5.340327032871074</v>
+        <v>2.729326850290031</v>
       </c>
       <c r="G9" t="n">
-        <v>5.326743785347681</v>
+        <v>2.716254872520532</v>
       </c>
       <c r="H9" t="n">
-        <v>5.323205970410276</v>
+        <v>2.712876972514243</v>
       </c>
       <c r="I9" t="n">
-        <v>5.340330263301977</v>
+        <v>2.729329696684039</v>
       </c>
       <c r="J9" t="n">
-        <v>5.298113984741016</v>
+        <v>2.687784986844973</v>
       </c>
       <c r="K9" t="n">
-        <v>4.434076647885055</v>
+        <v>2.51716180492444</v>
       </c>
       <c r="L9" t="n">
-        <v>5.279362705526967</v>
+        <v>2.669033707630931</v>
       </c>
     </row>
   </sheetData>
@@ -5663,34 +5663,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.471291819035816</v>
+        <v>6.471291819035813</v>
       </c>
       <c r="C2" t="n">
         <v>6.610488274637032</v>
       </c>
       <c r="D2" t="n">
-        <v>6.514467353406504</v>
+        <v>6.514467353406506</v>
       </c>
       <c r="E2" t="n">
-        <v>6.615476274853713</v>
+        <v>6.615476274853716</v>
       </c>
       <c r="F2" t="n">
-        <v>6.599617558396597</v>
+        <v>6.599617558396598</v>
       </c>
       <c r="G2" t="n">
-        <v>6.572948345526797</v>
+        <v>6.572948345526796</v>
       </c>
       <c r="H2" t="n">
         <v>6.615107028313508</v>
       </c>
       <c r="I2" t="n">
-        <v>6.58903444049313</v>
+        <v>6.589034440493132</v>
       </c>
       <c r="J2" t="n">
-        <v>6.570469879129168</v>
+        <v>6.570469879129167</v>
       </c>
       <c r="K2" t="n">
-        <v>6.514451952902945</v>
+        <v>6.514451952902944</v>
       </c>
       <c r="L2" t="n">
         <v>6.513523122853385</v>
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.658871225407512</v>
+        <v>6.658871225407509</v>
       </c>
       <c r="C3" t="n">
-        <v>6.815687062956972</v>
+        <v>6.815687062956973</v>
       </c>
       <c r="D3" t="n">
         <v>6.708532033718806</v>
@@ -5715,25 +5715,25 @@
         <v>6.820740382990325</v>
       </c>
       <c r="F3" t="n">
-        <v>6.804881666533209</v>
+        <v>6.80488166653321</v>
       </c>
       <c r="G3" t="n">
-        <v>6.775797288958159</v>
+        <v>6.775797288958161</v>
       </c>
       <c r="H3" t="n">
-        <v>6.824418034801827</v>
+        <v>6.824418034801826</v>
       </c>
       <c r="I3" t="n">
-        <v>6.794298584834729</v>
+        <v>6.794298584834731</v>
       </c>
       <c r="J3" t="n">
-        <v>6.766400324123148</v>
+        <v>6.766400324123146</v>
       </c>
       <c r="K3" t="n">
-        <v>6.705086066908152</v>
+        <v>6.70508606690815</v>
       </c>
       <c r="L3" t="n">
-        <v>6.707456341181718</v>
+        <v>6.707456341181716</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.2049553267517</v>
+        <v>2.105737191807653</v>
       </c>
       <c r="C4" t="n">
-        <v>2.277897551411775</v>
+        <v>2.176245729425726</v>
       </c>
       <c r="D4" t="n">
-        <v>2.230621352432494</v>
+        <v>2.131403217488448</v>
       </c>
       <c r="E4" t="n">
-        <v>2.278426626850905</v>
+        <v>2.1763388443394</v>
       </c>
       <c r="F4" t="n">
-        <v>2.278426626850906</v>
+        <v>2.1763388443394</v>
       </c>
       <c r="G4" t="n">
-        <v>2.265569949565579</v>
+        <v>2.166200095318607</v>
       </c>
       <c r="H4" t="n">
-        <v>2.290441972973471</v>
+        <v>2.191223838029424</v>
       </c>
       <c r="I4" t="n">
-        <v>2.275696249583965</v>
+        <v>2.1758599476511</v>
       </c>
       <c r="J4" t="n">
-        <v>2.238005275559387</v>
+        <v>2.138787140615339</v>
       </c>
       <c r="K4" t="n">
-        <v>2.217044593186244</v>
+        <v>2.117826458242197</v>
       </c>
       <c r="L4" t="n">
-        <v>2.230107771577826</v>
+        <v>2.13088963663378</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.158826245675116</v>
+        <v>2.449618471674813</v>
       </c>
       <c r="C5" t="n">
-        <v>9.997195206986332</v>
+        <v>3.534842109445153</v>
       </c>
       <c r="D5" t="n">
-        <v>6.364260718124049</v>
+        <v>2.858923741908018</v>
       </c>
       <c r="E5" t="n">
-        <v>9.997195204118473</v>
+        <v>3.534842106577301</v>
       </c>
       <c r="F5" t="n">
-        <v>9.997195204118473</v>
+        <v>3.534842106577301</v>
       </c>
       <c r="G5" t="n">
-        <v>9.585872957094383</v>
+        <v>3.454573417662467</v>
       </c>
       <c r="H5" t="n">
-        <v>12.79077260403665</v>
+        <v>4.039282019082649</v>
       </c>
       <c r="I5" t="n">
-        <v>9.997197206191387</v>
+        <v>3.5348441086502</v>
       </c>
       <c r="J5" t="n">
-        <v>7.521918807467471</v>
+        <v>3.068755917192026</v>
       </c>
       <c r="K5" t="n">
-        <v>5.036836678928987</v>
+        <v>2.614109862643755</v>
       </c>
       <c r="L5" t="n">
-        <v>7.189473572882996</v>
+        <v>3.003738012933872</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.402849730410228</v>
+        <v>3.196566600940781</v>
       </c>
       <c r="C6" t="n">
-        <v>8.559711034524719</v>
+        <v>3.281844896462792</v>
       </c>
       <c r="D6" t="n">
-        <v>78.82434713273399</v>
+        <v>15.61189888177602</v>
       </c>
       <c r="E6" t="n">
-        <v>8.538889981124203</v>
+        <v>3.278180388721061</v>
       </c>
       <c r="F6" t="n">
-        <v>8.55867574923016</v>
+        <v>3.281662683888834</v>
       </c>
       <c r="G6" t="n">
-        <v>8.463464353224088</v>
+        <v>3.257029504451734</v>
       </c>
       <c r="H6" t="n">
-        <v>78.88247261939786</v>
+        <v>15.67142115875627</v>
       </c>
       <c r="I6" t="n">
-        <v>78.87731657514051</v>
+        <v>15.65774505189605</v>
       </c>
       <c r="J6" t="n">
-        <v>78.83232206141045</v>
+        <v>3.230643890198328</v>
       </c>
       <c r="K6" t="n">
-        <v>8.318414532798727</v>
+        <v>3.191667561795272</v>
       </c>
       <c r="L6" t="n">
-        <v>8.419949456948254</v>
+        <v>3.220301767355884</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.549325516025925</v>
+        <v>2.166346344791499</v>
       </c>
       <c r="C7" t="n">
-        <v>2.620064439653136</v>
+        <v>2.236467101429891</v>
       </c>
       <c r="D7" t="n">
-        <v>2.574966319019652</v>
+        <v>2.192007931279393</v>
       </c>
       <c r="E7" t="n">
-        <v>2.620210135445639</v>
+        <v>2.236492741526122</v>
       </c>
       <c r="F7" t="n">
-        <v>2.620210135445639</v>
+        <v>2.236492741526122</v>
       </c>
       <c r="G7" t="n">
-        <v>2.609940138839795</v>
+        <v>2.226809248302452</v>
       </c>
       <c r="H7" t="n">
-        <v>2.634812162247689</v>
+        <v>2.251832991013269</v>
       </c>
       <c r="I7" t="n">
-        <v>2.620066438858184</v>
+        <v>2.236469100634946</v>
       </c>
       <c r="J7" t="n">
-        <v>2.582375464833605</v>
+        <v>2.199396293599185</v>
       </c>
       <c r="K7" t="n">
-        <v>2.561414782460467</v>
+        <v>2.178435611226042</v>
       </c>
       <c r="L7" t="n">
-        <v>2.574477960852045</v>
+        <v>2.191498789617625</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.597649945787688</v>
+        <v>2.174851444383485</v>
       </c>
       <c r="C8" t="n">
-        <v>2.945677174099629</v>
+        <v>2.293774942381943</v>
       </c>
       <c r="D8" t="n">
-        <v>2.957829504696956</v>
+        <v>2.259391851593472</v>
       </c>
       <c r="E8" t="n">
-        <v>2.86987229898945</v>
+        <v>2.28043328207174</v>
       </c>
       <c r="F8" t="n">
-        <v>2.677273291263875</v>
+        <v>2.246535856895714</v>
       </c>
       <c r="G8" t="n">
-        <v>2.935327332783964</v>
+        <v>2.28407739412631</v>
       </c>
       <c r="H8" t="n">
-        <v>2.960199356191811</v>
+        <v>2.309101136837121</v>
       </c>
       <c r="I8" t="n">
-        <v>2.945453632802342</v>
+        <v>2.293737246458805</v>
       </c>
       <c r="J8" t="n">
-        <v>2.907817109508128</v>
+        <v>2.256674022751535</v>
       </c>
       <c r="K8" t="n">
-        <v>2.60459262913769</v>
+        <v>2.186034912200056</v>
       </c>
       <c r="L8" t="n">
-        <v>3.189280379555965</v>
+        <v>2.299704014723191</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.332247274863718</v>
+        <v>2.480140572646625</v>
       </c>
       <c r="C9" t="n">
-        <v>5.003290550443446</v>
+        <v>2.655914894656161</v>
       </c>
       <c r="D9" t="n">
-        <v>4.958217551661528</v>
+        <v>2.611460145951519</v>
       </c>
       <c r="E9" t="n">
-        <v>5.696028329226448</v>
+        <v>2.777836740698219</v>
       </c>
       <c r="F9" t="n">
-        <v>5.003290050902351</v>
+        <v>2.655914804373821</v>
       </c>
       <c r="G9" t="n">
-        <v>4.993166249630102</v>
+        <v>2.646257041528725</v>
       </c>
       <c r="H9" t="n">
-        <v>5.018038273038002</v>
+        <v>2.67128078423954</v>
       </c>
       <c r="I9" t="n">
-        <v>5.003292549648499</v>
+        <v>2.655916893861219</v>
       </c>
       <c r="J9" t="n">
-        <v>4.965601575623914</v>
+        <v>2.618844086825458</v>
       </c>
       <c r="K9" t="n">
-        <v>4.596822151741577</v>
+        <v>2.536667306278404</v>
       </c>
       <c r="L9" t="n">
-        <v>4.957704071642347</v>
+        <v>2.610946582843898</v>
       </c>
     </row>
   </sheetData>
@@ -6074,16 +6074,16 @@
         <v>6.655981389042575</v>
       </c>
       <c r="G2" t="n">
-        <v>6.686885702940595</v>
+        <v>6.686885702940593</v>
       </c>
       <c r="H2" t="n">
-        <v>6.844394652143494</v>
+        <v>6.844394652143495</v>
       </c>
       <c r="I2" t="n">
-        <v>6.645791477312682</v>
+        <v>6.645791477312681</v>
       </c>
       <c r="J2" t="n">
-        <v>6.654262809307618</v>
+        <v>6.654262809307617</v>
       </c>
       <c r="K2" t="n">
         <v>6.541611729313106</v>
@@ -6099,34 +6099,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.639904597470248</v>
+        <v>6.639904597470247</v>
       </c>
       <c r="C3" t="n">
-        <v>6.880769002632034</v>
+        <v>6.880769002632033</v>
       </c>
       <c r="D3" t="n">
-        <v>6.693217304647329</v>
+        <v>6.693217304647328</v>
       </c>
       <c r="E3" t="n">
         <v>6.88597056470267</v>
       </c>
       <c r="F3" t="n">
-        <v>6.869670691067559</v>
+        <v>6.869670691067558</v>
       </c>
       <c r="G3" t="n">
         <v>6.906750065229406</v>
       </c>
       <c r="H3" t="n">
-        <v>7.088056162666789</v>
+        <v>7.088056162666788</v>
       </c>
       <c r="I3" t="n">
-        <v>6.85944509725084</v>
+        <v>6.859445097250839</v>
       </c>
       <c r="J3" t="n">
-        <v>6.86262128771532</v>
+        <v>6.862621287715318</v>
       </c>
       <c r="K3" t="n">
-        <v>6.73631566962623</v>
+        <v>6.736315669626229</v>
       </c>
       <c r="L3" t="n">
         <v>6.909864912851917</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.216413067041021</v>
+        <v>2.099245188535837</v>
       </c>
       <c r="C4" t="n">
-        <v>2.329339942836956</v>
+        <v>2.212623305309802</v>
       </c>
       <c r="D4" t="n">
-        <v>2.243966491120272</v>
+        <v>2.126798612615087</v>
       </c>
       <c r="E4" t="n">
-        <v>2.330245233885888</v>
+        <v>2.21278263932561</v>
       </c>
       <c r="F4" t="n">
-        <v>2.330245233885888</v>
+        <v>2.21278263932561</v>
       </c>
       <c r="G4" t="n">
-        <v>2.354393622644256</v>
+        <v>2.237169938474425</v>
       </c>
       <c r="H4" t="n">
-        <v>2.447926646593542</v>
+        <v>2.330758768088356</v>
       </c>
       <c r="I4" t="n">
-        <v>2.329895153058426</v>
+        <v>2.212716202331185</v>
       </c>
       <c r="J4" t="n">
-        <v>2.308790378873604</v>
+        <v>2.191622500368419</v>
       </c>
       <c r="K4" t="n">
-        <v>2.25475137780681</v>
+        <v>2.137583499301625</v>
       </c>
       <c r="L4" t="n">
-        <v>2.355969322591068</v>
+        <v>2.238801444085882</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.048029417514944</v>
+        <v>2.245609665426155</v>
       </c>
       <c r="C5" t="n">
-        <v>13.44897637713192</v>
+        <v>4.169679307141209</v>
       </c>
       <c r="D5" t="n">
-        <v>5.528049400481042</v>
+        <v>2.704797201530637</v>
       </c>
       <c r="E5" t="n">
-        <v>13.44897638052035</v>
+        <v>4.169679310529625</v>
       </c>
       <c r="F5" t="n">
-        <v>13.44897638052035</v>
+        <v>4.169679310529625</v>
       </c>
       <c r="G5" t="n">
-        <v>15.89500997834461</v>
+        <v>4.620318404164347</v>
       </c>
       <c r="H5" t="n">
-        <v>25.90098321934033</v>
+        <v>6.458496702525213</v>
       </c>
       <c r="I5" t="n">
-        <v>13.44897052764516</v>
+        <v>4.169673457654483</v>
       </c>
       <c r="J5" t="n">
-        <v>12.60188115426818</v>
+        <v>4.003206467021609</v>
       </c>
       <c r="K5" t="n">
-        <v>6.525864111714768</v>
+        <v>2.889299336396173</v>
       </c>
       <c r="L5" t="n">
-        <v>23.12351248476597</v>
+        <v>5.064536434850776</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.894396182730283</v>
+        <v>3.274570210528528</v>
       </c>
       <c r="C6" t="n">
-        <v>9.090007319458183</v>
+        <v>3.402500757147666</v>
       </c>
       <c r="D6" t="n">
-        <v>8.890148725611009</v>
+        <v>16.60420235374254</v>
       </c>
       <c r="E6" t="n">
-        <v>9.066840264144494</v>
+        <v>3.398423358226607</v>
       </c>
       <c r="F6" t="n">
-        <v>9.09310576810357</v>
+        <v>3.403046086898349</v>
       </c>
       <c r="G6" t="n">
-        <v>84.62303179409487</v>
+        <v>3.412494960467111</v>
       </c>
       <c r="H6" t="n">
-        <v>84.7072826858499</v>
+        <v>16.80840535254884</v>
       </c>
       <c r="I6" t="n">
-        <v>84.59853332450906</v>
+        <v>3.388041224323869</v>
       </c>
       <c r="J6" t="n">
-        <v>84.56918688576984</v>
+        <v>16.66945220713252</v>
       </c>
       <c r="K6" t="n">
-        <v>8.816265602814216</v>
+        <v>3.292409996645382</v>
       </c>
       <c r="L6" t="n">
-        <v>9.022182083378002</v>
+        <v>3.412054883626985</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.605243341179362</v>
+        <v>2.167679316413367</v>
       </c>
       <c r="C7" t="n">
-        <v>2.718731276683491</v>
+        <v>2.281156179695441</v>
       </c>
       <c r="D7" t="n">
-        <v>2.632769554332978</v>
+        <v>2.195227951369732</v>
       </c>
       <c r="E7" t="n">
-        <v>2.718663619461076</v>
+        <v>2.281144274816418</v>
       </c>
       <c r="F7" t="n">
-        <v>2.718663619461076</v>
+        <v>2.281144274816418</v>
       </c>
       <c r="G7" t="n">
-        <v>2.743223896782597</v>
+        <v>2.305604066351955</v>
       </c>
       <c r="H7" t="n">
-        <v>2.836756920731882</v>
+        <v>2.399192895965888</v>
       </c>
       <c r="I7" t="n">
-        <v>2.718725427196765</v>
+        <v>2.281150330208715</v>
       </c>
       <c r="J7" t="n">
-        <v>2.697620653011944</v>
+        <v>2.26005662824595</v>
       </c>
       <c r="K7" t="n">
-        <v>2.64358165194515</v>
+        <v>2.206017627179156</v>
       </c>
       <c r="L7" t="n">
-        <v>2.744799596729408</v>
+        <v>2.307235571963414</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.678188601676408</v>
+        <v>2.180517682191281</v>
       </c>
       <c r="C8" t="n">
-        <v>3.117877694964264</v>
+        <v>2.351405948931978</v>
       </c>
       <c r="D8" t="n">
-        <v>3.099542587393142</v>
+        <v>2.277380004743172</v>
       </c>
       <c r="E8" t="n">
-        <v>3.028663033026088</v>
+        <v>2.335704171308221</v>
       </c>
       <c r="F8" t="n">
-        <v>2.801991419291218</v>
+        <v>2.295809967507056</v>
       </c>
       <c r="G8" t="n">
-        <v>3.142336744853618</v>
+        <v>2.375847927231832</v>
       </c>
       <c r="H8" t="n">
-        <v>3.235869768802826</v>
+        <v>2.46943675684575</v>
       </c>
       <c r="I8" t="n">
-        <v>3.117838275267788</v>
+        <v>2.351394191088591</v>
       </c>
       <c r="J8" t="n">
-        <v>3.096797602306009</v>
+        <v>2.33031177094102</v>
       </c>
       <c r="K8" t="n">
-        <v>2.710468182054038</v>
+        <v>2.217789656414531</v>
       </c>
       <c r="L8" t="n">
-        <v>3.484621763659474</v>
+        <v>2.437444272637556</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.174646219839409</v>
+        <v>2.61989422060716</v>
       </c>
       <c r="C9" t="n">
-        <v>6.120507952032159</v>
+        <v>2.879868871312617</v>
       </c>
       <c r="D9" t="n">
-        <v>6.034573274794105</v>
+        <v>2.793945402926678</v>
       </c>
       <c r="E9" t="n">
-        <v>7.081048569798846</v>
+        <v>3.048924021915572</v>
       </c>
       <c r="F9" t="n">
-        <v>6.12050719707331</v>
+        <v>2.879868741231918</v>
       </c>
       <c r="G9" t="n">
-        <v>6.14500057213126</v>
+        <v>2.904316757969131</v>
       </c>
       <c r="H9" t="n">
-        <v>6.238533596080544</v>
+        <v>2.997905587583066</v>
       </c>
       <c r="I9" t="n">
-        <v>6.120502102545424</v>
+        <v>2.879863021825893</v>
       </c>
       <c r="J9" t="n">
-        <v>6.099397328360614</v>
+        <v>2.858769319863126</v>
       </c>
       <c r="K9" t="n">
-        <v>4.997251182041053</v>
+        <v>2.719848913147752</v>
       </c>
       <c r="L9" t="n">
-        <v>6.146576272078082</v>
+        <v>2.905948263580592</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.450982750103113</v>
+        <v>6.450982750103114</v>
       </c>
       <c r="C2" t="n">
         <v>6.627119482509553</v>
       </c>
       <c r="D2" t="n">
-        <v>6.482496788198695</v>
+        <v>6.482496788198698</v>
       </c>
       <c r="E2" t="n">
-        <v>6.632118212777866</v>
+        <v>6.632118212777864</v>
       </c>
       <c r="F2" t="n">
         <v>6.616232241713529</v>
       </c>
       <c r="G2" t="n">
-        <v>6.613442552640043</v>
+        <v>6.613442552640044</v>
       </c>
       <c r="H2" t="n">
         <v>6.683927171900665</v>
       </c>
       <c r="I2" t="n">
-        <v>6.605943779287781</v>
+        <v>6.605943779287783</v>
       </c>
       <c r="J2" t="n">
-        <v>6.595731650845633</v>
+        <v>6.595731650845634</v>
       </c>
       <c r="K2" t="n">
-        <v>6.502091502109097</v>
+        <v>6.502091502109095</v>
       </c>
       <c r="L2" t="n">
-        <v>6.605479746488777</v>
+        <v>6.605479746488778</v>
       </c>
     </row>
     <row r="3">
@@ -6495,22 +6495,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.635416363572162</v>
+        <v>6.635416363572164</v>
       </c>
       <c r="C3" t="n">
         <v>6.834765813099766</v>
       </c>
       <c r="D3" t="n">
-        <v>6.671664035495407</v>
+        <v>6.671664035495408</v>
       </c>
       <c r="E3" t="n">
-        <v>6.839826460244509</v>
+        <v>6.83982646024451</v>
       </c>
       <c r="F3" t="n">
-        <v>6.823940489180173</v>
+        <v>6.823940489180174</v>
       </c>
       <c r="G3" t="n">
-        <v>6.822278789936344</v>
+        <v>6.822278789936346</v>
       </c>
       <c r="H3" t="n">
         <v>6.903484925976506</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.197466949284614</v>
+        <v>2.094289576308732</v>
       </c>
       <c r="C4" t="n">
-        <v>2.290964568854524</v>
+        <v>2.186644911311779</v>
       </c>
       <c r="D4" t="n">
-        <v>2.216200709569368</v>
+        <v>2.113023336593486</v>
       </c>
       <c r="E4" t="n">
-        <v>2.291574712655984</v>
+        <v>2.186752297106368</v>
       </c>
       <c r="F4" t="n">
-        <v>2.291574712655984</v>
+        <v>2.186752297106368</v>
       </c>
       <c r="G4" t="n">
-        <v>2.294182595158959</v>
+        <v>2.190889716110876</v>
       </c>
       <c r="H4" t="n">
-        <v>2.33593070895993</v>
+        <v>2.232753335984048</v>
       </c>
       <c r="I4" t="n">
-        <v>2.290049167742368</v>
+        <v>2.186482788995971</v>
       </c>
       <c r="J4" t="n">
-        <v>2.257773775460775</v>
+        <v>2.154596402484892</v>
       </c>
       <c r="K4" t="n">
-        <v>2.214994441848922</v>
+        <v>2.11181706887304</v>
       </c>
       <c r="L4" t="n">
-        <v>2.28934631531217</v>
+        <v>2.186168942336288</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.006513785478312</v>
+        <v>2.236681818707256</v>
       </c>
       <c r="C5" t="n">
-        <v>10.67620728151948</v>
+        <v>3.662447620744028</v>
       </c>
       <c r="D5" t="n">
-        <v>4.55236561455309</v>
+        <v>2.52418835764268</v>
       </c>
       <c r="E5" t="n">
-        <v>10.67620728210946</v>
+        <v>3.662447621333974</v>
       </c>
       <c r="F5" t="n">
-        <v>10.67620728210946</v>
+        <v>3.662447621333974</v>
       </c>
       <c r="G5" t="n">
-        <v>11.157705981939</v>
+        <v>3.750869823731246</v>
       </c>
       <c r="H5" t="n">
-        <v>14.91318816399649</v>
+        <v>4.446350636075872</v>
       </c>
       <c r="I5" t="n">
-        <v>10.67620605370283</v>
+        <v>3.66244639292735</v>
       </c>
       <c r="J5" t="n">
-        <v>8.502368676536433</v>
+        <v>3.253645099118895</v>
       </c>
       <c r="K5" t="n">
-        <v>4.475418995858778</v>
+        <v>2.509651788223065</v>
       </c>
       <c r="L5" t="n">
-        <v>12.43678694617296</v>
+        <v>3.972118483690422</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.401467967903612</v>
+        <v>15.57908096884235</v>
       </c>
       <c r="C6" t="n">
-        <v>8.578742820514298</v>
+        <v>3.293293877607396</v>
       </c>
       <c r="D6" t="n">
-        <v>8.400561757015121</v>
+        <v>3.201471032598</v>
       </c>
       <c r="E6" t="n">
-        <v>8.557679214855769</v>
+        <v>3.28958668351771</v>
       </c>
       <c r="F6" t="n">
-        <v>8.579199601054098</v>
+        <v>3.293374271468094</v>
       </c>
       <c r="G6" t="n">
-        <v>8.498183613777961</v>
+        <v>3.282793889471221</v>
       </c>
       <c r="H6" t="n">
-        <v>78.94542974499029</v>
+        <v>3.323801734580301</v>
       </c>
       <c r="I6" t="n">
-        <v>8.494050186361381</v>
+        <v>3.27838696235632</v>
       </c>
       <c r="J6" t="n">
-        <v>8.46842812056993</v>
+        <v>15.63817297607299</v>
       </c>
       <c r="K6" t="n">
-        <v>8.318342210906016</v>
+        <v>3.186006270406485</v>
       </c>
       <c r="L6" t="n">
-        <v>8.486984096858453</v>
+        <v>3.2769531859779</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.545936914295651</v>
+        <v>2.155620289818347</v>
       </c>
       <c r="C7" t="n">
-        <v>2.63852036057008</v>
+        <v>2.247814730322262</v>
       </c>
       <c r="D7" t="n">
-        <v>2.56464543771138</v>
+        <v>2.174349608414177</v>
       </c>
       <c r="E7" t="n">
-        <v>2.638512900976016</v>
+        <v>2.247813417919827</v>
       </c>
       <c r="F7" t="n">
-        <v>2.638512900976016</v>
+        <v>2.247813417919827</v>
       </c>
       <c r="G7" t="n">
-        <v>2.642652560169996</v>
+        <v>2.252220429620491</v>
       </c>
       <c r="H7" t="n">
-        <v>2.684400673970968</v>
+        <v>2.294084049493663</v>
       </c>
       <c r="I7" t="n">
-        <v>2.638519132753405</v>
+        <v>2.247813502505586</v>
       </c>
       <c r="J7" t="n">
-        <v>2.60624374047181</v>
+        <v>2.215927115994508</v>
       </c>
       <c r="K7" t="n">
-        <v>2.563464406859959</v>
+        <v>2.173147782382655</v>
       </c>
       <c r="L7" t="n">
-        <v>2.637816280323209</v>
+        <v>2.247499655845904</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.600068580889736</v>
+        <v>2.165147463087282</v>
       </c>
       <c r="C8" t="n">
-        <v>2.976844765837646</v>
+        <v>2.307359825326702</v>
       </c>
       <c r="D8" t="n">
-        <v>2.961827170117506</v>
+        <v>2.244253592938874</v>
       </c>
       <c r="E8" t="n">
-        <v>2.899127342932472</v>
+        <v>2.293681559455623</v>
       </c>
       <c r="F8" t="n">
-        <v>2.701668553457708</v>
+        <v>2.258928812696375</v>
       </c>
       <c r="G8" t="n">
-        <v>2.980896520736076</v>
+        <v>2.311751366357548</v>
       </c>
       <c r="H8" t="n">
-        <v>3.022644634537035</v>
+        <v>2.353614986230717</v>
       </c>
       <c r="I8" t="n">
-        <v>2.976763093319483</v>
+        <v>2.307344439242642</v>
       </c>
       <c r="J8" t="n">
-        <v>2.94454353719923</v>
+        <v>2.275467879895906</v>
       </c>
       <c r="K8" t="n">
-        <v>2.612318541734825</v>
+        <v>2.181746110074041</v>
       </c>
       <c r="L8" t="n">
-        <v>3.27283928898296</v>
+        <v>2.359263704764414</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.581506278947768</v>
+        <v>2.51388049605585</v>
       </c>
       <c r="C9" t="n">
-        <v>5.345727373329954</v>
+        <v>2.724283161986206</v>
       </c>
       <c r="D9" t="n">
-        <v>5.271877580448876</v>
+        <v>2.65082246295416</v>
       </c>
       <c r="E9" t="n">
-        <v>6.120782182905003</v>
+        <v>2.860692808218379</v>
       </c>
       <c r="F9" t="n">
-        <v>5.345726814491232</v>
+        <v>2.724283064116703</v>
       </c>
       <c r="G9" t="n">
-        <v>5.349859572929862</v>
+        <v>2.728688861284434</v>
       </c>
       <c r="H9" t="n">
-        <v>5.391607686730838</v>
+        <v>2.770552481157607</v>
       </c>
       <c r="I9" t="n">
-        <v>5.345726145513288</v>
+        <v>2.724281934169528</v>
       </c>
       <c r="J9" t="n">
-        <v>5.313450753231682</v>
+        <v>2.692395547658452</v>
       </c>
       <c r="K9" t="n">
-        <v>4.865733599715635</v>
+        <v>2.578347158129641</v>
       </c>
       <c r="L9" t="n">
-        <v>5.345023293083075</v>
+        <v>2.723968087509848</v>
       </c>
     </row>
   </sheetData>
@@ -6854,13 +6854,13 @@
         <v>6.448809346758061</v>
       </c>
       <c r="C2" t="n">
-        <v>6.573371035517873</v>
+        <v>6.573371035517874</v>
       </c>
       <c r="D2" t="n">
         <v>6.460085225767332</v>
       </c>
       <c r="E2" t="n">
-        <v>6.57823522666733</v>
+        <v>6.578235226667331</v>
       </c>
       <c r="F2" t="n">
         <v>6.562745848369326</v>
@@ -6921,7 +6921,7 @@
         <v>6.660607918230236</v>
       </c>
       <c r="L3" t="n">
-        <v>6.725770231390375</v>
+        <v>6.725770231390374</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.18104936685053</v>
+        <v>2.090612120958373</v>
       </c>
       <c r="C4" t="n">
-        <v>2.245102807389523</v>
+        <v>2.152843412353647</v>
       </c>
       <c r="D4" t="n">
-        <v>2.187752399122017</v>
+        <v>2.097315153229861</v>
       </c>
       <c r="E4" t="n">
-        <v>2.245545827272875</v>
+        <v>2.152921383590664</v>
       </c>
       <c r="F4" t="n">
-        <v>2.245545827272875</v>
+        <v>2.152921383590664</v>
       </c>
       <c r="G4" t="n">
-        <v>2.236731763656687</v>
+        <v>2.146148295910667</v>
       </c>
       <c r="H4" t="n">
-        <v>2.277530546286368</v>
+        <v>2.187093300394211</v>
       </c>
       <c r="I4" t="n">
-        <v>2.243598907747252</v>
+        <v>2.15257978994122</v>
       </c>
       <c r="J4" t="n">
-        <v>2.209579038032971</v>
+        <v>2.119141792140814</v>
       </c>
       <c r="K4" t="n">
-        <v>2.184327606914911</v>
+        <v>2.093890361022753</v>
       </c>
       <c r="L4" t="n">
-        <v>2.229036250588605</v>
+        <v>2.138599004696447</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.128671880464987</v>
+        <v>2.257393682450795</v>
       </c>
       <c r="C5" t="n">
-        <v>8.418767384812259</v>
+        <v>3.239408372092376</v>
       </c>
       <c r="D5" t="n">
-        <v>3.713102476269848</v>
+        <v>2.365776765353191</v>
       </c>
       <c r="E5" t="n">
-        <v>8.418767384494259</v>
+        <v>3.239408371774379</v>
       </c>
       <c r="F5" t="n">
-        <v>8.418767384494259</v>
+        <v>3.239408371774379</v>
       </c>
       <c r="G5" t="n">
-        <v>7.975059114880804</v>
+        <v>3.156093904253627</v>
       </c>
       <c r="H5" t="n">
-        <v>12.31127680621549</v>
+        <v>3.953032632572811</v>
       </c>
       <c r="I5" t="n">
-        <v>8.418768675981166</v>
+        <v>3.239409663261288</v>
       </c>
       <c r="J5" t="n">
-        <v>5.812642711355685</v>
+        <v>2.753280995209461</v>
       </c>
       <c r="K5" t="n">
-        <v>3.388553497120736</v>
+        <v>2.30583411655054</v>
       </c>
       <c r="L5" t="n">
-        <v>10.72034480313046</v>
+        <v>3.182618168934958</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.366702130017737</v>
+        <v>3.179287001376701</v>
       </c>
       <c r="C6" t="n">
-        <v>8.51958282131811</v>
+        <v>3.257151888821269</v>
       </c>
       <c r="D6" t="n">
-        <v>78.75975054733918</v>
+        <v>3.184066206324157</v>
       </c>
       <c r="E6" t="n">
-        <v>8.499159748360832</v>
+        <v>3.253557427738228</v>
       </c>
       <c r="F6" t="n">
-        <v>8.518935243345</v>
+        <v>3.257037914836593</v>
       </c>
       <c r="G6" t="n">
-        <v>8.422384526823878</v>
+        <v>15.62429089628914</v>
       </c>
       <c r="H6" t="n">
-        <v>78.84893047322045</v>
+        <v>15.66365961451044</v>
       </c>
       <c r="I6" t="n">
-        <v>8.429251670914475</v>
+        <v>3.241254670359551</v>
       </c>
       <c r="J6" t="n">
-        <v>8.405363107258554</v>
+        <v>15.59596584198316</v>
       </c>
       <c r="K6" t="n">
-        <v>8.277659126764993</v>
+        <v>3.166316702705315</v>
       </c>
       <c r="L6" t="n">
-        <v>8.412270238808569</v>
+        <v>3.226848180726367</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.516316605966153</v>
+        <v>2.149619154722987</v>
       </c>
       <c r="C7" t="n">
-        <v>2.578864855693969</v>
+        <v>2.211585532536929</v>
       </c>
       <c r="D7" t="n">
-        <v>2.522994712965913</v>
+        <v>2.156317800146675</v>
       </c>
       <c r="E7" t="n">
-        <v>2.578855217005929</v>
+        <v>2.211583835865813</v>
       </c>
       <c r="F7" t="n">
-        <v>2.578855217005929</v>
+        <v>2.211583835865813</v>
       </c>
       <c r="G7" t="n">
-        <v>2.571999002772309</v>
+        <v>2.205155329675281</v>
       </c>
       <c r="H7" t="n">
-        <v>2.612797785401992</v>
+        <v>2.246100334158825</v>
       </c>
       <c r="I7" t="n">
-        <v>2.578866146862874</v>
+        <v>2.211586823705834</v>
       </c>
       <c r="J7" t="n">
-        <v>2.544846277148595</v>
+        <v>2.178148825905427</v>
       </c>
       <c r="K7" t="n">
-        <v>2.519594846030533</v>
+        <v>2.152897394787368</v>
       </c>
       <c r="L7" t="n">
-        <v>2.564303489704227</v>
+        <v>2.197606038461061</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.557444236425315</v>
+        <v>2.156857617644577</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8851397457459</v>
+        <v>2.265489912894152</v>
       </c>
       <c r="D8" t="n">
-        <v>2.884184861527076</v>
+        <v>2.219887265948981</v>
       </c>
       <c r="E8" t="n">
-        <v>2.812630092618694</v>
+        <v>2.252728213750714</v>
       </c>
       <c r="F8" t="n">
-        <v>2.628404009498583</v>
+        <v>2.220304423297267</v>
       </c>
       <c r="G8" t="n">
-        <v>2.878199616246613</v>
+        <v>2.259046637354742</v>
       </c>
       <c r="H8" t="n">
-        <v>2.918998398876354</v>
+        <v>2.299991641838297</v>
       </c>
       <c r="I8" t="n">
-        <v>2.885066760337179</v>
+        <v>2.265478131385296</v>
       </c>
       <c r="J8" t="n">
-        <v>2.851098985022054</v>
+        <v>2.232049302199091</v>
       </c>
       <c r="K8" t="n">
-        <v>2.555798609745496</v>
+        <v>2.159269257166675</v>
       </c>
       <c r="L8" t="n">
-        <v>3.147394998944074</v>
+        <v>2.300230143531196</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.267430170073453</v>
+        <v>2.457815140335879</v>
       </c>
       <c r="C9" t="n">
-        <v>4.918257810479276</v>
+        <v>2.623318690348125</v>
       </c>
       <c r="D9" t="n">
-        <v>4.862412452207654</v>
+        <v>2.568055320022177</v>
       </c>
       <c r="E9" t="n">
-        <v>5.597118991787742</v>
+        <v>2.74279825734897</v>
       </c>
       <c r="F9" t="n">
-        <v>4.918257302653563</v>
+        <v>2.623318600708768</v>
       </c>
       <c r="G9" t="n">
-        <v>4.911391957557605</v>
+        <v>2.616888487486474</v>
       </c>
       <c r="H9" t="n">
-        <v>4.952190740187302</v>
+        <v>2.657833491970018</v>
       </c>
       <c r="I9" t="n">
-        <v>4.918259101648182</v>
+        <v>2.623319981517029</v>
       </c>
       <c r="J9" t="n">
-        <v>4.884239231933901</v>
+        <v>2.589881983716624</v>
       </c>
       <c r="K9" t="n">
-        <v>4.518136352279406</v>
+        <v>2.502206834806357</v>
       </c>
       <c r="L9" t="n">
-        <v>4.903696444489534</v>
+        <v>2.609339196272257</v>
       </c>
     </row>
   </sheetData>
@@ -7256,7 +7256,7 @@
         <v>6.532546656592634</v>
       </c>
       <c r="E2" t="n">
-        <v>6.669386864273988</v>
+        <v>6.669386864273989</v>
       </c>
       <c r="F2" t="n">
         <v>6.653488979602571</v>
@@ -7268,7 +7268,7 @@
         <v>6.639890286091762</v>
       </c>
       <c r="I2" t="n">
-        <v>6.64245032637228</v>
+        <v>6.642450326372281</v>
       </c>
       <c r="J2" t="n">
         <v>6.640894493006638</v>
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.219740821881066</v>
+        <v>2.107357009969848</v>
       </c>
       <c r="C4" t="n">
-        <v>2.324652910304757</v>
+        <v>2.210471041011238</v>
       </c>
       <c r="D4" t="n">
-        <v>2.257142253062392</v>
+        <v>2.144758441151175</v>
       </c>
       <c r="E4" t="n">
-        <v>2.325351750617191</v>
+        <v>2.210594037282497</v>
       </c>
       <c r="F4" t="n">
-        <v>2.325351750617191</v>
+        <v>2.210594037282497</v>
       </c>
       <c r="G4" t="n">
-        <v>2.317425512772767</v>
+        <v>2.204904834013642</v>
       </c>
       <c r="H4" t="n">
-        <v>2.320956637573254</v>
+        <v>2.208572825662036</v>
       </c>
       <c r="I4" t="n">
-        <v>2.323111014186895</v>
+        <v>2.210200465702966</v>
       </c>
       <c r="J4" t="n">
-        <v>2.295448542034736</v>
+        <v>2.183064730123518</v>
       </c>
       <c r="K4" t="n">
-        <v>2.24993438026699</v>
+        <v>2.137550568355772</v>
       </c>
       <c r="L4" t="n">
-        <v>2.280953447834612</v>
+        <v>2.168569635923393</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.018949476328258</v>
+        <v>2.424017731436698</v>
       </c>
       <c r="C5" t="n">
-        <v>13.42705901434991</v>
+        <v>4.164494504735089</v>
       </c>
       <c r="D5" t="n">
-        <v>7.487689337489044</v>
+        <v>3.065334723022026</v>
       </c>
       <c r="E5" t="n">
-        <v>13.42705901480734</v>
+        <v>4.164494505192541</v>
       </c>
       <c r="F5" t="n">
-        <v>13.42705901480734</v>
+        <v>4.164494505192541</v>
       </c>
       <c r="G5" t="n">
-        <v>13.44054245669607</v>
+        <v>4.162573405536305</v>
       </c>
       <c r="H5" t="n">
-        <v>14.40059429182861</v>
+        <v>4.334589041290942</v>
       </c>
       <c r="I5" t="n">
-        <v>13.42705998329041</v>
+        <v>4.164495473675628</v>
       </c>
       <c r="J5" t="n">
-        <v>11.96132433929797</v>
+        <v>3.884258861223752</v>
       </c>
       <c r="K5" t="n">
-        <v>6.876997872268543</v>
+        <v>2.951913738535335</v>
       </c>
       <c r="L5" t="n">
-        <v>11.30717570213773</v>
+        <v>3.757184744072673</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.891453165845045</v>
+        <v>3.281578376144866</v>
       </c>
       <c r="C6" t="n">
-        <v>9.08191174545267</v>
+        <v>3.399748589553046</v>
       </c>
       <c r="D6" t="n">
-        <v>8.905465906493683</v>
+        <v>3.314863397814749</v>
       </c>
       <c r="E6" t="n">
-        <v>9.058917653261872</v>
+        <v>3.395701629726334</v>
       </c>
       <c r="F6" t="n">
-        <v>9.081276815516903</v>
+        <v>3.399636842261895</v>
       </c>
       <c r="G6" t="n">
-        <v>84.5620220049443</v>
+        <v>16.67995373820124</v>
       </c>
       <c r="H6" t="n">
-        <v>84.55407258387623</v>
+        <v>16.68160115378774</v>
       </c>
       <c r="I6" t="n">
-        <v>8.994823358150864</v>
+        <v>16.68524936989057</v>
       </c>
       <c r="J6" t="n">
-        <v>84.53164140139286</v>
+        <v>16.65663459494399</v>
       </c>
       <c r="K6" t="n">
-        <v>8.810148913736066</v>
+        <v>3.29214831999002</v>
       </c>
       <c r="L6" t="n">
-        <v>8.939423399176631</v>
+        <v>3.340460341009573</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.599041432002078</v>
+        <v>2.174113916989417</v>
       </c>
       <c r="C7" t="n">
-        <v>2.702410655367371</v>
+        <v>2.276956403782</v>
       </c>
       <c r="D7" t="n">
-        <v>2.636415711742454</v>
+        <v>2.211510569517162</v>
       </c>
       <c r="E7" t="n">
-        <v>2.702387887395171</v>
+        <v>2.276952396995852</v>
       </c>
       <c r="F7" t="n">
-        <v>2.702387887395171</v>
+        <v>2.276952396995852</v>
       </c>
       <c r="G7" t="n">
-        <v>2.69672612289378</v>
+        <v>2.27166174103321</v>
       </c>
       <c r="H7" t="n">
-        <v>2.700257247694265</v>
+        <v>2.275329732681605</v>
       </c>
       <c r="I7" t="n">
-        <v>2.702411624307907</v>
+        <v>2.276957372722535</v>
       </c>
       <c r="J7" t="n">
-        <v>2.674749152155748</v>
+        <v>2.249821637143088</v>
       </c>
       <c r="K7" t="n">
-        <v>2.629234990388003</v>
+        <v>2.204307475375341</v>
       </c>
       <c r="L7" t="n">
-        <v>2.660254057955625</v>
+        <v>2.235326542942962</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.661523464093369</v>
+        <v>2.185110754577896</v>
       </c>
       <c r="C8" t="n">
-        <v>3.076183822980562</v>
+        <v>2.342740480925664</v>
       </c>
       <c r="D8" t="n">
-        <v>3.0746755348832</v>
+        <v>2.288644297971976</v>
       </c>
       <c r="E8" t="n">
-        <v>2.991053597502008</v>
+        <v>2.327757561699362</v>
       </c>
       <c r="F8" t="n">
-        <v>2.774760421115122</v>
+        <v>2.289689962861543</v>
       </c>
       <c r="G8" t="n">
-        <v>3.070425790482183</v>
+        <v>2.337432882172382</v>
       </c>
       <c r="H8" t="n">
-        <v>3.073956915282577</v>
+        <v>2.341100873820761</v>
       </c>
       <c r="I8" t="n">
-        <v>3.076111291896308</v>
+        <v>2.342728513861705</v>
       </c>
       <c r="J8" t="n">
-        <v>3.04850998288352</v>
+        <v>2.31560354299473</v>
       </c>
       <c r="K8" t="n">
-        <v>2.685935995125219</v>
+        <v>2.214286852155016</v>
       </c>
       <c r="L8" t="n">
-        <v>3.359046569374009</v>
+        <v>2.358314024286179</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.113501333864373</v>
+        <v>2.616658857319206</v>
       </c>
       <c r="C9" t="n">
-        <v>6.03043614572296</v>
+        <v>2.862688886910733</v>
       </c>
       <c r="D9" t="n">
-        <v>5.964468275870638</v>
+        <v>2.797247817629846</v>
       </c>
       <c r="E9" t="n">
-        <v>6.969272795977907</v>
+        <v>3.027924136837195</v>
       </c>
       <c r="F9" t="n">
-        <v>6.030435571190839</v>
+        <v>2.862688786170019</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02475161324938</v>
+        <v>2.857394224161943</v>
       </c>
       <c r="H9" t="n">
-        <v>6.028282738049866</v>
+        <v>2.861062215810338</v>
       </c>
       <c r="I9" t="n">
-        <v>6.030437114663487</v>
+        <v>2.86268985585127</v>
       </c>
       <c r="J9" t="n">
-        <v>6.002774642511349</v>
+        <v>2.835554120271819</v>
       </c>
       <c r="K9" t="n">
-        <v>5.46675274511596</v>
+        <v>2.707076528116137</v>
       </c>
       <c r="L9" t="n">
-        <v>5.988279548311226</v>
+        <v>2.821059026071694</v>
       </c>
     </row>
   </sheetData>
@@ -7646,7 +7646,7 @@
         <v>6.447622419629688</v>
       </c>
       <c r="C2" t="n">
-        <v>6.628087412676779</v>
+        <v>6.628087412676778</v>
       </c>
       <c r="D2" t="n">
         <v>6.514162323856572</v>
@@ -7670,7 +7670,7 @@
         <v>6.601951677493833</v>
       </c>
       <c r="K2" t="n">
-        <v>6.508660620153155</v>
+        <v>6.508660620153156</v>
       </c>
       <c r="L2" t="n">
         <v>6.568664857305648</v>
@@ -7689,7 +7689,7 @@
         <v>6.835852770049128</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7081051178663</v>
+        <v>6.708105117866301</v>
       </c>
       <c r="E3" t="n">
         <v>6.840930355988525</v>
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.195473373673435</v>
+        <v>2.09237771045747</v>
       </c>
       <c r="C4" t="n">
-        <v>2.291901870218865</v>
+        <v>2.187224806236474</v>
       </c>
       <c r="D4" t="n">
-        <v>2.235028527201401</v>
+        <v>2.131932863985436</v>
       </c>
       <c r="E4" t="n">
-        <v>2.292502888896643</v>
+        <v>2.187330585978356</v>
       </c>
       <c r="F4" t="n">
-        <v>2.292502888896644</v>
+        <v>2.187330585978356</v>
       </c>
       <c r="G4" t="n">
-        <v>2.287363789029373</v>
+        <v>2.184137468351981</v>
       </c>
       <c r="H4" t="n">
-        <v>2.406826611920891</v>
+        <v>2.303730948704926</v>
       </c>
       <c r="I4" t="n">
-        <v>2.290572077583915</v>
+        <v>2.186991118462773</v>
       </c>
       <c r="J4" t="n">
-        <v>2.261244778064011</v>
+        <v>2.158149114848047</v>
       </c>
       <c r="K4" t="n">
-        <v>2.218615119529949</v>
+        <v>2.115519456313984</v>
       </c>
       <c r="L4" t="n">
-        <v>2.267470847130307</v>
+        <v>2.164375183914341</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.852025072885497</v>
+        <v>2.207930808892657</v>
       </c>
       <c r="C5" t="n">
-        <v>10.81866469614778</v>
+        <v>3.687935055468196</v>
       </c>
       <c r="D5" t="n">
-        <v>6.165269204977467</v>
+        <v>2.823655219525856</v>
       </c>
       <c r="E5" t="n">
-        <v>10.81866469670011</v>
+        <v>3.687935056020581</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81866469670011</v>
+        <v>3.687935056020581</v>
       </c>
       <c r="G5" t="n">
-        <v>10.84629569461883</v>
+        <v>3.690509475573296</v>
       </c>
       <c r="H5" t="n">
-        <v>22.29886422994245</v>
+        <v>5.804729550506192</v>
       </c>
       <c r="I5" t="n">
-        <v>10.81866512785742</v>
+        <v>3.687935487177888</v>
       </c>
       <c r="J5" t="n">
-        <v>9.209283854926248</v>
+        <v>3.381003985749636</v>
       </c>
       <c r="K5" t="n">
-        <v>4.802922677266175</v>
+        <v>2.570357584010973</v>
       </c>
       <c r="L5" t="n">
-        <v>10.39412244013258</v>
+        <v>5.065807640104795</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.400509366408617</v>
+        <v>15.57695273521741</v>
       </c>
       <c r="C6" t="n">
-        <v>8.579453240902565</v>
+        <v>3.293833841480534</v>
       </c>
       <c r="D6" t="n">
-        <v>8.422814993067462</v>
+        <v>3.220983276076725</v>
       </c>
       <c r="E6" t="n">
-        <v>8.558400906021998</v>
+        <v>3.290128631016791</v>
       </c>
       <c r="F6" t="n">
-        <v>8.579182355320579</v>
+        <v>3.29378616607352</v>
       </c>
       <c r="G6" t="n">
-        <v>78.90426775395846</v>
+        <v>3.276223797155794</v>
       </c>
       <c r="H6" t="n">
-        <v>79.01612889841149</v>
+        <v>15.78696807806694</v>
       </c>
       <c r="I6" t="n">
-        <v>78.907476042513</v>
+        <v>15.67156614322271</v>
       </c>
       <c r="J6" t="n">
-        <v>78.87056656586259</v>
+        <v>3.2511210900407</v>
       </c>
       <c r="K6" t="n">
-        <v>8.322627550566397</v>
+        <v>3.189825638355157</v>
       </c>
       <c r="L6" t="n">
-        <v>8.463775994873949</v>
+        <v>3.254924884007971</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.544154856521472</v>
+        <v>2.153745651106196</v>
       </c>
       <c r="C7" t="n">
-        <v>2.639253128722264</v>
+        <v>2.248358627401812</v>
       </c>
       <c r="D7" t="n">
-        <v>2.583684772939927</v>
+        <v>2.193296362902912</v>
       </c>
       <c r="E7" t="n">
-        <v>2.639257716584875</v>
+        <v>2.248359435320793</v>
       </c>
       <c r="F7" t="n">
-        <v>2.639257716584875</v>
+        <v>2.248359435320793</v>
       </c>
       <c r="G7" t="n">
-        <v>2.636045271877409</v>
+        <v>2.245505409000708</v>
       </c>
       <c r="H7" t="n">
-        <v>2.755508094768928</v>
+        <v>2.365098889353653</v>
       </c>
       <c r="I7" t="n">
-        <v>2.639253560431951</v>
+        <v>2.248359059111499</v>
       </c>
       <c r="J7" t="n">
-        <v>2.60992626091205</v>
+        <v>2.219517055496773</v>
       </c>
       <c r="K7" t="n">
-        <v>2.567296602377986</v>
+        <v>2.17688739696271</v>
       </c>
       <c r="L7" t="n">
-        <v>2.616152329978342</v>
+        <v>2.225743124563067</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.597850105421887</v>
+        <v>2.163196014861461</v>
       </c>
       <c r="C8" t="n">
-        <v>2.976808772153612</v>
+        <v>2.307768420324005</v>
       </c>
       <c r="D8" t="n">
-        <v>2.980014998867409</v>
+        <v>2.263050482288179</v>
       </c>
       <c r="E8" t="n">
-        <v>2.899184157270653</v>
+        <v>2.294106488633605</v>
       </c>
       <c r="F8" t="n">
-        <v>2.701961193010463</v>
+        <v>2.259395247111898</v>
       </c>
       <c r="G8" t="n">
-        <v>2.973509014869047</v>
+        <v>2.304899027445405</v>
       </c>
       <c r="H8" t="n">
-        <v>3.092971837760577</v>
+        <v>2.424492507798352</v>
       </c>
       <c r="I8" t="n">
-        <v>2.976717303423588</v>
+        <v>2.307752677556198</v>
       </c>
       <c r="J8" t="n">
-        <v>2.947445772500785</v>
+        <v>2.278920489214506</v>
       </c>
       <c r="K8" t="n">
-        <v>2.615720705818243</v>
+        <v>2.185410039122015</v>
       </c>
       <c r="L8" t="n">
-        <v>3.250035993342265</v>
+        <v>2.337306648710598</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.570667416720682</v>
+        <v>2.510411859768624</v>
       </c>
       <c r="C9" t="n">
-        <v>5.334869804646379</v>
+        <v>2.722787159793718</v>
       </c>
       <c r="D9" t="n">
-        <v>5.279326459622589</v>
+        <v>2.667729297188293</v>
       </c>
       <c r="E9" t="n">
-        <v>6.107000738537522</v>
+        <v>2.858682203877362</v>
       </c>
       <c r="F9" t="n">
-        <v>5.334869145764363</v>
+        <v>2.722787044285645</v>
       </c>
       <c r="G9" t="n">
-        <v>5.331661947801538</v>
+        <v>2.71993394139261</v>
       </c>
       <c r="H9" t="n">
-        <v>5.451124770693047</v>
+        <v>2.839527421745557</v>
       </c>
       <c r="I9" t="n">
-        <v>5.33487023635607</v>
+        <v>2.722787591503403</v>
       </c>
       <c r="J9" t="n">
-        <v>5.30554293683617</v>
+        <v>2.693945587888675</v>
       </c>
       <c r="K9" t="n">
-        <v>4.875231630674338</v>
+        <v>2.503032153603891</v>
       </c>
       <c r="L9" t="n">
-        <v>5.311769005902462</v>
+        <v>2.70017165695497</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia water use results.xlsx
+++ b/Results/Ammonia/ammonia water use results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.491225505566486</v>
+        <v>2.397974324484816</v>
       </c>
       <c r="C2" t="n">
-        <v>6.639490404758444</v>
+        <v>2.422089040702594</v>
       </c>
       <c r="D2" t="n">
-        <v>6.537427915876171</v>
+        <v>2.400405865574037</v>
       </c>
       <c r="E2" t="n">
-        <v>6.644441448965914</v>
+        <v>2.426497121365932</v>
       </c>
       <c r="F2" t="n">
-        <v>6.62872142172553</v>
+        <v>2.413407725419</v>
       </c>
       <c r="G2" t="n">
-        <v>6.618843619443798</v>
+        <v>2.404690612348189</v>
       </c>
       <c r="H2" t="n">
-        <v>6.634493297760852</v>
+        <v>2.405450282604843</v>
       </c>
       <c r="I2" t="n">
-        <v>6.61822829981751</v>
+        <v>2.404657714226174</v>
       </c>
       <c r="J2" t="n">
-        <v>6.627942474853321</v>
+        <v>2.438810056512719</v>
       </c>
       <c r="K2" t="n">
-        <v>6.54694377780394</v>
+        <v>2.418847312395473</v>
       </c>
       <c r="L2" t="n">
-        <v>6.506298318706068</v>
+        <v>2.398640430815095</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.681732470129892</v>
+        <v>2.408217778759851</v>
       </c>
       <c r="C3" t="n">
-        <v>6.84901918413682</v>
+        <v>2.484712759580956</v>
       </c>
       <c r="D3" t="n">
-        <v>6.734874812786491</v>
+        <v>2.425548992923985</v>
       </c>
       <c r="E3" t="n">
-        <v>6.854023671133934</v>
+        <v>2.491803276451297</v>
       </c>
       <c r="F3" t="n">
-        <v>6.838303643893549</v>
+        <v>2.470199776616411</v>
       </c>
       <c r="G3" t="n">
-        <v>6.828519737101446</v>
+        <v>2.456132922882182</v>
       </c>
       <c r="H3" t="n">
-        <v>6.846667210889946</v>
+        <v>2.462317989666232</v>
       </c>
       <c r="I3" t="n">
-        <v>6.827799348139285</v>
+        <v>2.455761298317353</v>
       </c>
       <c r="J3" t="n">
-        <v>6.832504879351635</v>
+        <v>2.502725894079616</v>
       </c>
       <c r="K3" t="n">
-        <v>6.742363990838283</v>
+        <v>2.452106824192623</v>
       </c>
       <c r="L3" t="n">
-        <v>6.69908316303466</v>
+        <v>2.414006472094175</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.119593681223303</v>
+        <v>2.119593681223304</v>
       </c>
       <c r="C4" t="n">
-        <v>2.195367948191963</v>
+        <v>2.195367948191962</v>
       </c>
       <c r="D4" t="n">
         <v>2.147059056390215</v>
@@ -610,7 +610,7 @@
         <v>2.195494908039985</v>
       </c>
       <c r="G4" t="n">
-        <v>2.19548314496337</v>
+        <v>2.195483144963371</v>
       </c>
       <c r="H4" t="n">
         <v>2.204761188950388</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.701613148477835</v>
+        <v>2.701613148477847</v>
       </c>
       <c r="C5" t="n">
-        <v>4.129132531955372</v>
+        <v>4.129132531955375</v>
       </c>
       <c r="D5" t="n">
-        <v>3.241146159618843</v>
+        <v>3.241146159618847</v>
       </c>
       <c r="E5" t="n">
-        <v>4.129132532909463</v>
+        <v>4.129132532909467</v>
       </c>
       <c r="F5" t="n">
-        <v>4.129132532909463</v>
+        <v>4.129132532909467</v>
       </c>
       <c r="G5" t="n">
-        <v>4.217874945765017</v>
+        <v>4.217874945765</v>
       </c>
       <c r="H5" t="n">
-        <v>4.625343267693369</v>
+        <v>4.625343267693363</v>
       </c>
       <c r="I5" t="n">
-        <v>4.129132232163367</v>
+        <v>4.129132232163368</v>
       </c>
       <c r="J5" t="n">
-        <v>3.871190014066447</v>
+        <v>3.871190014066451</v>
       </c>
       <c r="K5" t="n">
-        <v>3.087144936792961</v>
+        <v>3.087144936792965</v>
       </c>
       <c r="L5" t="n">
-        <v>12.81239218836569</v>
+        <v>3.014511813948371</v>
       </c>
     </row>
     <row r="6">
@@ -675,34 +675,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.373741105498577</v>
+        <v>3.37374110549858</v>
       </c>
       <c r="C6" t="n">
-        <v>3.465437388501965</v>
+        <v>3.465437388501964</v>
       </c>
       <c r="D6" t="n">
-        <v>3.397179806152655</v>
+        <v>3.397179636446144</v>
       </c>
       <c r="E6" t="n">
-        <v>3.461163970028605</v>
+        <v>3.461163970028606</v>
       </c>
       <c r="F6" t="n">
-        <v>3.465473729255891</v>
+        <v>3.46547372925589</v>
       </c>
       <c r="G6" t="n">
-        <v>17.66255399153954</v>
+        <v>17.66255399153955</v>
       </c>
       <c r="H6" t="n">
         <v>17.66988011662018</v>
       </c>
       <c r="I6" t="n">
-        <v>3.449323762314956</v>
+        <v>17.66224718461586</v>
       </c>
       <c r="J6" t="n">
-        <v>3.429770634173319</v>
+        <v>17.64086079970541</v>
       </c>
       <c r="K6" t="n">
-        <v>3.372578071342062</v>
+        <v>3.372578071342059</v>
       </c>
       <c r="L6" t="n">
         <v>3.380021330844657</v>
@@ -758,7 +758,7 @@
         <v>2.200931502436253</v>
       </c>
       <c r="C8" t="n">
-        <v>2.333723653194269</v>
+        <v>2.333723653194431</v>
       </c>
       <c r="D8" t="n">
         <v>2.297458746379784</v>
@@ -773,10 +773,10 @@
         <v>2.334021857506912</v>
       </c>
       <c r="H8" t="n">
-        <v>2.343299901493928</v>
+        <v>2.343299901493927</v>
       </c>
       <c r="I8" t="n">
-        <v>2.333715050583226</v>
+        <v>2.333715050583227</v>
       </c>
       <c r="J8" t="n">
         <v>2.313769239724795</v>
@@ -785,7 +785,7 @@
         <v>2.219313567094203</v>
       </c>
       <c r="L8" t="n">
-        <v>2.326905474194115</v>
+        <v>2.326905474194113</v>
       </c>
     </row>
     <row r="9">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.731575000438018</v>
+        <v>2.731575000438017</v>
       </c>
       <c r="C9" t="n">
         <v>2.978807015460094</v>
       </c>
       <c r="D9" t="n">
-        <v>2.930689420336561</v>
+        <v>2.93068942033656</v>
       </c>
       <c r="E9" t="n">
-        <v>3.176886245836324</v>
+        <v>3.176886245836323</v>
       </c>
       <c r="F9" t="n">
         <v>2.978806910757267</v>
@@ -813,19 +813,19 @@
         <v>2.979113522591775</v>
       </c>
       <c r="H9" t="n">
-        <v>2.988391566578795</v>
+        <v>2.988391566578794</v>
       </c>
       <c r="I9" t="n">
         <v>2.978806715668087</v>
       </c>
       <c r="J9" t="n">
-        <v>2.958849663202151</v>
+        <v>2.95884966320215</v>
       </c>
       <c r="K9" t="n">
-        <v>2.823214515115028</v>
+        <v>2.706531859187109</v>
       </c>
       <c r="L9" t="n">
-        <v>2.912246025229919</v>
+        <v>2.912246025229917</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.443827313004368</v>
+        <v>2.390607844864272</v>
       </c>
       <c r="C2" t="n">
-        <v>6.583158917902469</v>
+        <v>2.413753664184544</v>
       </c>
       <c r="D2" t="n">
-        <v>6.485974837310073</v>
+        <v>2.392825985356754</v>
       </c>
       <c r="E2" t="n">
-        <v>6.588143184535159</v>
+        <v>2.418158974718839</v>
       </c>
       <c r="F2" t="n">
-        <v>6.572306463094841</v>
+        <v>2.404972423023362</v>
       </c>
       <c r="G2" t="n">
-        <v>6.570910040197683</v>
+        <v>2.397295956389829</v>
       </c>
       <c r="H2" t="n">
-        <v>6.657478327167045</v>
+        <v>2.401842782058986</v>
       </c>
       <c r="I2" t="n">
-        <v>6.562577341608246</v>
+        <v>2.396856811496239</v>
       </c>
       <c r="J2" t="n">
-        <v>6.563894173329428</v>
+        <v>2.430384323315769</v>
       </c>
       <c r="K2" t="n">
-        <v>6.487771275066654</v>
+        <v>2.409683789034782</v>
       </c>
       <c r="L2" t="n">
-        <v>6.515400546091565</v>
+        <v>2.394298497364424</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.627280155689519</v>
+        <v>2.387975174678119</v>
       </c>
       <c r="C3" t="n">
-        <v>6.784380154742939</v>
+        <v>2.460371415581574</v>
       </c>
       <c r="D3" t="n">
-        <v>6.675758539474437</v>
+        <v>2.403715580950774</v>
       </c>
       <c r="E3" t="n">
-        <v>6.789431385156989</v>
+        <v>2.467475192080378</v>
       </c>
       <c r="F3" t="n">
-        <v>6.77359466371667</v>
+        <v>2.445711333900275</v>
       </c>
       <c r="G3" t="n">
-        <v>6.773451617069461</v>
+        <v>2.435509646897977</v>
       </c>
       <c r="H3" t="n">
-        <v>6.873150977748995</v>
+        <v>2.468261156673532</v>
       </c>
       <c r="I3" t="n">
-        <v>6.763848342993218</v>
+        <v>2.432320052022268</v>
       </c>
       <c r="J3" t="n">
-        <v>6.758936741484163</v>
+        <v>2.475913797866554</v>
       </c>
       <c r="K3" t="n">
-        <v>6.67459558874666</v>
+        <v>2.425884001220347</v>
       </c>
       <c r="L3" t="n">
-        <v>6.709614331693823</v>
+        <v>2.4149486895879</v>
       </c>
     </row>
     <row r="4">
@@ -1000,7 +1000,7 @@
         <v>2.113397477294969</v>
       </c>
       <c r="E4" t="n">
-        <v>2.159239153876659</v>
+        <v>2.15923915387666</v>
       </c>
       <c r="F4" t="n">
         <v>2.15923915387666</v>
@@ -1034,34 +1034,34 @@
         <v>2.193464240858866</v>
       </c>
       <c r="C5" t="n">
-        <v>3.310164872658557</v>
+        <v>3.310164872658559</v>
       </c>
       <c r="D5" t="n">
-        <v>2.589664632256791</v>
+        <v>2.58966463225679</v>
       </c>
       <c r="E5" t="n">
-        <v>3.310164873379809</v>
+        <v>3.31016487337981</v>
       </c>
       <c r="F5" t="n">
-        <v>3.310164873379809</v>
+        <v>3.31016487337981</v>
       </c>
       <c r="G5" t="n">
-        <v>3.426549751557051</v>
+        <v>3.426549751557042</v>
       </c>
       <c r="H5" t="n">
-        <v>4.467703193018334</v>
+        <v>4.467703193018337</v>
       </c>
       <c r="I5" t="n">
         <v>3.31016355664643</v>
       </c>
       <c r="J5" t="n">
-        <v>3.005659686501829</v>
+        <v>3.005659686501831</v>
       </c>
       <c r="K5" t="n">
-        <v>2.39818459632707</v>
+        <v>2.398184596327069</v>
       </c>
       <c r="L5" t="n">
-        <v>3.019720681250444</v>
+        <v>3.019720681250445</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.5696076562709</v>
+        <v>3.178654612515513</v>
       </c>
       <c r="C6" t="n">
-        <v>3.26404216579219</v>
+        <v>3.264042165792189</v>
       </c>
       <c r="D6" t="n">
-        <v>15.59313059909953</v>
+        <v>15.59313059909952</v>
       </c>
       <c r="E6" t="n">
-        <v>3.260414599516879</v>
+        <v>3.260414599516877</v>
       </c>
       <c r="F6" t="n">
-        <v>3.264169834821485</v>
+        <v>3.264169834821486</v>
       </c>
       <c r="G6" t="n">
-        <v>3.254223898668407</v>
+        <v>15.64517694242378</v>
       </c>
       <c r="H6" t="n">
-        <v>15.6949851895301</v>
+        <v>15.69498518953011</v>
       </c>
       <c r="I6" t="n">
         <v>3.249316732741507</v>
       </c>
       <c r="J6" t="n">
-        <v>15.61410355962223</v>
+        <v>3.225501817443873</v>
       </c>
       <c r="K6" t="n">
-        <v>3.174652730163112</v>
+        <v>3.174652730163114</v>
       </c>
       <c r="L6" t="n">
-        <v>3.219840212901636</v>
+        <v>3.219840212901635</v>
       </c>
     </row>
     <row r="7">
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.157050632323218</v>
+        <v>2.157050632323219</v>
       </c>
       <c r="C8" t="n">
-        <v>2.276173046037384</v>
+        <v>2.276173046037566</v>
       </c>
       <c r="D8" t="n">
         <v>2.24059703986523</v>
@@ -1169,13 +1169,13 @@
         <v>2.28106583282502</v>
       </c>
       <c r="H8" t="n">
-        <v>2.332487320400732</v>
+        <v>2.332487320400733</v>
       </c>
       <c r="I8" t="n">
         <v>2.276158666898123</v>
       </c>
       <c r="J8" t="n">
-        <v>2.251373396374037</v>
+        <v>2.251373396374038</v>
       </c>
       <c r="K8" t="n">
         <v>2.169493609092117</v>
@@ -1200,7 +1200,7 @@
         <v>2.59124420589415</v>
       </c>
       <c r="E9" t="n">
-        <v>2.758198805606034</v>
+        <v>2.758198805606035</v>
       </c>
       <c r="F9" t="n">
         <v>2.636852653413156</v>
@@ -1215,7 +1215,7 @@
         <v>2.636851433736412</v>
       </c>
       <c r="J9" t="n">
-        <v>2.612056642209247</v>
+        <v>2.612056642209246</v>
       </c>
       <c r="K9" t="n">
         <v>2.518605189201674</v>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.980716642081835</v>
+        <v>2.434833255239304</v>
       </c>
       <c r="C2" t="n">
-        <v>6.981369302163861</v>
+        <v>2.438691042779654</v>
       </c>
       <c r="D2" t="n">
-        <v>6.518116251304467</v>
+        <v>2.410487515471072</v>
       </c>
       <c r="E2" t="n">
-        <v>6.538533542789486</v>
+        <v>2.411484678763527</v>
       </c>
       <c r="F2" t="n">
-        <v>6.538533542789486</v>
+        <v>2.41148014806102</v>
       </c>
       <c r="G2" t="n">
-        <v>6.607366925615918</v>
+        <v>2.415184601193967</v>
       </c>
       <c r="H2" t="n">
-        <v>6.627642508006224</v>
+        <v>2.416196766458854</v>
       </c>
       <c r="I2" t="n">
-        <v>6.5386704479566</v>
+        <v>2.411568103090747</v>
       </c>
       <c r="J2" t="n">
-        <v>6.575843290069748</v>
+        <v>2.420960984417868</v>
       </c>
       <c r="K2" t="n">
-        <v>6.513837796658112</v>
+        <v>2.41511337443342</v>
       </c>
       <c r="L2" t="n">
-        <v>6.792224365619632</v>
+        <v>2.425010228603088</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.243706136023093</v>
+        <v>2.604101339434884</v>
       </c>
       <c r="C3" t="n">
-        <v>7.243637643452911</v>
+        <v>2.609198349256018</v>
       </c>
       <c r="D3" t="n">
-        <v>6.711619859246863</v>
+        <v>2.430400987276863</v>
       </c>
       <c r="E3" t="n">
-        <v>6.735121287376209</v>
+        <v>2.43796833901929</v>
       </c>
       <c r="F3" t="n">
-        <v>6.735121287376209</v>
+        <v>2.437963808316784</v>
       </c>
       <c r="G3" t="n">
-        <v>6.814276622926515</v>
+        <v>2.463942534580254</v>
       </c>
       <c r="H3" t="n">
-        <v>6.837745095875483</v>
+        <v>2.471841281355951</v>
       </c>
       <c r="I3" t="n">
-        <v>6.73522708206266</v>
+        <v>2.438114191390594</v>
       </c>
       <c r="J3" t="n">
-        <v>6.776585576060243</v>
+        <v>2.461682213996258</v>
       </c>
       <c r="K3" t="n">
-        <v>6.705764262533624</v>
+        <v>2.435018103643104</v>
       </c>
       <c r="L3" t="n">
-        <v>7.026899333062342</v>
+        <v>2.534226763757991</v>
       </c>
     </row>
     <row r="4">
@@ -1402,10 +1402,10 @@
         <v>2.14067291206103</v>
       </c>
       <c r="G4" t="n">
-        <v>2.181264622173742</v>
+        <v>2.181264622173743</v>
       </c>
       <c r="H4" t="n">
-        <v>2.193316318587897</v>
+        <v>2.193316318587898</v>
       </c>
       <c r="I4" t="n">
         <v>2.140335275259472</v>
@@ -1414,7 +1414,7 @@
         <v>2.156855486735501</v>
       </c>
       <c r="K4" t="n">
-        <v>2.12196612546246</v>
+        <v>2.121966125462459</v>
       </c>
       <c r="L4" t="n">
         <v>2.291145769637868</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.925047056126449</v>
+        <v>7.925047056126456</v>
       </c>
       <c r="C5" t="n">
-        <v>7.857975756770358</v>
+        <v>7.857975756770365</v>
       </c>
       <c r="D5" t="n">
-        <v>2.836232563573246</v>
+        <v>2.836232563573245</v>
       </c>
       <c r="E5" t="n">
-        <v>3.063946184645203</v>
+        <v>3.0639461846452</v>
       </c>
       <c r="F5" t="n">
-        <v>3.063946184645203</v>
+        <v>3.0639461846452</v>
       </c>
       <c r="G5" t="n">
-        <v>3.833950201790383</v>
+        <v>3.833950201790389</v>
       </c>
       <c r="H5" t="n">
-        <v>4.243304029682843</v>
+        <v>4.243304029682842</v>
       </c>
       <c r="I5" t="n">
-        <v>3.063936684549922</v>
+        <v>3.063936684549919</v>
       </c>
       <c r="J5" t="n">
-        <v>3.41239009687726</v>
+        <v>3.412390096877258</v>
       </c>
       <c r="K5" t="n">
         <v>2.727120499594363</v>
       </c>
       <c r="L5" t="n">
-        <v>6.294039404760627</v>
+        <v>6.294039404760619</v>
       </c>
     </row>
     <row r="6">
@@ -1467,13 +1467,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.560456110088748</v>
+        <v>16.64604894100139</v>
       </c>
       <c r="C6" t="n">
-        <v>3.581142064299175</v>
+        <v>3.581142064299176</v>
       </c>
       <c r="D6" t="n">
-        <v>3.282647760819785</v>
+        <v>3.282647628856491</v>
       </c>
       <c r="E6" t="n">
         <v>3.307784833062871</v>
@@ -1482,13 +1482,13 @@
         <v>3.313025339990205</v>
       </c>
       <c r="G6" t="n">
-        <v>16.42410943296614</v>
+        <v>3.338516602053488</v>
       </c>
       <c r="H6" t="n">
         <v>16.43552881752117</v>
       </c>
       <c r="I6" t="n">
-        <v>16.38318008605186</v>
+        <v>3.29758725513922</v>
       </c>
       <c r="J6" t="n">
         <v>16.39890700848815</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.467014547223996</v>
+        <v>2.467014547223997</v>
       </c>
       <c r="C7" t="n">
         <v>2.464511642375715</v>
@@ -1537,7 +1537,7 @@
         <v>2.185776542477451</v>
       </c>
       <c r="L7" t="n">
-        <v>2.354956186652861</v>
+        <v>2.35495618665286</v>
       </c>
     </row>
     <row r="8">
@@ -1556,16 +1556,16 @@
         <v>2.265046921822214</v>
       </c>
       <c r="E8" t="n">
-        <v>2.252244389388151</v>
+        <v>2.25224438938815</v>
       </c>
       <c r="F8" t="n">
-        <v>2.215959360085537</v>
+        <v>2.215959360085538</v>
       </c>
       <c r="G8" t="n">
-        <v>2.307289370643916</v>
+        <v>2.307289370643918</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3193410670581</v>
+        <v>2.319341067058099</v>
       </c>
       <c r="I8" t="n">
         <v>2.266360023729647</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.891399616916602</v>
+        <v>2.891399616916603</v>
       </c>
       <c r="C9" t="n">
         <v>3.026180235009889</v>
@@ -1596,7 +1596,7 @@
         <v>2.753686773227019</v>
       </c>
       <c r="E9" t="n">
-        <v>2.924245870145234</v>
+        <v>2.924245870145233</v>
       </c>
       <c r="F9" t="n">
         <v>2.765823659733508</v>
@@ -1605,16 +1605,16 @@
         <v>2.80674363182291</v>
       </c>
       <c r="H9" t="n">
-        <v>2.818795328237065</v>
+        <v>2.818795328237064</v>
       </c>
       <c r="I9" t="n">
-        <v>2.765814284908639</v>
+        <v>2.76581428490864</v>
       </c>
       <c r="J9" t="n">
         <v>2.782334496384669</v>
       </c>
       <c r="K9" t="n">
-        <v>2.667902507474399</v>
+        <v>2.667902507474398</v>
       </c>
       <c r="L9" t="n">
         <v>2.916624779287036</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.925871330393241</v>
+        <v>2.429703053678421</v>
       </c>
       <c r="C2" t="n">
-        <v>6.911515666916994</v>
+        <v>2.43202835108421</v>
       </c>
       <c r="D2" t="n">
-        <v>6.507140994339605</v>
+        <v>2.407666107757353</v>
       </c>
       <c r="E2" t="n">
-        <v>6.515306940188</v>
+        <v>2.408864395475312</v>
       </c>
       <c r="F2" t="n">
-        <v>6.515306940188</v>
+        <v>2.408859840863781</v>
       </c>
       <c r="G2" t="n">
-        <v>6.574700962910765</v>
+        <v>2.411221654718347</v>
       </c>
       <c r="H2" t="n">
-        <v>6.586837308884091</v>
+        <v>2.411808917446671</v>
       </c>
       <c r="I2" t="n">
-        <v>6.514356149364061</v>
+        <v>2.408044893722706</v>
       </c>
       <c r="J2" t="n">
-        <v>6.543804988327399</v>
+        <v>2.418646366652476</v>
       </c>
       <c r="K2" t="n">
-        <v>6.497341341031915</v>
+        <v>2.413695319026635</v>
       </c>
       <c r="L2" t="n">
-        <v>6.691472606501716</v>
+        <v>2.417419273658469</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.180921897940681</v>
+        <v>2.582291885403675</v>
       </c>
       <c r="C3" t="n">
-        <v>7.16372852169367</v>
+        <v>2.580811829106532</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6992952717512</v>
+        <v>2.425066368786559</v>
       </c>
       <c r="E3" t="n">
-        <v>6.708542321671892</v>
+        <v>2.429121095424067</v>
       </c>
       <c r="F3" t="n">
-        <v>6.708542321671891</v>
+        <v>2.429116540812536</v>
       </c>
       <c r="G3" t="n">
-        <v>6.777003230613362</v>
+        <v>2.450460587794999</v>
       </c>
       <c r="H3" t="n">
-        <v>6.791104034157029</v>
+        <v>2.455234005600895</v>
       </c>
       <c r="I3" t="n">
-        <v>6.707666107174751</v>
+        <v>2.427777032096342</v>
       </c>
       <c r="J3" t="n">
-        <v>6.739722957872586</v>
+        <v>2.450490806726509</v>
       </c>
       <c r="K3" t="n">
-        <v>6.686762840602813</v>
+        <v>2.429783306484745</v>
       </c>
       <c r="L3" t="n">
-        <v>6.911316171329733</v>
+        <v>2.494920122639078</v>
       </c>
     </row>
     <row r="4">
@@ -1789,7 +1789,7 @@
         <v>2.360805144725701</v>
       </c>
       <c r="D4" t="n">
-        <v>2.120861674612752</v>
+        <v>2.120861674612753</v>
       </c>
       <c r="E4" t="n">
         <v>2.12803723717138</v>
@@ -1801,10 +1801,10 @@
         <v>2.161030710005164</v>
       </c>
       <c r="H4" t="n">
-        <v>2.168239430605013</v>
+        <v>2.168239430605014</v>
       </c>
       <c r="I4" t="n">
-        <v>2.125102865836663</v>
+        <v>2.125102865836664</v>
       </c>
       <c r="J4" t="n">
         <v>2.135756807777532</v>
@@ -1826,25 +1826,25 @@
         <v>7.076632138000154</v>
       </c>
       <c r="C5" t="n">
-        <v>6.869471219093692</v>
+        <v>6.869471219093696</v>
       </c>
       <c r="D5" t="n">
         <v>2.701719676498321</v>
       </c>
       <c r="E5" t="n">
-        <v>2.781120625817891</v>
+        <v>2.781120625817892</v>
       </c>
       <c r="F5" t="n">
-        <v>2.781120625817891</v>
+        <v>2.781120625817892</v>
       </c>
       <c r="G5" t="n">
-        <v>3.42143172602921</v>
+        <v>3.421431726029216</v>
       </c>
       <c r="H5" t="n">
-        <v>3.68661223811086</v>
+        <v>3.686612238110862</v>
       </c>
       <c r="I5" t="n">
-        <v>2.781112336728515</v>
+        <v>2.781112336728516</v>
       </c>
       <c r="J5" t="n">
         <v>2.998709820668611</v>
@@ -1853,7 +1853,7 @@
         <v>2.519617513543321</v>
       </c>
       <c r="L5" t="n">
-        <v>4.930781208543627</v>
+        <v>4.930781208543626</v>
       </c>
     </row>
     <row r="6">
@@ -1863,10 +1863,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.85718999095203</v>
+        <v>15.85718999095204</v>
       </c>
       <c r="C6" t="n">
-        <v>3.474625012261898</v>
+        <v>3.474625012261896</v>
       </c>
       <c r="D6" t="n">
         <v>15.60786731378191</v>
@@ -1878,7 +1878,7 @@
         <v>3.234434783003602</v>
       </c>
       <c r="G6" t="n">
-        <v>3.255469341240774</v>
+        <v>15.64844158467</v>
       </c>
       <c r="H6" t="n">
         <v>15.65589653707601</v>
@@ -1890,10 +1890,10 @@
         <v>3.231527730189529</v>
       </c>
       <c r="K6" t="n">
-        <v>3.187724775052752</v>
+        <v>3.187724775052751</v>
       </c>
       <c r="L6" t="n">
-        <v>3.324108056795769</v>
+        <v>3.32410805679577</v>
       </c>
     </row>
     <row r="7">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.430584176679461</v>
+        <v>2.430584176679462</v>
       </c>
       <c r="C7" t="n">
         <v>2.419735508671822</v>
@@ -1918,16 +1918,16 @@
         <v>2.186796669159091</v>
       </c>
       <c r="G7" t="n">
-        <v>2.221835770397431</v>
+        <v>2.221835770397432</v>
       </c>
       <c r="H7" t="n">
         <v>2.229044490997281</v>
       </c>
       <c r="I7" t="n">
-        <v>2.185907926228931</v>
+        <v>2.185907926228932</v>
       </c>
       <c r="J7" t="n">
-        <v>2.196561868169799</v>
+        <v>2.1965618681698</v>
       </c>
       <c r="K7" t="n">
         <v>2.170851533229178</v>
@@ -1946,7 +1946,7 @@
         <v>2.43972949519159</v>
       </c>
       <c r="C8" t="n">
-        <v>2.479480997573444</v>
+        <v>2.479480997573076</v>
       </c>
       <c r="D8" t="n">
         <v>2.250869960784965</v>
@@ -1961,7 +1961,7 @@
         <v>2.28072439716439</v>
       </c>
       <c r="H8" t="n">
-        <v>2.287933117764364</v>
+        <v>2.287933117764366</v>
       </c>
       <c r="I8" t="n">
         <v>2.24479655299589</v>
@@ -1970,7 +1970,7 @@
         <v>2.255460270905731</v>
       </c>
       <c r="K8" t="n">
-        <v>2.179072844253456</v>
+        <v>2.179072844253457</v>
       </c>
       <c r="L8" t="n">
         <v>2.402100580244728</v>
@@ -1992,28 +1992,28 @@
         <v>2.644623854513348</v>
       </c>
       <c r="E9" t="n">
-        <v>2.781898164411441</v>
+        <v>2.781898164411442</v>
       </c>
       <c r="F9" t="n">
-        <v>2.648873257357124</v>
+        <v>2.648873257357125</v>
       </c>
       <c r="G9" t="n">
-        <v>2.684792917525085</v>
+        <v>2.684792917525086</v>
       </c>
       <c r="H9" t="n">
-        <v>2.692001638124934</v>
+        <v>2.692001638124935</v>
       </c>
       <c r="I9" t="n">
         <v>2.648865073356585</v>
       </c>
       <c r="J9" t="n">
-        <v>2.659519015297453</v>
+        <v>2.659519015297454</v>
       </c>
       <c r="K9" t="n">
-        <v>2.567017854651286</v>
+        <v>2.567017854651287</v>
       </c>
       <c r="L9" t="n">
-        <v>2.754208055680172</v>
+        <v>2.754208055680174</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.885334228729078</v>
+        <v>2.424872235739061</v>
       </c>
       <c r="C2" t="n">
-        <v>6.860590935556651</v>
+        <v>2.426484632993257</v>
       </c>
       <c r="D2" t="n">
-        <v>6.496883386591977</v>
+        <v>2.404428839442901</v>
       </c>
       <c r="E2" t="n">
-        <v>6.495622747006122</v>
+        <v>2.405727611047464</v>
       </c>
       <c r="F2" t="n">
-        <v>6.495622747006122</v>
+        <v>2.405723053243396</v>
       </c>
       <c r="G2" t="n">
-        <v>6.552514848352312</v>
+        <v>2.407356612782365</v>
       </c>
       <c r="H2" t="n">
-        <v>6.555195072201269</v>
+        <v>2.407446362558005</v>
       </c>
       <c r="I2" t="n">
-        <v>6.493905822819513</v>
+        <v>2.404271241753335</v>
       </c>
       <c r="J2" t="n">
-        <v>6.520160597343116</v>
+        <v>2.415717508021113</v>
       </c>
       <c r="K2" t="n">
-        <v>6.486057019975298</v>
+        <v>2.411254217003547</v>
       </c>
       <c r="L2" t="n">
-        <v>6.623725646160929</v>
+        <v>2.41112650398895</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.134528486871743</v>
+        <v>2.565205451354521</v>
       </c>
       <c r="C3" t="n">
-        <v>7.10541626288827</v>
+        <v>2.55961994791106</v>
       </c>
       <c r="D3" t="n">
-        <v>6.687729551064547</v>
+        <v>2.419351943235239</v>
       </c>
       <c r="E3" t="n">
-        <v>6.686019107316027</v>
+        <v>2.420634499125598</v>
       </c>
       <c r="F3" t="n">
-        <v>6.686019107316027</v>
+        <v>2.420629941321527</v>
       </c>
       <c r="G3" t="n">
-        <v>6.751717256111517</v>
+        <v>2.440264051505318</v>
       </c>
       <c r="H3" t="n">
-        <v>6.754937834619509</v>
+        <v>2.441433257863088</v>
       </c>
       <c r="I3" t="n">
-        <v>6.684397947321231</v>
+        <v>2.418239023981103</v>
       </c>
       <c r="J3" t="n">
-        <v>6.712564535578373</v>
+        <v>2.44103450285164</v>
       </c>
       <c r="K3" t="n">
-        <v>6.673852406814401</v>
+        <v>2.424772709529432</v>
       </c>
       <c r="L3" t="n">
-        <v>6.833627875836017</v>
+        <v>2.467444442290749</v>
       </c>
     </row>
     <row r="4">
@@ -2203,7 +2203,7 @@
         <v>2.113002480405915</v>
       </c>
       <c r="J4" t="n">
-        <v>2.120980144506539</v>
+        <v>2.120980144506538</v>
       </c>
       <c r="K4" t="n">
         <v>2.10274140863073</v>
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.67627925516182</v>
+        <v>6.676279255161826</v>
       </c>
       <c r="C5" t="n">
-        <v>6.365246661559886</v>
+        <v>6.365246661559891</v>
       </c>
       <c r="D5" t="n">
-        <v>2.619084495479634</v>
+        <v>2.619084495479632</v>
       </c>
       <c r="E5" t="n">
-        <v>2.593723215872467</v>
+        <v>2.593723215872465</v>
       </c>
       <c r="F5" t="n">
-        <v>2.593723215872467</v>
+        <v>2.593723215872465</v>
       </c>
       <c r="G5" t="n">
-        <v>3.212521479244641</v>
+        <v>3.212521479244634</v>
       </c>
       <c r="H5" t="n">
-        <v>3.350482325884998</v>
+        <v>3.350482325884995</v>
       </c>
       <c r="I5" t="n">
         <v>2.59371516884741</v>
       </c>
       <c r="J5" t="n">
-        <v>2.756161965570945</v>
+        <v>2.756161965570944</v>
       </c>
       <c r="K5" t="n">
-        <v>2.415183340885743</v>
+        <v>2.41518334088574</v>
       </c>
       <c r="L5" t="n">
-        <v>4.169736480701032</v>
+        <v>4.16973648070103</v>
       </c>
     </row>
     <row r="6">
@@ -2262,16 +2262,16 @@
         <v>3.438905451893313</v>
       </c>
       <c r="C6" t="n">
-        <v>3.442747706821078</v>
+        <v>3.442747706821079</v>
       </c>
       <c r="D6" t="n">
-        <v>3.205944504159584</v>
+        <v>3.205944595173168</v>
       </c>
       <c r="E6" t="n">
-        <v>3.216654381918636</v>
+        <v>3.216654381918635</v>
       </c>
       <c r="F6" t="n">
-        <v>3.221169731909608</v>
+        <v>3.221169731909607</v>
       </c>
       <c r="G6" t="n">
         <v>15.63307040086132</v>
@@ -2280,7 +2280,7 @@
         <v>15.63534526090347</v>
       </c>
       <c r="I6" t="n">
-        <v>15.59817910034035</v>
+        <v>15.59817910034037</v>
       </c>
       <c r="J6" t="n">
         <v>15.60601907808969</v>
@@ -2302,16 +2302,16 @@
         <v>2.406202016315842</v>
       </c>
       <c r="C7" t="n">
-        <v>2.389306842355644</v>
+        <v>2.389306842355643</v>
       </c>
       <c r="D7" t="n">
-        <v>2.175279990250084</v>
+        <v>2.175279990250083</v>
       </c>
       <c r="E7" t="n">
-        <v>2.174519016510449</v>
+        <v>2.174519016510448</v>
       </c>
       <c r="F7" t="n">
-        <v>2.174519016510449</v>
+        <v>2.174519016510448</v>
       </c>
       <c r="G7" t="n">
         <v>2.208363109896308</v>
@@ -2342,19 +2342,19 @@
         <v>2.414989684304668</v>
       </c>
       <c r="C8" t="n">
-        <v>2.448488526307543</v>
+        <v>2.448488526308112</v>
       </c>
       <c r="D8" t="n">
         <v>2.243697508892748</v>
       </c>
       <c r="E8" t="n">
-        <v>2.219046973677456</v>
+        <v>2.219046973677454</v>
       </c>
       <c r="F8" t="n">
         <v>2.184455525308632</v>
       </c>
       <c r="G8" t="n">
-        <v>2.266535851366532</v>
+        <v>2.266535851366531</v>
       </c>
       <c r="H8" t="n">
         <v>2.26812482749878</v>
@@ -2363,13 +2363,13 @@
         <v>2.23164455084557</v>
       </c>
       <c r="J8" t="n">
-        <v>2.239631920508257</v>
+        <v>2.239631920508256</v>
       </c>
       <c r="K8" t="n">
-        <v>2.171081052495992</v>
+        <v>2.171081052495991</v>
       </c>
       <c r="L8" t="n">
-        <v>2.360462912251967</v>
+        <v>2.360462912251965</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.712570566116963</v>
+        <v>2.712570566116962</v>
       </c>
       <c r="C9" t="n">
-        <v>2.799467947977632</v>
+        <v>2.799467947977631</v>
       </c>
       <c r="D9" t="n">
-        <v>2.585445533032632</v>
+        <v>2.585445533032631</v>
       </c>
       <c r="E9" t="n">
-        <v>2.703415228552952</v>
+        <v>2.703415228552951</v>
       </c>
       <c r="F9" t="n">
-        <v>2.583640865178724</v>
+        <v>2.583640865178723</v>
       </c>
       <c r="G9" t="n">
-        <v>2.618524215518295</v>
+        <v>2.618524215518293</v>
       </c>
       <c r="H9" t="n">
         <v>2.620113191650306</v>
       </c>
       <c r="I9" t="n">
-        <v>2.583632914997331</v>
+        <v>2.58363291499733</v>
       </c>
       <c r="J9" t="n">
         <v>2.591610579097955</v>
       </c>
       <c r="K9" t="n">
-        <v>2.442678494580285</v>
+        <v>2.510794152398991</v>
       </c>
       <c r="L9" t="n">
-        <v>2.660864437657128</v>
+        <v>2.660864437657127</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.970095143568499</v>
+        <v>2.436095571205189</v>
       </c>
       <c r="C2" t="n">
-        <v>7.051477830862397</v>
+        <v>2.445578330922287</v>
       </c>
       <c r="D2" t="n">
-        <v>6.504161237759538</v>
+        <v>2.411574395161739</v>
       </c>
       <c r="E2" t="n">
-        <v>6.530618973265909</v>
+        <v>2.413613356853172</v>
       </c>
       <c r="F2" t="n">
-        <v>6.530618973265909</v>
+        <v>2.413608793022316</v>
       </c>
       <c r="G2" t="n">
-        <v>6.595051609198262</v>
+        <v>2.416357774887741</v>
       </c>
       <c r="H2" t="n">
-        <v>6.681341837976551</v>
+        <v>2.420885320331668</v>
       </c>
       <c r="I2" t="n">
-        <v>6.52982481266763</v>
+        <v>2.412924123154321</v>
       </c>
       <c r="J2" t="n">
-        <v>6.58346713817273</v>
+        <v>2.424492584258647</v>
       </c>
       <c r="K2" t="n">
-        <v>6.509727372826792</v>
+        <v>2.418580076234738</v>
       </c>
       <c r="L2" t="n">
-        <v>6.802793718100082</v>
+        <v>2.427406787479968</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.23169251171238</v>
+        <v>2.601473163426665</v>
       </c>
       <c r="C3" t="n">
-        <v>7.32421835430655</v>
+        <v>2.638612952274585</v>
       </c>
       <c r="D3" t="n">
-        <v>6.69577200211426</v>
+        <v>2.426530344560414</v>
       </c>
       <c r="E3" t="n">
-        <v>6.726082035653669</v>
+        <v>2.437287028732301</v>
       </c>
       <c r="F3" t="n">
-        <v>6.726082035653669</v>
+        <v>2.437282464901444</v>
       </c>
       <c r="G3" t="n">
-        <v>6.800314757152513</v>
+        <v>2.460678923087252</v>
       </c>
       <c r="H3" t="n">
-        <v>6.899712018863305</v>
+        <v>2.493490378152388</v>
       </c>
       <c r="I3" t="n">
-        <v>6.725415594706487</v>
+        <v>2.436158460221891</v>
       </c>
       <c r="J3" t="n">
-        <v>6.78530570487257</v>
+        <v>2.467581711601622</v>
       </c>
       <c r="K3" t="n">
-        <v>6.70088108631735</v>
+        <v>2.437222397435832</v>
       </c>
       <c r="L3" t="n">
-        <v>7.039257986338495</v>
+        <v>2.539590882877849</v>
       </c>
     </row>
     <row r="4">
@@ -2593,13 +2593,13 @@
         <v>2.17452330476832</v>
       </c>
       <c r="H4" t="n">
-        <v>2.225795732601954</v>
+        <v>2.225795732601955</v>
       </c>
       <c r="I4" t="n">
         <v>2.135694730874941</v>
       </c>
       <c r="J4" t="n">
-        <v>2.160962156507105</v>
+        <v>2.160962156507104</v>
       </c>
       <c r="K4" t="n">
         <v>2.118675937084995</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.795117343024327</v>
+        <v>7.795117343024321</v>
       </c>
       <c r="C5" t="n">
-        <v>8.590708112244627</v>
+        <v>8.590708112244631</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6746795043472</v>
+        <v>2.674679504347199</v>
       </c>
       <c r="E5" t="n">
-        <v>2.955773547518416</v>
+        <v>2.955773547518412</v>
       </c>
       <c r="F5" t="n">
-        <v>2.955773547518416</v>
+        <v>2.955773547518412</v>
       </c>
       <c r="G5" t="n">
-        <v>3.685707031104339</v>
+        <v>3.685707031104341</v>
       </c>
       <c r="H5" t="n">
-        <v>4.871388831375361</v>
+        <v>4.871388831375363</v>
       </c>
       <c r="I5" t="n">
-        <v>2.955764633834655</v>
+        <v>2.955764633834651</v>
       </c>
       <c r="J5" t="n">
-        <v>3.464957048836464</v>
+        <v>3.464957048836465</v>
       </c>
       <c r="K5" t="n">
-        <v>2.644540075657209</v>
+        <v>2.644540075657211</v>
       </c>
       <c r="L5" t="n">
-        <v>6.407775772253297</v>
+        <v>6.407775772253296</v>
       </c>
     </row>
     <row r="6">
@@ -2658,28 +2658,28 @@
         <v>3.555666440751517</v>
       </c>
       <c r="C6" t="n">
-        <v>3.624847362371365</v>
+        <v>3.624847362371366</v>
       </c>
       <c r="D6" t="n">
-        <v>3.275716053953643</v>
+        <v>3.275716177748025</v>
       </c>
       <c r="E6" t="n">
-        <v>3.304596951282578</v>
+        <v>3.304596951282577</v>
       </c>
       <c r="F6" t="n">
-        <v>3.30960124976442</v>
+        <v>3.309601249764419</v>
       </c>
       <c r="G6" t="n">
         <v>3.332727026883318</v>
       </c>
       <c r="H6" t="n">
-        <v>16.46960924782719</v>
+        <v>16.4696092478272</v>
       </c>
       <c r="I6" t="n">
-        <v>3.293898452989944</v>
+        <v>16.37973069382852</v>
       </c>
       <c r="J6" t="n">
-        <v>16.40469391202726</v>
+        <v>3.320681583701828</v>
       </c>
       <c r="K6" t="n">
         <v>3.258994097978229</v>
@@ -2698,7 +2698,7 @@
         <v>2.462315756034279</v>
       </c>
       <c r="C7" t="n">
-        <v>2.506788701260134</v>
+        <v>2.506788701260135</v>
       </c>
       <c r="D7" t="n">
         <v>2.18533322973042</v>
@@ -2710,19 +2710,19 @@
         <v>2.201877186057675</v>
       </c>
       <c r="G7" t="n">
-        <v>2.239376342166087</v>
+        <v>2.239376342166088</v>
       </c>
       <c r="H7" t="n">
-        <v>2.290648769999723</v>
+        <v>2.290648769999724</v>
       </c>
       <c r="I7" t="n">
         <v>2.200547768272709</v>
       </c>
       <c r="J7" t="n">
-        <v>2.225815193904872</v>
+        <v>2.225815193904873</v>
       </c>
       <c r="K7" t="n">
-        <v>2.183528974482763</v>
+        <v>2.183528974482764</v>
       </c>
       <c r="L7" t="n">
         <v>2.362848771536211</v>
@@ -2738,13 +2738,13 @@
         <v>2.472379494857007</v>
       </c>
       <c r="C8" t="n">
-        <v>2.571355503341479</v>
+        <v>2.571355503341743</v>
       </c>
       <c r="D8" t="n">
-        <v>2.259662947957855</v>
+        <v>2.259662947957856</v>
       </c>
       <c r="E8" t="n">
-        <v>2.250430779488785</v>
+        <v>2.250430779488786</v>
       </c>
       <c r="F8" t="n">
         <v>2.213098034196824</v>
@@ -2762,7 +2762,7 @@
         <v>2.289114282215621</v>
       </c>
       <c r="K8" t="n">
-        <v>2.192604033662931</v>
+        <v>2.192604033662932</v>
       </c>
       <c r="L8" t="n">
         <v>2.481735247087457</v>
@@ -2778,16 +2778,16 @@
         <v>2.884291890409524</v>
       </c>
       <c r="C9" t="n">
-        <v>3.06584767216974</v>
+        <v>3.065847672169741</v>
       </c>
       <c r="D9" t="n">
         <v>2.744396713251733</v>
       </c>
       <c r="E9" t="n">
-        <v>2.917806124571782</v>
+        <v>2.917806124571781</v>
       </c>
       <c r="F9" t="n">
-        <v>2.759615516989465</v>
+        <v>2.759615516989464</v>
       </c>
       <c r="G9" t="n">
         <v>2.798435313075692</v>
@@ -2796,13 +2796,13 @@
         <v>2.849707740909329</v>
       </c>
       <c r="I9" t="n">
-        <v>2.759606739182315</v>
+        <v>2.759606739182314</v>
       </c>
       <c r="J9" t="n">
         <v>2.784874164814477</v>
       </c>
       <c r="K9" t="n">
-        <v>2.569976197950409</v>
+        <v>2.663161590515864</v>
       </c>
       <c r="L9" t="n">
         <v>2.921907742445817</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.859616661830869</v>
+        <v>2.42506505576783</v>
       </c>
       <c r="C2" t="n">
-        <v>6.914738976881194</v>
+        <v>2.43190063503482</v>
       </c>
       <c r="D2" t="n">
-        <v>6.480451604497501</v>
+        <v>2.405110351882837</v>
       </c>
       <c r="E2" t="n">
-        <v>6.505222679226359</v>
+        <v>2.408314114952566</v>
       </c>
       <c r="F2" t="n">
-        <v>6.505222679226359</v>
+        <v>2.408309530369737</v>
       </c>
       <c r="G2" t="n">
-        <v>6.548717649896679</v>
+        <v>2.408703058264908</v>
       </c>
       <c r="H2" t="n">
-        <v>6.719344401963199</v>
+        <v>2.41773055061556</v>
       </c>
       <c r="I2" t="n">
-        <v>6.502816792281746</v>
+        <v>2.406286712627542</v>
       </c>
       <c r="J2" t="n">
-        <v>6.535368872036806</v>
+        <v>2.418433897446724</v>
       </c>
       <c r="K2" t="n">
-        <v>6.487379477657186</v>
+        <v>2.413829033118536</v>
       </c>
       <c r="L2" t="n">
-        <v>6.642618742560834</v>
+        <v>2.413684659717567</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.10495726755449</v>
+        <v>2.556551463040178</v>
       </c>
       <c r="C3" t="n">
-        <v>7.167519326877866</v>
+        <v>2.582235888268882</v>
       </c>
       <c r="D3" t="n">
-        <v>6.668838907816115</v>
+        <v>2.414194609284271</v>
       </c>
       <c r="E3" t="n">
-        <v>6.696967468059001</v>
+        <v>2.42592105364466</v>
       </c>
       <c r="F3" t="n">
-        <v>6.696967468059001</v>
+        <v>2.42591646906183</v>
       </c>
       <c r="G3" t="n">
-        <v>6.747359001293871</v>
+        <v>2.439839667112428</v>
       </c>
       <c r="H3" t="n">
-        <v>6.943753312619209</v>
+        <v>2.504439590573593</v>
       </c>
       <c r="I3" t="n">
-        <v>6.694746311023635</v>
+        <v>2.42258365878179</v>
       </c>
       <c r="J3" t="n">
-        <v>6.729995289357077</v>
+        <v>2.44822354039195</v>
       </c>
       <c r="K3" t="n">
-        <v>6.675198090938997</v>
+        <v>2.427498688554976</v>
       </c>
       <c r="L3" t="n">
-        <v>6.855366781315192</v>
+        <v>2.47559331704242</v>
       </c>
     </row>
     <row r="4">
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.397909966043914</v>
+        <v>6.397909966043917</v>
       </c>
       <c r="C5" t="n">
-        <v>6.902919362041216</v>
+        <v>6.902919362041221</v>
       </c>
       <c r="D5" t="n">
         <v>2.442922710462044</v>
@@ -3026,22 +3026,22 @@
         <v>2.674485411815575</v>
       </c>
       <c r="G5" t="n">
-        <v>3.162619667211971</v>
+        <v>3.162619667211974</v>
       </c>
       <c r="H5" t="n">
-        <v>5.205874707209419</v>
+        <v>5.205874707209412</v>
       </c>
       <c r="I5" t="n">
-        <v>2.674479180199197</v>
+        <v>2.674479180199205</v>
       </c>
       <c r="J5" t="n">
-        <v>2.901821529351125</v>
+        <v>2.901821529351124</v>
       </c>
       <c r="K5" t="n">
-        <v>2.405949868557119</v>
+        <v>2.405949868557118</v>
       </c>
       <c r="L5" t="n">
-        <v>4.376919711799776</v>
+        <v>4.376919711799777</v>
       </c>
     </row>
     <row r="6">
@@ -3057,28 +3057,28 @@
         <v>3.47688561048698</v>
       </c>
       <c r="D6" t="n">
-        <v>3.197437333859377</v>
+        <v>15.5917428621071</v>
       </c>
       <c r="E6" t="n">
-        <v>3.224012918995321</v>
+        <v>3.22401291899532</v>
       </c>
       <c r="F6" t="n">
-        <v>3.228312117898687</v>
+        <v>3.228312117898686</v>
       </c>
       <c r="G6" t="n">
-        <v>15.63243256427428</v>
+        <v>3.240358423457934</v>
       </c>
       <c r="H6" t="n">
         <v>15.73568065847047</v>
       </c>
       <c r="I6" t="n">
-        <v>15.60513768802992</v>
+        <v>15.60513768802993</v>
       </c>
       <c r="J6" t="n">
-        <v>3.22595144478697</v>
+        <v>15.61659708090971</v>
       </c>
       <c r="K6" t="n">
-        <v>3.181086446132742</v>
+        <v>3.181086446132741</v>
       </c>
       <c r="L6" t="n">
         <v>3.2954385080724</v>
@@ -3106,7 +3106,7 @@
         <v>2.1816311689615</v>
       </c>
       <c r="G7" t="n">
-        <v>2.20730384660147</v>
+        <v>2.207303846601471</v>
       </c>
       <c r="H7" t="n">
         <v>2.308683723092461</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.40073140365165</v>
+        <v>2.400731403651651</v>
       </c>
       <c r="C8" t="n">
-        <v>2.481844820681911</v>
+        <v>2.481844820681381</v>
       </c>
       <c r="D8" t="n">
         <v>2.235371244729372</v>
@@ -3146,7 +3146,7 @@
         <v>2.191184923397132</v>
       </c>
       <c r="G8" t="n">
-        <v>2.265656972361958</v>
+        <v>2.265656972361959</v>
       </c>
       <c r="H8" t="n">
         <v>2.367036848853354</v>
@@ -3155,7 +3155,7 @@
         <v>2.238362096117626</v>
       </c>
       <c r="J8" t="n">
-        <v>2.249761766855437</v>
+        <v>2.249761766855438</v>
       </c>
       <c r="K8" t="n">
         <v>2.172159512253663</v>
@@ -3177,19 +3177,19 @@
         <v>2.879324192714809</v>
       </c>
       <c r="D9" t="n">
-        <v>2.624099582076156</v>
+        <v>2.624099582076155</v>
       </c>
       <c r="E9" t="n">
         <v>2.769164381836672</v>
       </c>
       <c r="F9" t="n">
-        <v>2.637407671202744</v>
+        <v>2.637407671202743</v>
       </c>
       <c r="G9" t="n">
         <v>2.66469643687292</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76607631336391</v>
+        <v>2.766076313363909</v>
       </c>
       <c r="I9" t="n">
         <v>2.637401560628587</v>
@@ -3198,7 +3198,7 @@
         <v>2.648791458739922</v>
       </c>
       <c r="K9" t="n">
-        <v>2.478080928870821</v>
+        <v>2.555694897109829</v>
       </c>
       <c r="L9" t="n">
         <v>2.720512292714876</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.766127989767456</v>
+        <v>2.415886956756596</v>
       </c>
       <c r="C2" t="n">
-        <v>6.774784663640061</v>
+        <v>2.419071817731355</v>
       </c>
       <c r="D2" t="n">
-        <v>6.474994184473312</v>
+        <v>2.400565162822277</v>
       </c>
       <c r="E2" t="n">
-        <v>6.483416504105327</v>
+        <v>2.403961633038093</v>
       </c>
       <c r="F2" t="n">
-        <v>6.483416504105327</v>
+        <v>2.403957093233154</v>
       </c>
       <c r="G2" t="n">
-        <v>6.515837814519633</v>
+        <v>2.402714681949631</v>
       </c>
       <c r="H2" t="n">
-        <v>6.638222290695239</v>
+        <v>2.409183133484956</v>
       </c>
       <c r="I2" t="n">
-        <v>6.479657665212383</v>
+        <v>2.400809982188519</v>
       </c>
       <c r="J2" t="n">
-        <v>6.513289203952197</v>
+        <v>2.415127882075917</v>
       </c>
       <c r="K2" t="n">
-        <v>6.47553230034021</v>
+        <v>2.41007909932483</v>
       </c>
       <c r="L2" t="n">
-        <v>6.54216865662598</v>
+        <v>2.404095318572255</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.99808349336871</v>
+        <v>2.51823668150913</v>
       </c>
       <c r="C3" t="n">
-        <v>7.007435851644481</v>
+        <v>2.524963858743043</v>
       </c>
       <c r="D3" t="n">
-        <v>6.66321930909436</v>
+        <v>2.408929080735145</v>
       </c>
       <c r="E3" t="n">
-        <v>6.672340374820557</v>
+        <v>2.41587374241374</v>
       </c>
       <c r="F3" t="n">
-        <v>6.672340374820557</v>
+        <v>2.415869202608801</v>
       </c>
       <c r="G3" t="n">
-        <v>6.710197944380105</v>
+        <v>2.424279507881694</v>
       </c>
       <c r="H3" t="n">
-        <v>6.851101442407236</v>
+        <v>2.470609176990743</v>
       </c>
       <c r="I3" t="n">
-        <v>6.668708154873555</v>
+        <v>2.410679990227143</v>
       </c>
       <c r="J3" t="n">
-        <v>6.704849433062471</v>
+        <v>2.439415894349929</v>
       </c>
       <c r="K3" t="n">
-        <v>6.662010971955288</v>
+        <v>2.421287367016368</v>
       </c>
       <c r="L3" t="n">
-        <v>6.740488830244359</v>
+        <v>2.434407410443328</v>
       </c>
     </row>
     <row r="4">
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.277405737707265</v>
+        <v>2.277405737707266</v>
       </c>
       <c r="C4" t="n">
-        <v>2.28391385628848</v>
+        <v>2.283913856288481</v>
       </c>
       <c r="D4" t="n">
-        <v>2.104339026845691</v>
+        <v>2.104339026845692</v>
       </c>
       <c r="E4" t="n">
         <v>2.110973597773795</v>
@@ -3382,22 +3382,22 @@
         <v>2.110973597773795</v>
       </c>
       <c r="G4" t="n">
-        <v>2.128634697688072</v>
+        <v>2.128634697688081</v>
       </c>
       <c r="H4" t="n">
-        <v>2.201347266726589</v>
+        <v>2.201347266726588</v>
       </c>
       <c r="I4" t="n">
-        <v>2.107124697855573</v>
+        <v>2.107124697855572</v>
       </c>
       <c r="J4" t="n">
-        <v>2.117537987792066</v>
+        <v>2.117537987792067</v>
       </c>
       <c r="K4" t="n">
         <v>2.097427289868652</v>
       </c>
       <c r="L4" t="n">
-        <v>2.144296976202433</v>
+        <v>2.144296976202432</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.461816264612366</v>
+        <v>5.461816264612374</v>
       </c>
       <c r="C5" t="n">
-        <v>5.504832468397226</v>
+        <v>5.504832468397223</v>
       </c>
       <c r="D5" t="n">
         <v>2.424065660096847</v>
       </c>
       <c r="E5" t="n">
-        <v>2.474877399704606</v>
+        <v>2.474877399704611</v>
       </c>
       <c r="F5" t="n">
-        <v>2.474877399704606</v>
+        <v>2.474877399704611</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8582786732864</v>
+        <v>2.858278673286407</v>
       </c>
       <c r="H5" t="n">
         <v>4.324099382558485</v>
       </c>
       <c r="I5" t="n">
-        <v>2.474872450309386</v>
+        <v>2.474872450309392</v>
       </c>
       <c r="J5" t="n">
-        <v>2.676921187537767</v>
+        <v>2.676921187537765</v>
       </c>
       <c r="K5" t="n">
         <v>2.307480263820139</v>
       </c>
       <c r="L5" t="n">
-        <v>3.254238947216853</v>
+        <v>3.254238947216854</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.76048472740482</v>
+        <v>15.7604847274048</v>
       </c>
       <c r="C6" t="n">
         <v>3.392594635210383</v>
       </c>
       <c r="D6" t="n">
-        <v>3.194305861726631</v>
+        <v>3.19430586172663</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2099306373055</v>
+        <v>3.209930637305501</v>
       </c>
       <c r="F6" t="n">
         <v>3.214208734567899</v>
       </c>
       <c r="G6" t="n">
-        <v>15.61171368738564</v>
+        <v>15.61171368738566</v>
       </c>
       <c r="H6" t="n">
-        <v>15.68699262561247</v>
+        <v>3.292642752229205</v>
       </c>
       <c r="I6" t="n">
-        <v>3.198817435510513</v>
+        <v>15.59020368755314</v>
       </c>
       <c r="J6" t="n">
-        <v>15.600474320767</v>
+        <v>3.210878668465139</v>
       </c>
       <c r="K6" t="n">
-        <v>3.173128993781289</v>
+        <v>3.173128993781288</v>
       </c>
       <c r="L6" t="n">
         <v>3.235231702170027</v>
@@ -3502,19 +3502,19 @@
         <v>2.168576469129365</v>
       </c>
       <c r="G7" t="n">
-        <v>2.188917673581049</v>
+        <v>2.18891767358105</v>
       </c>
       <c r="H7" t="n">
-        <v>2.261630242619566</v>
+        <v>2.261630242619565</v>
       </c>
       <c r="I7" t="n">
-        <v>2.16740767374855</v>
+        <v>2.167407673748551</v>
       </c>
       <c r="J7" t="n">
         <v>2.177820963685044</v>
       </c>
       <c r="K7" t="n">
-        <v>2.15771026576163</v>
+        <v>2.157710265761628</v>
       </c>
       <c r="L7" t="n">
         <v>2.20457995209541</v>
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.346320687114932</v>
+        <v>2.346320687114931</v>
       </c>
       <c r="C8" t="n">
-        <v>2.400310654348508</v>
+        <v>2.400310654349605</v>
       </c>
       <c r="D8" t="n">
         <v>2.233326034392269</v>
@@ -3542,7 +3542,7 @@
         <v>2.178318995192905</v>
       </c>
       <c r="G8" t="n">
-        <v>2.247304675892573</v>
+        <v>2.247304675892574</v>
       </c>
       <c r="H8" t="n">
         <v>2.320017244931705</v>
@@ -3557,7 +3557,7 @@
         <v>2.165418014074707</v>
       </c>
       <c r="L8" t="n">
-        <v>2.314940242400555</v>
+        <v>2.314940242400554</v>
       </c>
     </row>
     <row r="9">
@@ -3570,31 +3570,31 @@
         <v>2.638148744756832</v>
       </c>
       <c r="C9" t="n">
-        <v>2.743617097994087</v>
+        <v>2.743617097994088</v>
       </c>
       <c r="D9" t="n">
-        <v>2.567444618038711</v>
+        <v>2.56744461803871</v>
       </c>
       <c r="E9" t="n">
         <v>2.688359408767508</v>
       </c>
       <c r="F9" t="n">
-        <v>2.570235173371338</v>
+        <v>2.570235173371339</v>
       </c>
       <c r="G9" t="n">
         <v>2.591740324742504</v>
       </c>
       <c r="H9" t="n">
-        <v>2.664452893781023</v>
+        <v>2.664452893781024</v>
       </c>
       <c r="I9" t="n">
-        <v>2.570230324910005</v>
+        <v>2.570230324910006</v>
       </c>
       <c r="J9" t="n">
         <v>2.580643614846497</v>
       </c>
       <c r="K9" t="n">
-        <v>2.498817345259346</v>
+        <v>2.501223597800107</v>
       </c>
       <c r="L9" t="n">
         <v>2.607402603256869</v>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.960973509632156</v>
+        <v>2.435696222050406</v>
       </c>
       <c r="C2" t="n">
-        <v>7.041156551097612</v>
+        <v>2.445652399701582</v>
       </c>
       <c r="D2" t="n">
-        <v>6.490193119586618</v>
+        <v>2.41091998516749</v>
       </c>
       <c r="E2" t="n">
-        <v>6.529432273248582</v>
+        <v>2.414056278081486</v>
       </c>
       <c r="F2" t="n">
-        <v>6.529432273248582</v>
+        <v>2.414051710658287</v>
       </c>
       <c r="G2" t="n">
-        <v>6.592564185747462</v>
+        <v>2.416307571054221</v>
       </c>
       <c r="H2" t="n">
-        <v>6.677738238429038</v>
+        <v>2.420776115424853</v>
       </c>
       <c r="I2" t="n">
-        <v>6.528092991026989</v>
+        <v>2.412913730033591</v>
       </c>
       <c r="J2" t="n">
-        <v>6.564310945516738</v>
+        <v>2.424029665098462</v>
       </c>
       <c r="K2" t="n">
-        <v>6.504323449675639</v>
+        <v>2.418936457689208</v>
       </c>
       <c r="L2" t="n">
-        <v>6.818094847103302</v>
+        <v>2.428306227277545</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.221334791311013</v>
+        <v>2.597884314798709</v>
       </c>
       <c r="C3" t="n">
-        <v>7.312376163046432</v>
+        <v>2.635263492737006</v>
       </c>
       <c r="D3" t="n">
-        <v>6.679839820894643</v>
+        <v>2.421130322964121</v>
       </c>
       <c r="E3" t="n">
-        <v>6.724769379933313</v>
+        <v>2.437221514053182</v>
       </c>
       <c r="F3" t="n">
-        <v>6.72476937993331</v>
+        <v>2.43721694662998</v>
       </c>
       <c r="G3" t="n">
-        <v>6.797587753082084</v>
+        <v>2.459580783933872</v>
       </c>
       <c r="H3" t="n">
-        <v>6.895700596519558</v>
+        <v>2.491966594886512</v>
       </c>
       <c r="I3" t="n">
-        <v>6.723586569593985</v>
+        <v>2.435344850544672</v>
       </c>
       <c r="J3" t="n">
-        <v>6.763316677783257</v>
+        <v>2.460813171007849</v>
       </c>
       <c r="K3" t="n">
-        <v>6.694691612229247</v>
+        <v>2.435749611098063</v>
       </c>
       <c r="L3" t="n">
-        <v>7.056990488589354</v>
+        <v>2.545217186801176</v>
       </c>
     </row>
     <row r="4">
@@ -3763,13 +3763,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.392250140087168</v>
+        <v>2.392250140087169</v>
       </c>
       <c r="C4" t="n">
         <v>2.438266382212747</v>
       </c>
       <c r="D4" t="n">
-        <v>2.112391146862418</v>
+        <v>2.11239114686242</v>
       </c>
       <c r="E4" t="n">
         <v>2.140198260997822</v>
@@ -3778,22 +3778,22 @@
         <v>2.140198260997822</v>
       </c>
       <c r="G4" t="n">
-        <v>2.173255545631184</v>
+        <v>2.173255545631185</v>
       </c>
       <c r="H4" t="n">
-        <v>2.223863672815862</v>
+        <v>2.223863672815863</v>
       </c>
       <c r="I4" t="n">
         <v>2.134881976233304</v>
       </c>
       <c r="J4" t="n">
-        <v>2.149430311457157</v>
+        <v>2.149430311457158</v>
       </c>
       <c r="K4" t="n">
-        <v>2.115246391378895</v>
+        <v>2.115246391378896</v>
       </c>
       <c r="L4" t="n">
-        <v>2.307297284296598</v>
+        <v>2.307297284296599</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.696727988430064</v>
+        <v>7.696727988430067</v>
       </c>
       <c r="C5" t="n">
-        <v>8.4721424217283</v>
+        <v>8.472142421728293</v>
       </c>
       <c r="D5" t="n">
         <v>2.527691756483934</v>
       </c>
       <c r="E5" t="n">
-        <v>2.938768566535492</v>
+        <v>2.938768566535464</v>
       </c>
       <c r="F5" t="n">
-        <v>2.938768566535492</v>
+        <v>2.938768566535464</v>
       </c>
       <c r="G5" t="n">
-        <v>3.660107034477641</v>
+        <v>3.660107034477631</v>
       </c>
       <c r="H5" t="n">
-        <v>4.829997365368806</v>
+        <v>4.82999736536881</v>
       </c>
       <c r="I5" t="n">
-        <v>2.93875976648366</v>
+        <v>2.93875976648364</v>
       </c>
       <c r="J5" t="n">
-        <v>3.245965980763438</v>
+        <v>3.245965980763436</v>
       </c>
       <c r="K5" t="n">
-        <v>2.580738855835147</v>
+        <v>2.580738855835148</v>
       </c>
       <c r="L5" t="n">
-        <v>6.596312390751208</v>
+        <v>6.59631239075121</v>
       </c>
     </row>
     <row r="6">
@@ -3843,31 +3843,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.550159637346336</v>
+        <v>3.55015963734634</v>
       </c>
       <c r="C6" t="n">
         <v>3.618046420723904</v>
       </c>
       <c r="D6" t="n">
-        <v>3.267108779642359</v>
+        <v>3.267108779642361</v>
       </c>
       <c r="E6" t="n">
-        <v>3.303640691009842</v>
+        <v>3.303640691009841</v>
       </c>
       <c r="F6" t="n">
-        <v>3.308566214445919</v>
+        <v>3.308566214445918</v>
       </c>
       <c r="G6" t="n">
-        <v>16.41720605971867</v>
+        <v>3.331165042890357</v>
       </c>
       <c r="H6" t="n">
-        <v>16.46759723255743</v>
+        <v>16.46759723255742</v>
       </c>
       <c r="I6" t="n">
-        <v>16.37883249032079</v>
+        <v>3.29279147349247</v>
       </c>
       <c r="J6" t="n">
-        <v>16.39313537965096</v>
+        <v>3.308811601258104</v>
       </c>
       <c r="K6" t="n">
         <v>3.255205377713696</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.457414302250193</v>
+        <v>2.457414302250194</v>
       </c>
       <c r="C7" t="n">
         <v>2.500764838559817</v>
@@ -3898,10 +3898,10 @@
         <v>2.20158658967591</v>
       </c>
       <c r="G7" t="n">
-        <v>2.238419707794209</v>
+        <v>2.23841970779421</v>
       </c>
       <c r="H7" t="n">
-        <v>2.289027834978886</v>
+        <v>2.289027834978887</v>
       </c>
       <c r="I7" t="n">
         <v>2.200046138396328</v>
@@ -3926,10 +3926,10 @@
         <v>2.46755537110545</v>
       </c>
       <c r="C8" t="n">
-        <v>2.566000063913874</v>
+        <v>2.566000063913605</v>
       </c>
       <c r="D8" t="n">
-        <v>2.252427816118196</v>
+        <v>2.252427816118197</v>
       </c>
       <c r="E8" t="n">
         <v>2.250469720013223</v>
@@ -3947,13 +3947,13 @@
         <v>2.263801394500477</v>
       </c>
       <c r="J8" t="n">
-        <v>2.278360266429243</v>
+        <v>2.278360266429246</v>
       </c>
       <c r="K8" t="n">
         <v>2.189555711345369</v>
       </c>
       <c r="L8" t="n">
-        <v>2.49222120427259</v>
+        <v>2.492221204272589</v>
       </c>
     </row>
     <row r="9">
@@ -3963,13 +3963,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.87875826118906</v>
+        <v>2.878758261189061</v>
       </c>
       <c r="C9" t="n">
         <v>3.059164859425573</v>
       </c>
       <c r="D9" t="n">
-        <v>2.735955280497782</v>
+        <v>2.735955280497784</v>
       </c>
       <c r="E9" t="n">
         <v>2.916614535598695</v>
@@ -3978,10 +3978,10 @@
         <v>2.758454824537568</v>
       </c>
       <c r="G9" t="n">
-        <v>2.796819728659967</v>
+        <v>2.796819728659968</v>
       </c>
       <c r="H9" t="n">
-        <v>2.847427855844643</v>
+        <v>2.847427855844644</v>
       </c>
       <c r="I9" t="n">
         <v>2.758446159262083</v>
@@ -3990,10 +3990,10 @@
         <v>2.772994494485939</v>
       </c>
       <c r="K9" t="n">
-        <v>2.659399733091905</v>
+        <v>2.659399733091907</v>
       </c>
       <c r="L9" t="n">
-        <v>2.930861467325378</v>
+        <v>2.93086146732538</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.831843648859834</v>
+        <v>2.423058648994835</v>
       </c>
       <c r="C2" t="n">
-        <v>6.889428674804726</v>
+        <v>2.431936890360708</v>
       </c>
       <c r="D2" t="n">
-        <v>6.482133424369983</v>
+        <v>2.404654094460386</v>
       </c>
       <c r="E2" t="n">
-        <v>6.50266141986815</v>
+        <v>2.409699964520145</v>
       </c>
       <c r="F2" t="n">
-        <v>6.50266141986815</v>
+        <v>2.409695375740845</v>
       </c>
       <c r="G2" t="n">
-        <v>6.546314061514162</v>
+        <v>2.408031793920271</v>
       </c>
       <c r="H2" t="n">
-        <v>6.692411405916043</v>
+        <v>2.415753788502832</v>
       </c>
       <c r="I2" t="n">
-        <v>6.497606397626091</v>
+        <v>2.405467773856385</v>
       </c>
       <c r="J2" t="n">
-        <v>6.534752618419953</v>
+        <v>2.420054110781892</v>
       </c>
       <c r="K2" t="n">
-        <v>6.489196319474838</v>
+        <v>2.416077160004444</v>
       </c>
       <c r="L2" t="n">
-        <v>6.65376795586378</v>
+        <v>2.413736529645053</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.073585816213031</v>
+        <v>2.544171420452686</v>
       </c>
       <c r="C3" t="n">
-        <v>7.138608096926845</v>
+        <v>2.573239021853729</v>
       </c>
       <c r="D3" t="n">
-        <v>6.67134661579494</v>
+        <v>2.412870375470256</v>
       </c>
       <c r="E3" t="n">
-        <v>6.694196957390958</v>
+        <v>2.425652321581209</v>
       </c>
       <c r="F3" t="n">
-        <v>6.694196957390958</v>
+        <v>2.425647732801909</v>
       </c>
       <c r="G3" t="n">
-        <v>6.74516764348968</v>
+        <v>2.436983888446965</v>
       </c>
       <c r="H3" t="n">
-        <v>6.913348334037714</v>
+        <v>2.492317120678585</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6893761106149</v>
+        <v>2.418675778016286</v>
       </c>
       <c r="J3" t="n">
-        <v>6.729436433311216</v>
+        <v>2.448852241236339</v>
       </c>
       <c r="K3" t="n">
-        <v>6.677341506185445</v>
+        <v>2.429681375347492</v>
       </c>
       <c r="L3" t="n">
-        <v>6.868763261871369</v>
+        <v>2.477863472397248</v>
       </c>
     </row>
     <row r="4">
@@ -4202,10 +4202,10 @@
         <v>6.1281307487821</v>
       </c>
       <c r="C5" t="n">
-        <v>6.634426570870446</v>
+        <v>6.63442657087044</v>
       </c>
       <c r="D5" t="n">
-        <v>2.478848291248541</v>
+        <v>2.478848291248539</v>
       </c>
       <c r="E5" t="n">
         <v>2.640453346947315</v>
@@ -4214,19 +4214,19 @@
         <v>2.640453346947315</v>
       </c>
       <c r="G5" t="n">
-        <v>3.157130257645744</v>
+        <v>3.157130257645734</v>
       </c>
       <c r="H5" t="n">
-        <v>4.920937101942997</v>
+        <v>4.920937101942995</v>
       </c>
       <c r="I5" t="n">
-        <v>2.640446706225557</v>
+        <v>2.640446706225558</v>
       </c>
       <c r="J5" t="n">
         <v>2.885289965819871</v>
       </c>
       <c r="K5" t="n">
-        <v>2.408298409607194</v>
+        <v>2.408298409607193</v>
       </c>
       <c r="L5" t="n">
         <v>4.527958194578241</v>
@@ -4239,13 +4239,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.409226500413517</v>
+        <v>15.80141336850395</v>
       </c>
       <c r="C6" t="n">
         <v>3.46044971051235</v>
       </c>
       <c r="D6" t="n">
-        <v>3.199153385899486</v>
+        <v>3.199153295654212</v>
       </c>
       <c r="E6" t="n">
         <v>3.221686123162881</v>
@@ -4254,19 +4254,19 @@
         <v>3.225934015890054</v>
       </c>
       <c r="G6" t="n">
-        <v>3.239506370775768</v>
+        <v>3.239506370775767</v>
       </c>
       <c r="H6" t="n">
-        <v>15.72025419651757</v>
+        <v>15.72025419651755</v>
       </c>
       <c r="I6" t="n">
-        <v>15.60272679771888</v>
+        <v>15.6027267977189</v>
       </c>
       <c r="J6" t="n">
-        <v>15.61537826299657</v>
+        <v>3.224565278006599</v>
       </c>
       <c r="K6" t="n">
-        <v>3.180819589056127</v>
+        <v>3.180819589056128</v>
       </c>
       <c r="L6" t="n">
         <v>3.302760543445206</v>
@@ -4294,7 +4294,7 @@
         <v>2.180086815861943</v>
       </c>
       <c r="G7" t="n">
-        <v>2.207078690264541</v>
+        <v>2.20707869026454</v>
       </c>
       <c r="H7" t="n">
         <v>2.293883014513645</v>
@@ -4309,7 +4309,7 @@
         <v>2.164684190021685</v>
       </c>
       <c r="L7" t="n">
-        <v>2.27094844213766</v>
+        <v>2.270948442137659</v>
       </c>
     </row>
     <row r="8">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.385443978807953</v>
+        <v>2.385443978807952</v>
       </c>
       <c r="C8" t="n">
         <v>2.467330089349349</v>
@@ -4331,25 +4331,25 @@
         <v>2.224902598737027</v>
       </c>
       <c r="F8" t="n">
-        <v>2.189530668888192</v>
+        <v>2.189530668888191</v>
       </c>
       <c r="G8" t="n">
-        <v>2.265886910122259</v>
+        <v>2.265886910122258</v>
       </c>
       <c r="H8" t="n">
-        <v>2.352691234371708</v>
+        <v>2.352691234371707</v>
       </c>
       <c r="I8" t="n">
         <v>2.236920468974956</v>
       </c>
       <c r="J8" t="n">
-        <v>2.249379447978269</v>
+        <v>2.249379447978268</v>
       </c>
       <c r="K8" t="n">
         <v>2.172397544318667</v>
       </c>
       <c r="L8" t="n">
-        <v>2.382156173704802</v>
+        <v>2.382156173704801</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.719755249316241</v>
+        <v>2.71975524931624</v>
       </c>
       <c r="C9" t="n">
-        <v>2.86387124170795</v>
+        <v>2.863871241707949</v>
       </c>
       <c r="D9" t="n">
-        <v>2.626156469121113</v>
+        <v>2.626156469121111</v>
       </c>
       <c r="E9" t="n">
-        <v>2.76725159232883</v>
+        <v>2.767251592328828</v>
       </c>
       <c r="F9" t="n">
-        <v>2.635364377709943</v>
+        <v>2.635364377709942</v>
       </c>
       <c r="G9" t="n">
-        <v>2.664324294149326</v>
+        <v>2.664324294149324</v>
       </c>
       <c r="H9" t="n">
-        <v>2.751128618398429</v>
+        <v>2.751128618398428</v>
       </c>
       <c r="I9" t="n">
-        <v>2.635357853002023</v>
+        <v>2.635357853002021</v>
       </c>
       <c r="J9" t="n">
-        <v>2.64780697355052</v>
+        <v>2.647806973550518</v>
       </c>
       <c r="K9" t="n">
-        <v>2.555710178575134</v>
+        <v>2.478019334283875</v>
       </c>
       <c r="L9" t="n">
-        <v>2.728194046022444</v>
+        <v>2.728194046022442</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.77287225692178</v>
+        <v>2.419283214966139</v>
       </c>
       <c r="C2" t="n">
-        <v>6.795101842256027</v>
+        <v>2.423936443758433</v>
       </c>
       <c r="D2" t="n">
-        <v>6.481266650802941</v>
+        <v>2.403936591091489</v>
       </c>
       <c r="E2" t="n">
-        <v>6.483525839735821</v>
+        <v>2.406631352319659</v>
       </c>
       <c r="F2" t="n">
-        <v>6.483525839735821</v>
+        <v>2.406626789024841</v>
       </c>
       <c r="G2" t="n">
-        <v>6.521084302216748</v>
+        <v>2.406032115001172</v>
       </c>
       <c r="H2" t="n">
-        <v>6.631884399893028</v>
+        <v>2.411882801888741</v>
       </c>
       <c r="I2" t="n">
-        <v>6.480251614211048</v>
+        <v>2.403882539660569</v>
       </c>
       <c r="J2" t="n">
-        <v>6.514125210809934</v>
+        <v>2.417455765026009</v>
       </c>
       <c r="K2" t="n">
-        <v>6.479451620098476</v>
+        <v>2.413352264059838</v>
       </c>
       <c r="L2" t="n">
-        <v>6.560362691012197</v>
+        <v>2.408103373225098</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.006103911560329</v>
+        <v>2.521453765428408</v>
       </c>
       <c r="C3" t="n">
-        <v>7.030918392043924</v>
+        <v>2.534238375461445</v>
       </c>
       <c r="D3" t="n">
-        <v>6.670697058604335</v>
+        <v>2.411965875886249</v>
       </c>
       <c r="E3" t="n">
-        <v>6.672801977771634</v>
+        <v>2.416116853307891</v>
       </c>
       <c r="F3" t="n">
-        <v>6.672801977771634</v>
+        <v>2.416112290013073</v>
       </c>
       <c r="G3" t="n">
-        <v>6.716495605931855</v>
+        <v>2.426934241925547</v>
       </c>
       <c r="H3" t="n">
-        <v>6.844073844365798</v>
+        <v>2.468895384123653</v>
       </c>
       <c r="I3" t="n">
-        <v>6.669696669738132</v>
+        <v>2.411588186731887</v>
       </c>
       <c r="J3" t="n">
-        <v>6.70622003816713</v>
+        <v>2.43944545477611</v>
       </c>
       <c r="K3" t="n">
-        <v>6.666777188203091</v>
+        <v>2.423475177322054</v>
       </c>
       <c r="L3" t="n">
-        <v>6.761678542652779</v>
+        <v>2.441970429399995</v>
       </c>
     </row>
     <row r="4">
@@ -4561,7 +4561,7 @@
         <v>2.29337965784965</v>
       </c>
       <c r="D4" t="n">
-        <v>2.106882287819736</v>
+        <v>2.106882287819737</v>
       </c>
       <c r="E4" t="n">
         <v>2.111203984474094</v>
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.52367663456896</v>
+        <v>5.523676634568957</v>
       </c>
       <c r="C5" t="n">
-        <v>5.697260501205013</v>
+        <v>5.697260501205015</v>
       </c>
       <c r="D5" t="n">
-        <v>2.479371346442471</v>
+        <v>2.479371346442469</v>
       </c>
       <c r="E5" t="n">
-        <v>2.472764148323872</v>
+        <v>2.472764148323873</v>
       </c>
       <c r="F5" t="n">
-        <v>2.472764148323872</v>
+        <v>2.472764148323873</v>
       </c>
       <c r="G5" t="n">
-        <v>2.904507187230187</v>
+        <v>2.904507187230185</v>
       </c>
       <c r="H5" t="n">
-        <v>4.243002119808069</v>
+        <v>4.243002119808064</v>
       </c>
       <c r="I5" t="n">
-        <v>2.47275854397474</v>
+        <v>2.472758543974739</v>
       </c>
       <c r="J5" t="n">
         <v>2.687642340404494</v>
       </c>
       <c r="K5" t="n">
-        <v>2.338802972997007</v>
+        <v>2.338802972997008</v>
       </c>
       <c r="L5" t="n">
-        <v>3.455949825537832</v>
+        <v>3.455949825537834</v>
       </c>
     </row>
     <row r="6">
@@ -4635,13 +4635,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.372211225835743</v>
+        <v>15.76340940247578</v>
       </c>
       <c r="C6" t="n">
-        <v>3.403297193389036</v>
+        <v>3.403297193389037</v>
       </c>
       <c r="D6" t="n">
-        <v>3.197210914855931</v>
+        <v>3.197210987191291</v>
       </c>
       <c r="E6" t="n">
         <v>3.209456422870184</v>
@@ -4650,22 +4650,22 @@
         <v>3.213687035140568</v>
       </c>
       <c r="G6" t="n">
-        <v>15.61374495876146</v>
+        <v>3.222546782121439</v>
       </c>
       <c r="H6" t="n">
-        <v>15.68161896910052</v>
+        <v>15.68161896910051</v>
       </c>
       <c r="I6" t="n">
-        <v>15.58945068926357</v>
+        <v>3.198252512623561</v>
       </c>
       <c r="J6" t="n">
-        <v>3.21102851475545</v>
+        <v>15.60057835807228</v>
       </c>
       <c r="K6" t="n">
         <v>3.174614169109554</v>
       </c>
       <c r="L6" t="n">
-        <v>3.245224001132138</v>
+        <v>3.245224001132139</v>
       </c>
     </row>
     <row r="7">
@@ -4684,22 +4684,22 @@
         <v>2.167368920125701</v>
       </c>
       <c r="E7" t="n">
-        <v>2.168253364570154</v>
+        <v>2.168253364570155</v>
       </c>
       <c r="F7" t="n">
-        <v>2.168253364570154</v>
+        <v>2.168253364570155</v>
       </c>
       <c r="G7" t="n">
         <v>2.191056443270408</v>
       </c>
       <c r="H7" t="n">
-        <v>2.256888459481514</v>
+        <v>2.256888459481515</v>
       </c>
       <c r="I7" t="n">
         <v>2.166762173772529</v>
       </c>
       <c r="J7" t="n">
-        <v>2.177918378548021</v>
+        <v>2.177918378548022</v>
       </c>
       <c r="K7" t="n">
         <v>2.159043627600545</v>
@@ -4718,7 +4718,7 @@
         <v>2.349012878801257</v>
       </c>
       <c r="C8" t="n">
-        <v>2.410521933930923</v>
+        <v>2.410521933929985</v>
       </c>
       <c r="D8" t="n">
         <v>2.235393925503275</v>
@@ -4730,22 +4730,22 @@
         <v>2.177516982481517</v>
       </c>
       <c r="G8" t="n">
-        <v>2.248818680579674</v>
+        <v>2.248818680579675</v>
       </c>
       <c r="H8" t="n">
-        <v>2.314650696791298</v>
+        <v>2.314650696791299</v>
       </c>
       <c r="I8" t="n">
         <v>2.224524411081796</v>
       </c>
       <c r="J8" t="n">
-        <v>2.235690338147964</v>
+        <v>2.235690338147965</v>
       </c>
       <c r="K8" t="n">
         <v>2.166416684211393</v>
       </c>
       <c r="L8" t="n">
-        <v>2.323853660589579</v>
+        <v>2.32385366058958</v>
       </c>
     </row>
     <row r="9">
@@ -4755,13 +4755,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.641958101390056</v>
+        <v>2.641958101390057</v>
       </c>
       <c r="C9" t="n">
-        <v>2.755108128642637</v>
+        <v>2.755108128642638</v>
       </c>
       <c r="D9" t="n">
-        <v>2.571158513765361</v>
+        <v>2.571158513765362</v>
       </c>
       <c r="E9" t="n">
         <v>2.688890241957515</v>
@@ -4776,7 +4776,7 @@
         <v>2.660673298644889</v>
       </c>
       <c r="I9" t="n">
-        <v>2.570547012935906</v>
+        <v>2.570547012935905</v>
       </c>
       <c r="J9" t="n">
         <v>2.581703217711399</v>
@@ -4785,7 +4785,7 @@
         <v>2.501001353660921</v>
       </c>
       <c r="L9" t="n">
-        <v>2.618200454418817</v>
+        <v>2.618200454418818</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.48274277388511</v>
+        <v>2.39827632449968</v>
       </c>
       <c r="C2" t="n">
-        <v>6.656480037472093</v>
+        <v>2.424153388726872</v>
       </c>
       <c r="D2" t="n">
-        <v>6.533057525924829</v>
+        <v>2.400924289966384</v>
       </c>
       <c r="E2" t="n">
-        <v>6.661418669739065</v>
+        <v>2.428553727842743</v>
       </c>
       <c r="F2" t="n">
-        <v>6.645681762327516</v>
+        <v>2.415450281306107</v>
       </c>
       <c r="G2" t="n">
-        <v>6.622263689895372</v>
+        <v>2.405619033198441</v>
       </c>
       <c r="H2" t="n">
-        <v>6.634857325510506</v>
+        <v>2.40621518829122</v>
       </c>
       <c r="I2" t="n">
-        <v>6.634671395980721</v>
+        <v>2.406271635964151</v>
       </c>
       <c r="J2" t="n">
-        <v>6.605936118631112</v>
+        <v>2.438639497346715</v>
       </c>
       <c r="K2" t="n">
-        <v>6.544793981819989</v>
+        <v>2.419605253766588</v>
       </c>
       <c r="L2" t="n">
-        <v>6.505383468792633</v>
+        <v>2.399336902592728</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.671986990341714</v>
+        <v>2.405515217827778</v>
       </c>
       <c r="C3" t="n">
-        <v>6.868485331969246</v>
+        <v>2.491957849706884</v>
       </c>
       <c r="D3" t="n">
-        <v>6.729859377856878</v>
+        <v>2.42437269532331</v>
       </c>
       <c r="E3" t="n">
-        <v>6.873482537856886</v>
+        <v>2.499037451712436</v>
       </c>
       <c r="F3" t="n">
-        <v>6.857745630445335</v>
+        <v>2.477410758839887</v>
       </c>
       <c r="G3" t="n">
-        <v>6.832464945424198</v>
+        <v>2.457860430117215</v>
       </c>
       <c r="H3" t="n">
-        <v>6.847091673517507</v>
+        <v>2.462904740662428</v>
       </c>
       <c r="I3" t="n">
-        <v>6.84672848494363</v>
+        <v>2.462264787776556</v>
       </c>
       <c r="J3" t="n">
-        <v>6.807158358390695</v>
+        <v>2.495237908693643</v>
       </c>
       <c r="K3" t="n">
-        <v>6.739879071728489</v>
+        <v>2.451922791686994</v>
       </c>
       <c r="L3" t="n">
-        <v>6.69804249698907</v>
+        <v>2.414130697316518</v>
       </c>
     </row>
     <row r="4">
@@ -4951,19 +4951,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.114762697201099</v>
+        <v>2.1147626972011</v>
       </c>
       <c r="C4" t="n">
-        <v>2.20544867570852</v>
+        <v>2.205448675708519</v>
       </c>
       <c r="D4" t="n">
         <v>2.144672685271816</v>
       </c>
       <c r="E4" t="n">
-        <v>2.20557006913461</v>
+        <v>2.205570069134609</v>
       </c>
       <c r="F4" t="n">
-        <v>2.20557006913461</v>
+        <v>2.205570069134609</v>
       </c>
       <c r="G4" t="n">
         <v>2.197732270339194</v>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.567329688706049</v>
+        <v>2.567329688706055</v>
       </c>
       <c r="C5" t="n">
-        <v>4.100755769246889</v>
+        <v>4.100755769246883</v>
       </c>
       <c r="D5" t="n">
-        <v>3.109960286695349</v>
+        <v>3.109960286695348</v>
       </c>
       <c r="E5" t="n">
-        <v>4.100755770544967</v>
+        <v>4.100755770544962</v>
       </c>
       <c r="F5" t="n">
-        <v>4.100755770544967</v>
+        <v>4.100755770544962</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1021621371293</v>
+        <v>4.102162137129291</v>
       </c>
       <c r="H5" t="n">
-        <v>4.454925859555992</v>
+        <v>4.454925859555994</v>
       </c>
       <c r="I5" t="n">
-        <v>4.10075723629939</v>
+        <v>4.100757236299387</v>
       </c>
       <c r="J5" t="n">
-        <v>3.503160131655608</v>
+        <v>3.503160131655607</v>
       </c>
       <c r="K5" t="n">
-        <v>2.989171439185711</v>
+        <v>2.989171439185714</v>
       </c>
       <c r="L5" t="n">
-        <v>8.325178311757268</v>
+        <v>8.325178311757261</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.58839567329868</v>
+        <v>3.288363948118211</v>
       </c>
       <c r="C6" t="n">
-        <v>3.394235947584551</v>
+        <v>3.39423594758455</v>
       </c>
       <c r="D6" t="n">
-        <v>3.314440973414808</v>
+        <v>3.31444081229272</v>
       </c>
       <c r="E6" t="n">
-        <v>3.390222219120718</v>
+        <v>3.390222219120717</v>
       </c>
       <c r="F6" t="n">
-        <v>3.394086114564105</v>
+        <v>3.394086114564104</v>
       </c>
       <c r="G6" t="n">
-        <v>16.67136524643676</v>
+        <v>3.371333521256303</v>
       </c>
       <c r="H6" t="n">
-        <v>16.67692163721</v>
+        <v>16.67692163720999</v>
       </c>
       <c r="I6" t="n">
         <v>16.67882696823526</v>
       </c>
       <c r="J6" t="n">
-        <v>16.63442973957541</v>
+        <v>3.336189760848204</v>
       </c>
       <c r="K6" t="n">
-        <v>3.292153766882871</v>
+        <v>3.29215376688287</v>
       </c>
       <c r="L6" t="n">
-        <v>3.299418899915987</v>
+        <v>3.299418899915988</v>
       </c>
     </row>
     <row r="7">
@@ -5074,16 +5074,16 @@
         <v>2.181218309902455</v>
       </c>
       <c r="C7" t="n">
-        <v>2.271648137786531</v>
+        <v>2.27164813778653</v>
       </c>
       <c r="D7" t="n">
         <v>2.211123535675005</v>
       </c>
       <c r="E7" t="n">
-        <v>2.271634778961397</v>
+        <v>2.271634778961396</v>
       </c>
       <c r="F7" t="n">
-        <v>2.271634778961397</v>
+        <v>2.271634778961396</v>
       </c>
       <c r="G7" t="n">
         <v>2.264187883040547</v>
@@ -5114,16 +5114,16 @@
         <v>2.191802913873071</v>
       </c>
       <c r="C8" t="n">
-        <v>2.336500811931695</v>
+        <v>2.33650081193188</v>
       </c>
       <c r="D8" t="n">
         <v>2.287229135549273</v>
       </c>
       <c r="E8" t="n">
-        <v>2.321658368717197</v>
+        <v>2.321658368717196</v>
       </c>
       <c r="F8" t="n">
-        <v>2.283947705343903</v>
+        <v>2.283947705343902</v>
       </c>
       <c r="G8" t="n">
         <v>2.329036685551475</v>
@@ -5135,13 +5135,13 @@
         <v>2.33649840734996</v>
       </c>
       <c r="J8" t="n">
-        <v>2.293481827424288</v>
+        <v>2.293481827424287</v>
       </c>
       <c r="K8" t="n">
         <v>2.213910684219896</v>
       </c>
       <c r="L8" t="n">
-        <v>2.316272502470039</v>
+        <v>2.316272502470038</v>
       </c>
     </row>
     <row r="9">
@@ -5154,7 +5154,7 @@
         <v>2.621209928060057</v>
       </c>
       <c r="C9" t="n">
-        <v>2.854013143666957</v>
+        <v>2.854013143666956</v>
       </c>
       <c r="D9" t="n">
         <v>2.793493291330382</v>
@@ -5163,13 +5163,13 @@
         <v>3.018308882368146</v>
       </c>
       <c r="F9" t="n">
-        <v>2.854013047441051</v>
+        <v>2.85401304744105</v>
       </c>
       <c r="G9" t="n">
         <v>2.846552888920975</v>
       </c>
       <c r="H9" t="n">
-        <v>2.854010592094265</v>
+        <v>2.854010592094264</v>
       </c>
       <c r="I9" t="n">
         <v>2.854014610719458</v>
@@ -5178,10 +5178,10 @@
         <v>2.810987366331088</v>
       </c>
       <c r="K9" t="n">
-        <v>2.704207366218886</v>
+        <v>2.704207366218885</v>
       </c>
       <c r="L9" t="n">
-        <v>2.777105212972668</v>
+        <v>2.777105212972667</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.475470680080565</v>
+        <v>2.395614375517089</v>
       </c>
       <c r="C2" t="n">
-        <v>6.639803167246678</v>
+        <v>2.421071194863416</v>
       </c>
       <c r="D2" t="n">
-        <v>6.524879013269048</v>
+        <v>2.398214637959945</v>
       </c>
       <c r="E2" t="n">
-        <v>6.644774248001859</v>
+        <v>2.425483230171922</v>
       </c>
       <c r="F2" t="n">
-        <v>6.628947741739689</v>
+        <v>2.412305189739582</v>
       </c>
       <c r="G2" t="n">
-        <v>6.596104916027867</v>
+        <v>2.401963115756105</v>
       </c>
       <c r="H2" t="n">
-        <v>6.590470387738628</v>
+        <v>2.401596576273721</v>
       </c>
       <c r="I2" t="n">
-        <v>6.617916781567272</v>
+        <v>2.403110725016439</v>
       </c>
       <c r="J2" t="n">
-        <v>6.59203930126998</v>
+        <v>2.435877756125165</v>
       </c>
       <c r="K2" t="n">
-        <v>6.533654856471781</v>
+        <v>2.41681332626307</v>
       </c>
       <c r="L2" t="n">
-        <v>6.516637050842065</v>
+        <v>2.397682393137082</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.663641901193023</v>
+        <v>2.401592919714514</v>
       </c>
       <c r="C3" t="n">
-        <v>6.849308359341035</v>
+        <v>2.484563334640296</v>
       </c>
       <c r="D3" t="n">
-        <v>6.720471719265166</v>
+        <v>2.420081547791488</v>
       </c>
       <c r="E3" t="n">
-        <v>6.854341018876954</v>
+        <v>2.491675104706366</v>
       </c>
       <c r="F3" t="n">
-        <v>6.838514512614785</v>
+        <v>2.469925290418996</v>
       </c>
       <c r="G3" t="n">
-        <v>6.802396261839115</v>
+        <v>2.446809580622942</v>
       </c>
       <c r="H3" t="n">
-        <v>6.796051631708759</v>
+        <v>2.444975976991522</v>
       </c>
       <c r="I3" t="n">
-        <v>6.827485083865504</v>
+        <v>2.454753213328139</v>
       </c>
       <c r="J3" t="n">
-        <v>6.791145526364305</v>
+        <v>2.48913098469468</v>
       </c>
       <c r="K3" t="n">
-        <v>6.727071929551938</v>
+        <v>2.446569399014667</v>
       </c>
       <c r="L3" t="n">
-        <v>6.71100347345662</v>
+        <v>2.41721189982288</v>
       </c>
     </row>
     <row r="4">
@@ -5362,7 +5362,7 @@
         <v>2.194607048544149</v>
       </c>
       <c r="G4" t="n">
-        <v>2.181057065093114</v>
+        <v>2.181057065093115</v>
       </c>
       <c r="H4" t="n">
         <v>2.177679165086824</v>
@@ -5390,34 +5390,34 @@
         <v>2.482457735952149</v>
       </c>
       <c r="C5" t="n">
-        <v>3.803225812098383</v>
+        <v>3.803225812098378</v>
       </c>
       <c r="D5" t="n">
-        <v>2.965879897435718</v>
+        <v>2.965879897435722</v>
       </c>
       <c r="E5" t="n">
-        <v>3.803225810734296</v>
+        <v>3.803225810734293</v>
       </c>
       <c r="F5" t="n">
-        <v>3.803225810734296</v>
+        <v>3.803225810734293</v>
       </c>
       <c r="G5" t="n">
-        <v>3.701804253933356</v>
+        <v>3.701804253933361</v>
       </c>
       <c r="H5" t="n">
-        <v>3.823832232741435</v>
+        <v>3.823832232741432</v>
       </c>
       <c r="I5" t="n">
-        <v>3.803228575101004</v>
+        <v>3.803228575101002</v>
       </c>
       <c r="J5" t="n">
         <v>3.276945400699288</v>
       </c>
       <c r="K5" t="n">
-        <v>2.797753638339997</v>
+        <v>2.79775363834</v>
       </c>
       <c r="L5" t="n">
-        <v>5.708623184360368</v>
+        <v>5.70862318436037</v>
       </c>
     </row>
     <row r="6">
@@ -5427,13 +5427,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.59324260596944</v>
+        <v>3.201323155327308</v>
       </c>
       <c r="C6" t="n">
-        <v>3.301303494995302</v>
+        <v>3.301303494995301</v>
       </c>
       <c r="D6" t="n">
-        <v>3.228021399572415</v>
+        <v>3.228021399572418</v>
       </c>
       <c r="E6" t="n">
         <v>3.297590675535617</v>
@@ -5442,22 +5442,22 @@
         <v>3.301042373293136</v>
       </c>
       <c r="G6" t="n">
-        <v>15.66498870412094</v>
+        <v>3.273069253478798</v>
       </c>
       <c r="H6" t="n">
         <v>15.65985321961333</v>
       </c>
       <c r="I6" t="n">
-        <v>15.67806352828443</v>
+        <v>15.67806352828444</v>
       </c>
       <c r="J6" t="n">
-        <v>15.63531749906761</v>
+        <v>3.245582386138545</v>
       </c>
       <c r="K6" t="n">
-        <v>3.204914271558462</v>
+        <v>3.204914271558461</v>
       </c>
       <c r="L6" t="n">
-        <v>3.224269943337743</v>
+        <v>3.224269943337744</v>
       </c>
     </row>
     <row r="7">
@@ -5473,7 +5473,7 @@
         <v>2.255376626860963</v>
       </c>
       <c r="D7" t="n">
-        <v>2.199925169670351</v>
+        <v>2.199925169670352</v>
       </c>
       <c r="E7" t="n">
         <v>2.2553867358972</v>
@@ -5494,10 +5494,10 @@
         <v>2.213834680024521</v>
       </c>
       <c r="K7" t="n">
-        <v>2.191319374883229</v>
+        <v>2.19131937488323</v>
       </c>
       <c r="L7" t="n">
-        <v>2.195083400810478</v>
+        <v>2.195083400810479</v>
       </c>
     </row>
     <row r="8">
@@ -5510,13 +5510,13 @@
         <v>2.179755304587871</v>
       </c>
       <c r="C8" t="n">
-        <v>2.314274873898493</v>
+        <v>2.314274873898494</v>
       </c>
       <c r="D8" t="n">
         <v>2.269103555753832</v>
       </c>
       <c r="E8" t="n">
-        <v>2.300684985650633</v>
+        <v>2.300684985650634</v>
       </c>
       <c r="F8" t="n">
         <v>2.266156817777288</v>
@@ -5528,10 +5528,10 @@
         <v>2.29779987419382</v>
       </c>
       <c r="I8" t="n">
-        <v>2.314252598363636</v>
+        <v>2.314252598363637</v>
       </c>
       <c r="J8" t="n">
-        <v>2.272717651347706</v>
+        <v>2.272717651347707</v>
       </c>
       <c r="K8" t="n">
         <v>2.199593447819499</v>
@@ -5550,7 +5550,7 @@
         <v>2.526886150464137</v>
       </c>
       <c r="C9" t="n">
-        <v>2.729326933681416</v>
+        <v>2.729326933681417</v>
       </c>
       <c r="D9" t="n">
         <v>2.673879926039599</v>
@@ -5568,13 +5568,13 @@
         <v>2.712876972514243</v>
       </c>
       <c r="I9" t="n">
-        <v>2.729329696684039</v>
+        <v>2.72932969668404</v>
       </c>
       <c r="J9" t="n">
         <v>2.687784986844973</v>
       </c>
       <c r="K9" t="n">
-        <v>2.51716180492444</v>
+        <v>2.597118667771721</v>
       </c>
       <c r="L9" t="n">
         <v>2.669033707630931</v>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.471291819035813</v>
+        <v>2.393015923284578</v>
       </c>
       <c r="C2" t="n">
-        <v>6.610488274637032</v>
+        <v>2.416828074881267</v>
       </c>
       <c r="D2" t="n">
-        <v>6.514467353406506</v>
+        <v>2.395288165904989</v>
       </c>
       <c r="E2" t="n">
-        <v>6.615476274853716</v>
+        <v>2.421239784085733</v>
       </c>
       <c r="F2" t="n">
-        <v>6.599617558396598</v>
+        <v>2.408034920892503</v>
       </c>
       <c r="G2" t="n">
-        <v>6.572948345526796</v>
+        <v>2.398365904367674</v>
       </c>
       <c r="H2" t="n">
-        <v>6.615107028313508</v>
+        <v>2.400548943246883</v>
       </c>
       <c r="I2" t="n">
-        <v>6.589034440493132</v>
+        <v>2.399212104578927</v>
       </c>
       <c r="J2" t="n">
-        <v>6.570469879129167</v>
+        <v>2.432217573667053</v>
       </c>
       <c r="K2" t="n">
-        <v>6.514451952902944</v>
+        <v>2.413083785452027</v>
       </c>
       <c r="L2" t="n">
-        <v>6.513523122853385</v>
+        <v>2.39515910492739</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.658871225407509</v>
+        <v>2.398729315434226</v>
       </c>
       <c r="C3" t="n">
-        <v>6.815687062956973</v>
+        <v>2.47189053739652</v>
       </c>
       <c r="D3" t="n">
-        <v>6.708532033718806</v>
+        <v>2.414860282608265</v>
       </c>
       <c r="E3" t="n">
-        <v>6.820740382990325</v>
+        <v>2.479009675103717</v>
       </c>
       <c r="F3" t="n">
-        <v>6.80488166653321</v>
+        <v>2.457215592732887</v>
       </c>
       <c r="G3" t="n">
-        <v>6.775797288958161</v>
+        <v>2.436789109823015</v>
       </c>
       <c r="H3" t="n">
-        <v>6.824418034801826</v>
+        <v>2.452858861779322</v>
       </c>
       <c r="I3" t="n">
-        <v>6.794298584834731</v>
+        <v>2.442656966874057</v>
       </c>
       <c r="J3" t="n">
-        <v>6.766400324123146</v>
+        <v>2.479558405652682</v>
       </c>
       <c r="K3" t="n">
-        <v>6.70508606690815</v>
+        <v>2.437631740659325</v>
       </c>
       <c r="L3" t="n">
-        <v>6.707456341181716</v>
+        <v>2.414749154040907</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.105737191807653</v>
+        <v>2.105737191807654</v>
       </c>
       <c r="C4" t="n">
-        <v>2.176245729425726</v>
+        <v>2.176245729425727</v>
       </c>
       <c r="D4" t="n">
-        <v>2.131403217488448</v>
+        <v>2.131403217488449</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1763388443394</v>
+        <v>2.176338844339401</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1763388443394</v>
+        <v>2.176338844339401</v>
       </c>
       <c r="G4" t="n">
-        <v>2.166200095318607</v>
+        <v>2.166200095318606</v>
       </c>
       <c r="H4" t="n">
-        <v>2.191223838029424</v>
+        <v>2.191223838029425</v>
       </c>
       <c r="I4" t="n">
         <v>2.1758599476511</v>
       </c>
       <c r="J4" t="n">
-        <v>2.138787140615339</v>
+        <v>2.13878714061534</v>
       </c>
       <c r="K4" t="n">
-        <v>2.117826458242197</v>
+        <v>2.117826458242198</v>
       </c>
       <c r="L4" t="n">
-        <v>2.13088963663378</v>
+        <v>2.130889636633781</v>
       </c>
     </row>
     <row r="5">
@@ -5786,34 +5786,34 @@
         <v>2.449618471674813</v>
       </c>
       <c r="C5" t="n">
-        <v>3.534842109445153</v>
+        <v>3.534842109445161</v>
       </c>
       <c r="D5" t="n">
-        <v>2.858923741908018</v>
+        <v>2.858923741908021</v>
       </c>
       <c r="E5" t="n">
-        <v>3.534842106577301</v>
+        <v>3.534842106577309</v>
       </c>
       <c r="F5" t="n">
-        <v>3.534842106577301</v>
+        <v>3.534842106577309</v>
       </c>
       <c r="G5" t="n">
-        <v>3.454573417662467</v>
+        <v>3.454573417662469</v>
       </c>
       <c r="H5" t="n">
-        <v>4.039282019082649</v>
+        <v>4.039282019082655</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5348441086502</v>
+        <v>3.534844108650212</v>
       </c>
       <c r="J5" t="n">
-        <v>3.068755917192026</v>
+        <v>3.068755917192025</v>
       </c>
       <c r="K5" t="n">
         <v>2.614109862643755</v>
       </c>
       <c r="L5" t="n">
-        <v>3.003738012933872</v>
+        <v>4.854956529860346</v>
       </c>
     </row>
     <row r="6">
@@ -5823,13 +5823,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.196566600940781</v>
+        <v>3.196566600940782</v>
       </c>
       <c r="C6" t="n">
         <v>3.281844896462792</v>
       </c>
       <c r="D6" t="n">
-        <v>15.61189888177602</v>
+        <v>3.219899779740422</v>
       </c>
       <c r="E6" t="n">
         <v>3.278180388721061</v>
@@ -5838,22 +5838,22 @@
         <v>3.281662683888834</v>
       </c>
       <c r="G6" t="n">
-        <v>3.257029504451734</v>
+        <v>15.64808519956355</v>
       </c>
       <c r="H6" t="n">
-        <v>15.67142115875627</v>
+        <v>15.67142115875626</v>
       </c>
       <c r="I6" t="n">
-        <v>15.65774505189605</v>
+        <v>3.266689356784221</v>
       </c>
       <c r="J6" t="n">
-        <v>3.230643890198328</v>
+        <v>15.6193868218791</v>
       </c>
       <c r="K6" t="n">
         <v>3.191667561795272</v>
       </c>
       <c r="L6" t="n">
-        <v>3.220301767355884</v>
+        <v>3.220301767355885</v>
       </c>
     </row>
     <row r="7">
@@ -5866,22 +5866,22 @@
         <v>2.166346344791499</v>
       </c>
       <c r="C7" t="n">
-        <v>2.236467101429891</v>
+        <v>2.23646710142989</v>
       </c>
       <c r="D7" t="n">
         <v>2.192007931279393</v>
       </c>
       <c r="E7" t="n">
-        <v>2.236492741526122</v>
+        <v>2.236492741526124</v>
       </c>
       <c r="F7" t="n">
-        <v>2.236492741526122</v>
+        <v>2.236492741526123</v>
       </c>
       <c r="G7" t="n">
-        <v>2.226809248302452</v>
+        <v>2.226809248302451</v>
       </c>
       <c r="H7" t="n">
-        <v>2.251832991013269</v>
+        <v>2.25183299101327</v>
       </c>
       <c r="I7" t="n">
         <v>2.236469100634946</v>
@@ -5890,10 +5890,10 @@
         <v>2.199396293599185</v>
       </c>
       <c r="K7" t="n">
-        <v>2.178435611226042</v>
+        <v>2.178435611226043</v>
       </c>
       <c r="L7" t="n">
-        <v>2.191498789617625</v>
+        <v>2.191498789617626</v>
       </c>
     </row>
     <row r="8">
@@ -5903,13 +5903,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.174851444383485</v>
+        <v>2.174851444383486</v>
       </c>
       <c r="C8" t="n">
-        <v>2.293774942381943</v>
+        <v>2.293774942381944</v>
       </c>
       <c r="D8" t="n">
-        <v>2.259391851593472</v>
+        <v>2.259391851593473</v>
       </c>
       <c r="E8" t="n">
         <v>2.28043328207174</v>
@@ -5918,22 +5918,22 @@
         <v>2.246535856895714</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28407739412631</v>
+        <v>2.284077394126311</v>
       </c>
       <c r="H8" t="n">
-        <v>2.309101136837121</v>
+        <v>2.309101136837122</v>
       </c>
       <c r="I8" t="n">
-        <v>2.293737246458805</v>
+        <v>2.293737246458804</v>
       </c>
       <c r="J8" t="n">
-        <v>2.256674022751535</v>
+        <v>2.256674022751537</v>
       </c>
       <c r="K8" t="n">
-        <v>2.186034912200056</v>
+        <v>2.186034912200058</v>
       </c>
       <c r="L8" t="n">
-        <v>2.299704014723191</v>
+        <v>2.299704014723193</v>
       </c>
     </row>
     <row r="9">
@@ -5946,34 +5946,34 @@
         <v>2.480140572646625</v>
       </c>
       <c r="C9" t="n">
-        <v>2.655914894656161</v>
+        <v>2.655914894656163</v>
       </c>
       <c r="D9" t="n">
-        <v>2.611460145951519</v>
+        <v>2.61146014595152</v>
       </c>
       <c r="E9" t="n">
-        <v>2.777836740698219</v>
+        <v>2.777836740698218</v>
       </c>
       <c r="F9" t="n">
-        <v>2.655914804373821</v>
+        <v>2.655914804373822</v>
       </c>
       <c r="G9" t="n">
         <v>2.646257041528725</v>
       </c>
       <c r="H9" t="n">
-        <v>2.67128078423954</v>
+        <v>2.671280784239542</v>
       </c>
       <c r="I9" t="n">
-        <v>2.655916893861219</v>
+        <v>2.65591689386122</v>
       </c>
       <c r="J9" t="n">
-        <v>2.618844086825458</v>
+        <v>2.618844086825459</v>
       </c>
       <c r="K9" t="n">
         <v>2.536667306278404</v>
       </c>
       <c r="L9" t="n">
-        <v>2.610946582843898</v>
+        <v>2.610946582843899</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.454887955487937</v>
+        <v>2.401714376183725</v>
       </c>
       <c r="C2" t="n">
-        <v>6.667139864438336</v>
+        <v>2.429231822263825</v>
       </c>
       <c r="D2" t="n">
-        <v>6.501238482178722</v>
+        <v>2.4041537123439</v>
       </c>
       <c r="E2" t="n">
-        <v>6.672281262677688</v>
+        <v>2.433835447133797</v>
       </c>
       <c r="F2" t="n">
-        <v>6.655981389042575</v>
+        <v>2.420263438747676</v>
       </c>
       <c r="G2" t="n">
-        <v>6.686885702940593</v>
+        <v>2.413923956847518</v>
       </c>
       <c r="H2" t="n">
-        <v>6.844394652143495</v>
+        <v>2.422214008873584</v>
       </c>
       <c r="I2" t="n">
-        <v>6.645791477312681</v>
+        <v>2.411760403658618</v>
       </c>
       <c r="J2" t="n">
-        <v>6.654262809307617</v>
+        <v>2.446497936101261</v>
       </c>
       <c r="K2" t="n">
-        <v>6.541611729313106</v>
+        <v>2.423612791095188</v>
       </c>
       <c r="L2" t="n">
-        <v>6.689586389769747</v>
+        <v>2.414011983620946</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.639904597470247</v>
+        <v>2.398049511786049</v>
       </c>
       <c r="C3" t="n">
-        <v>6.880769002632033</v>
+        <v>2.498403467409923</v>
       </c>
       <c r="D3" t="n">
-        <v>6.693217304647328</v>
+        <v>2.415348072941635</v>
       </c>
       <c r="E3" t="n">
-        <v>6.88597056470267</v>
+        <v>2.505781088254383</v>
       </c>
       <c r="F3" t="n">
-        <v>6.869670691067558</v>
+        <v>2.483380926114596</v>
       </c>
       <c r="G3" t="n">
-        <v>6.906750065229406</v>
+        <v>2.484771045073918</v>
       </c>
       <c r="H3" t="n">
-        <v>7.088056162666788</v>
+        <v>2.544039241491773</v>
       </c>
       <c r="I3" t="n">
-        <v>6.859445097250839</v>
+        <v>2.46935024247709</v>
       </c>
       <c r="J3" t="n">
-        <v>6.862621287715318</v>
+        <v>2.516861622578532</v>
       </c>
       <c r="K3" t="n">
-        <v>6.736315669626229</v>
+        <v>2.452672304839622</v>
       </c>
       <c r="L3" t="n">
-        <v>6.909864912851917</v>
+        <v>2.486494861042407</v>
       </c>
     </row>
     <row r="4">
@@ -6157,7 +6157,7 @@
         <v>2.237169938474425</v>
       </c>
       <c r="H4" t="n">
-        <v>2.330758768088356</v>
+        <v>2.330758768088357</v>
       </c>
       <c r="I4" t="n">
         <v>2.212716202331185</v>
@@ -6179,34 +6179,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.245609665426155</v>
+        <v>2.245609665426167</v>
       </c>
       <c r="C5" t="n">
-        <v>4.169679307141209</v>
+        <v>4.169679307141206</v>
       </c>
       <c r="D5" t="n">
-        <v>2.704797201530637</v>
+        <v>2.704797201530639</v>
       </c>
       <c r="E5" t="n">
         <v>4.169679310529625</v>
       </c>
       <c r="F5" t="n">
-        <v>4.169679310529625</v>
+        <v>4.169679310529626</v>
       </c>
       <c r="G5" t="n">
-        <v>4.620318404164347</v>
+        <v>4.620318404164346</v>
       </c>
       <c r="H5" t="n">
         <v>6.458496702525213</v>
       </c>
       <c r="I5" t="n">
-        <v>4.169673457654483</v>
+        <v>4.16967345765448</v>
       </c>
       <c r="J5" t="n">
-        <v>4.003206467021609</v>
+        <v>4.003206467021613</v>
       </c>
       <c r="K5" t="n">
-        <v>2.889299336396173</v>
+        <v>2.889299336396178</v>
       </c>
       <c r="L5" t="n">
         <v>5.064536434850776</v>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.274570210528528</v>
+        <v>16.57852542825368</v>
       </c>
       <c r="C6" t="n">
-        <v>3.402500757147666</v>
+        <v>3.402500757147665</v>
       </c>
       <c r="D6" t="n">
         <v>16.60420235374254</v>
@@ -6231,22 +6231,22 @@
         <v>3.398423358226607</v>
       </c>
       <c r="F6" t="n">
-        <v>3.403046086898349</v>
+        <v>3.40304608689835</v>
       </c>
       <c r="G6" t="n">
-        <v>3.412494960467111</v>
+        <v>16.71645017819227</v>
       </c>
       <c r="H6" t="n">
-        <v>16.80840535254884</v>
+        <v>3.504563422987177</v>
       </c>
       <c r="I6" t="n">
-        <v>3.388041224323869</v>
+        <v>16.69199644204902</v>
       </c>
       <c r="J6" t="n">
-        <v>16.66945220713252</v>
+        <v>16.66945220713251</v>
       </c>
       <c r="K6" t="n">
-        <v>3.292409996645382</v>
+        <v>3.292409996645383</v>
       </c>
       <c r="L6" t="n">
         <v>3.412054883626985</v>
@@ -6286,7 +6286,7 @@
         <v>2.26005662824595</v>
       </c>
       <c r="K7" t="n">
-        <v>2.206017627179156</v>
+        <v>2.206017627179155</v>
       </c>
       <c r="L7" t="n">
         <v>2.307235571963414</v>
@@ -6314,7 +6314,7 @@
         <v>2.295809967507056</v>
       </c>
       <c r="G8" t="n">
-        <v>2.375847927231832</v>
+        <v>2.375847927231831</v>
       </c>
       <c r="H8" t="n">
         <v>2.46943675684575</v>
@@ -6326,7 +6326,7 @@
         <v>2.33031177094102</v>
       </c>
       <c r="K8" t="n">
-        <v>2.217789656414531</v>
+        <v>2.217789656414533</v>
       </c>
       <c r="L8" t="n">
         <v>2.437444272637556</v>
@@ -6342,19 +6342,19 @@
         <v>2.61989422060716</v>
       </c>
       <c r="C9" t="n">
-        <v>2.879868871312617</v>
+        <v>2.879868871312616</v>
       </c>
       <c r="D9" t="n">
-        <v>2.793945402926678</v>
+        <v>2.793945402926679</v>
       </c>
       <c r="E9" t="n">
         <v>3.048924021915572</v>
       </c>
       <c r="F9" t="n">
-        <v>2.879868741231918</v>
+        <v>2.879868741231917</v>
       </c>
       <c r="G9" t="n">
-        <v>2.904316757969131</v>
+        <v>2.90431675796913</v>
       </c>
       <c r="H9" t="n">
         <v>2.997905587583066</v>
@@ -6363,7 +6363,7 @@
         <v>2.879863021825893</v>
       </c>
       <c r="J9" t="n">
-        <v>2.858769319863126</v>
+        <v>2.858769319863127</v>
       </c>
       <c r="K9" t="n">
         <v>2.719848913147752</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.450982750103114</v>
+        <v>2.394779553555966</v>
       </c>
       <c r="C2" t="n">
-        <v>6.627119482509553</v>
+        <v>2.420299781033662</v>
       </c>
       <c r="D2" t="n">
-        <v>6.482496788198698</v>
+        <v>2.396438074789016</v>
       </c>
       <c r="E2" t="n">
-        <v>6.632118212777864</v>
+        <v>2.424742379946948</v>
       </c>
       <c r="F2" t="n">
-        <v>6.616232241713529</v>
+        <v>2.411514849860822</v>
       </c>
       <c r="G2" t="n">
-        <v>6.613442552640044</v>
+        <v>2.403329490292327</v>
       </c>
       <c r="H2" t="n">
-        <v>6.683927171900665</v>
+        <v>2.407009196909387</v>
       </c>
       <c r="I2" t="n">
-        <v>6.605943779287783</v>
+        <v>2.402934276984484</v>
       </c>
       <c r="J2" t="n">
-        <v>6.595731650845634</v>
+        <v>2.436160529264976</v>
       </c>
       <c r="K2" t="n">
-        <v>6.502091502109095</v>
+        <v>2.414330360361873</v>
       </c>
       <c r="L2" t="n">
-        <v>6.605479746488778</v>
+        <v>2.402861942399054</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.635416363572164</v>
+        <v>2.392904086711672</v>
       </c>
       <c r="C3" t="n">
-        <v>6.834765813099766</v>
+        <v>2.479553186303289</v>
       </c>
       <c r="D3" t="n">
-        <v>6.671664035495408</v>
+        <v>2.404656456432824</v>
       </c>
       <c r="E3" t="n">
-        <v>6.83982646024451</v>
+        <v>2.486702394958372</v>
       </c>
       <c r="F3" t="n">
-        <v>6.823940489180174</v>
+        <v>2.46487088436162</v>
       </c>
       <c r="G3" t="n">
-        <v>6.822278789936346</v>
+        <v>2.453551185348668</v>
       </c>
       <c r="H3" t="n">
-        <v>6.903484925976506</v>
+        <v>2.479902114302758</v>
       </c>
       <c r="I3" t="n">
-        <v>6.813635660524573</v>
+        <v>2.450712147515281</v>
       </c>
       <c r="J3" t="n">
-        <v>6.795403552201751</v>
+        <v>2.490407020426949</v>
       </c>
       <c r="K3" t="n">
-        <v>6.690953950497317</v>
+        <v>2.433618166170777</v>
       </c>
       <c r="L3" t="n">
-        <v>6.81312814043053</v>
+        <v>2.450991486628534</v>
       </c>
     </row>
     <row r="4">
@@ -6538,7 +6538,7 @@
         <v>2.094289576308732</v>
       </c>
       <c r="C4" t="n">
-        <v>2.186644911311779</v>
+        <v>2.18664491131178</v>
       </c>
       <c r="D4" t="n">
         <v>2.113023336593486</v>
@@ -6550,7 +6550,7 @@
         <v>2.186752297106368</v>
       </c>
       <c r="G4" t="n">
-        <v>2.190889716110876</v>
+        <v>2.190889716110877</v>
       </c>
       <c r="H4" t="n">
         <v>2.232753335984048</v>
@@ -6578,25 +6578,25 @@
         <v>2.236681818707256</v>
       </c>
       <c r="C5" t="n">
-        <v>3.662447620744028</v>
+        <v>3.662447620744031</v>
       </c>
       <c r="D5" t="n">
         <v>2.52418835764268</v>
       </c>
       <c r="E5" t="n">
-        <v>3.662447621333974</v>
+        <v>3.662447621333976</v>
       </c>
       <c r="F5" t="n">
-        <v>3.662447621333974</v>
+        <v>3.662447621333976</v>
       </c>
       <c r="G5" t="n">
-        <v>3.750869823731246</v>
+        <v>3.750869823731249</v>
       </c>
       <c r="H5" t="n">
         <v>4.446350636075872</v>
       </c>
       <c r="I5" t="n">
-        <v>3.66244639292735</v>
+        <v>3.662446392927351</v>
       </c>
       <c r="J5" t="n">
         <v>3.253645099118895</v>
@@ -6605,7 +6605,7 @@
         <v>2.509651788223065</v>
       </c>
       <c r="L5" t="n">
-        <v>3.972118483690422</v>
+        <v>3.972118483690421</v>
       </c>
     </row>
     <row r="6">
@@ -6615,31 +6615,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.57908096884235</v>
+        <v>15.57908096884236</v>
       </c>
       <c r="C6" t="n">
-        <v>3.293293877607396</v>
+        <v>3.293293877607395</v>
       </c>
       <c r="D6" t="n">
-        <v>3.201471032598</v>
+        <v>3.201470875046069</v>
       </c>
       <c r="E6" t="n">
-        <v>3.28958668351771</v>
+        <v>3.289586683517709</v>
       </c>
       <c r="F6" t="n">
-        <v>3.293374271468094</v>
+        <v>3.293374271468093</v>
       </c>
       <c r="G6" t="n">
-        <v>3.282793889471221</v>
+        <v>15.67568110864452</v>
       </c>
       <c r="H6" t="n">
-        <v>3.323801734580301</v>
+        <v>15.71602509326489</v>
       </c>
       <c r="I6" t="n">
-        <v>3.27838696235632</v>
+        <v>15.6712741815296</v>
       </c>
       <c r="J6" t="n">
-        <v>15.63817297607299</v>
+        <v>3.247671561301161</v>
       </c>
       <c r="K6" t="n">
         <v>3.186006270406485</v>
@@ -6664,19 +6664,19 @@
         <v>2.174349608414177</v>
       </c>
       <c r="E7" t="n">
-        <v>2.247813417919827</v>
+        <v>2.247813417919828</v>
       </c>
       <c r="F7" t="n">
-        <v>2.247813417919827</v>
+        <v>2.247813417919828</v>
       </c>
       <c r="G7" t="n">
-        <v>2.252220429620491</v>
+        <v>2.252220429620492</v>
       </c>
       <c r="H7" t="n">
         <v>2.294084049493663</v>
       </c>
       <c r="I7" t="n">
-        <v>2.247813502505586</v>
+        <v>2.247813502505587</v>
       </c>
       <c r="J7" t="n">
         <v>2.215927115994508</v>
@@ -6744,28 +6744,28 @@
         <v>2.65082246295416</v>
       </c>
       <c r="E9" t="n">
-        <v>2.860692808218379</v>
+        <v>2.86069280821838</v>
       </c>
       <c r="F9" t="n">
         <v>2.724283064116703</v>
       </c>
       <c r="G9" t="n">
-        <v>2.728688861284434</v>
+        <v>2.728688861284435</v>
       </c>
       <c r="H9" t="n">
         <v>2.770552481157607</v>
       </c>
       <c r="I9" t="n">
-        <v>2.724281934169528</v>
+        <v>2.724281934169529</v>
       </c>
       <c r="J9" t="n">
-        <v>2.692395547658452</v>
+        <v>2.692395547658453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.578347158129641</v>
+        <v>2.581125896082406</v>
       </c>
       <c r="L9" t="n">
-        <v>2.723968087509848</v>
+        <v>2.723968087509849</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.448809346758061</v>
+        <v>2.388118574133959</v>
       </c>
       <c r="C2" t="n">
-        <v>6.573371035517874</v>
+        <v>2.410454592493204</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460085225767332</v>
+        <v>2.388712001250518</v>
       </c>
       <c r="E2" t="n">
-        <v>6.578235226667331</v>
+        <v>2.414743576104343</v>
       </c>
       <c r="F2" t="n">
-        <v>6.562745848369326</v>
+        <v>2.401846125138585</v>
       </c>
       <c r="G2" t="n">
-        <v>6.542180077714672</v>
+        <v>2.393032490254998</v>
       </c>
       <c r="H2" t="n">
-        <v>6.611130337171922</v>
+        <v>2.396649869220294</v>
       </c>
       <c r="I2" t="n">
-        <v>6.552848932591884</v>
+        <v>2.393593525490604</v>
       </c>
       <c r="J2" t="n">
-        <v>6.539116878052806</v>
+        <v>2.425865849830976</v>
       </c>
       <c r="K2" t="n">
-        <v>6.475606462105678</v>
+        <v>2.406123654882478</v>
       </c>
       <c r="L2" t="n">
-        <v>6.529473190135469</v>
+        <v>2.39232458858249</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.632982459409228</v>
+        <v>2.388361165181847</v>
       </c>
       <c r="C3" t="n">
-        <v>6.773105116587335</v>
+        <v>2.455196272072623</v>
       </c>
       <c r="D3" t="n">
-        <v>6.645952056061191</v>
+        <v>2.392576857273863</v>
       </c>
       <c r="E3" t="n">
-        <v>6.778034557681082</v>
+        <v>2.462124330259889</v>
       </c>
       <c r="F3" t="n">
-        <v>6.762545179383078</v>
+        <v>2.440837696885451</v>
       </c>
       <c r="G3" t="n">
-        <v>6.740378141697979</v>
+        <v>2.423271814211925</v>
       </c>
       <c r="H3" t="n">
-        <v>6.819813269982817</v>
+        <v>2.44929179813568</v>
       </c>
       <c r="I3" t="n">
-        <v>6.75264133552815</v>
+        <v>2.427220257520458</v>
       </c>
       <c r="J3" t="n">
-        <v>6.730498848645386</v>
+        <v>2.464510422607034</v>
       </c>
       <c r="K3" t="n">
-        <v>6.660607918230236</v>
+        <v>2.419655725059835</v>
       </c>
       <c r="L3" t="n">
-        <v>6.725770231390374</v>
+        <v>2.418787029567332</v>
       </c>
     </row>
     <row r="4">
@@ -6937,7 +6937,7 @@
         <v>2.152843412353647</v>
       </c>
       <c r="D4" t="n">
-        <v>2.097315153229861</v>
+        <v>2.09731515322986</v>
       </c>
       <c r="E4" t="n">
         <v>2.152921383590664</v>
@@ -6946,7 +6946,7 @@
         <v>2.152921383590664</v>
       </c>
       <c r="G4" t="n">
-        <v>2.146148295910667</v>
+        <v>2.146148295910666</v>
       </c>
       <c r="H4" t="n">
         <v>2.187093300394211</v>
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.257393682450795</v>
+        <v>2.257393682450794</v>
       </c>
       <c r="C5" t="n">
-        <v>3.239408372092376</v>
+        <v>3.239408372092379</v>
       </c>
       <c r="D5" t="n">
         <v>2.365776765353191</v>
       </c>
       <c r="E5" t="n">
-        <v>3.239408371774379</v>
+        <v>3.239408371774381</v>
       </c>
       <c r="F5" t="n">
-        <v>3.239408371774379</v>
+        <v>3.239408371774381</v>
       </c>
       <c r="G5" t="n">
-        <v>3.156093904253627</v>
+        <v>3.156093904253619</v>
       </c>
       <c r="H5" t="n">
         <v>3.953032632572811</v>
       </c>
       <c r="I5" t="n">
-        <v>3.239409663261288</v>
+        <v>3.239409663261287</v>
       </c>
       <c r="J5" t="n">
         <v>2.753280995209461</v>
       </c>
       <c r="K5" t="n">
-        <v>2.30583411655054</v>
+        <v>2.305834116550539</v>
       </c>
       <c r="L5" t="n">
-        <v>3.182618168934958</v>
+        <v>3.633069301845864</v>
       </c>
     </row>
     <row r="6">
@@ -7014,34 +7014,34 @@
         <v>3.179287001376701</v>
       </c>
       <c r="C6" t="n">
-        <v>3.257151888821269</v>
+        <v>3.257151888821268</v>
       </c>
       <c r="D6" t="n">
-        <v>3.184066206324157</v>
+        <v>3.184066206324153</v>
       </c>
       <c r="E6" t="n">
-        <v>3.253557427738228</v>
+        <v>3.253557427738229</v>
       </c>
       <c r="F6" t="n">
         <v>3.257037914836593</v>
       </c>
       <c r="G6" t="n">
-        <v>15.62429089628914</v>
+        <v>3.234823176328993</v>
       </c>
       <c r="H6" t="n">
         <v>15.66365961451044</v>
       </c>
       <c r="I6" t="n">
-        <v>3.241254670359551</v>
+        <v>3.24125467035955</v>
       </c>
       <c r="J6" t="n">
-        <v>15.59596584198316</v>
+        <v>3.209599782415759</v>
       </c>
       <c r="K6" t="n">
-        <v>3.166316702705315</v>
+        <v>3.166316702705318</v>
       </c>
       <c r="L6" t="n">
-        <v>3.226848180726367</v>
+        <v>3.226848180726368</v>
       </c>
     </row>
     <row r="7">
@@ -7072,10 +7072,10 @@
         <v>2.246100334158825</v>
       </c>
       <c r="I7" t="n">
-        <v>2.211586823705834</v>
+        <v>2.211586823705835</v>
       </c>
       <c r="J7" t="n">
-        <v>2.178148825905427</v>
+        <v>2.178148825905428</v>
       </c>
       <c r="K7" t="n">
         <v>2.152897394787368</v>
@@ -7091,7 +7091,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.156857617644577</v>
+        <v>2.156857617644576</v>
       </c>
       <c r="C8" t="n">
         <v>2.265489912894152</v>
@@ -7118,7 +7118,7 @@
         <v>2.232049302199091</v>
       </c>
       <c r="K8" t="n">
-        <v>2.159269257166675</v>
+        <v>2.159269257166674</v>
       </c>
       <c r="L8" t="n">
         <v>2.300230143531196</v>
@@ -7143,7 +7143,7 @@
         <v>2.74279825734897</v>
       </c>
       <c r="F9" t="n">
-        <v>2.623318600708768</v>
+        <v>2.623318600708767</v>
       </c>
       <c r="G9" t="n">
         <v>2.616888487486474</v>
@@ -7155,7 +7155,7 @@
         <v>2.623319981517029</v>
       </c>
       <c r="J9" t="n">
-        <v>2.589881983716624</v>
+        <v>2.589881983716623</v>
       </c>
       <c r="K9" t="n">
         <v>2.502206834806357</v>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.469629756346138</v>
+        <v>2.39853908438364</v>
       </c>
       <c r="C2" t="n">
-        <v>6.664385479408383</v>
+        <v>2.425615111616863</v>
       </c>
       <c r="D2" t="n">
-        <v>6.532546656592634</v>
+        <v>2.401850275880583</v>
       </c>
       <c r="E2" t="n">
-        <v>6.669386864273989</v>
+        <v>2.430073706472405</v>
       </c>
       <c r="F2" t="n">
-        <v>6.653488979602571</v>
+        <v>2.416836270647269</v>
       </c>
       <c r="G2" t="n">
-        <v>6.633676083647836</v>
+        <v>2.407172516767278</v>
       </c>
       <c r="H2" t="n">
-        <v>6.639890286091762</v>
+        <v>2.407426399391084</v>
       </c>
       <c r="I2" t="n">
-        <v>6.642450326372281</v>
+        <v>2.407633887092276</v>
       </c>
       <c r="J2" t="n">
-        <v>6.640894493006638</v>
+        <v>2.441789902878757</v>
       </c>
       <c r="K2" t="n">
-        <v>6.543406909633762</v>
+        <v>2.420344481318589</v>
       </c>
       <c r="L2" t="n">
-        <v>6.572516883054493</v>
+        <v>2.403862051797532</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.656849111047853</v>
+        <v>2.40123068559452</v>
       </c>
       <c r="C3" t="n">
-        <v>6.87750419550042</v>
+        <v>2.49563954817474</v>
       </c>
       <c r="D3" t="n">
-        <v>6.729216579527945</v>
+        <v>2.424744393323147</v>
       </c>
       <c r="E3" t="n">
-        <v>6.882563960667297</v>
+        <v>2.502810462613295</v>
       </c>
       <c r="F3" t="n">
-        <v>6.866666075995878</v>
+        <v>2.480962593764007</v>
       </c>
       <c r="G3" t="n">
-        <v>6.845536369539131</v>
+        <v>2.462658503999674</v>
       </c>
       <c r="H3" t="n">
-        <v>6.85282489958997</v>
+        <v>2.465104814568032</v>
       </c>
       <c r="I3" t="n">
-        <v>6.855620982212846</v>
+        <v>2.465777456205469</v>
       </c>
       <c r="J3" t="n">
-        <v>6.847243623027741</v>
+        <v>2.509448128578948</v>
       </c>
       <c r="K3" t="n">
-        <v>6.738255552165611</v>
+        <v>2.451812610494853</v>
       </c>
       <c r="L3" t="n">
-        <v>6.775201887296332</v>
+        <v>2.440127736425795</v>
       </c>
     </row>
     <row r="4">
@@ -7342,7 +7342,7 @@
         <v>2.210594037282497</v>
       </c>
       <c r="G4" t="n">
-        <v>2.204904834013642</v>
+        <v>2.204904834013641</v>
       </c>
       <c r="H4" t="n">
         <v>2.208572825662036</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.424017731436698</v>
+        <v>2.424017731436694</v>
       </c>
       <c r="C5" t="n">
-        <v>4.164494504735089</v>
+        <v>4.164494504735086</v>
       </c>
       <c r="D5" t="n">
-        <v>3.065334723022026</v>
+        <v>3.065334723022025</v>
       </c>
       <c r="E5" t="n">
-        <v>4.164494505192541</v>
+        <v>4.164494505192543</v>
       </c>
       <c r="F5" t="n">
-        <v>4.164494505192541</v>
+        <v>4.164494505192543</v>
       </c>
       <c r="G5" t="n">
-        <v>4.162573405536305</v>
+        <v>4.1625734055363</v>
       </c>
       <c r="H5" t="n">
-        <v>4.334589041290942</v>
+        <v>4.334589041290938</v>
       </c>
       <c r="I5" t="n">
-        <v>4.164495473675628</v>
+        <v>4.164495473675629</v>
       </c>
       <c r="J5" t="n">
-        <v>3.884258861223752</v>
+        <v>3.884258861223753</v>
       </c>
       <c r="K5" t="n">
-        <v>2.951913738535335</v>
+        <v>2.951913738535334</v>
       </c>
       <c r="L5" t="n">
-        <v>3.757184744072673</v>
+        <v>8.872944409110236</v>
       </c>
     </row>
     <row r="6">
@@ -7410,13 +7410,13 @@
         <v>3.281578376144866</v>
       </c>
       <c r="C6" t="n">
-        <v>3.399748589553046</v>
+        <v>3.399748589553047</v>
       </c>
       <c r="D6" t="n">
         <v>3.314863397814749</v>
       </c>
       <c r="E6" t="n">
-        <v>3.395701629726334</v>
+        <v>3.395701629726332</v>
       </c>
       <c r="F6" t="n">
         <v>3.399636842261895</v>
@@ -7431,13 +7431,13 @@
         <v>16.68524936989057</v>
       </c>
       <c r="J6" t="n">
-        <v>16.65663459494399</v>
+        <v>16.656634594944</v>
       </c>
       <c r="K6" t="n">
-        <v>3.29214831999002</v>
+        <v>3.292148319990019</v>
       </c>
       <c r="L6" t="n">
-        <v>3.340460341009573</v>
+        <v>3.340460341009572</v>
       </c>
     </row>
     <row r="7">
@@ -7450,7 +7450,7 @@
         <v>2.174113916989417</v>
       </c>
       <c r="C7" t="n">
-        <v>2.276956403782</v>
+        <v>2.276956403781999</v>
       </c>
       <c r="D7" t="n">
         <v>2.211510569517162</v>
@@ -7471,7 +7471,7 @@
         <v>2.276957372722535</v>
       </c>
       <c r="J7" t="n">
-        <v>2.249821637143088</v>
+        <v>2.249821637143087</v>
       </c>
       <c r="K7" t="n">
         <v>2.204307475375341</v>
@@ -7490,7 +7490,7 @@
         <v>2.185110754577896</v>
       </c>
       <c r="C8" t="n">
-        <v>2.342740480925664</v>
+        <v>2.342740480925463</v>
       </c>
       <c r="D8" t="n">
         <v>2.288644297971976</v>
@@ -7502,22 +7502,22 @@
         <v>2.289689962861543</v>
       </c>
       <c r="G8" t="n">
-        <v>2.337432882172382</v>
+        <v>2.337432882172381</v>
       </c>
       <c r="H8" t="n">
-        <v>2.341100873820761</v>
+        <v>2.341100873820759</v>
       </c>
       <c r="I8" t="n">
         <v>2.342728513861705</v>
       </c>
       <c r="J8" t="n">
-        <v>2.31560354299473</v>
+        <v>2.315603542994729</v>
       </c>
       <c r="K8" t="n">
         <v>2.214286852155016</v>
       </c>
       <c r="L8" t="n">
-        <v>2.358314024286179</v>
+        <v>2.358314024286178</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.616658857319206</v>
+        <v>2.616658857319205</v>
       </c>
       <c r="C9" t="n">
-        <v>2.862688886910733</v>
+        <v>2.862688886910732</v>
       </c>
       <c r="D9" t="n">
         <v>2.797247817629846</v>
       </c>
       <c r="E9" t="n">
-        <v>3.027924136837195</v>
+        <v>3.027924136837194</v>
       </c>
       <c r="F9" t="n">
-        <v>2.862688786170019</v>
+        <v>2.86268878617002</v>
       </c>
       <c r="G9" t="n">
-        <v>2.857394224161943</v>
+        <v>2.857394224161942</v>
       </c>
       <c r="H9" t="n">
         <v>2.861062215810338</v>
       </c>
       <c r="I9" t="n">
-        <v>2.86268985585127</v>
+        <v>2.862689855851269</v>
       </c>
       <c r="J9" t="n">
-        <v>2.835554120271819</v>
+        <v>2.835554120271818</v>
       </c>
       <c r="K9" t="n">
-        <v>2.707076528116137</v>
+        <v>2.707076528116136</v>
       </c>
       <c r="L9" t="n">
-        <v>2.821059026071694</v>
+        <v>2.821059026071693</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.447622419629688</v>
+        <v>2.394143884982218</v>
       </c>
       <c r="C2" t="n">
-        <v>6.628087412676778</v>
+        <v>2.420127195945656</v>
       </c>
       <c r="D2" t="n">
-        <v>6.514162323856572</v>
+        <v>2.397645747982784</v>
       </c>
       <c r="E2" t="n">
-        <v>6.63310178015412</v>
+        <v>2.42457705493117</v>
       </c>
       <c r="F2" t="n">
-        <v>6.617167943974485</v>
+        <v>2.411309678355071</v>
       </c>
       <c r="G2" t="n">
-        <v>6.601934260206813</v>
+        <v>2.402265010663791</v>
       </c>
       <c r="H2" t="n">
-        <v>6.803232853036457</v>
+        <v>2.412908297082556</v>
       </c>
       <c r="I2" t="n">
-        <v>6.606615471875973</v>
+        <v>2.402510903343795</v>
       </c>
       <c r="J2" t="n">
-        <v>6.601951677493833</v>
+        <v>2.436331449397805</v>
       </c>
       <c r="K2" t="n">
-        <v>6.508660620153156</v>
+        <v>2.414595526883999</v>
       </c>
       <c r="L2" t="n">
-        <v>6.568664857305648</v>
+        <v>2.400448847195292</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.631570444305749</v>
+        <v>2.391302377903414</v>
       </c>
       <c r="C3" t="n">
-        <v>6.835852770049128</v>
+        <v>2.479896368685783</v>
       </c>
       <c r="D3" t="n">
-        <v>6.708105117866301</v>
+        <v>2.416133500475814</v>
       </c>
       <c r="E3" t="n">
-        <v>6.840930355988525</v>
+        <v>2.487064585624057</v>
       </c>
       <c r="F3" t="n">
-        <v>6.824996519808888</v>
+        <v>2.46516730437333</v>
       </c>
       <c r="G3" t="n">
-        <v>6.809061026570919</v>
+        <v>2.44899333832744</v>
       </c>
       <c r="H3" t="n">
-        <v>7.040725952175496</v>
+        <v>2.524626517516869</v>
       </c>
       <c r="I3" t="n">
-        <v>6.814434709315091</v>
+        <v>2.450648379543707</v>
       </c>
       <c r="J3" t="n">
-        <v>6.802518775969479</v>
+        <v>2.492905695398254</v>
       </c>
       <c r="K3" t="n">
-        <v>6.698456085457925</v>
+        <v>2.436211384950692</v>
       </c>
       <c r="L3" t="n">
-        <v>6.770803688198535</v>
+        <v>2.436943720670854</v>
       </c>
     </row>
     <row r="4">
@@ -7744,7 +7744,7 @@
         <v>2.303730948704926</v>
       </c>
       <c r="I4" t="n">
-        <v>2.186991118462773</v>
+        <v>2.186991118462774</v>
       </c>
       <c r="J4" t="n">
         <v>2.158149114848047</v>
@@ -7766,34 +7766,34 @@
         <v>2.207930808892657</v>
       </c>
       <c r="C5" t="n">
-        <v>3.687935055468196</v>
+        <v>3.687935055468197</v>
       </c>
       <c r="D5" t="n">
-        <v>2.823655219525856</v>
+        <v>2.823655219525857</v>
       </c>
       <c r="E5" t="n">
-        <v>3.687935056020581</v>
+        <v>3.687935056020582</v>
       </c>
       <c r="F5" t="n">
-        <v>3.687935056020581</v>
+        <v>3.687935056020582</v>
       </c>
       <c r="G5" t="n">
-        <v>3.690509475573296</v>
+        <v>3.690509475573295</v>
       </c>
       <c r="H5" t="n">
-        <v>5.804729550506192</v>
+        <v>5.804729550506202</v>
       </c>
       <c r="I5" t="n">
-        <v>3.687935487177888</v>
+        <v>3.687935487177887</v>
       </c>
       <c r="J5" t="n">
-        <v>3.381003985749636</v>
+        <v>3.381003985749638</v>
       </c>
       <c r="K5" t="n">
         <v>2.570357584010973</v>
       </c>
       <c r="L5" t="n">
-        <v>5.065807640104795</v>
+        <v>3.594665856532567</v>
       </c>
     </row>
     <row r="6">
@@ -7803,22 +7803,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.57695273521741</v>
+        <v>15.5769527352174</v>
       </c>
       <c r="C6" t="n">
         <v>3.293833841480534</v>
       </c>
       <c r="D6" t="n">
-        <v>3.220983276076725</v>
+        <v>3.220983134049648</v>
       </c>
       <c r="E6" t="n">
         <v>3.290128631016791</v>
       </c>
       <c r="F6" t="n">
-        <v>3.29378616607352</v>
+        <v>3.293786166073521</v>
       </c>
       <c r="G6" t="n">
-        <v>3.276223797155794</v>
+        <v>15.66871249311194</v>
       </c>
       <c r="H6" t="n">
         <v>15.78696807806694</v>
@@ -7830,7 +7830,7 @@
         <v>3.2511210900407</v>
       </c>
       <c r="K6" t="n">
-        <v>3.189825638355157</v>
+        <v>3.189825638355159</v>
       </c>
       <c r="L6" t="n">
         <v>3.254924884007971</v>
@@ -7870,7 +7870,7 @@
         <v>2.219517055496773</v>
       </c>
       <c r="K7" t="n">
-        <v>2.17688739696271</v>
+        <v>2.176887396962711</v>
       </c>
       <c r="L7" t="n">
         <v>2.225743124563067</v>
@@ -7898,13 +7898,13 @@
         <v>2.259395247111898</v>
       </c>
       <c r="G8" t="n">
-        <v>2.304899027445405</v>
+        <v>2.304899027445406</v>
       </c>
       <c r="H8" t="n">
         <v>2.424492507798352</v>
       </c>
       <c r="I8" t="n">
-        <v>2.307752677556198</v>
+        <v>2.307752677556197</v>
       </c>
       <c r="J8" t="n">
         <v>2.278920489214506</v>
@@ -7929,7 +7929,7 @@
         <v>2.722787159793718</v>
       </c>
       <c r="D9" t="n">
-        <v>2.667729297188293</v>
+        <v>2.667729297188292</v>
       </c>
       <c r="E9" t="n">
         <v>2.858682203877362</v>
@@ -7950,10 +7950,10 @@
         <v>2.693945587888675</v>
       </c>
       <c r="K9" t="n">
-        <v>2.503032153603891</v>
+        <v>2.583083959741851</v>
       </c>
       <c r="L9" t="n">
-        <v>2.70017165695497</v>
+        <v>2.700171656954969</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia water use results.xlsx
+++ b/Results/Ammonia/ammonia water use results.xlsx
@@ -515,31 +515,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.397974324484816</v>
+        <v>2.397974324484815</v>
       </c>
       <c r="C2" t="n">
-        <v>2.422089040702594</v>
+        <v>2.422089040702593</v>
       </c>
       <c r="D2" t="n">
-        <v>2.400405865574037</v>
+        <v>2.400405865574036</v>
       </c>
       <c r="E2" t="n">
-        <v>2.426497121365932</v>
+        <v>2.426497121365931</v>
       </c>
       <c r="F2" t="n">
-        <v>2.413407725419</v>
+        <v>2.413407725419001</v>
       </c>
       <c r="G2" t="n">
-        <v>2.404690612348189</v>
+        <v>2.404690612348188</v>
       </c>
       <c r="H2" t="n">
         <v>2.405450282604843</v>
       </c>
       <c r="I2" t="n">
-        <v>2.404657714226174</v>
+        <v>2.404657714226173</v>
       </c>
       <c r="J2" t="n">
-        <v>2.438810056512719</v>
+        <v>2.43881005651272</v>
       </c>
       <c r="K2" t="n">
         <v>2.418847312395473</v>
@@ -555,31 +555,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.408217778759851</v>
+        <v>2.408217778759852</v>
       </c>
       <c r="C3" t="n">
         <v>2.484712759580956</v>
       </c>
       <c r="D3" t="n">
-        <v>2.425548992923985</v>
+        <v>2.425548992923986</v>
       </c>
       <c r="E3" t="n">
-        <v>2.491803276451297</v>
+        <v>2.491803276451298</v>
       </c>
       <c r="F3" t="n">
-        <v>2.470199776616411</v>
+        <v>2.470199776616412</v>
       </c>
       <c r="G3" t="n">
-        <v>2.456132922882182</v>
+        <v>2.456132922882183</v>
       </c>
       <c r="H3" t="n">
         <v>2.462317989666232</v>
       </c>
       <c r="I3" t="n">
-        <v>2.455761298317353</v>
+        <v>2.455761298317354</v>
       </c>
       <c r="J3" t="n">
-        <v>2.502725894079616</v>
+        <v>2.502725894079617</v>
       </c>
       <c r="K3" t="n">
         <v>2.452106824192623</v>
@@ -610,10 +610,10 @@
         <v>2.195494908039985</v>
       </c>
       <c r="G4" t="n">
-        <v>2.195483144963371</v>
+        <v>2.19548314496337</v>
       </c>
       <c r="H4" t="n">
-        <v>2.204761188950388</v>
+        <v>2.204761188950387</v>
       </c>
       <c r="I4" t="n">
         <v>2.195176338039683</v>
@@ -622,7 +622,7 @@
         <v>2.175219285573747</v>
       </c>
       <c r="K4" t="n">
-        <v>2.139038281803965</v>
+        <v>2.139038281803964</v>
       </c>
       <c r="L4" t="n">
         <v>2.128615647601511</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.701613148477847</v>
+        <v>2.701613148477849</v>
       </c>
       <c r="C5" t="n">
-        <v>4.129132531955375</v>
+        <v>4.12913253195538</v>
       </c>
       <c r="D5" t="n">
-        <v>3.241146159618847</v>
+        <v>3.241146159618848</v>
       </c>
       <c r="E5" t="n">
-        <v>4.129132532909467</v>
+        <v>4.129132532909468</v>
       </c>
       <c r="F5" t="n">
-        <v>4.129132532909467</v>
+        <v>4.129132532909468</v>
       </c>
       <c r="G5" t="n">
-        <v>4.217874945765</v>
+        <v>4.217874945764984</v>
       </c>
       <c r="H5" t="n">
         <v>4.625343267693363</v>
       </c>
       <c r="I5" t="n">
-        <v>4.129132232163368</v>
+        <v>4.129132232163373</v>
       </c>
       <c r="J5" t="n">
-        <v>3.871190014066451</v>
+        <v>3.871190014066453</v>
       </c>
       <c r="K5" t="n">
-        <v>3.087144936792965</v>
+        <v>3.087144936792967</v>
       </c>
       <c r="L5" t="n">
-        <v>3.014511813948371</v>
+        <v>3.014511813948372</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.37374110549858</v>
+        <v>3.373741105498579</v>
       </c>
       <c r="C6" t="n">
         <v>3.465437388501964</v>
@@ -684,13 +684,13 @@
         <v>3.397179636446144</v>
       </c>
       <c r="E6" t="n">
-        <v>3.461163970028606</v>
+        <v>3.461163970028605</v>
       </c>
       <c r="F6" t="n">
-        <v>3.46547372925589</v>
+        <v>3.465473729255891</v>
       </c>
       <c r="G6" t="n">
-        <v>17.66255399153955</v>
+        <v>17.66255399153954</v>
       </c>
       <c r="H6" t="n">
         <v>17.66988011662018</v>
@@ -699,10 +699,10 @@
         <v>17.66224718461586</v>
       </c>
       <c r="J6" t="n">
-        <v>17.64086079970541</v>
+        <v>17.64086079970542</v>
       </c>
       <c r="K6" t="n">
-        <v>3.372578071342059</v>
+        <v>3.372578071342061</v>
       </c>
       <c r="L6" t="n">
         <v>3.380021330844657</v>
@@ -730,13 +730,13 @@
         <v>2.265685147648794</v>
       </c>
       <c r="G7" t="n">
-        <v>2.266001342310386</v>
+        <v>2.266001342310387</v>
       </c>
       <c r="H7" t="n">
         <v>2.275279386297405</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2656945353867</v>
+        <v>2.265694535386699</v>
       </c>
       <c r="J7" t="n">
         <v>2.245737482920763</v>
@@ -779,13 +779,13 @@
         <v>2.333715050583227</v>
       </c>
       <c r="J8" t="n">
-        <v>2.313769239724795</v>
+        <v>2.313769239724796</v>
       </c>
       <c r="K8" t="n">
         <v>2.219313567094203</v>
       </c>
       <c r="L8" t="n">
-        <v>2.326905474194113</v>
+        <v>2.326905474194114</v>
       </c>
     </row>
     <row r="9">
@@ -804,16 +804,16 @@
         <v>2.93068942033656</v>
       </c>
       <c r="E9" t="n">
-        <v>3.176886245836323</v>
+        <v>3.176886245836324</v>
       </c>
       <c r="F9" t="n">
         <v>2.978806910757267</v>
       </c>
       <c r="G9" t="n">
-        <v>2.979113522591775</v>
+        <v>2.979113522591774</v>
       </c>
       <c r="H9" t="n">
-        <v>2.988391566578794</v>
+        <v>2.988391566578795</v>
       </c>
       <c r="I9" t="n">
         <v>2.978806715668087</v>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.390607844864272</v>
+        <v>2.390607844864271</v>
       </c>
       <c r="C2" t="n">
         <v>2.413753664184544</v>
@@ -923,10 +923,10 @@
         <v>2.418158974718839</v>
       </c>
       <c r="F2" t="n">
-        <v>2.404972423023362</v>
+        <v>2.404972423023361</v>
       </c>
       <c r="G2" t="n">
-        <v>2.397295956389829</v>
+        <v>2.39729595638983</v>
       </c>
       <c r="H2" t="n">
         <v>2.401842782058986</v>
@@ -935,13 +935,13 @@
         <v>2.396856811496239</v>
       </c>
       <c r="J2" t="n">
-        <v>2.430384323315769</v>
+        <v>2.43038432331577</v>
       </c>
       <c r="K2" t="n">
         <v>2.409683789034782</v>
       </c>
       <c r="L2" t="n">
-        <v>2.394298497364424</v>
+        <v>2.394298497364423</v>
       </c>
     </row>
     <row r="3">
@@ -951,34 +951,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.387975174678119</v>
+        <v>2.38797517467812</v>
       </c>
       <c r="C3" t="n">
         <v>2.460371415581574</v>
       </c>
       <c r="D3" t="n">
-        <v>2.403715580950774</v>
+        <v>2.403715580950775</v>
       </c>
       <c r="E3" t="n">
-        <v>2.467475192080378</v>
+        <v>2.46747519208038</v>
       </c>
       <c r="F3" t="n">
-        <v>2.445711333900275</v>
+        <v>2.445711333900276</v>
       </c>
       <c r="G3" t="n">
-        <v>2.435509646897977</v>
+        <v>2.435509646897978</v>
       </c>
       <c r="H3" t="n">
         <v>2.468261156673532</v>
       </c>
       <c r="I3" t="n">
-        <v>2.432320052022268</v>
+        <v>2.432320052022269</v>
       </c>
       <c r="J3" t="n">
         <v>2.475913797866554</v>
       </c>
       <c r="K3" t="n">
-        <v>2.425884001220347</v>
+        <v>2.425884001220349</v>
       </c>
       <c r="L3" t="n">
         <v>2.4149486895879</v>
@@ -997,13 +997,13 @@
         <v>2.15913919869676</v>
       </c>
       <c r="D4" t="n">
-        <v>2.113397477294969</v>
+        <v>2.113397477294968</v>
       </c>
       <c r="E4" t="n">
-        <v>2.15923915387666</v>
+        <v>2.159239153876659</v>
       </c>
       <c r="F4" t="n">
-        <v>2.15923915387666</v>
+        <v>2.159239153876659</v>
       </c>
       <c r="G4" t="n">
         <v>2.16391184619022</v>
@@ -1037,31 +1037,31 @@
         <v>3.310164872658559</v>
       </c>
       <c r="D5" t="n">
-        <v>2.58966463225679</v>
+        <v>2.589664632256791</v>
       </c>
       <c r="E5" t="n">
-        <v>3.31016487337981</v>
+        <v>3.310164873379809</v>
       </c>
       <c r="F5" t="n">
-        <v>3.31016487337981</v>
+        <v>3.310164873379809</v>
       </c>
       <c r="G5" t="n">
-        <v>3.426549751557042</v>
+        <v>3.426549751557043</v>
       </c>
       <c r="H5" t="n">
-        <v>4.467703193018337</v>
+        <v>4.467703193018336</v>
       </c>
       <c r="I5" t="n">
-        <v>3.31016355664643</v>
+        <v>3.310163556646433</v>
       </c>
       <c r="J5" t="n">
-        <v>3.005659686501831</v>
+        <v>3.005659686501826</v>
       </c>
       <c r="K5" t="n">
         <v>2.398184596327069</v>
       </c>
       <c r="L5" t="n">
-        <v>3.019720681250445</v>
+        <v>3.019720681250444</v>
       </c>
     </row>
     <row r="6">
@@ -1074,13 +1074,13 @@
         <v>3.178654612515513</v>
       </c>
       <c r="C6" t="n">
-        <v>3.264042165792189</v>
+        <v>3.26404216579219</v>
       </c>
       <c r="D6" t="n">
-        <v>15.59313059909952</v>
+        <v>15.59313059909953</v>
       </c>
       <c r="E6" t="n">
-        <v>3.260414599516877</v>
+        <v>3.260414599516879</v>
       </c>
       <c r="F6" t="n">
         <v>3.264169834821486</v>
@@ -1089,13 +1089,13 @@
         <v>15.64517694242378</v>
       </c>
       <c r="H6" t="n">
-        <v>15.69498518953011</v>
+        <v>15.6949851895301</v>
       </c>
       <c r="I6" t="n">
         <v>3.249316732741507</v>
       </c>
       <c r="J6" t="n">
-        <v>3.225501817443873</v>
+        <v>3.225501817443872</v>
       </c>
       <c r="K6" t="n">
         <v>3.174652730163114</v>
@@ -1132,7 +1132,7 @@
         <v>2.275508026510348</v>
       </c>
       <c r="I7" t="n">
-        <v>2.219179373007741</v>
+        <v>2.21917937300774</v>
       </c>
       <c r="J7" t="n">
         <v>2.194384581480575</v>
@@ -1154,7 +1154,7 @@
         <v>2.157050632323219</v>
       </c>
       <c r="C8" t="n">
-        <v>2.276173046037566</v>
+        <v>2.276173046037567</v>
       </c>
       <c r="D8" t="n">
         <v>2.24059703986523</v>
@@ -1175,7 +1175,7 @@
         <v>2.276158666898123</v>
       </c>
       <c r="J8" t="n">
-        <v>2.251373396374038</v>
+        <v>2.251373396374037</v>
       </c>
       <c r="K8" t="n">
         <v>2.169493609092117</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.461034696023029</v>
+        <v>2.461034696023028</v>
       </c>
       <c r="C9" t="n">
         <v>2.636852749748535</v>
@@ -1215,7 +1215,7 @@
         <v>2.636851433736412</v>
       </c>
       <c r="J9" t="n">
-        <v>2.612056642209246</v>
+        <v>2.612056642209247</v>
       </c>
       <c r="K9" t="n">
         <v>2.518605189201674</v>
@@ -1310,16 +1310,16 @@
         <v>2.434833255239304</v>
       </c>
       <c r="C2" t="n">
-        <v>2.438691042779654</v>
+        <v>2.438691042779653</v>
       </c>
       <c r="D2" t="n">
         <v>2.410487515471072</v>
       </c>
       <c r="E2" t="n">
-        <v>2.411484678763527</v>
+        <v>2.411484678763528</v>
       </c>
       <c r="F2" t="n">
-        <v>2.41148014806102</v>
+        <v>2.411480148061021</v>
       </c>
       <c r="G2" t="n">
         <v>2.415184601193967</v>
@@ -1334,7 +1334,7 @@
         <v>2.420960984417868</v>
       </c>
       <c r="K2" t="n">
-        <v>2.41511337443342</v>
+        <v>2.415113374433419</v>
       </c>
       <c r="L2" t="n">
         <v>2.425010228603088</v>
@@ -1353,31 +1353,31 @@
         <v>2.609198349256018</v>
       </c>
       <c r="D3" t="n">
-        <v>2.430400987276863</v>
+        <v>2.430400987276862</v>
       </c>
       <c r="E3" t="n">
-        <v>2.43796833901929</v>
+        <v>2.437968339019291</v>
       </c>
       <c r="F3" t="n">
-        <v>2.437963808316784</v>
+        <v>2.437963808316783</v>
       </c>
       <c r="G3" t="n">
-        <v>2.463942534580254</v>
+        <v>2.463942534580253</v>
       </c>
       <c r="H3" t="n">
         <v>2.471841281355951</v>
       </c>
       <c r="I3" t="n">
-        <v>2.438114191390594</v>
+        <v>2.438114191390592</v>
       </c>
       <c r="J3" t="n">
         <v>2.461682213996258</v>
       </c>
       <c r="K3" t="n">
-        <v>2.435018103643104</v>
+        <v>2.435018103643102</v>
       </c>
       <c r="L3" t="n">
-        <v>2.534226763757991</v>
+        <v>2.53422676375799</v>
       </c>
     </row>
     <row r="4">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.403204130209005</v>
+        <v>2.403204130209004</v>
       </c>
       <c r="C4" t="n">
         <v>2.403271500690576</v>
@@ -1402,10 +1402,10 @@
         <v>2.14067291206103</v>
       </c>
       <c r="G4" t="n">
-        <v>2.181264622173743</v>
+        <v>2.181264622173742</v>
       </c>
       <c r="H4" t="n">
-        <v>2.193316318587898</v>
+        <v>2.193316318587897</v>
       </c>
       <c r="I4" t="n">
         <v>2.140335275259472</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.925047056126456</v>
+        <v>7.925047056126458</v>
       </c>
       <c r="C5" t="n">
-        <v>7.857975756770365</v>
+        <v>7.85797575677037</v>
       </c>
       <c r="D5" t="n">
         <v>2.836232563573245</v>
@@ -1442,22 +1442,22 @@
         <v>3.0639461846452</v>
       </c>
       <c r="G5" t="n">
-        <v>3.833950201790389</v>
+        <v>3.833950201790372</v>
       </c>
       <c r="H5" t="n">
-        <v>4.243304029682842</v>
+        <v>4.243304029682846</v>
       </c>
       <c r="I5" t="n">
-        <v>3.063936684549919</v>
+        <v>3.06393668454992</v>
       </c>
       <c r="J5" t="n">
-        <v>3.412390096877258</v>
+        <v>3.412390096877255</v>
       </c>
       <c r="K5" t="n">
         <v>2.727120499594363</v>
       </c>
       <c r="L5" t="n">
-        <v>6.294039404760619</v>
+        <v>6.294039404760624</v>
       </c>
     </row>
     <row r="6">
@@ -1470,7 +1470,7 @@
         <v>16.64604894100139</v>
       </c>
       <c r="C6" t="n">
-        <v>3.581142064299176</v>
+        <v>3.581142064299177</v>
       </c>
       <c r="D6" t="n">
         <v>3.282647628856491</v>
@@ -1491,7 +1491,7 @@
         <v>3.29758725513922</v>
       </c>
       <c r="J6" t="n">
-        <v>16.39890700848815</v>
+        <v>16.39890700848816</v>
       </c>
       <c r="K6" t="n">
         <v>3.261272928974456</v>
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.467014547223997</v>
+        <v>2.467014547223996</v>
       </c>
       <c r="C7" t="n">
-        <v>2.464511642375715</v>
+        <v>2.464511642375714</v>
       </c>
       <c r="D7" t="n">
         <v>2.192013600344985</v>
@@ -1528,7 +1528,7 @@
         <v>2.25712673560289</v>
       </c>
       <c r="I7" t="n">
-        <v>2.204145692274465</v>
+        <v>2.204145692274464</v>
       </c>
       <c r="J7" t="n">
         <v>2.220665903750493</v>
@@ -1559,10 +1559,10 @@
         <v>2.25224438938815</v>
       </c>
       <c r="F8" t="n">
-        <v>2.215959360085538</v>
+        <v>2.215959360085537</v>
       </c>
       <c r="G8" t="n">
-        <v>2.307289370643918</v>
+        <v>2.307289370643917</v>
       </c>
       <c r="H8" t="n">
         <v>2.319341067058099</v>
@@ -1587,16 +1587,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.891399616916603</v>
+        <v>2.891399616916601</v>
       </c>
       <c r="C9" t="n">
-        <v>3.026180235009889</v>
+        <v>3.02618023500989</v>
       </c>
       <c r="D9" t="n">
-        <v>2.753686773227019</v>
+        <v>2.75368677322702</v>
       </c>
       <c r="E9" t="n">
-        <v>2.924245870145233</v>
+        <v>2.924245870145231</v>
       </c>
       <c r="F9" t="n">
         <v>2.765823659733508</v>
@@ -1605,19 +1605,19 @@
         <v>2.80674363182291</v>
       </c>
       <c r="H9" t="n">
-        <v>2.818795328237064</v>
+        <v>2.818795328237066</v>
       </c>
       <c r="I9" t="n">
-        <v>2.76581428490864</v>
+        <v>2.765814284908639</v>
       </c>
       <c r="J9" t="n">
         <v>2.782334496384669</v>
       </c>
       <c r="K9" t="n">
-        <v>2.667902507474398</v>
+        <v>2.667902507474399</v>
       </c>
       <c r="L9" t="n">
-        <v>2.916624779287036</v>
+        <v>2.916624779287037</v>
       </c>
     </row>
   </sheetData>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.429703053678421</v>
+        <v>2.429703053678422</v>
       </c>
       <c r="C2" t="n">
         <v>2.43202835108421</v>
@@ -1712,16 +1712,16 @@
         <v>2.407666107757353</v>
       </c>
       <c r="E2" t="n">
-        <v>2.408864395475312</v>
+        <v>2.408864395475313</v>
       </c>
       <c r="F2" t="n">
-        <v>2.408859840863781</v>
+        <v>2.408859840863782</v>
       </c>
       <c r="G2" t="n">
-        <v>2.411221654718347</v>
+        <v>2.411221654718348</v>
       </c>
       <c r="H2" t="n">
-        <v>2.411808917446671</v>
+        <v>2.41180891744667</v>
       </c>
       <c r="I2" t="n">
         <v>2.408044893722706</v>
@@ -1743,19 +1743,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.582291885403675</v>
+        <v>2.582291885403674</v>
       </c>
       <c r="C3" t="n">
         <v>2.580811829106532</v>
       </c>
       <c r="D3" t="n">
-        <v>2.425066368786559</v>
+        <v>2.42506636878656</v>
       </c>
       <c r="E3" t="n">
         <v>2.429121095424067</v>
       </c>
       <c r="F3" t="n">
-        <v>2.429116540812536</v>
+        <v>2.429116540812537</v>
       </c>
       <c r="G3" t="n">
         <v>2.450460587794999</v>
@@ -1764,13 +1764,13 @@
         <v>2.455234005600895</v>
       </c>
       <c r="I3" t="n">
-        <v>2.427777032096342</v>
+        <v>2.427777032096341</v>
       </c>
       <c r="J3" t="n">
         <v>2.450490806726509</v>
       </c>
       <c r="K3" t="n">
-        <v>2.429783306484745</v>
+        <v>2.429783306484744</v>
       </c>
       <c r="L3" t="n">
         <v>2.494920122639078</v>
@@ -1789,7 +1789,7 @@
         <v>2.360805144725701</v>
       </c>
       <c r="D4" t="n">
-        <v>2.120861674612753</v>
+        <v>2.120861674612752</v>
       </c>
       <c r="E4" t="n">
         <v>2.12803723717138</v>
@@ -1813,7 +1813,7 @@
         <v>2.11004647283691</v>
       </c>
       <c r="L4" t="n">
-        <v>2.230445848160253</v>
+        <v>2.230445848160252</v>
       </c>
     </row>
     <row r="5">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.076632138000154</v>
+        <v>7.076632138000153</v>
       </c>
       <c r="C5" t="n">
-        <v>6.869471219093696</v>
+        <v>6.869471219093705</v>
       </c>
       <c r="D5" t="n">
-        <v>2.701719676498321</v>
+        <v>2.701719676498322</v>
       </c>
       <c r="E5" t="n">
-        <v>2.781120625817892</v>
+        <v>2.781120625817893</v>
       </c>
       <c r="F5" t="n">
-        <v>2.781120625817892</v>
+        <v>2.781120625817893</v>
       </c>
       <c r="G5" t="n">
-        <v>3.421431726029216</v>
+        <v>3.421431726029214</v>
       </c>
       <c r="H5" t="n">
-        <v>3.686612238110862</v>
+        <v>3.686612238110859</v>
       </c>
       <c r="I5" t="n">
-        <v>2.781112336728516</v>
+        <v>2.781112336728515</v>
       </c>
       <c r="J5" t="n">
         <v>2.998709820668611</v>
@@ -1853,7 +1853,7 @@
         <v>2.519617513543321</v>
       </c>
       <c r="L5" t="n">
-        <v>4.930781208543626</v>
+        <v>4.93078120854363</v>
       </c>
     </row>
     <row r="6">
@@ -1866,10 +1866,10 @@
         <v>15.85718999095204</v>
       </c>
       <c r="C6" t="n">
-        <v>3.474625012261896</v>
+        <v>3.474625012261897</v>
       </c>
       <c r="D6" t="n">
-        <v>15.60786731378191</v>
+        <v>15.6078673137819</v>
       </c>
       <c r="E6" t="n">
         <v>3.229815596413161</v>
@@ -1878,22 +1878,22 @@
         <v>3.234434783003602</v>
       </c>
       <c r="G6" t="n">
-        <v>15.64844158467</v>
+        <v>15.64844158466999</v>
       </c>
       <c r="H6" t="n">
         <v>15.65589653707601</v>
       </c>
       <c r="I6" t="n">
-        <v>3.219541497072275</v>
+        <v>3.219541497072274</v>
       </c>
       <c r="J6" t="n">
-        <v>3.231527730189529</v>
+        <v>3.231527730189528</v>
       </c>
       <c r="K6" t="n">
         <v>3.187724775052751</v>
       </c>
       <c r="L6" t="n">
-        <v>3.32410805679577</v>
+        <v>3.324108056795769</v>
       </c>
     </row>
     <row r="7">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.430584176679462</v>
+        <v>2.430584176679461</v>
       </c>
       <c r="C7" t="n">
         <v>2.419735508671822</v>
@@ -1918,13 +1918,13 @@
         <v>2.186796669159091</v>
       </c>
       <c r="G7" t="n">
-        <v>2.221835770397432</v>
+        <v>2.221835770397431</v>
       </c>
       <c r="H7" t="n">
         <v>2.229044490997281</v>
       </c>
       <c r="I7" t="n">
-        <v>2.185907926228932</v>
+        <v>2.185907926228931</v>
       </c>
       <c r="J7" t="n">
         <v>2.1965618681698</v>
@@ -1949,7 +1949,7 @@
         <v>2.479480997573076</v>
       </c>
       <c r="D8" t="n">
-        <v>2.250869960784965</v>
+        <v>2.250869960784964</v>
       </c>
       <c r="E8" t="n">
         <v>2.231965554929321</v>
@@ -1961,7 +1961,7 @@
         <v>2.28072439716439</v>
       </c>
       <c r="H8" t="n">
-        <v>2.287933117764366</v>
+        <v>2.287933117764365</v>
       </c>
       <c r="I8" t="n">
         <v>2.24479655299589</v>
@@ -1970,7 +1970,7 @@
         <v>2.255460270905731</v>
       </c>
       <c r="K8" t="n">
-        <v>2.179072844253457</v>
+        <v>2.179072844253456</v>
       </c>
       <c r="L8" t="n">
         <v>2.402100580244728</v>
@@ -1986,34 +1986,34 @@
         <v>2.778266278296306</v>
       </c>
       <c r="C9" t="n">
-        <v>2.882692655799473</v>
+        <v>2.882692655799474</v>
       </c>
       <c r="D9" t="n">
         <v>2.644623854513348</v>
       </c>
       <c r="E9" t="n">
-        <v>2.781898164411442</v>
+        <v>2.781898164411441</v>
       </c>
       <c r="F9" t="n">
-        <v>2.648873257357125</v>
+        <v>2.648873257357124</v>
       </c>
       <c r="G9" t="n">
-        <v>2.684792917525086</v>
+        <v>2.684792917525085</v>
       </c>
       <c r="H9" t="n">
-        <v>2.692001638124935</v>
+        <v>2.692001638124934</v>
       </c>
       <c r="I9" t="n">
         <v>2.648865073356585</v>
       </c>
       <c r="J9" t="n">
-        <v>2.659519015297454</v>
+        <v>2.659519015297453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.567017854651287</v>
+        <v>2.567017854651286</v>
       </c>
       <c r="L9" t="n">
-        <v>2.754208055680174</v>
+        <v>2.754208055680173</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.424872235739061</v>
+        <v>2.424872235739064</v>
       </c>
       <c r="C2" t="n">
         <v>2.426484632993257</v>
       </c>
       <c r="D2" t="n">
-        <v>2.404428839442901</v>
+        <v>2.404428839442904</v>
       </c>
       <c r="E2" t="n">
-        <v>2.405727611047464</v>
+        <v>2.405727611047468</v>
       </c>
       <c r="F2" t="n">
-        <v>2.405723053243396</v>
+        <v>2.405723053243397</v>
       </c>
       <c r="G2" t="n">
-        <v>2.407356612782365</v>
+        <v>2.407356612782368</v>
       </c>
       <c r="H2" t="n">
-        <v>2.407446362558005</v>
+        <v>2.407446362558006</v>
       </c>
       <c r="I2" t="n">
-        <v>2.404271241753335</v>
+        <v>2.404271241753337</v>
       </c>
       <c r="J2" t="n">
-        <v>2.415717508021113</v>
+        <v>2.415717508021115</v>
       </c>
       <c r="K2" t="n">
-        <v>2.411254217003547</v>
+        <v>2.411254217003548</v>
       </c>
       <c r="L2" t="n">
-        <v>2.41112650398895</v>
+        <v>2.411126503988951</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.565205451354521</v>
+        <v>2.565205451354522</v>
       </c>
       <c r="C3" t="n">
         <v>2.55961994791106</v>
       </c>
       <c r="D3" t="n">
-        <v>2.419351943235239</v>
+        <v>2.419351943235241</v>
       </c>
       <c r="E3" t="n">
-        <v>2.420634499125598</v>
+        <v>2.420634499125599</v>
       </c>
       <c r="F3" t="n">
-        <v>2.420629941321527</v>
+        <v>2.420629941321529</v>
       </c>
       <c r="G3" t="n">
-        <v>2.440264051505318</v>
+        <v>2.44026405150532</v>
       </c>
       <c r="H3" t="n">
-        <v>2.441433257863088</v>
+        <v>2.441433257863089</v>
       </c>
       <c r="I3" t="n">
-        <v>2.418239023981103</v>
+        <v>2.418239023981104</v>
       </c>
       <c r="J3" t="n">
-        <v>2.44103450285164</v>
+        <v>2.441034502851644</v>
       </c>
       <c r="K3" t="n">
-        <v>2.424772709529432</v>
+        <v>2.424772709529436</v>
       </c>
       <c r="L3" t="n">
-        <v>2.467444442290749</v>
+        <v>2.46744444229075</v>
       </c>
     </row>
     <row r="4">
@@ -2203,7 +2203,7 @@
         <v>2.113002480405915</v>
       </c>
       <c r="J4" t="n">
-        <v>2.120980144506538</v>
+        <v>2.120980144506539</v>
       </c>
       <c r="K4" t="n">
         <v>2.10274140863073</v>
@@ -2219,25 +2219,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.676279255161826</v>
+        <v>6.676279255161831</v>
       </c>
       <c r="C5" t="n">
-        <v>6.365246661559891</v>
+        <v>6.365246661559892</v>
       </c>
       <c r="D5" t="n">
-        <v>2.619084495479632</v>
+        <v>2.619084495479631</v>
       </c>
       <c r="E5" t="n">
-        <v>2.593723215872465</v>
+        <v>2.593723215872467</v>
       </c>
       <c r="F5" t="n">
-        <v>2.593723215872465</v>
+        <v>2.593723215872467</v>
       </c>
       <c r="G5" t="n">
-        <v>3.212521479244634</v>
+        <v>3.212521479244638</v>
       </c>
       <c r="H5" t="n">
-        <v>3.350482325884995</v>
+        <v>3.350482325885</v>
       </c>
       <c r="I5" t="n">
         <v>2.59371516884741</v>
@@ -2246,7 +2246,7 @@
         <v>2.756161965570944</v>
       </c>
       <c r="K5" t="n">
-        <v>2.41518334088574</v>
+        <v>2.415183340885742</v>
       </c>
       <c r="L5" t="n">
         <v>4.16973648070103</v>
@@ -2262,31 +2262,31 @@
         <v>3.438905451893313</v>
       </c>
       <c r="C6" t="n">
-        <v>3.442747706821079</v>
+        <v>3.442747706821078</v>
       </c>
       <c r="D6" t="n">
-        <v>3.205944595173168</v>
+        <v>3.205944595173167</v>
       </c>
       <c r="E6" t="n">
         <v>3.216654381918635</v>
       </c>
       <c r="F6" t="n">
-        <v>3.221169731909607</v>
+        <v>3.221169731909608</v>
       </c>
       <c r="G6" t="n">
-        <v>15.63307040086132</v>
+        <v>15.63307040086131</v>
       </c>
       <c r="H6" t="n">
         <v>15.63534526090347</v>
       </c>
       <c r="I6" t="n">
-        <v>15.59817910034037</v>
+        <v>15.59817910034034</v>
       </c>
       <c r="J6" t="n">
         <v>15.60601907808969</v>
       </c>
       <c r="K6" t="n">
-        <v>3.179338640242691</v>
+        <v>3.179338640242688</v>
       </c>
       <c r="L6" t="n">
         <v>3.282530653043302</v>
@@ -2299,19 +2299,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.406202016315842</v>
+        <v>2.406202016315843</v>
       </c>
       <c r="C7" t="n">
-        <v>2.389306842355643</v>
+        <v>2.389306842355644</v>
       </c>
       <c r="D7" t="n">
         <v>2.175279990250083</v>
       </c>
       <c r="E7" t="n">
-        <v>2.174519016510448</v>
+        <v>2.174519016510449</v>
       </c>
       <c r="F7" t="n">
-        <v>2.174519016510448</v>
+        <v>2.174519016510449</v>
       </c>
       <c r="G7" t="n">
         <v>2.208363109896308</v>
@@ -2342,19 +2342,19 @@
         <v>2.414989684304668</v>
       </c>
       <c r="C8" t="n">
-        <v>2.448488526308112</v>
+        <v>2.448488526308113</v>
       </c>
       <c r="D8" t="n">
         <v>2.243697508892748</v>
       </c>
       <c r="E8" t="n">
-        <v>2.219046973677454</v>
+        <v>2.219046973677456</v>
       </c>
       <c r="F8" t="n">
-        <v>2.184455525308632</v>
+        <v>2.184455525308633</v>
       </c>
       <c r="G8" t="n">
-        <v>2.266535851366531</v>
+        <v>2.266535851366532</v>
       </c>
       <c r="H8" t="n">
         <v>2.26812482749878</v>
@@ -2366,10 +2366,10 @@
         <v>2.239631920508256</v>
       </c>
       <c r="K8" t="n">
-        <v>2.171081052495991</v>
+        <v>2.171081052495992</v>
       </c>
       <c r="L8" t="n">
-        <v>2.360462912251965</v>
+        <v>2.360462912251968</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.712570566116962</v>
+        <v>2.712570566116963</v>
       </c>
       <c r="C9" t="n">
-        <v>2.799467947977631</v>
+        <v>2.799467947977633</v>
       </c>
       <c r="D9" t="n">
-        <v>2.585445533032631</v>
+        <v>2.585445533032632</v>
       </c>
       <c r="E9" t="n">
-        <v>2.703415228552951</v>
+        <v>2.703415228552952</v>
       </c>
       <c r="F9" t="n">
-        <v>2.583640865178723</v>
+        <v>2.583640865178724</v>
       </c>
       <c r="G9" t="n">
-        <v>2.618524215518293</v>
+        <v>2.618524215518294</v>
       </c>
       <c r="H9" t="n">
-        <v>2.620113191650306</v>
+        <v>2.620113191650307</v>
       </c>
       <c r="I9" t="n">
-        <v>2.58363291499733</v>
+        <v>2.583632914997332</v>
       </c>
       <c r="J9" t="n">
-        <v>2.591610579097955</v>
+        <v>2.591610579097956</v>
       </c>
       <c r="K9" t="n">
-        <v>2.510794152398991</v>
+        <v>2.510794152398992</v>
       </c>
       <c r="L9" t="n">
-        <v>2.660864437657127</v>
+        <v>2.660864437657128</v>
       </c>
     </row>
   </sheetData>
@@ -2504,28 +2504,28 @@
         <v>2.411574395161739</v>
       </c>
       <c r="E2" t="n">
-        <v>2.413613356853172</v>
+        <v>2.413613356853173</v>
       </c>
       <c r="F2" t="n">
-        <v>2.413608793022316</v>
+        <v>2.413608793022317</v>
       </c>
       <c r="G2" t="n">
         <v>2.416357774887741</v>
       </c>
       <c r="H2" t="n">
-        <v>2.420885320331668</v>
+        <v>2.420885320331669</v>
       </c>
       <c r="I2" t="n">
-        <v>2.412924123154321</v>
+        <v>2.412924123154323</v>
       </c>
       <c r="J2" t="n">
-        <v>2.424492584258647</v>
+        <v>2.424492584258648</v>
       </c>
       <c r="K2" t="n">
-        <v>2.418580076234738</v>
+        <v>2.418580076234741</v>
       </c>
       <c r="L2" t="n">
-        <v>2.427406787479968</v>
+        <v>2.427406787479969</v>
       </c>
     </row>
     <row r="3">
@@ -2535,7 +2535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.601473163426665</v>
+        <v>2.601473163426666</v>
       </c>
       <c r="C3" t="n">
         <v>2.638612952274585</v>
@@ -2544,28 +2544,28 @@
         <v>2.426530344560414</v>
       </c>
       <c r="E3" t="n">
-        <v>2.437287028732301</v>
+        <v>2.4372870287323</v>
       </c>
       <c r="F3" t="n">
-        <v>2.437282464901444</v>
+        <v>2.437282464901443</v>
       </c>
       <c r="G3" t="n">
-        <v>2.460678923087252</v>
+        <v>2.460678923087253</v>
       </c>
       <c r="H3" t="n">
         <v>2.493490378152388</v>
       </c>
       <c r="I3" t="n">
-        <v>2.436158460221891</v>
+        <v>2.436158460221892</v>
       </c>
       <c r="J3" t="n">
         <v>2.467581711601622</v>
       </c>
       <c r="K3" t="n">
-        <v>2.437222397435832</v>
+        <v>2.437222397435835</v>
       </c>
       <c r="L3" t="n">
-        <v>2.539590882877849</v>
+        <v>2.53959088287785</v>
       </c>
     </row>
     <row r="4">
@@ -2578,7 +2578,7 @@
         <v>2.397462718636511</v>
       </c>
       <c r="C4" t="n">
-        <v>2.44478445094221</v>
+        <v>2.444784450942209</v>
       </c>
       <c r="D4" t="n">
         <v>2.120484754927451</v>
@@ -2593,7 +2593,7 @@
         <v>2.17452330476832</v>
       </c>
       <c r="H4" t="n">
-        <v>2.225795732601955</v>
+        <v>2.225795732601954</v>
       </c>
       <c r="I4" t="n">
         <v>2.135694730874941</v>
@@ -2605,7 +2605,7 @@
         <v>2.118675937084995</v>
       </c>
       <c r="L4" t="n">
-        <v>2.297995734138444</v>
+        <v>2.297995734138442</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.795117343024321</v>
+        <v>7.795117343024332</v>
       </c>
       <c r="C5" t="n">
-        <v>8.590708112244631</v>
+        <v>8.590708112244627</v>
       </c>
       <c r="D5" t="n">
-        <v>2.674679504347199</v>
+        <v>2.674679504347198</v>
       </c>
       <c r="E5" t="n">
-        <v>2.955773547518412</v>
+        <v>2.955773547518425</v>
       </c>
       <c r="F5" t="n">
-        <v>2.955773547518412</v>
+        <v>2.955773547518425</v>
       </c>
       <c r="G5" t="n">
-        <v>3.685707031104341</v>
+        <v>3.68570703110434</v>
       </c>
       <c r="H5" t="n">
-        <v>4.871388831375363</v>
+        <v>4.871388831375358</v>
       </c>
       <c r="I5" t="n">
-        <v>2.955764633834651</v>
+        <v>2.955764633834669</v>
       </c>
       <c r="J5" t="n">
-        <v>3.464957048836465</v>
+        <v>3.464957048836467</v>
       </c>
       <c r="K5" t="n">
-        <v>2.644540075657211</v>
+        <v>2.64454007565721</v>
       </c>
       <c r="L5" t="n">
-        <v>6.407775772253296</v>
+        <v>6.407775772253299</v>
       </c>
     </row>
     <row r="6">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.555666440751517</v>
+        <v>3.55566644075152</v>
       </c>
       <c r="C6" t="n">
-        <v>3.624847362371366</v>
+        <v>3.624847362371362</v>
       </c>
       <c r="D6" t="n">
         <v>3.275716177748025</v>
@@ -2679,10 +2679,10 @@
         <v>16.37973069382852</v>
       </c>
       <c r="J6" t="n">
-        <v>3.320681583701828</v>
+        <v>3.320681583701829</v>
       </c>
       <c r="K6" t="n">
-        <v>3.258994097978229</v>
+        <v>3.25899409797823</v>
       </c>
       <c r="L6" t="n">
         <v>3.455613585878766</v>
@@ -2698,34 +2698,34 @@
         <v>2.462315756034279</v>
       </c>
       <c r="C7" t="n">
-        <v>2.506788701260135</v>
+        <v>2.506788701260134</v>
       </c>
       <c r="D7" t="n">
-        <v>2.18533322973042</v>
+        <v>2.185333229730419</v>
       </c>
       <c r="E7" t="n">
-        <v>2.201877186057675</v>
+        <v>2.201877186057676</v>
       </c>
       <c r="F7" t="n">
-        <v>2.201877186057675</v>
+        <v>2.201877186057676</v>
       </c>
       <c r="G7" t="n">
-        <v>2.239376342166088</v>
+        <v>2.239376342166089</v>
       </c>
       <c r="H7" t="n">
         <v>2.290648769999724</v>
       </c>
       <c r="I7" t="n">
-        <v>2.200547768272709</v>
+        <v>2.20054776827271</v>
       </c>
       <c r="J7" t="n">
         <v>2.225815193904873</v>
       </c>
       <c r="K7" t="n">
-        <v>2.183528974482764</v>
+        <v>2.183528974482763</v>
       </c>
       <c r="L7" t="n">
-        <v>2.362848771536211</v>
+        <v>2.362848771536212</v>
       </c>
     </row>
     <row r="8">
@@ -2741,7 +2741,7 @@
         <v>2.571355503341743</v>
       </c>
       <c r="D8" t="n">
-        <v>2.259662947957856</v>
+        <v>2.259662947957855</v>
       </c>
       <c r="E8" t="n">
         <v>2.250430779488786</v>
@@ -2759,13 +2759,13 @@
         <v>2.263836396384568</v>
       </c>
       <c r="J8" t="n">
-        <v>2.289114282215621</v>
+        <v>2.289114282215622</v>
       </c>
       <c r="K8" t="n">
         <v>2.192604033662932</v>
       </c>
       <c r="L8" t="n">
-        <v>2.481735247087457</v>
+        <v>2.481735247087459</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.884291890409524</v>
+        <v>2.884291890409525</v>
       </c>
       <c r="C9" t="n">
-        <v>3.065847672169741</v>
+        <v>3.065847672169742</v>
       </c>
       <c r="D9" t="n">
-        <v>2.744396713251733</v>
+        <v>2.744396713251734</v>
       </c>
       <c r="E9" t="n">
-        <v>2.917806124571781</v>
+        <v>2.917806124571783</v>
       </c>
       <c r="F9" t="n">
-        <v>2.759615516989464</v>
+        <v>2.759615516989466</v>
       </c>
       <c r="G9" t="n">
         <v>2.798435313075692</v>
       </c>
       <c r="H9" t="n">
-        <v>2.849707740909329</v>
+        <v>2.849707740909331</v>
       </c>
       <c r="I9" t="n">
-        <v>2.759606739182314</v>
+        <v>2.759606739182316</v>
       </c>
       <c r="J9" t="n">
-        <v>2.784874164814477</v>
+        <v>2.784874164814479</v>
       </c>
       <c r="K9" t="n">
-        <v>2.663161590515864</v>
+        <v>2.663161590515865</v>
       </c>
       <c r="L9" t="n">
-        <v>2.921907742445817</v>
+        <v>2.921907742445819</v>
       </c>
     </row>
   </sheetData>
@@ -2891,31 +2891,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.42506505576783</v>
+        <v>2.425065055767832</v>
       </c>
       <c r="C2" t="n">
         <v>2.43190063503482</v>
       </c>
       <c r="D2" t="n">
-        <v>2.405110351882837</v>
+        <v>2.405110351882838</v>
       </c>
       <c r="E2" t="n">
-        <v>2.408314114952566</v>
+        <v>2.408314114952567</v>
       </c>
       <c r="F2" t="n">
-        <v>2.408309530369737</v>
+        <v>2.408309530369739</v>
       </c>
       <c r="G2" t="n">
-        <v>2.408703058264908</v>
+        <v>2.408703058264909</v>
       </c>
       <c r="H2" t="n">
         <v>2.41773055061556</v>
       </c>
       <c r="I2" t="n">
-        <v>2.406286712627542</v>
+        <v>2.406286712627544</v>
       </c>
       <c r="J2" t="n">
-        <v>2.418433897446724</v>
+        <v>2.418433897446725</v>
       </c>
       <c r="K2" t="n">
         <v>2.413829033118536</v>
@@ -2946,19 +2946,19 @@
         <v>2.42591646906183</v>
       </c>
       <c r="G3" t="n">
-        <v>2.439839667112428</v>
+        <v>2.439839667112429</v>
       </c>
       <c r="H3" t="n">
         <v>2.504439590573593</v>
       </c>
       <c r="I3" t="n">
-        <v>2.42258365878179</v>
+        <v>2.422583658781791</v>
       </c>
       <c r="J3" t="n">
-        <v>2.44822354039195</v>
+        <v>2.448223540391951</v>
       </c>
       <c r="K3" t="n">
-        <v>2.427498688554976</v>
+        <v>2.427498688554977</v>
       </c>
       <c r="L3" t="n">
         <v>2.47559331704242</v>
@@ -3014,34 +3014,34 @@
         <v>6.397909966043917</v>
       </c>
       <c r="C5" t="n">
-        <v>6.902919362041221</v>
+        <v>6.902919362041215</v>
       </c>
       <c r="D5" t="n">
-        <v>2.442922710462044</v>
+        <v>2.442922710462043</v>
       </c>
       <c r="E5" t="n">
-        <v>2.674485411815575</v>
+        <v>2.674485411815576</v>
       </c>
       <c r="F5" t="n">
-        <v>2.674485411815575</v>
+        <v>2.674485411815576</v>
       </c>
       <c r="G5" t="n">
-        <v>3.162619667211974</v>
+        <v>3.162619667211971</v>
       </c>
       <c r="H5" t="n">
-        <v>5.205874707209412</v>
+        <v>5.20587470720942</v>
       </c>
       <c r="I5" t="n">
         <v>2.674479180199205</v>
       </c>
       <c r="J5" t="n">
-        <v>2.901821529351124</v>
+        <v>2.901821529351125</v>
       </c>
       <c r="K5" t="n">
         <v>2.405949868557118</v>
       </c>
       <c r="L5" t="n">
-        <v>4.376919711799777</v>
+        <v>4.376919711799775</v>
       </c>
     </row>
     <row r="6">
@@ -3054,19 +3054,19 @@
         <v>3.425159178631191</v>
       </c>
       <c r="C6" t="n">
-        <v>3.47688561048698</v>
+        <v>3.476885610486979</v>
       </c>
       <c r="D6" t="n">
         <v>15.5917428621071</v>
       </c>
       <c r="E6" t="n">
-        <v>3.22401291899532</v>
+        <v>3.224012918995321</v>
       </c>
       <c r="F6" t="n">
-        <v>3.228312117898686</v>
+        <v>3.228312117898687</v>
       </c>
       <c r="G6" t="n">
-        <v>3.240358423457934</v>
+        <v>3.240358423457933</v>
       </c>
       <c r="H6" t="n">
         <v>15.73568065847047</v>
@@ -3075,10 +3075,10 @@
         <v>15.60513768802993</v>
       </c>
       <c r="J6" t="n">
-        <v>15.61659708090971</v>
+        <v>15.61659708090972</v>
       </c>
       <c r="K6" t="n">
-        <v>3.181086446132741</v>
+        <v>3.181086446132739</v>
       </c>
       <c r="L6" t="n">
         <v>3.2954385080724</v>
@@ -3094,7 +3094,7 @@
         <v>2.392104601774727</v>
       </c>
       <c r="C7" t="n">
-        <v>2.421931602443359</v>
+        <v>2.421931602443358</v>
       </c>
       <c r="D7" t="n">
         <v>2.166702567532107</v>
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.400731403651651</v>
+        <v>2.40073140365165</v>
       </c>
       <c r="C8" t="n">
-        <v>2.481844820681381</v>
+        <v>2.48184482068138</v>
       </c>
       <c r="D8" t="n">
         <v>2.235371244729372</v>
@@ -3155,7 +3155,7 @@
         <v>2.238362096117626</v>
       </c>
       <c r="J8" t="n">
-        <v>2.249761766855438</v>
+        <v>2.249761766855437</v>
       </c>
       <c r="K8" t="n">
         <v>2.172159512253663</v>
@@ -3174,25 +3174,25 @@
         <v>2.735321102798451</v>
       </c>
       <c r="C9" t="n">
-        <v>2.879324192714809</v>
+        <v>2.87932419271481</v>
       </c>
       <c r="D9" t="n">
-        <v>2.624099582076155</v>
+        <v>2.624099582076156</v>
       </c>
       <c r="E9" t="n">
         <v>2.769164381836672</v>
       </c>
       <c r="F9" t="n">
-        <v>2.637407671202743</v>
+        <v>2.637407671202744</v>
       </c>
       <c r="G9" t="n">
         <v>2.66469643687292</v>
       </c>
       <c r="H9" t="n">
-        <v>2.766076313363909</v>
+        <v>2.766076313363911</v>
       </c>
       <c r="I9" t="n">
-        <v>2.637401560628587</v>
+        <v>2.637401560628588</v>
       </c>
       <c r="J9" t="n">
         <v>2.648791458739922</v>
@@ -3311,7 +3311,7 @@
         <v>2.400809982188519</v>
       </c>
       <c r="J2" t="n">
-        <v>2.415127882075917</v>
+        <v>2.415127882075916</v>
       </c>
       <c r="K2" t="n">
         <v>2.41007909932483</v>
@@ -3339,7 +3339,7 @@
         <v>2.41587374241374</v>
       </c>
       <c r="F3" t="n">
-        <v>2.415869202608801</v>
+        <v>2.415869202608802</v>
       </c>
       <c r="G3" t="n">
         <v>2.424279507881694</v>
@@ -3351,10 +3351,10 @@
         <v>2.410679990227143</v>
       </c>
       <c r="J3" t="n">
-        <v>2.439415894349929</v>
+        <v>2.43941589434993</v>
       </c>
       <c r="K3" t="n">
-        <v>2.421287367016368</v>
+        <v>2.421287367016369</v>
       </c>
       <c r="L3" t="n">
         <v>2.434407410443328</v>
@@ -3367,13 +3367,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.277405737707266</v>
+        <v>2.277405737707265</v>
       </c>
       <c r="C4" t="n">
-        <v>2.283913856288481</v>
+        <v>2.28391385628848</v>
       </c>
       <c r="D4" t="n">
-        <v>2.104339026845692</v>
+        <v>2.104339026845691</v>
       </c>
       <c r="E4" t="n">
         <v>2.110973597773795</v>
@@ -3382,22 +3382,22 @@
         <v>2.110973597773795</v>
       </c>
       <c r="G4" t="n">
-        <v>2.128634697688081</v>
+        <v>2.128634697688073</v>
       </c>
       <c r="H4" t="n">
-        <v>2.201347266726588</v>
+        <v>2.201347266726589</v>
       </c>
       <c r="I4" t="n">
-        <v>2.107124697855572</v>
+        <v>2.107124697855573</v>
       </c>
       <c r="J4" t="n">
-        <v>2.117537987792067</v>
+        <v>2.117537987792066</v>
       </c>
       <c r="K4" t="n">
         <v>2.097427289868652</v>
       </c>
       <c r="L4" t="n">
-        <v>2.144296976202432</v>
+        <v>2.144296976202433</v>
       </c>
     </row>
     <row r="5">
@@ -3407,31 +3407,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.461816264612374</v>
+        <v>5.461816264612365</v>
       </c>
       <c r="C5" t="n">
-        <v>5.504832468397223</v>
+        <v>5.504832468397226</v>
       </c>
       <c r="D5" t="n">
         <v>2.424065660096847</v>
       </c>
       <c r="E5" t="n">
-        <v>2.474877399704611</v>
+        <v>2.474877399704607</v>
       </c>
       <c r="F5" t="n">
-        <v>2.474877399704611</v>
+        <v>2.474877399704607</v>
       </c>
       <c r="G5" t="n">
-        <v>2.858278673286407</v>
+        <v>2.858278673286403</v>
       </c>
       <c r="H5" t="n">
         <v>4.324099382558485</v>
       </c>
       <c r="I5" t="n">
-        <v>2.474872450309392</v>
+        <v>2.474872450309388</v>
       </c>
       <c r="J5" t="n">
-        <v>2.676921187537765</v>
+        <v>2.676921187537767</v>
       </c>
       <c r="K5" t="n">
         <v>2.307480263820139</v>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.7604847274048</v>
+        <v>15.76048472740479</v>
       </c>
       <c r="C6" t="n">
-        <v>3.392594635210383</v>
+        <v>3.392594635210382</v>
       </c>
       <c r="D6" t="n">
-        <v>3.19430586172663</v>
+        <v>3.194305861726631</v>
       </c>
       <c r="E6" t="n">
         <v>3.209930637305501</v>
@@ -3468,7 +3468,7 @@
         <v>3.292642752229205</v>
       </c>
       <c r="I6" t="n">
-        <v>15.59020368755314</v>
+        <v>15.59020368755316</v>
       </c>
       <c r="J6" t="n">
         <v>3.210878668465139</v>
@@ -3477,7 +3477,7 @@
         <v>3.173128993781288</v>
       </c>
       <c r="L6" t="n">
-        <v>3.235231702170027</v>
+        <v>3.235231702170029</v>
       </c>
     </row>
     <row r="7">
@@ -3505,7 +3505,7 @@
         <v>2.18891767358105</v>
       </c>
       <c r="H7" t="n">
-        <v>2.261630242619565</v>
+        <v>2.261630242619566</v>
       </c>
       <c r="I7" t="n">
         <v>2.167407673748551</v>
@@ -3514,10 +3514,10 @@
         <v>2.177820963685044</v>
       </c>
       <c r="K7" t="n">
-        <v>2.157710265761628</v>
+        <v>2.15771026576163</v>
       </c>
       <c r="L7" t="n">
-        <v>2.20457995209541</v>
+        <v>2.204579952095411</v>
       </c>
     </row>
     <row r="8">
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.346320687114931</v>
+        <v>2.346320687114932</v>
       </c>
       <c r="C8" t="n">
         <v>2.400310654349605</v>
@@ -3542,7 +3542,7 @@
         <v>2.178318995192905</v>
       </c>
       <c r="G8" t="n">
-        <v>2.247304675892574</v>
+        <v>2.247304675892575</v>
       </c>
       <c r="H8" t="n">
         <v>2.320017244931705</v>
@@ -3551,13 +3551,13 @@
         <v>2.225794676060076</v>
       </c>
       <c r="J8" t="n">
-        <v>2.236217744249147</v>
+        <v>2.236217744249148</v>
       </c>
       <c r="K8" t="n">
         <v>2.165418014074707</v>
       </c>
       <c r="L8" t="n">
-        <v>2.314940242400554</v>
+        <v>2.314940242400556</v>
       </c>
     </row>
     <row r="9">
@@ -3573,16 +3573,16 @@
         <v>2.743617097994088</v>
       </c>
       <c r="D9" t="n">
-        <v>2.56744461803871</v>
+        <v>2.567444618038712</v>
       </c>
       <c r="E9" t="n">
-        <v>2.688359408767508</v>
+        <v>2.688359408767509</v>
       </c>
       <c r="F9" t="n">
-        <v>2.570235173371339</v>
+        <v>2.57023517337134</v>
       </c>
       <c r="G9" t="n">
-        <v>2.591740324742504</v>
+        <v>2.591740324742506</v>
       </c>
       <c r="H9" t="n">
         <v>2.664452893781024</v>
@@ -3591,13 +3591,13 @@
         <v>2.570230324910006</v>
       </c>
       <c r="J9" t="n">
-        <v>2.580643614846497</v>
+        <v>2.580643614846498</v>
       </c>
       <c r="K9" t="n">
         <v>2.501223597800107</v>
       </c>
       <c r="L9" t="n">
-        <v>2.607402603256869</v>
+        <v>2.60740260325687</v>
       </c>
     </row>
   </sheetData>
@@ -3683,34 +3683,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.435696222050406</v>
+        <v>2.435696222050417</v>
       </c>
       <c r="C2" t="n">
-        <v>2.445652399701582</v>
+        <v>2.445652399701591</v>
       </c>
       <c r="D2" t="n">
-        <v>2.41091998516749</v>
+        <v>2.410919985167488</v>
       </c>
       <c r="E2" t="n">
-        <v>2.414056278081486</v>
+        <v>2.4140562780815</v>
       </c>
       <c r="F2" t="n">
-        <v>2.414051710658287</v>
+        <v>2.414051710658299</v>
       </c>
       <c r="G2" t="n">
-        <v>2.416307571054221</v>
+        <v>2.416307571054219</v>
       </c>
       <c r="H2" t="n">
-        <v>2.420776115424853</v>
+        <v>2.420776115424861</v>
       </c>
       <c r="I2" t="n">
         <v>2.412913730033591</v>
       </c>
       <c r="J2" t="n">
-        <v>2.424029665098462</v>
+        <v>2.424029665098467</v>
       </c>
       <c r="K2" t="n">
-        <v>2.418936457689208</v>
+        <v>2.418936457689215</v>
       </c>
       <c r="L2" t="n">
         <v>2.428306227277545</v>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.597884314798709</v>
+        <v>2.59788431479871</v>
       </c>
       <c r="C3" t="n">
         <v>2.635263492737006</v>
@@ -3732,25 +3732,25 @@
         <v>2.421130322964121</v>
       </c>
       <c r="E3" t="n">
-        <v>2.437221514053182</v>
+        <v>2.437221514053181</v>
       </c>
       <c r="F3" t="n">
         <v>2.43721694662998</v>
       </c>
       <c r="G3" t="n">
-        <v>2.459580783933872</v>
+        <v>2.459580783933874</v>
       </c>
       <c r="H3" t="n">
         <v>2.491966594886512</v>
       </c>
       <c r="I3" t="n">
-        <v>2.435344850544672</v>
+        <v>2.435344850544673</v>
       </c>
       <c r="J3" t="n">
-        <v>2.460813171007849</v>
+        <v>2.460813171007848</v>
       </c>
       <c r="K3" t="n">
-        <v>2.435749611098063</v>
+        <v>2.435749611098065</v>
       </c>
       <c r="L3" t="n">
         <v>2.545217186801176</v>
@@ -3781,7 +3781,7 @@
         <v>2.173255545631185</v>
       </c>
       <c r="H4" t="n">
-        <v>2.223863672815863</v>
+        <v>2.223863672815862</v>
       </c>
       <c r="I4" t="n">
         <v>2.134881976233304</v>
@@ -3793,7 +3793,7 @@
         <v>2.115246391378896</v>
       </c>
       <c r="L4" t="n">
-        <v>2.307297284296599</v>
+        <v>2.3072972842966</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.696727988430067</v>
+        <v>7.696727988430063</v>
       </c>
       <c r="C5" t="n">
-        <v>8.472142421728293</v>
+        <v>8.4721424217283</v>
       </c>
       <c r="D5" t="n">
-        <v>2.527691756483934</v>
+        <v>2.527691756483933</v>
       </c>
       <c r="E5" t="n">
-        <v>2.938768566535464</v>
+        <v>2.938768566535463</v>
       </c>
       <c r="F5" t="n">
-        <v>2.938768566535464</v>
+        <v>2.938768566535463</v>
       </c>
       <c r="G5" t="n">
-        <v>3.660107034477631</v>
+        <v>3.660107034477639</v>
       </c>
       <c r="H5" t="n">
-        <v>4.82999736536881</v>
+        <v>4.829997365368808</v>
       </c>
       <c r="I5" t="n">
-        <v>2.93875976648364</v>
+        <v>2.938759766483641</v>
       </c>
       <c r="J5" t="n">
-        <v>3.245965980763436</v>
+        <v>3.245965980763441</v>
       </c>
       <c r="K5" t="n">
         <v>2.580738855835148</v>
       </c>
       <c r="L5" t="n">
-        <v>6.59631239075121</v>
+        <v>6.596312390751209</v>
       </c>
     </row>
     <row r="6">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.55015963734634</v>
+        <v>3.550159637346338</v>
       </c>
       <c r="C6" t="n">
         <v>3.618046420723904</v>
@@ -3864,16 +3864,16 @@
         <v>16.46759723255742</v>
       </c>
       <c r="I6" t="n">
-        <v>3.29279147349247</v>
+        <v>3.292791473492469</v>
       </c>
       <c r="J6" t="n">
-        <v>3.308811601258104</v>
+        <v>3.308811601258103</v>
       </c>
       <c r="K6" t="n">
-        <v>3.255205377713696</v>
+        <v>3.2552053777137</v>
       </c>
       <c r="L6" t="n">
-        <v>3.464699699680962</v>
+        <v>3.464699699680964</v>
       </c>
     </row>
     <row r="7">
@@ -3886,7 +3886,7 @@
         <v>2.457414302250194</v>
       </c>
       <c r="C7" t="n">
-        <v>2.500764838559817</v>
+        <v>2.500764838559818</v>
       </c>
       <c r="D7" t="n">
         <v>2.177550777190073</v>
@@ -3910,10 +3910,10 @@
         <v>2.214594473620183</v>
       </c>
       <c r="K7" t="n">
-        <v>2.18041055354192</v>
+        <v>2.180410553541921</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372461446459624</v>
+        <v>2.372461446459625</v>
       </c>
     </row>
     <row r="8">
@@ -3932,7 +3932,7 @@
         <v>2.252427816118197</v>
       </c>
       <c r="E8" t="n">
-        <v>2.250469720013223</v>
+        <v>2.250469720013224</v>
       </c>
       <c r="F8" t="n">
         <v>2.212811902026963</v>
@@ -3950,10 +3950,10 @@
         <v>2.278360266429246</v>
       </c>
       <c r="K8" t="n">
-        <v>2.189555711345369</v>
+        <v>2.18955571134537</v>
       </c>
       <c r="L8" t="n">
-        <v>2.492221204272589</v>
+        <v>2.49222120427259</v>
       </c>
     </row>
     <row r="9">
@@ -3969,13 +3969,13 @@
         <v>3.059164859425573</v>
       </c>
       <c r="D9" t="n">
-        <v>2.735955280497784</v>
+        <v>2.735955280497785</v>
       </c>
       <c r="E9" t="n">
-        <v>2.916614535598695</v>
+        <v>2.916614535598696</v>
       </c>
       <c r="F9" t="n">
-        <v>2.758454824537568</v>
+        <v>2.758454824537567</v>
       </c>
       <c r="G9" t="n">
         <v>2.796819728659968</v>
@@ -3987,13 +3987,13 @@
         <v>2.758446159262083</v>
       </c>
       <c r="J9" t="n">
-        <v>2.772994494485939</v>
+        <v>2.77299449448594</v>
       </c>
       <c r="K9" t="n">
         <v>2.659399733091907</v>
       </c>
       <c r="L9" t="n">
-        <v>2.93086146732538</v>
+        <v>2.930861467325381</v>
       </c>
     </row>
   </sheetData>
@@ -4079,34 +4079,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.423058648994835</v>
+        <v>2.423058648994834</v>
       </c>
       <c r="C2" t="n">
         <v>2.431936890360708</v>
       </c>
       <c r="D2" t="n">
-        <v>2.404654094460386</v>
+        <v>2.404654094460384</v>
       </c>
       <c r="E2" t="n">
-        <v>2.409699964520145</v>
+        <v>2.409699964520144</v>
       </c>
       <c r="F2" t="n">
         <v>2.409695375740845</v>
       </c>
       <c r="G2" t="n">
-        <v>2.408031793920271</v>
+        <v>2.40803179392027</v>
       </c>
       <c r="H2" t="n">
         <v>2.415753788502832</v>
       </c>
       <c r="I2" t="n">
-        <v>2.405467773856385</v>
+        <v>2.405467773856384</v>
       </c>
       <c r="J2" t="n">
         <v>2.420054110781892</v>
       </c>
       <c r="K2" t="n">
-        <v>2.416077160004444</v>
+        <v>2.416077160004443</v>
       </c>
       <c r="L2" t="n">
         <v>2.413736529645053</v>
@@ -4125,10 +4125,10 @@
         <v>2.573239021853729</v>
       </c>
       <c r="D3" t="n">
-        <v>2.412870375470256</v>
+        <v>2.412870375470255</v>
       </c>
       <c r="E3" t="n">
-        <v>2.425652321581209</v>
+        <v>2.42565232158121</v>
       </c>
       <c r="F3" t="n">
         <v>2.425647732801909</v>
@@ -4146,10 +4146,10 @@
         <v>2.448852241236339</v>
       </c>
       <c r="K3" t="n">
-        <v>2.429681375347492</v>
+        <v>2.429681375347491</v>
       </c>
       <c r="L3" t="n">
-        <v>2.477863472397248</v>
+        <v>2.477863472397249</v>
       </c>
     </row>
     <row r="4">
@@ -4159,13 +4159,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.315372602683306</v>
+        <v>2.315372602683307</v>
       </c>
       <c r="C4" t="n">
         <v>2.346827117198273</v>
       </c>
       <c r="D4" t="n">
-        <v>2.107484692703318</v>
+        <v>2.107484692703319</v>
       </c>
       <c r="E4" t="n">
         <v>2.12348091826648</v>
@@ -4177,16 +4177,16 @@
         <v>2.145652473045555</v>
       </c>
       <c r="H4" t="n">
-        <v>2.23245679729466</v>
+        <v>2.232456797294661</v>
       </c>
       <c r="I4" t="n">
         <v>2.116686031898254</v>
       </c>
       <c r="J4" t="n">
-        <v>2.129135152446748</v>
+        <v>2.129135152446747</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1032579728027</v>
+        <v>2.103257972802701</v>
       </c>
       <c r="L4" t="n">
         <v>2.209522224918674</v>
@@ -4199,28 +4199,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.1281307487821</v>
+        <v>6.128130748782104</v>
       </c>
       <c r="C5" t="n">
-        <v>6.63442657087044</v>
+        <v>6.634426570870436</v>
       </c>
       <c r="D5" t="n">
-        <v>2.478848291248539</v>
+        <v>2.478848291248541</v>
       </c>
       <c r="E5" t="n">
-        <v>2.640453346947315</v>
+        <v>2.64045334694731</v>
       </c>
       <c r="F5" t="n">
-        <v>2.640453346947315</v>
+        <v>2.64045334694731</v>
       </c>
       <c r="G5" t="n">
-        <v>3.157130257645734</v>
+        <v>3.157130257645738</v>
       </c>
       <c r="H5" t="n">
         <v>4.920937101942995</v>
       </c>
       <c r="I5" t="n">
-        <v>2.640446706225558</v>
+        <v>2.64044670622556</v>
       </c>
       <c r="J5" t="n">
         <v>2.885289965819871</v>
@@ -4239,25 +4239,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.80141336850395</v>
+        <v>15.80141336850394</v>
       </c>
       <c r="C6" t="n">
-        <v>3.46044971051235</v>
+        <v>3.460449710512348</v>
       </c>
       <c r="D6" t="n">
-        <v>3.199153295654212</v>
+        <v>3.199153295654211</v>
       </c>
       <c r="E6" t="n">
-        <v>3.221686123162881</v>
+        <v>3.221686123162882</v>
       </c>
       <c r="F6" t="n">
         <v>3.225934015890054</v>
       </c>
       <c r="G6" t="n">
-        <v>3.239506370775767</v>
+        <v>3.239506370775768</v>
       </c>
       <c r="H6" t="n">
-        <v>15.72025419651755</v>
+        <v>15.72025419651756</v>
       </c>
       <c r="I6" t="n">
         <v>15.6027267977189</v>
@@ -4285,7 +4285,7 @@
         <v>2.406625637823165</v>
       </c>
       <c r="D7" t="n">
-        <v>2.168906609920021</v>
+        <v>2.168906609920023</v>
       </c>
       <c r="E7" t="n">
         <v>2.180086815861943</v>
@@ -4303,7 +4303,7 @@
         <v>2.178112249117239</v>
       </c>
       <c r="J7" t="n">
-        <v>2.190561369665734</v>
+        <v>2.190561369665733</v>
       </c>
       <c r="K7" t="n">
         <v>2.164684190021685</v>
@@ -4325,22 +4325,22 @@
         <v>2.467330089349349</v>
       </c>
       <c r="D8" t="n">
-        <v>2.238120767248499</v>
+        <v>2.2381207672485</v>
       </c>
       <c r="E8" t="n">
         <v>2.224902598737027</v>
       </c>
       <c r="F8" t="n">
-        <v>2.189530668888191</v>
+        <v>2.189530668888192</v>
       </c>
       <c r="G8" t="n">
         <v>2.265886910122258</v>
       </c>
       <c r="H8" t="n">
-        <v>2.352691234371707</v>
+        <v>2.352691234371708</v>
       </c>
       <c r="I8" t="n">
-        <v>2.236920468974956</v>
+        <v>2.236920468974957</v>
       </c>
       <c r="J8" t="n">
         <v>2.249379447978268</v>
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.71975524931624</v>
+        <v>2.719755249316241</v>
       </c>
       <c r="C9" t="n">
         <v>2.863871241707949</v>
       </c>
       <c r="D9" t="n">
-        <v>2.626156469121111</v>
+        <v>2.626156469121112</v>
       </c>
       <c r="E9" t="n">
-        <v>2.767251592328828</v>
+        <v>2.767251592328831</v>
       </c>
       <c r="F9" t="n">
-        <v>2.635364377709942</v>
+        <v>2.635364377709943</v>
       </c>
       <c r="G9" t="n">
-        <v>2.664324294149324</v>
+        <v>2.664324294149325</v>
       </c>
       <c r="H9" t="n">
-        <v>2.751128618398428</v>
+        <v>2.751128618398429</v>
       </c>
       <c r="I9" t="n">
-        <v>2.635357853002021</v>
+        <v>2.635357853002022</v>
       </c>
       <c r="J9" t="n">
-        <v>2.647806973550518</v>
+        <v>2.647806973550519</v>
       </c>
       <c r="K9" t="n">
-        <v>2.478019334283875</v>
+        <v>2.478019334283874</v>
       </c>
       <c r="L9" t="n">
-        <v>2.728194046022442</v>
+        <v>2.728194046022443</v>
       </c>
     </row>
   </sheetData>
@@ -4481,7 +4481,7 @@
         <v>2.423936443758433</v>
       </c>
       <c r="D2" t="n">
-        <v>2.403936591091489</v>
+        <v>2.403936591091488</v>
       </c>
       <c r="E2" t="n">
         <v>2.406631352319659</v>
@@ -4499,7 +4499,7 @@
         <v>2.403882539660569</v>
       </c>
       <c r="J2" t="n">
-        <v>2.417455765026009</v>
+        <v>2.417455765026008</v>
       </c>
       <c r="K2" t="n">
         <v>2.413352264059838</v>
@@ -4518,16 +4518,16 @@
         <v>2.521453765428408</v>
       </c>
       <c r="C3" t="n">
-        <v>2.534238375461445</v>
+        <v>2.534238375461444</v>
       </c>
       <c r="D3" t="n">
-        <v>2.411965875886249</v>
+        <v>2.411965875886248</v>
       </c>
       <c r="E3" t="n">
         <v>2.416116853307891</v>
       </c>
       <c r="F3" t="n">
-        <v>2.416112290013073</v>
+        <v>2.416112290013072</v>
       </c>
       <c r="G3" t="n">
         <v>2.426934241925547</v>
@@ -4539,10 +4539,10 @@
         <v>2.411588186731887</v>
       </c>
       <c r="J3" t="n">
-        <v>2.43944545477611</v>
+        <v>2.439445454776109</v>
       </c>
       <c r="K3" t="n">
-        <v>2.423475177322054</v>
+        <v>2.423475177322053</v>
       </c>
       <c r="L3" t="n">
         <v>2.441970429399995</v>
@@ -4558,7 +4558,7 @@
         <v>2.280229464279694</v>
       </c>
       <c r="C4" t="n">
-        <v>2.29337965784965</v>
+        <v>2.293379657849649</v>
       </c>
       <c r="D4" t="n">
         <v>2.106882287819737</v>
@@ -4598,10 +4598,10 @@
         <v>5.523676634568957</v>
       </c>
       <c r="C5" t="n">
-        <v>5.697260501205015</v>
+        <v>5.697260501205011</v>
       </c>
       <c r="D5" t="n">
-        <v>2.479371346442469</v>
+        <v>2.47937134644247</v>
       </c>
       <c r="E5" t="n">
         <v>2.472764148323873</v>
@@ -4610,22 +4610,22 @@
         <v>2.472764148323873</v>
       </c>
       <c r="G5" t="n">
-        <v>2.904507187230185</v>
+        <v>2.904507187230217</v>
       </c>
       <c r="H5" t="n">
-        <v>4.243002119808064</v>
+        <v>4.243002119808066</v>
       </c>
       <c r="I5" t="n">
         <v>2.472758543974739</v>
       </c>
       <c r="J5" t="n">
-        <v>2.687642340404494</v>
+        <v>2.687642340404495</v>
       </c>
       <c r="K5" t="n">
         <v>2.338802972997008</v>
       </c>
       <c r="L5" t="n">
-        <v>3.455949825537834</v>
+        <v>3.455949825537833</v>
       </c>
     </row>
     <row r="6">
@@ -4635,16 +4635,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.76340940247578</v>
+        <v>15.76340940247577</v>
       </c>
       <c r="C6" t="n">
-        <v>3.403297193389037</v>
+        <v>3.403297193389034</v>
       </c>
       <c r="D6" t="n">
         <v>3.197210987191291</v>
       </c>
       <c r="E6" t="n">
-        <v>3.209456422870184</v>
+        <v>3.209456422870185</v>
       </c>
       <c r="F6" t="n">
         <v>3.213687035140568</v>
@@ -4653,19 +4653,19 @@
         <v>3.222546782121439</v>
       </c>
       <c r="H6" t="n">
-        <v>15.68161896910051</v>
+        <v>15.68161896910052</v>
       </c>
       <c r="I6" t="n">
-        <v>3.198252512623561</v>
+        <v>3.198252512623562</v>
       </c>
       <c r="J6" t="n">
-        <v>15.60057835807228</v>
+        <v>15.60057835807227</v>
       </c>
       <c r="K6" t="n">
         <v>3.174614169109554</v>
       </c>
       <c r="L6" t="n">
-        <v>3.245224001132139</v>
+        <v>3.245224001132138</v>
       </c>
     </row>
     <row r="7">
@@ -4678,7 +4678,7 @@
         <v>2.340720886984714</v>
       </c>
       <c r="C7" t="n">
-        <v>2.35132328947926</v>
+        <v>2.351323289479261</v>
       </c>
       <c r="D7" t="n">
         <v>2.167368920125701</v>
@@ -4693,13 +4693,13 @@
         <v>2.191056443270408</v>
       </c>
       <c r="H7" t="n">
-        <v>2.256888459481515</v>
+        <v>2.256888459481514</v>
       </c>
       <c r="I7" t="n">
         <v>2.166762173772529</v>
       </c>
       <c r="J7" t="n">
-        <v>2.177918378548022</v>
+        <v>2.177918378548021</v>
       </c>
       <c r="K7" t="n">
         <v>2.159043627600545</v>
@@ -4718,7 +4718,7 @@
         <v>2.349012878801257</v>
       </c>
       <c r="C8" t="n">
-        <v>2.410521933929985</v>
+        <v>2.410521933929986</v>
       </c>
       <c r="D8" t="n">
         <v>2.235393925503275</v>
@@ -4733,10 +4733,10 @@
         <v>2.248818680579675</v>
       </c>
       <c r="H8" t="n">
-        <v>2.314650696791299</v>
+        <v>2.314650696791298</v>
       </c>
       <c r="I8" t="n">
-        <v>2.224524411081796</v>
+        <v>2.224524411081797</v>
       </c>
       <c r="J8" t="n">
         <v>2.235690338147965</v>
@@ -4758,28 +4758,28 @@
         <v>2.641958101390057</v>
       </c>
       <c r="C9" t="n">
-        <v>2.755108128642638</v>
+        <v>2.755108128642637</v>
       </c>
       <c r="D9" t="n">
         <v>2.571158513765362</v>
       </c>
       <c r="E9" t="n">
-        <v>2.688890241957515</v>
+        <v>2.688890241957516</v>
       </c>
       <c r="F9" t="n">
-        <v>2.570552515313747</v>
+        <v>2.570552515313748</v>
       </c>
       <c r="G9" t="n">
         <v>2.594841282433785</v>
       </c>
       <c r="H9" t="n">
-        <v>2.660673298644889</v>
+        <v>2.66067329864489</v>
       </c>
       <c r="I9" t="n">
-        <v>2.570547012935905</v>
+        <v>2.570547012935906</v>
       </c>
       <c r="J9" t="n">
-        <v>2.581703217711399</v>
+        <v>2.5817032177114</v>
       </c>
       <c r="K9" t="n">
         <v>2.501001353660921</v>
@@ -4871,34 +4871,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39827632449968</v>
+        <v>2.398276324499681</v>
       </c>
       <c r="C2" t="n">
         <v>2.424153388726872</v>
       </c>
       <c r="D2" t="n">
-        <v>2.400924289966384</v>
+        <v>2.400924289966385</v>
       </c>
       <c r="E2" t="n">
-        <v>2.428553727842743</v>
+        <v>2.428553727842745</v>
       </c>
       <c r="F2" t="n">
-        <v>2.415450281306107</v>
+        <v>2.415450281306108</v>
       </c>
       <c r="G2" t="n">
-        <v>2.405619033198441</v>
+        <v>2.405619033198442</v>
       </c>
       <c r="H2" t="n">
-        <v>2.40621518829122</v>
+        <v>2.406215188291221</v>
       </c>
       <c r="I2" t="n">
-        <v>2.406271635964151</v>
+        <v>2.406271635964152</v>
       </c>
       <c r="J2" t="n">
         <v>2.438639497346715</v>
       </c>
       <c r="K2" t="n">
-        <v>2.419605253766588</v>
+        <v>2.419605253766587</v>
       </c>
       <c r="L2" t="n">
         <v>2.399336902592728</v>
@@ -4911,22 +4911,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.405515217827778</v>
+        <v>2.405515217827779</v>
       </c>
       <c r="C3" t="n">
-        <v>2.491957849706884</v>
+        <v>2.491957849706885</v>
       </c>
       <c r="D3" t="n">
-        <v>2.42437269532331</v>
+        <v>2.424372695323309</v>
       </c>
       <c r="E3" t="n">
-        <v>2.499037451712436</v>
+        <v>2.499037451712437</v>
       </c>
       <c r="F3" t="n">
-        <v>2.477410758839887</v>
+        <v>2.477410758839886</v>
       </c>
       <c r="G3" t="n">
-        <v>2.457860430117215</v>
+        <v>2.457860430117214</v>
       </c>
       <c r="H3" t="n">
         <v>2.462904740662428</v>
@@ -4935,10 +4935,10 @@
         <v>2.462264787776556</v>
       </c>
       <c r="J3" t="n">
-        <v>2.495237908693643</v>
+        <v>2.495237908693644</v>
       </c>
       <c r="K3" t="n">
-        <v>2.451922791686994</v>
+        <v>2.451922791686995</v>
       </c>
       <c r="L3" t="n">
         <v>2.414130697316518</v>
@@ -4954,25 +4954,25 @@
         <v>2.1147626972011</v>
       </c>
       <c r="C4" t="n">
-        <v>2.205448675708519</v>
+        <v>2.20544867570852</v>
       </c>
       <c r="D4" t="n">
         <v>2.144672685271816</v>
       </c>
       <c r="E4" t="n">
-        <v>2.205570069134609</v>
+        <v>2.20557006913461</v>
       </c>
       <c r="F4" t="n">
-        <v>2.205570069134609</v>
+        <v>2.20557006913461</v>
       </c>
       <c r="G4" t="n">
         <v>2.197732270339194</v>
       </c>
       <c r="H4" t="n">
-        <v>2.205189973512482</v>
+        <v>2.205189973512483</v>
       </c>
       <c r="I4" t="n">
-        <v>2.205193992137677</v>
+        <v>2.205193992137678</v>
       </c>
       <c r="J4" t="n">
         <v>2.162166747749306</v>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.567329688706055</v>
+        <v>2.567329688706051</v>
       </c>
       <c r="C5" t="n">
-        <v>4.100755769246883</v>
+        <v>4.100755769246888</v>
       </c>
       <c r="D5" t="n">
-        <v>3.109960286695348</v>
+        <v>3.109960286695353</v>
       </c>
       <c r="E5" t="n">
-        <v>4.100755770544962</v>
+        <v>4.100755770544968</v>
       </c>
       <c r="F5" t="n">
-        <v>4.100755770544962</v>
+        <v>4.100755770544968</v>
       </c>
       <c r="G5" t="n">
-        <v>4.102162137129291</v>
+        <v>4.102162137129309</v>
       </c>
       <c r="H5" t="n">
-        <v>4.454925859555994</v>
+        <v>4.45492585955599</v>
       </c>
       <c r="I5" t="n">
-        <v>4.100757236299387</v>
+        <v>4.100757236299392</v>
       </c>
       <c r="J5" t="n">
-        <v>3.503160131655607</v>
+        <v>3.503160131655608</v>
       </c>
       <c r="K5" t="n">
-        <v>2.989171439185714</v>
+        <v>2.989171439185716</v>
       </c>
       <c r="L5" t="n">
-        <v>8.325178311757261</v>
+        <v>8.325178311757265</v>
       </c>
     </row>
     <row r="6">
@@ -5034,7 +5034,7 @@
         <v>3.288363948118211</v>
       </c>
       <c r="C6" t="n">
-        <v>3.39423594758455</v>
+        <v>3.394235947584551</v>
       </c>
       <c r="D6" t="n">
         <v>3.31444081229272</v>
@@ -5043,13 +5043,13 @@
         <v>3.390222219120717</v>
       </c>
       <c r="F6" t="n">
-        <v>3.394086114564104</v>
+        <v>3.394086114564105</v>
       </c>
       <c r="G6" t="n">
-        <v>3.371333521256303</v>
+        <v>3.371333521256305</v>
       </c>
       <c r="H6" t="n">
-        <v>16.67692163720999</v>
+        <v>16.67692163721</v>
       </c>
       <c r="I6" t="n">
         <v>16.67882696823526</v>
@@ -5058,7 +5058,7 @@
         <v>3.336189760848204</v>
       </c>
       <c r="K6" t="n">
-        <v>3.29215376688287</v>
+        <v>3.292153766882872</v>
       </c>
       <c r="L6" t="n">
         <v>3.299418899915988</v>
@@ -5074,34 +5074,34 @@
         <v>2.181218309902455</v>
       </c>
       <c r="C7" t="n">
-        <v>2.27164813778653</v>
+        <v>2.271648137786531</v>
       </c>
       <c r="D7" t="n">
-        <v>2.211123535675005</v>
+        <v>2.211123535675006</v>
       </c>
       <c r="E7" t="n">
-        <v>2.271634778961396</v>
+        <v>2.271634778961398</v>
       </c>
       <c r="F7" t="n">
-        <v>2.271634778961396</v>
+        <v>2.271634778961398</v>
       </c>
       <c r="G7" t="n">
-        <v>2.264187883040547</v>
+        <v>2.264187883040548</v>
       </c>
       <c r="H7" t="n">
-        <v>2.271645586213837</v>
+        <v>2.271645586213838</v>
       </c>
       <c r="I7" t="n">
-        <v>2.271649604839032</v>
+        <v>2.271649604839033</v>
       </c>
       <c r="J7" t="n">
         <v>2.228622360450661</v>
       </c>
       <c r="K7" t="n">
-        <v>2.204334065595676</v>
+        <v>2.204334065595677</v>
       </c>
       <c r="L7" t="n">
-        <v>2.194740207092241</v>
+        <v>2.194740207092242</v>
       </c>
     </row>
     <row r="8">
@@ -5114,13 +5114,13 @@
         <v>2.191802913873071</v>
       </c>
       <c r="C8" t="n">
-        <v>2.33650081193188</v>
+        <v>2.336500811931882</v>
       </c>
       <c r="D8" t="n">
         <v>2.287229135549273</v>
       </c>
       <c r="E8" t="n">
-        <v>2.321658368717196</v>
+        <v>2.321658368717197</v>
       </c>
       <c r="F8" t="n">
         <v>2.283947705343902</v>
@@ -5129,19 +5129,19 @@
         <v>2.329036685551475</v>
       </c>
       <c r="H8" t="n">
-        <v>2.336494388724748</v>
+        <v>2.336494388724749</v>
       </c>
       <c r="I8" t="n">
-        <v>2.33649840734996</v>
+        <v>2.336498407349961</v>
       </c>
       <c r="J8" t="n">
-        <v>2.293481827424287</v>
+        <v>2.293481827424288</v>
       </c>
       <c r="K8" t="n">
         <v>2.213910684219896</v>
       </c>
       <c r="L8" t="n">
-        <v>2.316272502470038</v>
+        <v>2.316272502470039</v>
       </c>
     </row>
     <row r="9">
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.621209928060057</v>
+        <v>2.621209928060058</v>
       </c>
       <c r="C9" t="n">
-        <v>2.854013143666956</v>
+        <v>2.854013143666957</v>
       </c>
       <c r="D9" t="n">
         <v>2.793493291330382</v>
@@ -5163,16 +5163,16 @@
         <v>3.018308882368146</v>
       </c>
       <c r="F9" t="n">
-        <v>2.85401304744105</v>
+        <v>2.854013047441052</v>
       </c>
       <c r="G9" t="n">
-        <v>2.846552888920975</v>
+        <v>2.846552888920976</v>
       </c>
       <c r="H9" t="n">
         <v>2.854010592094264</v>
       </c>
       <c r="I9" t="n">
-        <v>2.854014610719458</v>
+        <v>2.854014610719459</v>
       </c>
       <c r="J9" t="n">
         <v>2.810987366331088</v>
@@ -5181,7 +5181,7 @@
         <v>2.704207366218885</v>
       </c>
       <c r="L9" t="n">
-        <v>2.777105212972667</v>
+        <v>2.777105212972668</v>
       </c>
     </row>
   </sheetData>
@@ -5273,25 +5273,25 @@
         <v>2.421071194863416</v>
       </c>
       <c r="D2" t="n">
-        <v>2.398214637959945</v>
+        <v>2.398214637959944</v>
       </c>
       <c r="E2" t="n">
-        <v>2.425483230171922</v>
+        <v>2.425483230171921</v>
       </c>
       <c r="F2" t="n">
-        <v>2.412305189739582</v>
+        <v>2.412305189739581</v>
       </c>
       <c r="G2" t="n">
-        <v>2.401963115756105</v>
+        <v>2.401963115756104</v>
       </c>
       <c r="H2" t="n">
         <v>2.401596576273721</v>
       </c>
       <c r="I2" t="n">
-        <v>2.403110725016439</v>
+        <v>2.403110725016438</v>
       </c>
       <c r="J2" t="n">
-        <v>2.435877756125165</v>
+        <v>2.435877756125166</v>
       </c>
       <c r="K2" t="n">
         <v>2.41681332626307</v>
@@ -5331,7 +5331,7 @@
         <v>2.454753213328139</v>
       </c>
       <c r="J3" t="n">
-        <v>2.48913098469468</v>
+        <v>2.489130984694679</v>
       </c>
       <c r="K3" t="n">
         <v>2.446569399014667</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.482457735952149</v>
+        <v>2.482457735952151</v>
       </c>
       <c r="C5" t="n">
-        <v>3.803225812098378</v>
+        <v>3.803225812098386</v>
       </c>
       <c r="D5" t="n">
-        <v>2.965879897435722</v>
+        <v>2.965879897435723</v>
       </c>
       <c r="E5" t="n">
-        <v>3.803225810734293</v>
+        <v>3.803225810734297</v>
       </c>
       <c r="F5" t="n">
-        <v>3.803225810734293</v>
+        <v>3.803225810734297</v>
       </c>
       <c r="G5" t="n">
-        <v>3.701804253933361</v>
+        <v>3.701804253933362</v>
       </c>
       <c r="H5" t="n">
-        <v>3.823832232741432</v>
+        <v>3.823832232741433</v>
       </c>
       <c r="I5" t="n">
-        <v>3.803228575101002</v>
+        <v>3.803228575101007</v>
       </c>
       <c r="J5" t="n">
         <v>3.276945400699288</v>
       </c>
       <c r="K5" t="n">
-        <v>2.79775363834</v>
+        <v>2.797753638339997</v>
       </c>
       <c r="L5" t="n">
-        <v>5.70862318436037</v>
+        <v>5.708623184360365</v>
       </c>
     </row>
     <row r="6">
@@ -5430,34 +5430,34 @@
         <v>3.201323155327308</v>
       </c>
       <c r="C6" t="n">
-        <v>3.301303494995301</v>
+        <v>3.301303494995302</v>
       </c>
       <c r="D6" t="n">
-        <v>3.228021399572418</v>
+        <v>3.228021399572417</v>
       </c>
       <c r="E6" t="n">
-        <v>3.297590675535617</v>
+        <v>3.297590675535618</v>
       </c>
       <c r="F6" t="n">
-        <v>3.301042373293136</v>
+        <v>3.301042373293137</v>
       </c>
       <c r="G6" t="n">
         <v>3.273069253478798</v>
       </c>
       <c r="H6" t="n">
-        <v>15.65985321961333</v>
+        <v>15.65985321961332</v>
       </c>
       <c r="I6" t="n">
-        <v>15.67806352828444</v>
+        <v>15.67806352828443</v>
       </c>
       <c r="J6" t="n">
-        <v>3.245582386138545</v>
+        <v>3.245582386138546</v>
       </c>
       <c r="K6" t="n">
         <v>3.204914271558461</v>
       </c>
       <c r="L6" t="n">
-        <v>3.224269943337744</v>
+        <v>3.224269943337743</v>
       </c>
     </row>
     <row r="7">
@@ -5470,7 +5470,7 @@
         <v>2.170558467548596</v>
       </c>
       <c r="C7" t="n">
-        <v>2.255376626860963</v>
+        <v>2.255376626860962</v>
       </c>
       <c r="D7" t="n">
         <v>2.199925169670352</v>
@@ -5497,7 +5497,7 @@
         <v>2.19131937488323</v>
       </c>
       <c r="L7" t="n">
-        <v>2.195083400810479</v>
+        <v>2.195083400810478</v>
       </c>
     </row>
     <row r="8">
@@ -5510,13 +5510,13 @@
         <v>2.179755304587871</v>
       </c>
       <c r="C8" t="n">
-        <v>2.314274873898494</v>
+        <v>2.314274873898493</v>
       </c>
       <c r="D8" t="n">
         <v>2.269103555753832</v>
       </c>
       <c r="E8" t="n">
-        <v>2.300684985650634</v>
+        <v>2.300684985650633</v>
       </c>
       <c r="F8" t="n">
         <v>2.266156817777288</v>
@@ -5528,7 +5528,7 @@
         <v>2.29779987419382</v>
       </c>
       <c r="I8" t="n">
-        <v>2.314252598363637</v>
+        <v>2.314252598363636</v>
       </c>
       <c r="J8" t="n">
         <v>2.272717651347707</v>
@@ -5547,22 +5547,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.526886150464137</v>
+        <v>2.526886150464138</v>
       </c>
       <c r="C9" t="n">
-        <v>2.729326933681417</v>
+        <v>2.729326933681416</v>
       </c>
       <c r="D9" t="n">
-        <v>2.673879926039599</v>
+        <v>2.6738799260396</v>
       </c>
       <c r="E9" t="n">
         <v>2.865060835810888</v>
       </c>
       <c r="F9" t="n">
-        <v>2.729326850290031</v>
+        <v>2.729326850290032</v>
       </c>
       <c r="G9" t="n">
-        <v>2.716254872520532</v>
+        <v>2.716254872520533</v>
       </c>
       <c r="H9" t="n">
         <v>2.712876972514243</v>
@@ -5571,10 +5571,10 @@
         <v>2.72932969668404</v>
       </c>
       <c r="J9" t="n">
-        <v>2.687784986844973</v>
+        <v>2.687784986844974</v>
       </c>
       <c r="K9" t="n">
-        <v>2.597118667771721</v>
+        <v>2.597118667771722</v>
       </c>
       <c r="L9" t="n">
         <v>2.669033707630931</v>
@@ -5669,13 +5669,13 @@
         <v>2.416828074881267</v>
       </c>
       <c r="D2" t="n">
-        <v>2.395288165904989</v>
+        <v>2.39528816590499</v>
       </c>
       <c r="E2" t="n">
         <v>2.421239784085733</v>
       </c>
       <c r="F2" t="n">
-        <v>2.408034920892503</v>
+        <v>2.408034920892502</v>
       </c>
       <c r="G2" t="n">
         <v>2.398365904367674</v>
@@ -5721,10 +5721,10 @@
         <v>2.436789109823015</v>
       </c>
       <c r="H3" t="n">
-        <v>2.452858861779322</v>
+        <v>2.452858861779321</v>
       </c>
       <c r="I3" t="n">
-        <v>2.442656966874057</v>
+        <v>2.442656966874056</v>
       </c>
       <c r="J3" t="n">
         <v>2.479558405652682</v>
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.449618471674813</v>
+        <v>2.449618471674814</v>
       </c>
       <c r="C5" t="n">
-        <v>3.534842109445161</v>
+        <v>3.53484210944516</v>
       </c>
       <c r="D5" t="n">
-        <v>2.858923741908021</v>
+        <v>2.85892374190802</v>
       </c>
       <c r="E5" t="n">
-        <v>3.534842106577309</v>
+        <v>3.534842106577308</v>
       </c>
       <c r="F5" t="n">
-        <v>3.534842106577309</v>
+        <v>3.534842106577308</v>
       </c>
       <c r="G5" t="n">
-        <v>3.454573417662469</v>
+        <v>3.454573417662479</v>
       </c>
       <c r="H5" t="n">
-        <v>4.039282019082655</v>
+        <v>4.039282019082654</v>
       </c>
       <c r="I5" t="n">
-        <v>3.534844108650212</v>
+        <v>3.53484410865021</v>
       </c>
       <c r="J5" t="n">
         <v>3.068755917192025</v>
       </c>
       <c r="K5" t="n">
-        <v>2.614109862643755</v>
+        <v>2.614109862643756</v>
       </c>
       <c r="L5" t="n">
-        <v>4.854956529860346</v>
+        <v>4.854956529860356</v>
       </c>
     </row>
     <row r="6">
@@ -5823,16 +5823,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.196566600940782</v>
+        <v>3.196566600940781</v>
       </c>
       <c r="C6" t="n">
         <v>3.281844896462792</v>
       </c>
       <c r="D6" t="n">
-        <v>3.219899779740422</v>
+        <v>3.219899779740421</v>
       </c>
       <c r="E6" t="n">
-        <v>3.278180388721061</v>
+        <v>3.278180388721058</v>
       </c>
       <c r="F6" t="n">
         <v>3.281662683888834</v>
@@ -5844,16 +5844,16 @@
         <v>15.67142115875626</v>
       </c>
       <c r="I6" t="n">
-        <v>3.266689356784221</v>
+        <v>3.26668935678422</v>
       </c>
       <c r="J6" t="n">
         <v>15.6193868218791</v>
       </c>
       <c r="K6" t="n">
-        <v>3.191667561795272</v>
+        <v>3.191667561795273</v>
       </c>
       <c r="L6" t="n">
-        <v>3.220301767355885</v>
+        <v>3.220301767355884</v>
       </c>
     </row>
     <row r="7">
@@ -5872,13 +5872,13 @@
         <v>2.192007931279393</v>
       </c>
       <c r="E7" t="n">
-        <v>2.236492741526124</v>
+        <v>2.236492741526123</v>
       </c>
       <c r="F7" t="n">
         <v>2.236492741526123</v>
       </c>
       <c r="G7" t="n">
-        <v>2.226809248302451</v>
+        <v>2.226809248302453</v>
       </c>
       <c r="H7" t="n">
         <v>2.25183299101327</v>
@@ -5903,10 +5903,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.174851444383486</v>
+        <v>2.174851444383485</v>
       </c>
       <c r="C8" t="n">
-        <v>2.293774942381944</v>
+        <v>2.293774942381945</v>
       </c>
       <c r="D8" t="n">
         <v>2.259391851593473</v>
@@ -5927,10 +5927,10 @@
         <v>2.293737246458804</v>
       </c>
       <c r="J8" t="n">
-        <v>2.256674022751537</v>
+        <v>2.256674022751536</v>
       </c>
       <c r="K8" t="n">
-        <v>2.186034912200058</v>
+        <v>2.186034912200057</v>
       </c>
       <c r="L8" t="n">
         <v>2.299704014723193</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.480140572646625</v>
+        <v>2.480140572646626</v>
       </c>
       <c r="C9" t="n">
         <v>2.655914894656163</v>
@@ -5952,7 +5952,7 @@
         <v>2.61146014595152</v>
       </c>
       <c r="E9" t="n">
-        <v>2.777836740698218</v>
+        <v>2.777836740698219</v>
       </c>
       <c r="F9" t="n">
         <v>2.655914804373822</v>
@@ -6083,7 +6083,7 @@
         <v>2.411760403658618</v>
       </c>
       <c r="J2" t="n">
-        <v>2.446497936101261</v>
+        <v>2.446497936101262</v>
       </c>
       <c r="K2" t="n">
         <v>2.423612791095188</v>
@@ -6108,13 +6108,13 @@
         <v>2.415348072941635</v>
       </c>
       <c r="E3" t="n">
-        <v>2.505781088254383</v>
+        <v>2.505781088254382</v>
       </c>
       <c r="F3" t="n">
-        <v>2.483380926114596</v>
+        <v>2.483380926114597</v>
       </c>
       <c r="G3" t="n">
-        <v>2.484771045073918</v>
+        <v>2.484771045073917</v>
       </c>
       <c r="H3" t="n">
         <v>2.544039241491773</v>
@@ -6123,13 +6123,13 @@
         <v>2.46935024247709</v>
       </c>
       <c r="J3" t="n">
-        <v>2.516861622578532</v>
+        <v>2.516861622578533</v>
       </c>
       <c r="K3" t="n">
-        <v>2.452672304839622</v>
+        <v>2.452672304839621</v>
       </c>
       <c r="L3" t="n">
-        <v>2.486494861042407</v>
+        <v>2.486494861042408</v>
       </c>
     </row>
     <row r="4">
@@ -6142,7 +6142,7 @@
         <v>2.099245188535837</v>
       </c>
       <c r="C4" t="n">
-        <v>2.212623305309802</v>
+        <v>2.212623305309803</v>
       </c>
       <c r="D4" t="n">
         <v>2.126798612615087</v>
@@ -6160,7 +6160,7 @@
         <v>2.330758768088357</v>
       </c>
       <c r="I4" t="n">
-        <v>2.212716202331185</v>
+        <v>2.212716202331184</v>
       </c>
       <c r="J4" t="n">
         <v>2.191622500368419</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.245609665426167</v>
+        <v>2.245609665426155</v>
       </c>
       <c r="C5" t="n">
-        <v>4.169679307141206</v>
+        <v>4.169679307141207</v>
       </c>
       <c r="D5" t="n">
-        <v>2.704797201530639</v>
+        <v>2.704797201530638</v>
       </c>
       <c r="E5" t="n">
         <v>4.169679310529625</v>
       </c>
       <c r="F5" t="n">
-        <v>4.169679310529626</v>
+        <v>4.169679310529625</v>
       </c>
       <c r="G5" t="n">
-        <v>4.620318404164346</v>
+        <v>4.620318404164349</v>
       </c>
       <c r="H5" t="n">
-        <v>6.458496702525213</v>
+        <v>6.458496702525208</v>
       </c>
       <c r="I5" t="n">
-        <v>4.16967345765448</v>
+        <v>4.169673457654484</v>
       </c>
       <c r="J5" t="n">
-        <v>4.003206467021613</v>
+        <v>4.00320646702161</v>
       </c>
       <c r="K5" t="n">
-        <v>2.889299336396178</v>
+        <v>2.889299336396173</v>
       </c>
       <c r="L5" t="n">
-        <v>5.064536434850776</v>
+        <v>5.064536434850774</v>
       </c>
     </row>
     <row r="6">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16.57852542825368</v>
+        <v>16.57852542825369</v>
       </c>
       <c r="C6" t="n">
-        <v>3.402500757147665</v>
+        <v>3.402500757147666</v>
       </c>
       <c r="D6" t="n">
-        <v>16.60420235374254</v>
+        <v>16.60420235374253</v>
       </c>
       <c r="E6" t="n">
         <v>3.398423358226607</v>
@@ -6234,7 +6234,7 @@
         <v>3.40304608689835</v>
       </c>
       <c r="G6" t="n">
-        <v>16.71645017819227</v>
+        <v>16.71645017819228</v>
       </c>
       <c r="H6" t="n">
         <v>3.504563422987177</v>
@@ -6243,7 +6243,7 @@
         <v>16.69199644204902</v>
       </c>
       <c r="J6" t="n">
-        <v>16.66945220713251</v>
+        <v>16.66945220713252</v>
       </c>
       <c r="K6" t="n">
         <v>3.292409996645383</v>
@@ -6277,7 +6277,7 @@
         <v>2.305604066351955</v>
       </c>
       <c r="H7" t="n">
-        <v>2.399192895965888</v>
+        <v>2.399192895965887</v>
       </c>
       <c r="I7" t="n">
         <v>2.281150330208715</v>
@@ -6286,7 +6286,7 @@
         <v>2.26005662824595</v>
       </c>
       <c r="K7" t="n">
-        <v>2.206017627179155</v>
+        <v>2.206017627179156</v>
       </c>
       <c r="L7" t="n">
         <v>2.307235571963414</v>
@@ -6314,7 +6314,7 @@
         <v>2.295809967507056</v>
       </c>
       <c r="G8" t="n">
-        <v>2.375847927231831</v>
+        <v>2.375847927231832</v>
       </c>
       <c r="H8" t="n">
         <v>2.46943675684575</v>
@@ -6323,10 +6323,10 @@
         <v>2.351394191088591</v>
       </c>
       <c r="J8" t="n">
-        <v>2.33031177094102</v>
+        <v>2.330311770941021</v>
       </c>
       <c r="K8" t="n">
-        <v>2.217789656414533</v>
+        <v>2.217789656414532</v>
       </c>
       <c r="L8" t="n">
         <v>2.437444272637556</v>
@@ -6351,25 +6351,25 @@
         <v>3.048924021915572</v>
       </c>
       <c r="F9" t="n">
-        <v>2.879868741231917</v>
+        <v>2.879868741231918</v>
       </c>
       <c r="G9" t="n">
-        <v>2.90431675796913</v>
+        <v>2.904316757969131</v>
       </c>
       <c r="H9" t="n">
-        <v>2.997905587583066</v>
+        <v>2.997905587583065</v>
       </c>
       <c r="I9" t="n">
-        <v>2.879863021825893</v>
+        <v>2.879863021825892</v>
       </c>
       <c r="J9" t="n">
-        <v>2.858769319863127</v>
+        <v>2.858769319863125</v>
       </c>
       <c r="K9" t="n">
         <v>2.719848913147752</v>
       </c>
       <c r="L9" t="n">
-        <v>2.905948263580592</v>
+        <v>2.905948263580591</v>
       </c>
     </row>
   </sheetData>
@@ -6455,16 +6455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.394779553555966</v>
+        <v>2.394779553555964</v>
       </c>
       <c r="C2" t="n">
-        <v>2.420299781033662</v>
+        <v>2.420299781033661</v>
       </c>
       <c r="D2" t="n">
-        <v>2.396438074789016</v>
+        <v>2.396438074789014</v>
       </c>
       <c r="E2" t="n">
-        <v>2.424742379946948</v>
+        <v>2.424742379946947</v>
       </c>
       <c r="F2" t="n">
         <v>2.411514849860822</v>
@@ -6476,13 +6476,13 @@
         <v>2.407009196909387</v>
       </c>
       <c r="I2" t="n">
-        <v>2.402934276984484</v>
+        <v>2.402934276984483</v>
       </c>
       <c r="J2" t="n">
-        <v>2.436160529264976</v>
+        <v>2.436160529264975</v>
       </c>
       <c r="K2" t="n">
-        <v>2.414330360361873</v>
+        <v>2.414330360361872</v>
       </c>
       <c r="L2" t="n">
         <v>2.402861942399054</v>
@@ -6495,13 +6495,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.392904086711672</v>
+        <v>2.392904086711673</v>
       </c>
       <c r="C3" t="n">
         <v>2.479553186303289</v>
       </c>
       <c r="D3" t="n">
-        <v>2.404656456432824</v>
+        <v>2.404656456432825</v>
       </c>
       <c r="E3" t="n">
         <v>2.486702394958372</v>
@@ -6516,10 +6516,10 @@
         <v>2.479902114302758</v>
       </c>
       <c r="I3" t="n">
-        <v>2.450712147515281</v>
+        <v>2.45071214751528</v>
       </c>
       <c r="J3" t="n">
-        <v>2.490407020426949</v>
+        <v>2.490407020426948</v>
       </c>
       <c r="K3" t="n">
         <v>2.433618166170777</v>
@@ -6538,7 +6538,7 @@
         <v>2.094289576308732</v>
       </c>
       <c r="C4" t="n">
-        <v>2.18664491131178</v>
+        <v>2.186644911311779</v>
       </c>
       <c r="D4" t="n">
         <v>2.113023336593486</v>
@@ -6550,7 +6550,7 @@
         <v>2.186752297106368</v>
       </c>
       <c r="G4" t="n">
-        <v>2.190889716110877</v>
+        <v>2.190889716110876</v>
       </c>
       <c r="H4" t="n">
         <v>2.232753335984048</v>
@@ -6578,34 +6578,34 @@
         <v>2.236681818707256</v>
       </c>
       <c r="C5" t="n">
-        <v>3.662447620744031</v>
+        <v>3.662447620744029</v>
       </c>
       <c r="D5" t="n">
         <v>2.52418835764268</v>
       </c>
       <c r="E5" t="n">
-        <v>3.662447621333976</v>
+        <v>3.662447621333975</v>
       </c>
       <c r="F5" t="n">
-        <v>3.662447621333976</v>
+        <v>3.662447621333975</v>
       </c>
       <c r="G5" t="n">
-        <v>3.750869823731249</v>
+        <v>3.750869823731246</v>
       </c>
       <c r="H5" t="n">
         <v>4.446350636075872</v>
       </c>
       <c r="I5" t="n">
-        <v>3.662446392927351</v>
+        <v>3.66244639292735</v>
       </c>
       <c r="J5" t="n">
-        <v>3.253645099118895</v>
+        <v>3.253645099118894</v>
       </c>
       <c r="K5" t="n">
         <v>2.509651788223065</v>
       </c>
       <c r="L5" t="n">
-        <v>3.972118483690421</v>
+        <v>3.972118483690423</v>
       </c>
     </row>
     <row r="6">
@@ -6615,28 +6615,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15.57908096884236</v>
+        <v>15.57908096884235</v>
       </c>
       <c r="C6" t="n">
-        <v>3.293293877607395</v>
+        <v>3.293293877607394</v>
       </c>
       <c r="D6" t="n">
         <v>3.201470875046069</v>
       </c>
       <c r="E6" t="n">
-        <v>3.289586683517709</v>
+        <v>3.28958668351771</v>
       </c>
       <c r="F6" t="n">
-        <v>3.293374271468093</v>
+        <v>3.293374271468094</v>
       </c>
       <c r="G6" t="n">
         <v>15.67568110864452</v>
       </c>
       <c r="H6" t="n">
-        <v>15.71602509326489</v>
+        <v>15.71602509326488</v>
       </c>
       <c r="I6" t="n">
-        <v>15.6712741815296</v>
+        <v>15.67127418152961</v>
       </c>
       <c r="J6" t="n">
         <v>3.247671561301161</v>
@@ -6645,7 +6645,7 @@
         <v>3.186006270406485</v>
       </c>
       <c r="L6" t="n">
-        <v>3.2769531859779</v>
+        <v>3.276953185977899</v>
       </c>
     </row>
     <row r="7">
@@ -6664,19 +6664,19 @@
         <v>2.174349608414177</v>
       </c>
       <c r="E7" t="n">
-        <v>2.247813417919828</v>
+        <v>2.247813417919827</v>
       </c>
       <c r="F7" t="n">
-        <v>2.247813417919828</v>
+        <v>2.247813417919827</v>
       </c>
       <c r="G7" t="n">
-        <v>2.252220429620492</v>
+        <v>2.252220429620491</v>
       </c>
       <c r="H7" t="n">
         <v>2.294084049493663</v>
       </c>
       <c r="I7" t="n">
-        <v>2.247813502505587</v>
+        <v>2.247813502505586</v>
       </c>
       <c r="J7" t="n">
         <v>2.215927115994508</v>
@@ -6685,7 +6685,7 @@
         <v>2.173147782382655</v>
       </c>
       <c r="L7" t="n">
-        <v>2.247499655845904</v>
+        <v>2.247499655845905</v>
       </c>
     </row>
     <row r="8">
@@ -6738,13 +6738,13 @@
         <v>2.51388049605585</v>
       </c>
       <c r="C9" t="n">
-        <v>2.724283161986206</v>
+        <v>2.724283161986205</v>
       </c>
       <c r="D9" t="n">
         <v>2.65082246295416</v>
       </c>
       <c r="E9" t="n">
-        <v>2.86069280821838</v>
+        <v>2.860692808218379</v>
       </c>
       <c r="F9" t="n">
         <v>2.724283064116703</v>
@@ -6756,16 +6756,16 @@
         <v>2.770552481157607</v>
       </c>
       <c r="I9" t="n">
-        <v>2.724281934169529</v>
+        <v>2.724281934169528</v>
       </c>
       <c r="J9" t="n">
         <v>2.692395547658453</v>
       </c>
       <c r="K9" t="n">
-        <v>2.581125896082406</v>
+        <v>2.581125896082405</v>
       </c>
       <c r="L9" t="n">
-        <v>2.723968087509849</v>
+        <v>2.723968087509848</v>
       </c>
     </row>
   </sheetData>
@@ -6866,7 +6866,7 @@
         <v>2.401846125138585</v>
       </c>
       <c r="G2" t="n">
-        <v>2.393032490254998</v>
+        <v>2.393032490254997</v>
       </c>
       <c r="H2" t="n">
         <v>2.396649869220294</v>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.388361165181847</v>
+        <v>2.388361165181846</v>
       </c>
       <c r="C3" t="n">
         <v>2.455196272072623</v>
@@ -6909,7 +6909,7 @@
         <v>2.423271814211925</v>
       </c>
       <c r="H3" t="n">
-        <v>2.44929179813568</v>
+        <v>2.449291798135681</v>
       </c>
       <c r="I3" t="n">
         <v>2.427220257520458</v>
@@ -6946,7 +6946,7 @@
         <v>2.152921383590664</v>
       </c>
       <c r="G4" t="n">
-        <v>2.146148295910666</v>
+        <v>2.146148295910667</v>
       </c>
       <c r="H4" t="n">
         <v>2.187093300394211</v>
@@ -6974,31 +6974,31 @@
         <v>2.257393682450794</v>
       </c>
       <c r="C5" t="n">
-        <v>3.239408372092379</v>
+        <v>3.23940837209238</v>
       </c>
       <c r="D5" t="n">
-        <v>2.365776765353191</v>
+        <v>2.36577676535319</v>
       </c>
       <c r="E5" t="n">
-        <v>3.239408371774381</v>
+        <v>3.239408371774382</v>
       </c>
       <c r="F5" t="n">
-        <v>3.239408371774381</v>
+        <v>3.239408371774382</v>
       </c>
       <c r="G5" t="n">
-        <v>3.156093904253619</v>
+        <v>3.156093904253629</v>
       </c>
       <c r="H5" t="n">
-        <v>3.953032632572811</v>
+        <v>3.95303263257281</v>
       </c>
       <c r="I5" t="n">
-        <v>3.239409663261287</v>
+        <v>3.239409663261291</v>
       </c>
       <c r="J5" t="n">
-        <v>2.753280995209461</v>
+        <v>2.753280995209463</v>
       </c>
       <c r="K5" t="n">
-        <v>2.305834116550539</v>
+        <v>2.30583411655054</v>
       </c>
       <c r="L5" t="n">
         <v>3.633069301845864</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.179287001376701</v>
+        <v>3.1792870013767</v>
       </c>
       <c r="C6" t="n">
         <v>3.257151888821268</v>
@@ -7023,7 +7023,7 @@
         <v>3.253557427738229</v>
       </c>
       <c r="F6" t="n">
-        <v>3.257037914836593</v>
+        <v>3.257037914836592</v>
       </c>
       <c r="G6" t="n">
         <v>3.234823176328993</v>
@@ -7032,13 +7032,13 @@
         <v>15.66365961451044</v>
       </c>
       <c r="I6" t="n">
-        <v>3.24125467035955</v>
+        <v>3.241254670359551</v>
       </c>
       <c r="J6" t="n">
         <v>3.209599782415759</v>
       </c>
       <c r="K6" t="n">
-        <v>3.166316702705318</v>
+        <v>3.166316702705316</v>
       </c>
       <c r="L6" t="n">
         <v>3.226848180726368</v>
@@ -7051,19 +7051,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.149619154722987</v>
+        <v>2.149619154722986</v>
       </c>
       <c r="C7" t="n">
-        <v>2.211585532536929</v>
+        <v>2.211585532536928</v>
       </c>
       <c r="D7" t="n">
-        <v>2.156317800146675</v>
+        <v>2.156317800146674</v>
       </c>
       <c r="E7" t="n">
-        <v>2.211583835865813</v>
+        <v>2.211583835865812</v>
       </c>
       <c r="F7" t="n">
-        <v>2.211583835865813</v>
+        <v>2.211583835865812</v>
       </c>
       <c r="G7" t="n">
         <v>2.205155329675281</v>
@@ -7072,7 +7072,7 @@
         <v>2.246100334158825</v>
       </c>
       <c r="I7" t="n">
-        <v>2.211586823705835</v>
+        <v>2.211586823705834</v>
       </c>
       <c r="J7" t="n">
         <v>2.178148825905428</v>
@@ -7094,7 +7094,7 @@
         <v>2.156857617644576</v>
       </c>
       <c r="C8" t="n">
-        <v>2.265489912894152</v>
+        <v>2.265489912894151</v>
       </c>
       <c r="D8" t="n">
         <v>2.219887265948981</v>
@@ -7109,19 +7109,19 @@
         <v>2.259046637354742</v>
       </c>
       <c r="H8" t="n">
-        <v>2.299991641838297</v>
+        <v>2.299991641838296</v>
       </c>
       <c r="I8" t="n">
-        <v>2.265478131385296</v>
+        <v>2.265478131385295</v>
       </c>
       <c r="J8" t="n">
-        <v>2.232049302199091</v>
+        <v>2.232049302199092</v>
       </c>
       <c r="K8" t="n">
         <v>2.159269257166674</v>
       </c>
       <c r="L8" t="n">
-        <v>2.300230143531196</v>
+        <v>2.300230143531195</v>
       </c>
     </row>
     <row r="9">
@@ -7140,13 +7140,13 @@
         <v>2.568055320022177</v>
       </c>
       <c r="E9" t="n">
-        <v>2.74279825734897</v>
+        <v>2.742798257348969</v>
       </c>
       <c r="F9" t="n">
         <v>2.623318600708767</v>
       </c>
       <c r="G9" t="n">
-        <v>2.616888487486474</v>
+        <v>2.616888487486475</v>
       </c>
       <c r="H9" t="n">
         <v>2.657833491970018</v>
@@ -7155,10 +7155,10 @@
         <v>2.623319981517029</v>
       </c>
       <c r="J9" t="n">
-        <v>2.589881983716623</v>
+        <v>2.589881983716624</v>
       </c>
       <c r="K9" t="n">
-        <v>2.502206834806357</v>
+        <v>2.502206834806356</v>
       </c>
       <c r="L9" t="n">
         <v>2.609339196272257</v>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.39853908438364</v>
+        <v>2.398539084383639</v>
       </c>
       <c r="C2" t="n">
         <v>2.425615111616863</v>
@@ -7256,10 +7256,10 @@
         <v>2.401850275880583</v>
       </c>
       <c r="E2" t="n">
-        <v>2.430073706472405</v>
+        <v>2.430073706472404</v>
       </c>
       <c r="F2" t="n">
-        <v>2.416836270647269</v>
+        <v>2.416836270647268</v>
       </c>
       <c r="G2" t="n">
         <v>2.407172516767278</v>
@@ -7274,7 +7274,7 @@
         <v>2.441789902878757</v>
       </c>
       <c r="K2" t="n">
-        <v>2.420344481318589</v>
+        <v>2.42034448131859</v>
       </c>
       <c r="L2" t="n">
         <v>2.403862051797532</v>
@@ -7290,7 +7290,7 @@
         <v>2.40123068559452</v>
       </c>
       <c r="C3" t="n">
-        <v>2.49563954817474</v>
+        <v>2.495639548174741</v>
       </c>
       <c r="D3" t="n">
         <v>2.424744393323147</v>
@@ -7314,10 +7314,10 @@
         <v>2.509448128578948</v>
       </c>
       <c r="K3" t="n">
-        <v>2.451812610494853</v>
+        <v>2.451812610494852</v>
       </c>
       <c r="L3" t="n">
-        <v>2.440127736425795</v>
+        <v>2.440127736425796</v>
       </c>
     </row>
     <row r="4">
@@ -7333,7 +7333,7 @@
         <v>2.210471041011238</v>
       </c>
       <c r="D4" t="n">
-        <v>2.144758441151175</v>
+        <v>2.144758441151174</v>
       </c>
       <c r="E4" t="n">
         <v>2.210594037282497</v>
@@ -7342,7 +7342,7 @@
         <v>2.210594037282497</v>
       </c>
       <c r="G4" t="n">
-        <v>2.204904834013641</v>
+        <v>2.204904834013642</v>
       </c>
       <c r="H4" t="n">
         <v>2.208572825662036</v>
@@ -7370,34 +7370,34 @@
         <v>2.424017731436694</v>
       </c>
       <c r="C5" t="n">
-        <v>4.164494504735086</v>
+        <v>4.164494504735083</v>
       </c>
       <c r="D5" t="n">
-        <v>3.065334723022025</v>
+        <v>3.065334723022028</v>
       </c>
       <c r="E5" t="n">
-        <v>4.164494505192543</v>
+        <v>4.164494505192539</v>
       </c>
       <c r="F5" t="n">
-        <v>4.164494505192543</v>
+        <v>4.164494505192539</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1625734055363</v>
+        <v>4.162573405536301</v>
       </c>
       <c r="H5" t="n">
-        <v>4.334589041290938</v>
+        <v>4.33458904129094</v>
       </c>
       <c r="I5" t="n">
-        <v>4.164495473675629</v>
+        <v>4.164495473675626</v>
       </c>
       <c r="J5" t="n">
-        <v>3.884258861223753</v>
+        <v>3.884258861223754</v>
       </c>
       <c r="K5" t="n">
         <v>2.951913738535334</v>
       </c>
       <c r="L5" t="n">
-        <v>8.872944409110236</v>
+        <v>8.872944409110247</v>
       </c>
     </row>
     <row r="6">
@@ -7407,22 +7407,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.281578376144866</v>
+        <v>3.281578376144867</v>
       </c>
       <c r="C6" t="n">
-        <v>3.399748589553047</v>
+        <v>3.399748589553046</v>
       </c>
       <c r="D6" t="n">
         <v>3.314863397814749</v>
       </c>
       <c r="E6" t="n">
-        <v>3.395701629726332</v>
+        <v>3.395701629726334</v>
       </c>
       <c r="F6" t="n">
         <v>3.399636842261895</v>
       </c>
       <c r="G6" t="n">
-        <v>16.67995373820124</v>
+        <v>16.67995373820125</v>
       </c>
       <c r="H6" t="n">
         <v>16.68160115378774</v>
@@ -7434,7 +7434,7 @@
         <v>16.656634594944</v>
       </c>
       <c r="K6" t="n">
-        <v>3.292148319990019</v>
+        <v>3.29214831999002</v>
       </c>
       <c r="L6" t="n">
         <v>3.340460341009572</v>
@@ -7450,7 +7450,7 @@
         <v>2.174113916989417</v>
       </c>
       <c r="C7" t="n">
-        <v>2.276956403781999</v>
+        <v>2.276956403782</v>
       </c>
       <c r="D7" t="n">
         <v>2.211510569517162</v>
@@ -7505,7 +7505,7 @@
         <v>2.337432882172381</v>
       </c>
       <c r="H8" t="n">
-        <v>2.341100873820759</v>
+        <v>2.34110087382076</v>
       </c>
       <c r="I8" t="n">
         <v>2.342728513861705</v>
@@ -7536,13 +7536,13 @@
         <v>2.797247817629846</v>
       </c>
       <c r="E9" t="n">
-        <v>3.027924136837194</v>
+        <v>3.027924136837195</v>
       </c>
       <c r="F9" t="n">
-        <v>2.86268878617002</v>
+        <v>2.862688786170019</v>
       </c>
       <c r="G9" t="n">
-        <v>2.857394224161942</v>
+        <v>2.857394224161943</v>
       </c>
       <c r="H9" t="n">
         <v>2.861062215810338</v>
@@ -7551,10 +7551,10 @@
         <v>2.862689855851269</v>
       </c>
       <c r="J9" t="n">
-        <v>2.835554120271818</v>
+        <v>2.835554120271819</v>
       </c>
       <c r="K9" t="n">
-        <v>2.707076528116136</v>
+        <v>2.707076528116137</v>
       </c>
       <c r="L9" t="n">
         <v>2.821059026071693</v>
@@ -7692,13 +7692,13 @@
         <v>2.416133500475814</v>
       </c>
       <c r="E3" t="n">
-        <v>2.487064585624057</v>
+        <v>2.487064585624056</v>
       </c>
       <c r="F3" t="n">
         <v>2.46516730437333</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44899333832744</v>
+        <v>2.448993338327441</v>
       </c>
       <c r="H3" t="n">
         <v>2.524626517516869</v>
@@ -7713,7 +7713,7 @@
         <v>2.436211384950692</v>
       </c>
       <c r="L3" t="n">
-        <v>2.436943720670854</v>
+        <v>2.436943720670853</v>
       </c>
     </row>
     <row r="4">
@@ -7732,10 +7732,10 @@
         <v>2.131932863985436</v>
       </c>
       <c r="E4" t="n">
-        <v>2.187330585978356</v>
+        <v>2.187330585978355</v>
       </c>
       <c r="F4" t="n">
-        <v>2.187330585978356</v>
+        <v>2.187330585978355</v>
       </c>
       <c r="G4" t="n">
         <v>2.184137468351981</v>
@@ -7766,10 +7766,10 @@
         <v>2.207930808892657</v>
       </c>
       <c r="C5" t="n">
-        <v>3.687935055468197</v>
+        <v>3.687935055468198</v>
       </c>
       <c r="D5" t="n">
-        <v>2.823655219525857</v>
+        <v>2.823655219525855</v>
       </c>
       <c r="E5" t="n">
         <v>3.687935056020582</v>
@@ -7778,22 +7778,22 @@
         <v>3.687935056020582</v>
       </c>
       <c r="G5" t="n">
-        <v>3.690509475573295</v>
+        <v>3.690509475573286</v>
       </c>
       <c r="H5" t="n">
         <v>5.804729550506202</v>
       </c>
       <c r="I5" t="n">
-        <v>3.687935487177887</v>
+        <v>3.687935487177888</v>
       </c>
       <c r="J5" t="n">
-        <v>3.381003985749638</v>
+        <v>3.381003985749635</v>
       </c>
       <c r="K5" t="n">
         <v>2.570357584010973</v>
       </c>
       <c r="L5" t="n">
-        <v>3.594665856532567</v>
+        <v>3.594665856532563</v>
       </c>
     </row>
     <row r="6">
@@ -7806,13 +7806,13 @@
         <v>15.5769527352174</v>
       </c>
       <c r="C6" t="n">
-        <v>3.293833841480534</v>
+        <v>3.293833841480533</v>
       </c>
       <c r="D6" t="n">
-        <v>3.220983134049648</v>
+        <v>3.220983134049647</v>
       </c>
       <c r="E6" t="n">
-        <v>3.290128631016791</v>
+        <v>3.29012863101679</v>
       </c>
       <c r="F6" t="n">
         <v>3.293786166073521</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.153745651106196</v>
+        <v>2.153745651106195</v>
       </c>
       <c r="C7" t="n">
         <v>2.248358627401812</v>
@@ -7858,7 +7858,7 @@
         <v>2.248359435320793</v>
       </c>
       <c r="G7" t="n">
-        <v>2.245505409000708</v>
+        <v>2.245505409000706</v>
       </c>
       <c r="H7" t="n">
         <v>2.365098889353653</v>
@@ -7870,7 +7870,7 @@
         <v>2.219517055496773</v>
       </c>
       <c r="K7" t="n">
-        <v>2.176887396962711</v>
+        <v>2.17688739696271</v>
       </c>
       <c r="L7" t="n">
         <v>2.225743124563067</v>
@@ -7898,13 +7898,13 @@
         <v>2.259395247111898</v>
       </c>
       <c r="G8" t="n">
-        <v>2.304899027445406</v>
+        <v>2.304899027445405</v>
       </c>
       <c r="H8" t="n">
-        <v>2.424492507798352</v>
+        <v>2.424492507798353</v>
       </c>
       <c r="I8" t="n">
-        <v>2.307752677556197</v>
+        <v>2.307752677556198</v>
       </c>
       <c r="J8" t="n">
         <v>2.278920489214506</v>
@@ -7913,7 +7913,7 @@
         <v>2.185410039122015</v>
       </c>
       <c r="L8" t="n">
-        <v>2.337306648710598</v>
+        <v>2.337306648710599</v>
       </c>
     </row>
     <row r="9">
@@ -7923,13 +7923,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.510411859768624</v>
+        <v>2.510411859768623</v>
       </c>
       <c r="C9" t="n">
-        <v>2.722787159793718</v>
+        <v>2.722787159793717</v>
       </c>
       <c r="D9" t="n">
-        <v>2.667729297188292</v>
+        <v>2.667729297188291</v>
       </c>
       <c r="E9" t="n">
         <v>2.858682203877362</v>
@@ -7938,22 +7938,22 @@
         <v>2.722787044285645</v>
       </c>
       <c r="G9" t="n">
-        <v>2.71993394139261</v>
+        <v>2.719933941392609</v>
       </c>
       <c r="H9" t="n">
-        <v>2.839527421745557</v>
+        <v>2.839527421745556</v>
       </c>
       <c r="I9" t="n">
         <v>2.722787591503403</v>
       </c>
       <c r="J9" t="n">
-        <v>2.693945587888675</v>
+        <v>2.693945587888674</v>
       </c>
       <c r="K9" t="n">
-        <v>2.583083959741851</v>
+        <v>2.58308395974185</v>
       </c>
       <c r="L9" t="n">
-        <v>2.700171656954969</v>
+        <v>2.700171656954968</v>
       </c>
     </row>
   </sheetData>
